--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9378FB1E-D2D4-4E28-82EC-343E14965070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09A9310-51CB-4E03-B2F6-30A5259C1B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="-210" yWindow="0" windowWidth="9750" windowHeight="10170" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$84</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="99">
   <si>
     <t>S No.</t>
   </si>
@@ -98,9 +101,6 @@
     <t>ICICI Prudential AMC</t>
   </si>
   <si>
-    <t>Return</t>
-  </si>
-  <si>
     <t>TECHM</t>
   </si>
   <si>
@@ -261,6 +261,81 @@
   </si>
   <si>
     <t>LAURUSLABS</t>
+  </si>
+  <si>
+    <t>Today's closing price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIPLA </t>
+  </si>
+  <si>
+    <t>MEDANTA</t>
+  </si>
+  <si>
+    <t>SYRMA</t>
+  </si>
+  <si>
+    <t>Vedanta Alum</t>
+  </si>
+  <si>
+    <t>Dixon Technologies</t>
+  </si>
+  <si>
+    <t>Gokaldas Exports</t>
+  </si>
+  <si>
+    <t>Gujarat Fluorochem</t>
+  </si>
+  <si>
+    <t>Genus Power</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Excepted Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> bharat forge</t>
+  </si>
+  <si>
+    <t>shriram finance</t>
+  </si>
+  <si>
+    <t>Hind petro</t>
+  </si>
+  <si>
+    <t>Axis Bank</t>
+  </si>
+  <si>
+    <t>welcorp</t>
+  </si>
+  <si>
+    <t>Maruti</t>
+  </si>
+  <si>
+    <t>ABCentral</t>
+  </si>
+  <si>
+    <t>JSW steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Health </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Health </t>
+  </si>
+  <si>
+    <t>kirloskar oli engines</t>
+  </si>
+  <si>
+    <t>Marico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granules </t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals</t>
   </si>
 </sst>
 </file>
@@ -276,12 +351,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -296,11 +383,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -644,13 +733,14 @@
     <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.36328125" customWidth="1"/>
-    <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" customWidth="1"/>
+    <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -670,19 +760,25 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -701,8 +797,12 @@
       <c r="F2">
         <v>3450</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H2" s="2">
+        <f>(E2-D2)/D2</f>
+        <v>4.2962125494629737E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -715,8 +815,12 @@
       <c r="D3">
         <v>748</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H27" si="0">(E3-D3)/D3</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -729,14 +833,18 @@
       <c r="D4">
         <v>2056</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="I4" s="1">
         <v>46191</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>2365</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -752,14 +860,18 @@
       <c r="E5">
         <v>1160</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15308151093439365</v>
+      </c>
+      <c r="I5" s="1">
         <v>46175</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>1344</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -775,8 +887,12 @@
       <c r="E6">
         <v>6600</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12225811936745451</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -795,14 +911,18 @@
       <c r="F7">
         <v>1438</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
+        <f t="shared" si="0"/>
+        <v>1.8543956043956044E-2</v>
+      </c>
+      <c r="I7" s="1">
         <v>46175</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>1488</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -818,8 +938,12 @@
       <c r="E8">
         <v>580</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.3200118345888619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -835,8 +959,12 @@
       <c r="E9">
         <v>3850</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.23999948467553878</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -852,8 +980,12 @@
       <c r="E10">
         <v>1450</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.20000331035395966</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -869,8 +1001,12 @@
       <c r="E11">
         <v>1100</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.18000429092469422</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -886,13 +1022,17 @@
       <c r="E12">
         <v>3850</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15999843324886945</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1">
         <v>46175</v>
@@ -903,13 +1043,17 @@
       <c r="E13">
         <v>1720</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11471160077770577</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1">
         <v>46175</v>
@@ -917,13 +1061,17 @@
       <c r="D14">
         <v>434</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H14" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
         <v>46175</v>
@@ -934,13 +1082,17 @@
       <c r="E15">
         <v>235</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.27027027027027029</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1">
         <v>46175</v>
@@ -951,8 +1103,12 @@
       <c r="E16">
         <v>2050</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.14974761637689288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -971,13 +1127,17 @@
       <c r="F17">
         <v>705</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16036505867014342</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1">
         <v>46176</v>
@@ -985,13 +1145,17 @@
       <c r="D18">
         <v>835</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H18" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="1">
         <v>46176</v>
@@ -1005,13 +1169,17 @@
       <c r="F19">
         <v>510</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H19" s="2">
+        <f t="shared" si="0"/>
+        <v>8.0074487895716945E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1">
         <v>46176</v>
@@ -1019,13 +1187,17 @@
       <c r="D20">
         <v>1074</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H20" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1">
         <v>46176</v>
@@ -1033,13 +1205,17 @@
       <c r="D21">
         <v>406</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H21" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1">
         <v>46176</v>
@@ -1050,12 +1226,16 @@
       <c r="E22">
         <v>1200</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.10091743119266056</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="1">
@@ -1070,13 +1250,20 @@
       <c r="F23">
         <v>705</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G23">
+        <v>1153</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16036505867014342</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="1">
         <v>46177</v>
@@ -1090,13 +1277,17 @@
       <c r="F24">
         <v>2040</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H24" s="2">
+        <f t="shared" si="0"/>
+        <v>0.13476473275468251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" s="1">
         <v>46182</v>
@@ -1110,19 +1301,23 @@
       <c r="F25">
         <v>295</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="2">
+        <f t="shared" si="0"/>
+        <v>6.5573770491803282E-2</v>
+      </c>
+      <c r="I25" s="1">
         <v>46189</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="1">
         <v>46182</v>
@@ -1130,13 +1325,17 @@
       <c r="D26">
         <v>168.6</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H26" s="2">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="1">
         <v>46182</v>
@@ -1147,8 +1346,15 @@
       <c r="E27">
         <v>360</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H27" s="2">
+        <f t="shared" si="0"/>
+        <v>0.34328358208955223</v>
+      </c>
+      <c r="J27">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1167,19 +1373,19 @@
       <c r="F28">
         <v>705</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>46184</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>960</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1">
         <v>46184</v>
@@ -1194,12 +1400,12 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="1">
         <v>46184</v>
@@ -1211,12 +1417,12 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="1">
         <v>46184</v>
@@ -1228,12 +1434,12 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" s="1">
         <v>46184</v>
@@ -1250,7 +1456,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" s="1">
         <v>46185</v>
@@ -1270,7 +1476,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" s="1">
         <v>46185</v>
@@ -1284,7 +1490,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" s="1">
         <v>46185</v>
@@ -1298,7 +1504,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" s="1">
         <v>46185</v>
@@ -1315,7 +1521,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="1">
         <v>46185</v>
@@ -1335,7 +1541,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="1">
         <v>46188</v>
@@ -1355,7 +1561,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" s="1">
         <v>46188</v>
@@ -1372,7 +1578,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="1">
         <v>46188</v>
@@ -1386,7 +1592,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1">
         <v>46188</v>
@@ -1400,7 +1606,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" s="1">
         <v>46188</v>
@@ -1420,7 +1626,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" s="1">
         <v>46189</v>
@@ -1440,7 +1646,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="1">
         <v>46189</v>
@@ -1454,7 +1660,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="1">
         <v>46189</v>
@@ -1468,7 +1674,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="1">
         <v>46189</v>
@@ -1482,7 +1688,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" s="1">
         <v>46189</v>
@@ -1496,7 +1702,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" s="1">
         <v>46189</v>
@@ -1505,12 +1711,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" s="1">
         <v>46189</v>
@@ -1519,12 +1725,12 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" s="1">
         <v>46189</v>
@@ -1532,22 +1738,22 @@
       <c r="D50">
         <v>210</v>
       </c>
-      <c r="G50" s="2">
+      <c r="H50" s="2">
         <v>1.4E-2</v>
       </c>
-      <c r="H50" s="1">
+      <c r="I50" s="1">
         <v>46189</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C51" s="1">
         <v>46189</v>
@@ -1562,12 +1768,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" s="1">
         <v>46190</v>
@@ -1582,12 +1788,12 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C53" s="1">
         <v>46190</v>
@@ -1596,7 +1802,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1613,12 +1819,12 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C55" s="1">
         <v>46190</v>
@@ -1627,12 +1833,12 @@
         <v>374</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C56" s="1">
         <v>46190</v>
@@ -1641,12 +1847,12 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" s="1">
         <v>46190</v>
@@ -1660,14 +1866,14 @@
       <c r="F57">
         <v>204</v>
       </c>
-      <c r="H57" s="1"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" s="1">
         <v>46190</v>
@@ -1681,19 +1887,19 @@
       <c r="F58">
         <v>151</v>
       </c>
-      <c r="H58" s="1">
+      <c r="I58" s="1">
         <v>46190</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>156.6</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C59" s="1">
         <v>46191</v>
@@ -1705,7 +1911,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1721,13 +1927,16 @@
       <c r="E60">
         <v>2600</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J60">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C61" s="1">
         <v>46191</v>
@@ -1736,12 +1945,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="1">
         <v>46191</v>
@@ -1750,12 +1959,12 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C63" s="1">
         <v>46191</v>
@@ -1764,12 +1973,12 @@
         <v>420</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64" s="1">
         <v>46191</v>
@@ -1784,12 +1993,12 @@
         <v>930</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C65" s="1">
         <v>46192</v>
@@ -1804,12 +2013,12 @@
         <v>3415</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C66" s="1">
         <v>46192</v>
@@ -1821,12 +2030,12 @@
         <v>400</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C67" s="1">
         <v>46192</v>
@@ -1838,12 +2047,12 @@
         <v>8450</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C68" s="1">
         <v>46192</v>
@@ -1852,12 +2061,12 @@
         <v>406</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C69" s="1">
         <v>46192</v>
@@ -1866,12 +2075,12 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C70" s="1">
         <v>46192</v>
@@ -1886,26 +2095,26 @@
         <v>2845</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C71" s="1">
         <v>46192</v>
       </c>
-      <c r="G71" s="3">
+      <c r="H71" s="3">
         <v>0.09</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C72" s="1">
         <v>46195</v>
@@ -1920,12 +2129,15 @@
         <v>3415</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>70</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46195</v>
       </c>
       <c r="D73">
         <v>1992</v>
@@ -1933,69 +2145,84 @@
       <c r="E73">
         <v>2350</v>
       </c>
-      <c r="G73" s="3">
+      <c r="H73" s="3">
         <v>0.2</v>
       </c>
-      <c r="H73" s="1">
+      <c r="I73" s="1">
         <v>46195</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
         <v>15</v>
       </c>
+      <c r="C74" s="1">
+        <v>46195</v>
+      </c>
       <c r="D74">
         <v>416</v>
       </c>
       <c r="E74">
         <v>580</v>
       </c>
-      <c r="G74" s="3">
+      <c r="H74" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="C75" s="1">
+        <v>46195</v>
       </c>
       <c r="D75">
         <v>1889</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="C76" s="1">
+        <v>46195</v>
       </c>
       <c r="D76">
         <v>264</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C77" s="1">
+        <v>46195</v>
       </c>
       <c r="D77">
         <v>376</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="C78" s="1">
+        <v>46195</v>
       </c>
       <c r="D78">
         <v>1413</v>
@@ -2007,27 +2234,634 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D79">
+        <v>1415</v>
+      </c>
+      <c r="E79">
+        <v>1530</v>
+      </c>
+      <c r="F79">
+        <v>1360</v>
+      </c>
+      <c r="I79" s="1">
+        <v>46203</v>
+      </c>
+      <c r="J79">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D80">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D81">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
+      <c r="B82" t="s">
+        <v>76</v>
+      </c>
+      <c r="C82" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D82">
+        <v>1288</v>
+      </c>
+      <c r="E82">
+        <v>1490</v>
+      </c>
+      <c r="H82" s="3">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D83">
+        <v>1336</v>
+      </c>
+      <c r="E83">
+        <v>1620</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="J83">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>63</v>
+      </c>
+      <c r="C84" s="1">
+        <v>46196</v>
+      </c>
+      <c r="D84">
+        <v>3653</v>
+      </c>
+      <c r="E84">
+        <v>4100</v>
+      </c>
+      <c r="F84">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>78</v>
+      </c>
+      <c r="C85" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D85">
+        <v>454</v>
+      </c>
+      <c r="E85">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D86">
+        <v>12667</v>
+      </c>
+      <c r="E86">
+        <v>15290</v>
+      </c>
+      <c r="F86">
+        <v>11400</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C87" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D87">
+        <v>829</v>
+      </c>
+      <c r="E87">
+        <v>1110</v>
+      </c>
+      <c r="L87">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D88">
+        <v>3891</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>82</v>
+      </c>
+      <c r="C89" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D89">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C90" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D90">
+        <v>1112</v>
+      </c>
+      <c r="E90">
+        <v>1185</v>
+      </c>
+      <c r="F90">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>22</v>
+      </c>
+      <c r="C91" s="1">
+        <v>46197</v>
+      </c>
+      <c r="D91">
+        <v>199</v>
+      </c>
+      <c r="E91">
+        <v>204</v>
+      </c>
+      <c r="F91">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>63</v>
+      </c>
+      <c r="C92" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D92">
+        <v>3653</v>
+      </c>
+      <c r="E92">
+        <v>4100</v>
+      </c>
+      <c r="F92">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>85</v>
+      </c>
+      <c r="C93" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D93">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>86</v>
+      </c>
+      <c r="C94" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D94">
+        <v>1019</v>
+      </c>
+      <c r="E94">
+        <v>1175</v>
+      </c>
+      <c r="G94">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>87</v>
+      </c>
+      <c r="C95" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D95">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C96" s="1">
+        <v>46198</v>
+      </c>
+      <c r="D96">
+        <v>1384</v>
+      </c>
+      <c r="E96">
+        <v>1441</v>
+      </c>
+      <c r="F96">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C97" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D97">
+        <v>1455</v>
+      </c>
+      <c r="E97">
+        <v>1570</v>
+      </c>
+      <c r="F97">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>90</v>
+      </c>
+      <c r="C98" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D98">
+        <v>13735</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D99">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>92</v>
+      </c>
+      <c r="C100" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D100">
+        <v>1231</v>
+      </c>
+      <c r="E100">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>93</v>
+      </c>
+      <c r="C101" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D101">
+        <v>575</v>
+      </c>
+      <c r="E101">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>94</v>
+      </c>
+      <c r="C102" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D102">
+        <v>1132</v>
+      </c>
+      <c r="E102">
+        <v>1329</v>
+      </c>
+      <c r="F102">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>86</v>
+      </c>
+      <c r="C103" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D103">
+        <v>1046</v>
+      </c>
+      <c r="E103">
+        <v>1205</v>
+      </c>
+      <c r="F103">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>95</v>
+      </c>
+      <c r="D104">
+        <v>2441</v>
+      </c>
+      <c r="E104">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>96</v>
+      </c>
+      <c r="D105">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>97</v>
+      </c>
+      <c r="D106">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D107">
+        <v>4628</v>
+      </c>
+      <c r="E107">
+        <v>4850</v>
+      </c>
+      <c r="F107">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>130</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K84" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09A9310-51CB-4E03-B2F6-30A5259C1B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC81B6D7-3E67-4F6D-BD5E-669FE6738199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-210" yWindow="0" windowWidth="9750" windowHeight="10170" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="-50" yWindow="0" windowWidth="9610" windowHeight="10170" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
   <si>
     <t>S No.</t>
   </si>
@@ -336,6 +336,33 @@
   </si>
   <si>
     <t>Torrent Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Aditya Birla Real Estate</t>
+  </si>
+  <si>
+    <t>Credit access grameen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGPOWER </t>
+  </si>
+  <si>
+    <t>Bajaj Finance</t>
+  </si>
+  <si>
+    <t>Naukri</t>
+  </si>
+  <si>
+    <t>Aether</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>AADHAR HOUSING FINANCE</t>
+  </si>
+  <si>
+    <t>NYKAA</t>
   </si>
 </sst>
 </file>
@@ -728,8 +755,8 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.08984375" bestFit="1" customWidth="1"/>
@@ -2693,6 +2720,9 @@
       <c r="B104" t="s">
         <v>95</v>
       </c>
+      <c r="C104" s="1">
+        <v>46204</v>
+      </c>
       <c r="D104">
         <v>2441</v>
       </c>
@@ -2707,6 +2737,9 @@
       <c r="B105" t="s">
         <v>96</v>
       </c>
+      <c r="C105" s="1">
+        <v>46204</v>
+      </c>
       <c r="D105">
         <v>840</v>
       </c>
@@ -2718,6 +2751,9 @@
       <c r="B106" t="s">
         <v>97</v>
       </c>
+      <c r="C106" s="1">
+        <v>46204</v>
+      </c>
       <c r="D106">
         <v>802</v>
       </c>
@@ -2729,6 +2765,9 @@
       <c r="B107" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="C107" s="1">
+        <v>46204</v>
+      </c>
       <c r="D107">
         <v>4628</v>
       </c>
@@ -2743,103 +2782,265 @@
       <c r="A108">
         <v>107</v>
       </c>
+      <c r="B108" t="s">
+        <v>99</v>
+      </c>
+      <c r="C108" s="1">
+        <v>46205</v>
+      </c>
+      <c r="D108">
+        <v>1396</v>
+      </c>
+      <c r="E108">
+        <v>1940</v>
+      </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
+      <c r="B109" t="s">
+        <v>100</v>
+      </c>
+      <c r="C109" s="1">
+        <v>46205</v>
+      </c>
+      <c r="D109">
+        <v>1503</v>
+      </c>
+      <c r="E109">
+        <v>1780</v>
+      </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
+      <c r="B110" t="s">
+        <v>101</v>
+      </c>
+      <c r="C110" s="1">
+        <v>46205</v>
+      </c>
+      <c r="D110">
+        <v>976</v>
+      </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
+      <c r="B111" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111" s="1">
+        <v>46205</v>
+      </c>
+      <c r="D111">
+        <v>508</v>
+      </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B112" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C112" s="1">
+        <v>46205</v>
+      </c>
+      <c r="D112">
+        <v>1628</v>
+      </c>
+      <c r="E112">
+        <v>1760</v>
+      </c>
+      <c r="F112">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B113" t="s">
+        <v>99</v>
+      </c>
+      <c r="C113" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D113">
+        <v>1412</v>
+      </c>
+      <c r="E113">
+        <v>1586</v>
+      </c>
+      <c r="F113">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B114" t="s">
+        <v>102</v>
+      </c>
+      <c r="C114" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D114">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B115" t="s">
+        <v>96</v>
+      </c>
+      <c r="C115" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D115">
+        <v>856</v>
+      </c>
+      <c r="E115">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B116" t="s">
+        <v>103</v>
+      </c>
+      <c r="C116" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D116">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B117" t="s">
+        <v>104</v>
+      </c>
+      <c r="C117" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D117">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B118" t="s">
+        <v>23</v>
+      </c>
+      <c r="C118" s="1">
+        <v>46206</v>
+      </c>
+      <c r="D118">
+        <v>1882</v>
+      </c>
+      <c r="E118">
+        <v>2017</v>
+      </c>
+      <c r="F118">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B119" t="s">
+        <v>105</v>
+      </c>
+      <c r="C119" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D119">
+        <v>235</v>
+      </c>
+      <c r="E119">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B120" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D120">
+        <v>548</v>
+      </c>
+      <c r="E120">
+        <v>612</v>
+      </c>
+      <c r="F120">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
+        <v>107</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46209</v>
+      </c>
+      <c r="D121">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -2,23 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC81B6D7-3E67-4F6D-BD5E-669FE6738199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7D081D-0343-4D2E-8276-578E354BBF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50" yWindow="0" windowWidth="9610" windowHeight="10170" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="7860" windowHeight="10170" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Buy Sell" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$201</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,14 +43,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="159">
   <si>
     <t>S No.</t>
   </si>
   <si>
-    <t>Stock Name</t>
-  </si>
-  <si>
     <t>Day when told</t>
   </si>
   <si>
@@ -71,108 +72,30 @@
     <t>ICICI AMC</t>
   </si>
   <si>
-    <t>Aegis Logistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RR Kabel </t>
-  </si>
-  <si>
-    <t>Rubicon Research</t>
-  </si>
-  <si>
-    <t>Cummins India</t>
-  </si>
-  <si>
     <t>COFORGE</t>
   </si>
   <si>
-    <t>Delhivery</t>
-  </si>
-  <si>
-    <t>Waaree Energies</t>
-  </si>
-  <si>
-    <t>Jindal Steel</t>
-  </si>
-  <si>
-    <t>Fortis Healthcare</t>
-  </si>
-  <si>
-    <t>ICICI Prudential AMC</t>
-  </si>
-  <si>
     <t>TECHM</t>
   </si>
   <si>
-    <t>Nationalum</t>
-  </si>
-  <si>
-    <t>Groww</t>
-  </si>
-  <si>
-    <t>Adani Ports</t>
-  </si>
-  <si>
-    <t>Titagarh Rail system</t>
-  </si>
-  <si>
-    <t>Varun Beverages</t>
-  </si>
-  <si>
-    <t>Premier Energies</t>
-  </si>
-  <si>
-    <t>Exide</t>
-  </si>
-  <si>
     <t>AMC</t>
   </si>
   <si>
     <t>AZAD</t>
   </si>
   <si>
-    <t>Federal Bank</t>
-  </si>
-  <si>
     <t>GAIL</t>
   </si>
   <si>
-    <t xml:space="preserve">JSW Infrastructure </t>
-  </si>
-  <si>
-    <t>Nestle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pidilite </t>
-  </si>
-  <si>
-    <t>Hindalco Industries</t>
-  </si>
-  <si>
-    <t>Privi Speciality chemicals</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
     <t>MCX</t>
   </si>
   <si>
     <t>GLAND PHARMA</t>
   </si>
   <si>
-    <t>Nuvama  Wealth</t>
-  </si>
-  <si>
     <t>RBL BANK</t>
   </si>
   <si>
-    <t>Bank of Maharashtra</t>
-  </si>
-  <si>
-    <t>Indigo</t>
-  </si>
-  <si>
     <t>IOC</t>
   </si>
   <si>
@@ -185,27 +108,9 @@
     <t>BHARATFORG</t>
   </si>
   <si>
-    <t>Phoenixltd</t>
-  </si>
-  <si>
-    <t>Eichermot</t>
-  </si>
-  <si>
-    <t>Ixigo</t>
-  </si>
-  <si>
-    <t>Yatra</t>
-  </si>
-  <si>
     <t>TBO TEK</t>
   </si>
   <si>
-    <t>Bandhan Bank</t>
-  </si>
-  <si>
-    <t>Zydus LifeScience</t>
-  </si>
-  <si>
     <t xml:space="preserve">ABCAPITAL </t>
   </si>
   <si>
@@ -215,30 +120,12 @@
     <t>PINELAB</t>
   </si>
   <si>
-    <t>Bharat Electronics</t>
-  </si>
-  <si>
     <t>SUZLON</t>
   </si>
   <si>
     <t>SBIN</t>
   </si>
   <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>CG Power</t>
-  </si>
-  <si>
-    <t>Radico Khaitan</t>
-  </si>
-  <si>
-    <t>Angel one</t>
-  </si>
-  <si>
-    <t>Amber Enterprises</t>
-  </si>
-  <si>
     <t>BHEL</t>
   </si>
   <si>
@@ -251,9 +138,6 @@
     <t>WABAG</t>
   </si>
   <si>
-    <t>Kirloskar oil engines</t>
-  </si>
-  <si>
     <t>TATACOMM</t>
   </si>
   <si>
@@ -275,87 +159,12 @@
     <t>SYRMA</t>
   </si>
   <si>
-    <t>Vedanta Alum</t>
-  </si>
-  <si>
-    <t>Dixon Technologies</t>
-  </si>
-  <si>
-    <t>Gokaldas Exports</t>
-  </si>
-  <si>
-    <t>Gujarat Fluorochem</t>
-  </si>
-  <si>
-    <t>Genus Power</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
     <t>Excepted Return</t>
   </si>
   <si>
-    <t xml:space="preserve"> bharat forge</t>
-  </si>
-  <si>
-    <t>shriram finance</t>
-  </si>
-  <si>
-    <t>Hind petro</t>
-  </si>
-  <si>
-    <t>Axis Bank</t>
-  </si>
-  <si>
-    <t>welcorp</t>
-  </si>
-  <si>
-    <t>Maruti</t>
-  </si>
-  <si>
-    <t>ABCentral</t>
-  </si>
-  <si>
-    <t>JSW steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star Health </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Health </t>
-  </si>
-  <si>
-    <t>kirloskar oli engines</t>
-  </si>
-  <si>
-    <t>Marico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granules </t>
-  </si>
-  <si>
-    <t>Torrent Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>Aditya Birla Real Estate</t>
-  </si>
-  <si>
-    <t>Credit access grameen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CGPOWER </t>
-  </si>
-  <si>
-    <t>Bajaj Finance</t>
-  </si>
-  <si>
-    <t>Naukri</t>
-  </si>
-  <si>
-    <t>Aether</t>
-  </si>
-  <si>
     <t>ONGC</t>
   </si>
   <si>
@@ -363,16 +172,378 @@
   </si>
   <si>
     <t>NYKAA</t>
+  </si>
+  <si>
+    <t>LLOYD</t>
+  </si>
+  <si>
+    <t>Scrip name</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Sell</t>
+  </si>
+  <si>
+    <t>Buy</t>
+  </si>
+  <si>
+    <t>Order Price</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>AEGIS LOGISTICS</t>
+  </si>
+  <si>
+    <t>RUBICON RESEARCH</t>
+  </si>
+  <si>
+    <t>CUMMINS INDIA</t>
+  </si>
+  <si>
+    <t>DELHIVERY</t>
+  </si>
+  <si>
+    <t>WAAREE ENERGIES</t>
+  </si>
+  <si>
+    <t>JINDAL STEEL</t>
+  </si>
+  <si>
+    <t>FORTIS HEALTHCARE</t>
+  </si>
+  <si>
+    <t>ICICI PRUDENTIAL AMC</t>
+  </si>
+  <si>
+    <t>NATIONALUM</t>
+  </si>
+  <si>
+    <t>GROWW</t>
+  </si>
+  <si>
+    <t>ADANI PORTS</t>
+  </si>
+  <si>
+    <t>TITAGARH RAIL SYSTEM</t>
+  </si>
+  <si>
+    <t>VARUN BEVERAGES</t>
+  </si>
+  <si>
+    <t>PREMIER ENERGIES</t>
+  </si>
+  <si>
+    <t>EXIDE</t>
+  </si>
+  <si>
+    <t>FEDERAL BANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSW INFRASTRUCTURE </t>
+  </si>
+  <si>
+    <t>NESTLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIDILITE </t>
+  </si>
+  <si>
+    <t>HINDALCO INDUSTRIES</t>
+  </si>
+  <si>
+    <t>PRIVI SPECIALITY CHEMICALS</t>
+  </si>
+  <si>
+    <t>NUVAMA  WEALTH</t>
+  </si>
+  <si>
+    <t>BANK OF MAHARASHTRA</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>PHOENIXLTD</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>IXIGO</t>
+  </si>
+  <si>
+    <t>YATRA</t>
+  </si>
+  <si>
+    <t>BANDHAN BANK</t>
+  </si>
+  <si>
+    <t>ZYDUS LIFESCIENCE</t>
+  </si>
+  <si>
+    <t>BHARAT ELECTRONICS</t>
+  </si>
+  <si>
+    <t>CG POWER</t>
+  </si>
+  <si>
+    <t>RADICO KHAITAN</t>
+  </si>
+  <si>
+    <t>ANGEL ONE</t>
+  </si>
+  <si>
+    <t>AMBER ENTERPRISES</t>
+  </si>
+  <si>
+    <t>KIRLOSKAR OIL ENGINES</t>
+  </si>
+  <si>
+    <t>VEDANTA ALUM</t>
+  </si>
+  <si>
+    <t>DIXON TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>GOKALDAS EXPORTS</t>
+  </si>
+  <si>
+    <t>GUJARAT FLUOROCHEM</t>
+  </si>
+  <si>
+    <t>GENUS POWER</t>
+  </si>
+  <si>
+    <t>SHRIRAM FINANCE</t>
+  </si>
+  <si>
+    <t>HIND PETRO</t>
+  </si>
+  <si>
+    <t>AXIS BANK</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>ABCENTRAL</t>
+  </si>
+  <si>
+    <t>JSW STEEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAR HEALTH </t>
+  </si>
+  <si>
+    <t>MARICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRANULES </t>
+  </si>
+  <si>
+    <t>TORRENT PHARMACEUTICALS</t>
+  </si>
+  <si>
+    <t>ADITYA BIRLA REAL ESTATE</t>
+  </si>
+  <si>
+    <t>CREDIT ACCESS GRAMEEN</t>
+  </si>
+  <si>
+    <t>BAJAJ FINANCE</t>
+  </si>
+  <si>
+    <t>NAUKRI</t>
+  </si>
+  <si>
+    <t>AETHER</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>STOCK NAME</t>
+  </si>
+  <si>
+    <t>BHARAT FORGEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RR KABHARAT ELECTRONICS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CG POWER </t>
+  </si>
+  <si>
+    <t>GRASIM INDUSTRIESUSTRIESUSTRIES</t>
+  </si>
+  <si>
+    <t>GRASIM INDUSTRIESUSTRIESUSTRIES IND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAX HEALTHCARE </t>
+  </si>
+  <si>
+    <t>WELSPUN CORP</t>
+  </si>
+  <si>
+    <t>Frequency of Stocks</t>
+  </si>
+  <si>
+    <t>PNB HOUSING FIN</t>
+  </si>
+  <si>
+    <t>ASTRA MICROWAVE</t>
+  </si>
+  <si>
+    <t>UNO MINDA</t>
+  </si>
+  <si>
+    <t>EXIDE IND</t>
+  </si>
+  <si>
+    <t>ATHER ENERGY LTD</t>
+  </si>
+  <si>
+    <t>Idea Type</t>
+  </si>
+  <si>
+    <t>Conviction Delivery Idea</t>
+  </si>
+  <si>
+    <t>Velocity Idea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamental </t>
+  </si>
+  <si>
+    <t>Technical Radar</t>
+  </si>
+  <si>
+    <t>KAYNES</t>
+  </si>
+  <si>
+    <t>ALKYLAMINE</t>
+  </si>
+  <si>
+    <t>CDSL</t>
+  </si>
+  <si>
+    <t>DLF</t>
+  </si>
+  <si>
+    <t>RBL</t>
+  </si>
+  <si>
+    <t>Consolidation Breakout</t>
+  </si>
+  <si>
+    <t>L&amp;T FINANCE</t>
+  </si>
+  <si>
+    <t>INDIAN BANK</t>
+  </si>
+  <si>
+    <t>TATA TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>JSWINFRA</t>
+  </si>
+  <si>
+    <t>Range breakout bullish candle</t>
+  </si>
+  <si>
+    <t>KARARVYSYA</t>
+  </si>
+  <si>
+    <t>ICICI PREDENTIAL AMC</t>
+  </si>
+  <si>
+    <t>HCL TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>WELSPUN LIVING</t>
+  </si>
+  <si>
+    <t>SAATVIK GREEN ENERGY</t>
+  </si>
+  <si>
+    <t>Initiating coverage</t>
+  </si>
+  <si>
+    <t>ADANI GREEN</t>
+  </si>
+  <si>
+    <t>Watchlist</t>
+  </si>
+  <si>
+    <t>LLOYDS METALS</t>
+  </si>
+  <si>
+    <t>IPCA LABORATORIES</t>
+  </si>
+  <si>
+    <t>Technical conviction</t>
+  </si>
+  <si>
+    <t>ABB</t>
+  </si>
+  <si>
+    <t>FLUOROCHEM</t>
+  </si>
+  <si>
+    <t>UNIMECH AEROSPACE</t>
+  </si>
+  <si>
+    <t>TARIL</t>
+  </si>
+  <si>
+    <t>TECH MAHINDRA</t>
+  </si>
+  <si>
+    <t>PIRAMAL FINANCE</t>
+  </si>
+  <si>
+    <t>INFOEDGE</t>
+  </si>
+  <si>
+    <t>SONACOMS</t>
+  </si>
+  <si>
+    <t>HSCL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6" tint="-0.499984740745262"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -393,7 +564,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,18 +581,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -432,6 +646,2430 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ECO LOGIC" refreshedDate="46210.594272222224" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="125" xr:uid="{98144EDE-19C6-4FBA-BB3E-081ED993E514}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:M126" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="S No." numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="125"/>
+    </cacheField>
+    <cacheField name="STOCK NAME" numFmtId="0">
+      <sharedItems count="107">
+        <s v="ICICI AMC"/>
+        <s v="AEGIS LOGISTICS"/>
+        <s v="RR KABHARAT ELECTRONICS "/>
+        <s v="RUBICON RESEARCH"/>
+        <s v="CUMMINS INDIA"/>
+        <s v="COFORGE"/>
+        <s v="DELHIVERY"/>
+        <s v="WAAREE ENERGIES"/>
+        <s v="JINDAL STEEL"/>
+        <s v="FORTIS HEALTHCARE"/>
+        <s v="ICICI PRUDENTIAL AMC"/>
+        <s v="TECHM"/>
+        <s v="NATIONALUM"/>
+        <s v="GROWW"/>
+        <s v="ADANI PORTS"/>
+        <s v="TITAGARH RAIL SYSTEM"/>
+        <s v="VARUN BEVERAGES"/>
+        <s v="PREMIER ENERGIES"/>
+        <s v="EXIDE"/>
+        <s v="AMC"/>
+        <s v="AZAD"/>
+        <s v="FEDERAL BANK"/>
+        <s v="GAIL"/>
+        <s v="JSW INFRASTRUCTURE "/>
+        <s v="NESTLE"/>
+        <s v="PIDILITE "/>
+        <s v="HINDALCO INDUSTRIES"/>
+        <s v="PRIVI SPECIALITY CHEMICALS"/>
+        <s v="GRASIM INDUSTRIESUSTRIESUSTRIES"/>
+        <s v="MCX"/>
+        <s v="GLAND PHARMA"/>
+        <s v="NUVAMA  WEALTH"/>
+        <s v="RBL BANK"/>
+        <s v="BANK OF MAHARASHTRA"/>
+        <s v="INDIGO"/>
+        <s v="IOC"/>
+        <s v="SRF"/>
+        <s v="KTKBANK"/>
+        <s v="BHARAT FORGEE"/>
+        <s v="PHOENIXLTD"/>
+        <s v="EICHERMOT"/>
+        <s v="IXIGO"/>
+        <s v="YATRA"/>
+        <s v="TBO TEK"/>
+        <s v="BANDHAN BANK"/>
+        <s v="ZYDUS LIFESCIENCE"/>
+        <s v="ABCAPITAL "/>
+        <s v="PRESTIGE"/>
+        <s v="PINELAB"/>
+        <s v="BHARAT ELECTRONICS"/>
+        <s v="SUZLON"/>
+        <s v="SBIN"/>
+        <s v="CG POWER"/>
+        <s v="RADICO KHAITAN"/>
+        <s v="ANGEL ONE"/>
+        <s v="AMBER ENTERPRISES"/>
+        <s v="BHEL"/>
+        <s v="OLECTRA"/>
+        <s v="ADANIENT"/>
+        <s v="WABAG"/>
+        <s v="KIRLOSKAR OIL ENGINES"/>
+        <s v="TATACOMM"/>
+        <s v="ETERNAL"/>
+        <s v="LAURUSLABS"/>
+        <s v="CIPLA "/>
+        <s v="MEDANTA"/>
+        <s v="SYRMA"/>
+        <s v="VEDANTA ALUM"/>
+        <s v="DIXON TECHNOLOGIES"/>
+        <s v="GOKALDAS EXPORTS"/>
+        <s v="GUJARAT FLUOROCHEM"/>
+        <s v="GENUS POWER"/>
+        <s v="SHRIRAM FINANCE"/>
+        <s v="HIND PETRO"/>
+        <s v="AXIS BANK"/>
+        <s v="WELSPUN CORP"/>
+        <s v="MARUTI"/>
+        <s v="ABCENTRAL"/>
+        <s v="JSW STEEL"/>
+        <s v="STAR HEALTH "/>
+        <s v="MAX HEALTHCARE "/>
+        <s v="MARICO"/>
+        <s v="GRANULES "/>
+        <s v="TORRENT PHARMACEUTICALS"/>
+        <s v="ADITYA BIRLA REAL ESTATE"/>
+        <s v="CREDIT ACCESS GRAMEEN"/>
+        <s v="CG POWER "/>
+        <s v="BAJAJ FINANCE"/>
+        <s v="NAUKRI"/>
+        <s v="AETHER"/>
+        <s v="ONGC"/>
+        <s v="AADHAR HOUSING FINANCE"/>
+        <s v="NYKAA"/>
+        <s v="TITAN"/>
+        <s v="LLOYD"/>
+        <s v="GRASIM INDUSTRIESUSTRIESUSTRIES IND"/>
+        <s v="RR KABEL " u="1"/>
+        <s v="GRASIM" u="1"/>
+        <s v="BHARATFORG" u="1"/>
+        <s v="BEL" u="1"/>
+        <s v="BHARAT FORGE" u="1"/>
+        <s v="WELCORP" u="1"/>
+        <s v="MAX HEALTH " u="1"/>
+        <s v="KIRLOSKAR OLI ENGINES" u="1"/>
+        <s v="CGPOWER " u="1"/>
+        <s v="GRASIM IND" u="1"/>
+        <s v=" BHARAT FORGE" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Day when told" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-06-01T00:00:00" maxDate="2026-07-08T00:00:00"/>
+    </cacheField>
+    <cacheField name="Current price" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="59" maxValue="13735"/>
+    </cacheField>
+    <cacheField name="Target price" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="105" maxValue="15290"/>
+    </cacheField>
+    <cacheField name="Stop loss" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="76" maxValue="11400"/>
+    </cacheField>
+    <cacheField name="Today's closing price" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1033" maxValue="1153"/>
+    </cacheField>
+    <cacheField name="Excepted Return" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="-1" maxValue="0.34328358208955223"/>
+    </cacheField>
+    <cacheField name="Result date" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-02T00:00:00" maxDate="2026-07-01T00:00:00"/>
+    </cacheField>
+    <cacheField name="Result price" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="156.6" maxValue="2450"/>
+    </cacheField>
+    <cacheField name="Profit / loss" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="12" maxValue="12"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="125">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="3538"/>
+    <n v="3690"/>
+    <n v="3450"/>
+    <m/>
+    <n v="4.2962125494629737E-2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="748"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="2056"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="2365"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="1006"/>
+    <n v="1160"/>
+    <m/>
+    <m/>
+    <n v="0.15308151093439365"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="1344"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="5881"/>
+    <n v="6600"/>
+    <m/>
+    <m/>
+    <n v="0.12225811936745451"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <d v="2026-06-01T00:00:00"/>
+    <n v="1456"/>
+    <n v="1483"/>
+    <n v="1438"/>
+    <m/>
+    <n v="1.8543956043956044E-2"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="1488"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="439.39"/>
+    <n v="580"/>
+    <m/>
+    <m/>
+    <n v="0.3200118345888619"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="3104.84"/>
+    <n v="3850"/>
+    <m/>
+    <m/>
+    <n v="0.23999948467553878"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="1208.33"/>
+    <n v="1450"/>
+    <m/>
+    <m/>
+    <n v="0.20000331035395966"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="932.2"/>
+    <n v="1100"/>
+    <m/>
+    <m/>
+    <n v="0.18000429092469422"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="10"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="3318.97"/>
+    <n v="3850"/>
+    <m/>
+    <m/>
+    <n v="0.15999843324886945"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="12"/>
+    <x v="11"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="1543"/>
+    <n v="1720"/>
+    <m/>
+    <m/>
+    <n v="0.11471160077770577"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="13"/>
+    <x v="12"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="434"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="14"/>
+    <x v="13"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="185"/>
+    <n v="235"/>
+    <m/>
+    <m/>
+    <n v="0.27027027027027029"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="15"/>
+    <x v="14"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="1783"/>
+    <n v="2050"/>
+    <m/>
+    <m/>
+    <n v="0.14974761637689288"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="16"/>
+    <x v="1"/>
+    <d v="2026-06-02T00:00:00"/>
+    <n v="767"/>
+    <n v="890"/>
+    <n v="705"/>
+    <m/>
+    <n v="0.16036505867014342"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="17"/>
+    <x v="15"/>
+    <d v="2026-06-03T00:00:00"/>
+    <n v="835"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="18"/>
+    <x v="16"/>
+    <d v="2026-06-03T00:00:00"/>
+    <n v="537"/>
+    <n v="580"/>
+    <n v="510"/>
+    <m/>
+    <n v="8.0074487895716945E-2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="19"/>
+    <x v="17"/>
+    <d v="2026-06-03T00:00:00"/>
+    <n v="1074"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="20"/>
+    <x v="18"/>
+    <d v="2026-06-03T00:00:00"/>
+    <n v="406"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="21"/>
+    <x v="19"/>
+    <d v="2026-06-03T00:00:00"/>
+    <n v="1090"/>
+    <n v="1200"/>
+    <m/>
+    <m/>
+    <n v="0.10091743119266056"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="22"/>
+    <x v="1"/>
+    <d v="2026-06-03T00:00:00"/>
+    <n v="767"/>
+    <n v="890"/>
+    <n v="705"/>
+    <n v="1153"/>
+    <n v="0.16036505867014342"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="23"/>
+    <x v="20"/>
+    <d v="2026-06-04T00:00:00"/>
+    <n v="2189"/>
+    <n v="2484"/>
+    <n v="2040"/>
+    <m/>
+    <n v="0.13476473275468251"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="24"/>
+    <x v="21"/>
+    <d v="2026-06-09T00:00:00"/>
+    <n v="305"/>
+    <n v="325"/>
+    <n v="295"/>
+    <m/>
+    <n v="6.5573770491803282E-2"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="320"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="25"/>
+    <x v="22"/>
+    <d v="2026-06-09T00:00:00"/>
+    <n v="168.6"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="-1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="26"/>
+    <x v="23"/>
+    <d v="2026-06-09T00:00:00"/>
+    <n v="268"/>
+    <n v="360"/>
+    <m/>
+    <m/>
+    <n v="0.34328358208955223"/>
+    <m/>
+    <n v="348"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="27"/>
+    <x v="1"/>
+    <d v="2026-06-09T00:00:00"/>
+    <n v="767"/>
+    <n v="890"/>
+    <n v="705"/>
+    <m/>
+    <m/>
+    <d v="2026-06-11T00:00:00"/>
+    <n v="960"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="28"/>
+    <x v="24"/>
+    <d v="2026-06-11T00:00:00"/>
+    <n v="1438"/>
+    <n v="1550"/>
+    <n v="1388"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="29"/>
+    <x v="25"/>
+    <d v="2026-06-11T00:00:00"/>
+    <n v="1506"/>
+    <m/>
+    <n v="1450"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="30"/>
+    <x v="26"/>
+    <d v="2026-06-11T00:00:00"/>
+    <n v="1039"/>
+    <n v="1280"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="31"/>
+    <x v="27"/>
+    <d v="2026-06-11T00:00:00"/>
+    <n v="3145"/>
+    <n v="3900"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="32"/>
+    <x v="28"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="3089"/>
+    <n v="3270"/>
+    <n v="3000"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="33"/>
+    <x v="29"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="2779"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="34"/>
+    <x v="30"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="2306"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="35"/>
+    <x v="31"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="1510"/>
+    <n v="1860"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="36"/>
+    <x v="32"/>
+    <d v="2026-06-12T00:00:00"/>
+    <n v="351"/>
+    <n v="405"/>
+    <n v="322"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="37"/>
+    <x v="33"/>
+    <d v="2026-06-15T00:00:00"/>
+    <n v="86"/>
+    <n v="105"/>
+    <n v="76"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="38"/>
+    <x v="34"/>
+    <d v="2026-06-15T00:00:00"/>
+    <n v="4710"/>
+    <n v="5600"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="39"/>
+    <x v="35"/>
+    <d v="2026-06-15T00:00:00"/>
+    <n v="141"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="40"/>
+    <x v="36"/>
+    <d v="2026-06-15T00:00:00"/>
+    <n v="2743"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="41"/>
+    <x v="37"/>
+    <d v="2026-06-15T00:00:00"/>
+    <n v="276"/>
+    <n v="294"/>
+    <n v="265"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="42"/>
+    <x v="38"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="2020"/>
+    <n v="2200"/>
+    <n v="1940"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="43"/>
+    <x v="28"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="3171"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="44"/>
+    <x v="39"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="1860"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="45"/>
+    <x v="40"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="7625"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="46"/>
+    <x v="41"/>
+    <d v="2026-06-16T00:00:00"/>
+    <m/>
+    <n v="217"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="47"/>
+    <x v="42"/>
+    <d v="2026-06-16T00:00:00"/>
+    <m/>
+    <n v="125"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="48"/>
+    <x v="43"/>
+    <d v="2026-06-16T00:00:00"/>
+    <m/>
+    <n v="1765"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="49"/>
+    <x v="44"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="210"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="1.4E-2"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="218"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="50"/>
+    <x v="33"/>
+    <d v="2026-06-16T00:00:00"/>
+    <n v="86"/>
+    <n v="105"/>
+    <n v="76"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="51"/>
+    <x v="38"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="1953"/>
+    <n v="2220"/>
+    <n v="1820"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="52"/>
+    <x v="45"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="1079"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="53"/>
+    <x v="5"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="1465"/>
+    <n v="1900"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="54"/>
+    <x v="46"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="374"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="55"/>
+    <x v="47"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="1520"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="56"/>
+    <x v="44"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="217"/>
+    <n v="234"/>
+    <n v="204"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="57"/>
+    <x v="48"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="153"/>
+    <n v="159"/>
+    <n v="151"/>
+    <m/>
+    <m/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="156.6"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="58"/>
+    <x v="49"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="419"/>
+    <n v="510"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="59"/>
+    <x v="2"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="2210"/>
+    <n v="2600"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="2450"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="60"/>
+    <x v="50"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="59"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="61"/>
+    <x v="51"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="1026"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="62"/>
+    <x v="49"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="420"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="63"/>
+    <x v="52"/>
+    <d v="2026-06-18T00:00:00"/>
+    <n v="960"/>
+    <n v="1022"/>
+    <n v="930"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="64"/>
+    <x v="53"/>
+    <d v="2026-06-19T00:00:00"/>
+    <n v="3653"/>
+    <n v="4100"/>
+    <n v="3415"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="65"/>
+    <x v="54"/>
+    <d v="2026-06-19T00:00:00"/>
+    <n v="353"/>
+    <n v="400"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="66"/>
+    <x v="55"/>
+    <d v="2026-06-19T00:00:00"/>
+    <n v="7965"/>
+    <n v="8450"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="67"/>
+    <x v="56"/>
+    <d v="2026-06-19T00:00:00"/>
+    <n v="406"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="68"/>
+    <x v="57"/>
+    <d v="2026-06-19T00:00:00"/>
+    <n v="1446"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="69"/>
+    <x v="58"/>
+    <d v="2026-06-19T00:00:00"/>
+    <n v="3013"/>
+    <n v="3230"/>
+    <n v="2845"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="70"/>
+    <x v="59"/>
+    <d v="2026-06-19T00:00:00"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.09"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="71"/>
+    <x v="53"/>
+    <d v="2026-06-22T00:00:00"/>
+    <n v="3653"/>
+    <n v="4100"/>
+    <n v="3415"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="72"/>
+    <x v="60"/>
+    <d v="2026-06-22T00:00:00"/>
+    <n v="1992"/>
+    <n v="2350"/>
+    <m/>
+    <m/>
+    <n v="0.2"/>
+    <d v="2026-06-22T00:00:00"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="73"/>
+    <x v="6"/>
+    <d v="2026-06-22T00:00:00"/>
+    <n v="416"/>
+    <n v="580"/>
+    <m/>
+    <m/>
+    <n v="0.05"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="74"/>
+    <x v="61"/>
+    <d v="2026-06-22T00:00:00"/>
+    <n v="1889"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="75"/>
+    <x v="62"/>
+    <d v="2026-06-22T00:00:00"/>
+    <n v="264"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="76"/>
+    <x v="46"/>
+    <d v="2026-06-22T00:00:00"/>
+    <n v="376"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="77"/>
+    <x v="63"/>
+    <d v="2026-06-22T00:00:00"/>
+    <n v="1413"/>
+    <n v="1560"/>
+    <n v="1340"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="78"/>
+    <x v="64"/>
+    <d v="2026-06-23T00:00:00"/>
+    <n v="1415"/>
+    <n v="1530"/>
+    <n v="1360"/>
+    <m/>
+    <m/>
+    <d v="2026-06-30T00:00:00"/>
+    <n v="1485"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="79"/>
+    <x v="38"/>
+    <d v="2026-06-23T00:00:00"/>
+    <n v="2103"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="80"/>
+    <x v="6"/>
+    <d v="2026-06-23T00:00:00"/>
+    <n v="484"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="81"/>
+    <x v="65"/>
+    <d v="2026-06-23T00:00:00"/>
+    <n v="1288"/>
+    <n v="1490"/>
+    <m/>
+    <m/>
+    <n v="0.16"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="82"/>
+    <x v="66"/>
+    <d v="2026-06-23T00:00:00"/>
+    <n v="1336"/>
+    <n v="1620"/>
+    <m/>
+    <m/>
+    <n v="0.21"/>
+    <m/>
+    <n v="1430"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="83"/>
+    <x v="53"/>
+    <d v="2026-06-23T00:00:00"/>
+    <n v="3653"/>
+    <n v="4100"/>
+    <n v="3415"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="84"/>
+    <x v="67"/>
+    <d v="2026-06-24T00:00:00"/>
+    <n v="454"/>
+    <n v="540"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="85"/>
+    <x v="68"/>
+    <d v="2026-06-24T00:00:00"/>
+    <n v="12667"/>
+    <n v="15290"/>
+    <n v="11400"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="86"/>
+    <x v="69"/>
+    <d v="2026-06-24T00:00:00"/>
+    <n v="829"/>
+    <n v="1110"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="12"/>
+  </r>
+  <r>
+    <n v="87"/>
+    <x v="70"/>
+    <d v="2026-06-24T00:00:00"/>
+    <n v="3891"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="88"/>
+    <x v="71"/>
+    <d v="2026-06-24T00:00:00"/>
+    <n v="346"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="89"/>
+    <x v="45"/>
+    <d v="2026-06-24T00:00:00"/>
+    <n v="1112"/>
+    <n v="1185"/>
+    <n v="1080"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="90"/>
+    <x v="13"/>
+    <d v="2026-06-24T00:00:00"/>
+    <n v="199"/>
+    <n v="204"/>
+    <n v="197"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="91"/>
+    <x v="53"/>
+    <d v="2026-06-25T00:00:00"/>
+    <n v="3653"/>
+    <n v="4100"/>
+    <n v="3415"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="92"/>
+    <x v="38"/>
+    <d v="2026-06-25T00:00:00"/>
+    <n v="2123"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="93"/>
+    <x v="72"/>
+    <d v="2026-06-25T00:00:00"/>
+    <n v="1019"/>
+    <n v="1175"/>
+    <m/>
+    <n v="1033"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="94"/>
+    <x v="73"/>
+    <d v="2026-06-25T00:00:00"/>
+    <n v="413"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="95"/>
+    <x v="74"/>
+    <d v="2026-06-25T00:00:00"/>
+    <n v="1384"/>
+    <n v="1441"/>
+    <n v="1350"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="96"/>
+    <x v="75"/>
+    <d v="2026-06-29T00:00:00"/>
+    <n v="1455"/>
+    <n v="1570"/>
+    <n v="1380"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="97"/>
+    <x v="76"/>
+    <d v="2026-06-29T00:00:00"/>
+    <n v="13735"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="98"/>
+    <x v="77"/>
+    <d v="2026-06-29T00:00:00"/>
+    <n v="391"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="99"/>
+    <x v="78"/>
+    <d v="2026-06-29T00:00:00"/>
+    <n v="1231"/>
+    <n v="1520"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="100"/>
+    <x v="79"/>
+    <d v="2026-06-29T00:00:00"/>
+    <n v="575"/>
+    <n v="700"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="101"/>
+    <x v="80"/>
+    <d v="2026-06-29T00:00:00"/>
+    <n v="1132"/>
+    <n v="1329"/>
+    <n v="1035"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="102"/>
+    <x v="72"/>
+    <d v="2026-06-29T00:00:00"/>
+    <n v="1046"/>
+    <n v="1205"/>
+    <n v="968"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="103"/>
+    <x v="60"/>
+    <d v="2026-07-01T00:00:00"/>
+    <n v="2441"/>
+    <n v="2750"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="104"/>
+    <x v="81"/>
+    <d v="2026-07-01T00:00:00"/>
+    <n v="840"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="105"/>
+    <x v="82"/>
+    <d v="2026-07-01T00:00:00"/>
+    <n v="802"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="106"/>
+    <x v="83"/>
+    <d v="2026-07-01T00:00:00"/>
+    <n v="4628"/>
+    <n v="4850"/>
+    <n v="4500"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="107"/>
+    <x v="84"/>
+    <d v="2026-07-02T00:00:00"/>
+    <n v="1396"/>
+    <n v="1940"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="108"/>
+    <x v="85"/>
+    <d v="2026-07-02T00:00:00"/>
+    <n v="1503"/>
+    <n v="1780"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="109"/>
+    <x v="86"/>
+    <d v="2026-07-02T00:00:00"/>
+    <n v="976"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="110"/>
+    <x v="6"/>
+    <d v="2026-07-02T00:00:00"/>
+    <n v="508"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="111"/>
+    <x v="47"/>
+    <d v="2026-07-02T00:00:00"/>
+    <n v="1628"/>
+    <n v="1760"/>
+    <n v="1540"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="112"/>
+    <x v="84"/>
+    <d v="2026-07-03T00:00:00"/>
+    <n v="1412"/>
+    <n v="1586"/>
+    <n v="1331"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="113"/>
+    <x v="87"/>
+    <d v="2026-07-03T00:00:00"/>
+    <n v="1018"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="114"/>
+    <x v="81"/>
+    <d v="2026-07-03T00:00:00"/>
+    <n v="856"/>
+    <n v="950"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="115"/>
+    <x v="88"/>
+    <d v="2026-07-03T00:00:00"/>
+    <n v="1027"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="116"/>
+    <x v="89"/>
+    <d v="2026-07-03T00:00:00"/>
+    <n v="1360"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="117"/>
+    <x v="14"/>
+    <d v="2026-07-03T00:00:00"/>
+    <n v="1882"/>
+    <n v="2017"/>
+    <n v="1810"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="118"/>
+    <x v="90"/>
+    <d v="2026-07-06T00:00:00"/>
+    <n v="235"/>
+    <n v="288"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="119"/>
+    <x v="91"/>
+    <d v="2026-07-06T00:00:00"/>
+    <n v="548"/>
+    <n v="612"/>
+    <n v="514"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="120"/>
+    <x v="92"/>
+    <d v="2026-07-06T00:00:00"/>
+    <n v="310"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="121"/>
+    <x v="54"/>
+    <d v="2026-07-07T00:00:00"/>
+    <n v="352"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="122"/>
+    <x v="93"/>
+    <d v="2026-07-07T00:00:00"/>
+    <n v="4484"/>
+    <n v="5250"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="123"/>
+    <x v="20"/>
+    <d v="2026-07-07T00:00:00"/>
+    <n v="2246"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="124"/>
+    <x v="94"/>
+    <d v="2026-07-07T00:00:00"/>
+    <n v="78"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="125"/>
+    <x v="95"/>
+    <d v="2026-07-07T00:00:00"/>
+    <n v="3213"/>
+    <n v="3367"/>
+    <n v="3130"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BFCE9BB-D4F6-4469-A5D2-5B061F18340D}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="P1:Q98" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
+      <items count="108">
+        <item m="1" x="106"/>
+        <item x="91"/>
+        <item x="46"/>
+        <item x="77"/>
+        <item x="14"/>
+        <item x="58"/>
+        <item x="84"/>
+        <item x="1"/>
+        <item x="89"/>
+        <item x="55"/>
+        <item x="19"/>
+        <item x="54"/>
+        <item x="74"/>
+        <item x="20"/>
+        <item x="87"/>
+        <item x="44"/>
+        <item x="33"/>
+        <item m="1" x="99"/>
+        <item x="49"/>
+        <item m="1" x="100"/>
+        <item x="38"/>
+        <item m="1" x="98"/>
+        <item x="56"/>
+        <item x="52"/>
+        <item x="86"/>
+        <item m="1" x="104"/>
+        <item x="64"/>
+        <item x="5"/>
+        <item x="85"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="68"/>
+        <item x="40"/>
+        <item x="62"/>
+        <item x="18"/>
+        <item x="21"/>
+        <item x="9"/>
+        <item x="22"/>
+        <item x="71"/>
+        <item x="30"/>
+        <item x="69"/>
+        <item x="82"/>
+        <item m="1" x="97"/>
+        <item m="1" x="105"/>
+        <item x="28"/>
+        <item x="95"/>
+        <item x="13"/>
+        <item x="70"/>
+        <item x="73"/>
+        <item x="26"/>
+        <item x="0"/>
+        <item x="10"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="41"/>
+        <item x="8"/>
+        <item x="23"/>
+        <item x="78"/>
+        <item x="60"/>
+        <item m="1" x="103"/>
+        <item x="37"/>
+        <item x="63"/>
+        <item x="94"/>
+        <item x="81"/>
+        <item x="76"/>
+        <item m="1" x="102"/>
+        <item x="80"/>
+        <item x="29"/>
+        <item x="65"/>
+        <item x="12"/>
+        <item x="88"/>
+        <item x="24"/>
+        <item x="31"/>
+        <item x="92"/>
+        <item x="57"/>
+        <item x="90"/>
+        <item x="39"/>
+        <item x="25"/>
+        <item x="48"/>
+        <item x="17"/>
+        <item x="47"/>
+        <item x="27"/>
+        <item x="53"/>
+        <item x="32"/>
+        <item m="1" x="96"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="51"/>
+        <item x="72"/>
+        <item x="36"/>
+        <item x="79"/>
+        <item x="50"/>
+        <item x="66"/>
+        <item x="61"/>
+        <item x="43"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="93"/>
+        <item x="83"/>
+        <item x="16"/>
+        <item x="67"/>
+        <item x="7"/>
+        <item x="59"/>
+        <item m="1" x="101"/>
+        <item x="75"/>
+        <item x="42"/>
+        <item x="45"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="97">
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="82"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="106"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="85"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="79"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="93"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="89"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Frequency of Stocks" fld="1" subtotal="count" baseField="1" baseItem="1"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="4">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="4">
+            <x v="7"/>
+            <x v="20"/>
+            <x v="30"/>
+            <x v="82"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="4">
+            <x v="7"/>
+            <x v="20"/>
+            <x v="30"/>
+            <x v="82"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="4">
+            <x v="7"/>
+            <x v="20"/>
+            <x v="30"/>
+            <x v="82"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="4">
+            <x v="7"/>
+            <x v="20"/>
+            <x v="30"/>
+            <x v="82"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -751,2317 +3389,3941 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <dimension ref="A1:L131"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.36328125" customWidth="1"/>
-    <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.6328125" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.36328125" customWidth="1"/>
+    <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>46174</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>3538</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>3690</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>3450</v>
       </c>
-      <c r="H2" s="2">
-        <f>(E2-D2)/D2</f>
+      <c r="I2" s="2">
+        <f>(F2-E2)/E2</f>
         <v>4.2962125494629737E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1">
+        <v>52</v>
+      </c>
+      <c r="D3" s="1">
         <v>46174</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>748</v>
       </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H27" si="0">(E3-D3)/D3</f>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I27" si="0">(F3-E3)/E3</f>
         <v>-1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P3" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1">
+        <v>111</v>
+      </c>
+      <c r="D4" s="1">
         <v>46174</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>2056</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>46191</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>2365</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1">
+        <v>53</v>
+      </c>
+      <c r="D5" s="1">
         <v>46174</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>1006</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>1160</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <f t="shared" si="0"/>
         <v>0.15308151093439365</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>46175</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1344</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1">
+        <v>54</v>
+      </c>
+      <c r="D6" s="1">
         <v>46174</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>5881</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>6600</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <f t="shared" si="0"/>
         <v>0.12225811936745451</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1">
         <v>46174</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>1456</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>1483</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>1438</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="0"/>
         <v>1.8543956043956044E-2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>46175</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1488</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1">
         <v>46175</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>439.39</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>580</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <f t="shared" si="0"/>
         <v>0.3200118345888619</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1">
+        <v>56</v>
+      </c>
+      <c r="D9" s="1">
         <v>46175</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>3104.84</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>3850</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <f t="shared" si="0"/>
         <v>0.23999948467553878</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1">
+        <v>57</v>
+      </c>
+      <c r="D10" s="1">
         <v>46175</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>1208.33</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>1450</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <f t="shared" si="0"/>
         <v>0.20000331035395966</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1">
+        <v>58</v>
+      </c>
+      <c r="D11" s="1">
         <v>46175</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>932.2</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>1100</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <f t="shared" si="0"/>
         <v>0.18000429092469422</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="1">
+        <v>59</v>
+      </c>
+      <c r="D12" s="1">
         <v>46175</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>3318.97</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>3850</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <f t="shared" si="0"/>
         <v>0.15999843324886945</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P12" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="1">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1">
         <v>46175</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>1543</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>1720</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <f t="shared" si="0"/>
         <v>0.11471160077770577</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="1">
+        <v>60</v>
+      </c>
+      <c r="D14" s="1">
         <v>46175</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>434</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="1">
+        <v>61</v>
+      </c>
+      <c r="D15" s="1">
         <v>46175</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>185</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>235</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <f t="shared" si="0"/>
         <v>0.27027027027027029</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="1">
+        <v>62</v>
+      </c>
+      <c r="D16" s="1">
         <v>46175</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>1783</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>2050</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <f t="shared" si="0"/>
         <v>0.14974761637689288</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P16" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="1">
+        <v>52</v>
+      </c>
+      <c r="D17" s="1">
         <v>46175</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>767</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>890</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>705</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <f t="shared" si="0"/>
         <v>0.16036505867014342</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P17" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="1">
+        <v>63</v>
+      </c>
+      <c r="D18" s="1">
         <v>46176</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>835</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P18" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="1">
+        <v>64</v>
+      </c>
+      <c r="D19" s="1">
         <v>46176</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>537</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>580</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>510</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <f t="shared" si="0"/>
         <v>8.0074487895716945E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="1">
+        <v>65</v>
+      </c>
+      <c r="D20" s="1">
         <v>46176</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>1074</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P20" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="1">
+        <v>66</v>
+      </c>
+      <c r="D21" s="1">
         <v>46176</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>406</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="1">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1">
         <v>46176</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>1090</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>1200</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <f t="shared" si="0"/>
         <v>0.10091743119266056</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="1">
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="1">
         <v>46176</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>767</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>890</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>705</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>1153</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <f t="shared" si="0"/>
         <v>0.16036505867014342</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P23" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="1">
+        <v>12</v>
+      </c>
+      <c r="D24" s="1">
         <v>46177</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>2189</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>2484</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>2040</v>
       </c>
-      <c r="H24" s="2">
+      <c r="I24" s="2">
         <f t="shared" si="0"/>
         <v>0.13476473275468251</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P24" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="1">
+        <v>67</v>
+      </c>
+      <c r="D25" s="1">
         <v>46182</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>305</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>325</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>295</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <f t="shared" si="0"/>
         <v>6.5573770491803282E-2</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>46189</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>320</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="1">
+        <v>13</v>
+      </c>
+      <c r="D26" s="1">
         <v>46182</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>168.6</v>
       </c>
-      <c r="H26" s="2">
+      <c r="I26" s="2">
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="1">
+        <v>68</v>
+      </c>
+      <c r="D27" s="1">
         <v>46182</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>268</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>360</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="2">
         <f t="shared" si="0"/>
         <v>0.34328358208955223</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>348</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="1">
+        <v>52</v>
+      </c>
+      <c r="D28" s="1">
         <v>46182</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>767</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>890</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>705</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>46184</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>960</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="1">
+        <v>69</v>
+      </c>
+      <c r="D29" s="1">
         <v>46184</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>1438</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>1550</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>1388</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P29" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="1">
+        <v>70</v>
+      </c>
+      <c r="D30" s="1">
         <v>46184</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>1506</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>1450</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="1">
+        <v>71</v>
+      </c>
+      <c r="D31" s="1">
         <v>46184</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>1039</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>1280</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="1">
+        <v>72</v>
+      </c>
+      <c r="D32" s="1">
         <v>46184</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>3145</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>3900</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="1">
+        <v>113</v>
+      </c>
+      <c r="D33" s="1">
         <v>46185</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>3089</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>3270</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>3000</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P33" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="1">
+        <v>14</v>
+      </c>
+      <c r="D34" s="1">
         <v>46185</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>2779</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P34" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="1">
+        <v>15</v>
+      </c>
+      <c r="D35" s="1">
         <v>46185</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>2306</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P35" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="1">
+        <v>73</v>
+      </c>
+      <c r="D36" s="1">
         <v>46185</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>1510</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>1860</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P36" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="1">
         <v>46185</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>351</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>405</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>322</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="1">
+        <v>74</v>
+      </c>
+      <c r="D38" s="1">
         <v>46188</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>86</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>105</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P38" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="1">
+        <v>75</v>
+      </c>
+      <c r="D39" s="1">
         <v>46188</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>4710</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>5600</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="1">
+        <v>17</v>
+      </c>
+      <c r="D40" s="1">
         <v>46188</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>141</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P40" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="1">
+        <v>18</v>
+      </c>
+      <c r="D41" s="1">
         <v>46188</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>2743</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P41" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="1">
+        <v>19</v>
+      </c>
+      <c r="D42" s="1">
         <v>46188</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>276</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>294</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>265</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P42" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="1">
+        <v>110</v>
+      </c>
+      <c r="D43" s="1">
         <v>46189</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>2020</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>2200</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>1940</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P43" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="1">
+        <v>113</v>
+      </c>
+      <c r="D44" s="1">
         <v>46189</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>3171</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C45" s="1">
+        <v>76</v>
+      </c>
+      <c r="D45" s="1">
         <v>46189</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>1860</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P45" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
-      </c>
-      <c r="C46" s="1">
+        <v>77</v>
+      </c>
+      <c r="D46" s="1">
         <v>46189</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>7625</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P46" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
-      </c>
-      <c r="C47" s="1">
+        <v>78</v>
+      </c>
+      <c r="D47" s="1">
         <v>46189</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>217</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
-      </c>
-      <c r="C48" s="1">
+        <v>79</v>
+      </c>
+      <c r="D48" s="1">
         <v>46189</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>125</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="1">
+        <v>21</v>
+      </c>
+      <c r="D49" s="1">
         <v>46189</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>1765</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P49" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="1">
+        <v>80</v>
+      </c>
+      <c r="D50" s="1">
         <v>46189</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>210</v>
       </c>
-      <c r="H50" s="2">
+      <c r="I50" s="2">
         <v>1.4E-2</v>
       </c>
-      <c r="I50" s="1">
+      <c r="J50" s="1">
         <v>46189</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>218</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P50" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
-      </c>
-      <c r="C51" s="1">
+        <v>74</v>
+      </c>
+      <c r="D51" s="1">
         <v>46189</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>86</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>105</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>76</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P51" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" s="1">
+        <v>110</v>
+      </c>
+      <c r="D52" s="1">
         <v>46190</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>1953</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>2220</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>1820</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P52" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="1">
+        <v>81</v>
+      </c>
+      <c r="D53" s="1">
         <v>46190</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>1079</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P53" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="1">
+        <v>9</v>
+      </c>
+      <c r="D54" s="1">
         <v>46190</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>1465</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>1900</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P54" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
-      </c>
-      <c r="C55" s="1">
+        <v>22</v>
+      </c>
+      <c r="D55" s="1">
         <v>46190</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>374</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" s="1">
+        <v>23</v>
+      </c>
+      <c r="D56" s="1">
         <v>46190</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>1520</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P56" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C57" s="1">
+        <v>80</v>
+      </c>
+      <c r="D57" s="1">
         <v>46190</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>217</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>234</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>204</v>
       </c>
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J57" s="1"/>
+      <c r="P57" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
-      </c>
-      <c r="C58" s="1">
+        <v>24</v>
+      </c>
+      <c r="D58" s="1">
         <v>46190</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>153</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>159</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>151</v>
       </c>
-      <c r="I58" s="1">
+      <c r="J58" s="1">
         <v>46190</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>156.6</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P58" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
-      </c>
-      <c r="C59" s="1">
+        <v>82</v>
+      </c>
+      <c r="D59" s="1">
         <v>46191</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>419</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>510</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P59" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="1">
+        <v>111</v>
+      </c>
+      <c r="D60" s="1">
         <v>46191</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>2210</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>2600</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>2450</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P60" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" s="1">
+        <v>46191</v>
+      </c>
+      <c r="E61">
         <v>59</v>
       </c>
-      <c r="C61" s="1">
-        <v>46191</v>
-      </c>
-      <c r="D61">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P61" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
-      </c>
-      <c r="C62" s="1">
+        <v>26</v>
+      </c>
+      <c r="D62" s="1">
         <v>46191</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>1026</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C63" s="1">
+        <v>82</v>
+      </c>
+      <c r="D63" s="1">
         <v>46191</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>420</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P63" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
-      </c>
-      <c r="C64" s="1">
+        <v>83</v>
+      </c>
+      <c r="D64" s="1">
         <v>46191</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>960</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>1022</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>930</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
-      </c>
-      <c r="C65" s="1">
+        <v>84</v>
+      </c>
+      <c r="D65" s="1">
         <v>46192</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>3653</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>4100</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>3415</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="1">
+        <v>85</v>
+      </c>
+      <c r="D66" s="1">
         <v>46192</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>353</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>400</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
-      </c>
-      <c r="C67" s="1">
+        <v>86</v>
+      </c>
+      <c r="D67" s="1">
         <v>46192</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>7965</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>8450</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P67" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
-      </c>
-      <c r="C68" s="1">
+        <v>27</v>
+      </c>
+      <c r="D68" s="1">
         <v>46192</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>406</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P68" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
-      </c>
-      <c r="C69" s="1">
+        <v>28</v>
+      </c>
+      <c r="D69" s="1">
         <v>46192</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>1446</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
-      </c>
-      <c r="C70" s="1">
+        <v>29</v>
+      </c>
+      <c r="D70" s="1">
         <v>46192</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>3013</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>3230</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>2845</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P70" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
-      </c>
-      <c r="C71" s="1">
+        <v>30</v>
+      </c>
+      <c r="D71" s="1">
         <v>46192</v>
       </c>
-      <c r="H71" s="3">
+      <c r="I71" s="3">
         <v>0.09</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P71" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>63</v>
-      </c>
-      <c r="C72" s="1">
+        <v>84</v>
+      </c>
+      <c r="D72" s="1">
         <v>46195</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>3653</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>4100</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>3415</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P72" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
-      </c>
-      <c r="C73" s="1">
+        <v>87</v>
+      </c>
+      <c r="D73" s="1">
         <v>46195</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>1992</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>2350</v>
       </c>
-      <c r="H73" s="3">
+      <c r="I73" s="3">
         <v>0.2</v>
       </c>
-      <c r="I73" s="1">
+      <c r="J73" s="1">
         <v>46195</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P73" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="1">
+        <v>55</v>
+      </c>
+      <c r="D74" s="1">
         <v>46195</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>416</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>580</v>
       </c>
-      <c r="H74" s="3">
+      <c r="I74" s="3">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P74" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
-      </c>
-      <c r="C75" s="1">
+        <v>31</v>
+      </c>
+      <c r="D75" s="1">
         <v>46195</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>1889</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P75" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
-      </c>
-      <c r="C76" s="1">
+        <v>32</v>
+      </c>
+      <c r="D76" s="1">
         <v>46195</v>
       </c>
-      <c r="D76">
+      <c r="E76">
         <v>264</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P76" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>55</v>
-      </c>
-      <c r="C77" s="1">
+        <v>22</v>
+      </c>
+      <c r="D77" s="1">
         <v>46195</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>376</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P77" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
-      </c>
-      <c r="C78" s="1">
+        <v>33</v>
+      </c>
+      <c r="D78" s="1">
         <v>46195</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>1413</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>1560</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>1340</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P78" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
-      </c>
-      <c r="C79" s="1">
+        <v>35</v>
+      </c>
+      <c r="D79" s="1">
         <v>46196</v>
       </c>
-      <c r="D79">
+      <c r="E79">
         <v>1415</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>1530</v>
       </c>
-      <c r="F79">
+      <c r="G79">
         <v>1360</v>
       </c>
-      <c r="I79" s="1">
+      <c r="J79" s="1">
         <v>46203</v>
       </c>
-      <c r="J79">
+      <c r="K79">
         <v>1485</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="P79" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
-      </c>
-      <c r="C80" s="1">
+        <v>110</v>
+      </c>
+      <c r="D80" s="1">
         <v>46196</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>2103</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P80" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
-      </c>
-      <c r="C81" s="1">
+        <v>55</v>
+      </c>
+      <c r="D81" s="1">
         <v>46196</v>
       </c>
-      <c r="D81">
+      <c r="E81">
         <v>484</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P81" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
-      </c>
-      <c r="C82" s="1">
+        <v>36</v>
+      </c>
+      <c r="D82" s="1">
         <v>46196</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>1288</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>1490</v>
       </c>
-      <c r="H82" s="3">
+      <c r="I82" s="3">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P82" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C83" s="1">
+      <c r="B83" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="1">
         <v>46196</v>
       </c>
-      <c r="D83">
+      <c r="E83">
         <v>1336</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>1620</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>0.21</v>
       </c>
-      <c r="J83">
+      <c r="K83">
         <v>1430</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P83" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>63</v>
-      </c>
-      <c r="C84" s="1">
+        <v>84</v>
+      </c>
+      <c r="D84" s="1">
         <v>46196</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>3653</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>4100</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>3415</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P84" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
-      </c>
-      <c r="C85" s="1">
+        <v>88</v>
+      </c>
+      <c r="D85" s="1">
         <v>46197</v>
       </c>
-      <c r="D85">
+      <c r="E85">
         <v>454</v>
       </c>
-      <c r="E85">
+      <c r="F85">
         <v>540</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P85" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
-      </c>
-      <c r="C86" s="1">
+        <v>89</v>
+      </c>
+      <c r="D86" s="1">
         <v>46197</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>12667</v>
       </c>
-      <c r="E86">
+      <c r="F86">
         <v>15290</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>11400</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P86" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C87" s="1">
+      <c r="B87" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" s="1">
         <v>46197</v>
       </c>
-      <c r="D87">
+      <c r="E87">
         <v>829</v>
       </c>
-      <c r="E87">
+      <c r="F87">
         <v>1110</v>
       </c>
-      <c r="L87">
+      <c r="M87">
         <v>12</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P87" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
-      </c>
-      <c r="C88" s="1">
+        <v>91</v>
+      </c>
+      <c r="D88" s="1">
         <v>46197</v>
       </c>
-      <c r="D88">
+      <c r="E88">
         <v>3891</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P88" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>82</v>
-      </c>
-      <c r="C89" s="1">
+        <v>92</v>
+      </c>
+      <c r="D89" s="1">
         <v>46197</v>
       </c>
-      <c r="D89">
+      <c r="E89">
         <v>346</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P89" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C90" s="1">
+      <c r="B90" t="s">
+        <v>81</v>
+      </c>
+      <c r="D90" s="1">
         <v>46197</v>
       </c>
-      <c r="D90">
+      <c r="E90">
         <v>1112</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>1185</v>
       </c>
-      <c r="F90">
+      <c r="G90">
         <v>1080</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P90" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
-      </c>
-      <c r="C91" s="1">
+        <v>61</v>
+      </c>
+      <c r="D91" s="1">
         <v>46197</v>
       </c>
-      <c r="D91">
+      <c r="E91">
         <v>199</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>204</v>
       </c>
-      <c r="F91">
+      <c r="G91">
         <v>197</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P91" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>63</v>
-      </c>
-      <c r="C92" s="1">
+        <v>84</v>
+      </c>
+      <c r="D92" s="1">
         <v>46198</v>
       </c>
-      <c r="D92">
+      <c r="E92">
         <v>3653</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>4100</v>
       </c>
-      <c r="F92">
+      <c r="G92">
         <v>3415</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P92" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>85</v>
-      </c>
-      <c r="C93" s="1">
+        <v>110</v>
+      </c>
+      <c r="D93" s="1">
         <v>46198</v>
       </c>
-      <c r="D93">
+      <c r="E93">
         <v>2123</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P93" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>86</v>
-      </c>
-      <c r="C94" s="1">
+        <v>93</v>
+      </c>
+      <c r="D94" s="1">
         <v>46198</v>
       </c>
-      <c r="D94">
+      <c r="E94">
         <v>1019</v>
       </c>
-      <c r="E94">
+      <c r="F94">
         <v>1175</v>
       </c>
-      <c r="G94">
+      <c r="H94">
         <v>1033</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P94" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>87</v>
-      </c>
-      <c r="C95" s="1">
+        <v>94</v>
+      </c>
+      <c r="D95" s="1">
         <v>46198</v>
       </c>
-      <c r="D95">
+      <c r="E95">
         <v>413</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="P95" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C96" s="1">
+      <c r="B96" t="s">
+        <v>95</v>
+      </c>
+      <c r="D96" s="1">
         <v>46198</v>
       </c>
-      <c r="D96">
+      <c r="E96">
         <v>1384</v>
       </c>
-      <c r="E96">
+      <c r="F96">
         <v>1441</v>
       </c>
-      <c r="F96">
+      <c r="G96">
         <v>1350</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P96" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C97" s="1">
+      <c r="B97" t="s">
+        <v>116</v>
+      </c>
+      <c r="D97" s="1">
         <v>46202</v>
       </c>
-      <c r="D97">
+      <c r="E97">
         <v>1455</v>
       </c>
-      <c r="E97">
+      <c r="F97">
         <v>1570</v>
       </c>
-      <c r="F97">
+      <c r="G97">
         <v>1380</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P97" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>90</v>
-      </c>
-      <c r="C98" s="1">
+        <v>96</v>
+      </c>
+      <c r="D98" s="1">
         <v>46202</v>
       </c>
-      <c r="D98">
+      <c r="E98">
         <v>13735</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="P98" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q98">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>91</v>
-      </c>
-      <c r="C99" s="1">
+        <v>97</v>
+      </c>
+      <c r="D99" s="1">
         <v>46202</v>
       </c>
-      <c r="D99">
+      <c r="E99">
         <v>391</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
-      </c>
-      <c r="C100" s="1">
+        <v>98</v>
+      </c>
+      <c r="D100" s="1">
         <v>46202</v>
       </c>
-      <c r="D100">
+      <c r="E100">
         <v>1231</v>
       </c>
-      <c r="E100">
+      <c r="F100">
         <v>1520</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
-      </c>
-      <c r="C101" s="1">
+        <v>99</v>
+      </c>
+      <c r="D101" s="1">
         <v>46202</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>575</v>
       </c>
-      <c r="E101">
+      <c r="F101">
         <v>700</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>94</v>
-      </c>
-      <c r="C102" s="1">
+        <v>115</v>
+      </c>
+      <c r="D102" s="1">
         <v>46202</v>
       </c>
-      <c r="D102">
+      <c r="E102">
         <v>1132</v>
       </c>
-      <c r="E102">
+      <c r="F102">
         <v>1329</v>
       </c>
-      <c r="F102">
+      <c r="G102">
         <v>1035</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>86</v>
-      </c>
-      <c r="C103" s="1">
+        <v>93</v>
+      </c>
+      <c r="D103" s="1">
         <v>46202</v>
       </c>
-      <c r="D103">
+      <c r="E103">
         <v>1046</v>
       </c>
-      <c r="E103">
+      <c r="F103">
         <v>1205</v>
       </c>
-      <c r="F103">
+      <c r="G103">
         <v>968</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>95</v>
-      </c>
-      <c r="C104" s="1">
+        <v>87</v>
+      </c>
+      <c r="D104" s="1">
         <v>46204</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>2441</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>2750</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>96</v>
-      </c>
-      <c r="C105" s="1">
+        <v>100</v>
+      </c>
+      <c r="D105" s="1">
         <v>46204</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>840</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>97</v>
-      </c>
-      <c r="C106" s="1">
+        <v>101</v>
+      </c>
+      <c r="D106" s="1">
         <v>46204</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>802</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C107" s="1">
+      <c r="B107" t="s">
+        <v>102</v>
+      </c>
+      <c r="D107" s="1">
         <v>46204</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>4628</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>4850</v>
       </c>
-      <c r="F107">
+      <c r="G107">
         <v>4500</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>99</v>
-      </c>
-      <c r="C108" s="1">
+        <v>103</v>
+      </c>
+      <c r="D108" s="1">
         <v>46205</v>
       </c>
-      <c r="D108">
+      <c r="E108">
         <v>1396</v>
       </c>
-      <c r="E108">
+      <c r="F108">
         <v>1940</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>100</v>
-      </c>
-      <c r="C109" s="1">
+        <v>104</v>
+      </c>
+      <c r="D109" s="1">
         <v>46205</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>1503</v>
       </c>
-      <c r="E109">
+      <c r="F109">
         <v>1780</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>101</v>
-      </c>
-      <c r="C110" s="1">
+        <v>112</v>
+      </c>
+      <c r="D110" s="1">
         <v>46205</v>
       </c>
-      <c r="D110">
+      <c r="E110">
         <v>976</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
-      </c>
-      <c r="C111" s="1">
+        <v>55</v>
+      </c>
+      <c r="D111" s="1">
         <v>46205</v>
       </c>
-      <c r="D111">
+      <c r="E111">
         <v>508</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
-      <c r="B112" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C112" s="1">
+      <c r="B112" t="s">
+        <v>23</v>
+      </c>
+      <c r="D112" s="1">
         <v>46205</v>
       </c>
-      <c r="D112">
+      <c r="E112">
         <v>1628</v>
       </c>
-      <c r="E112">
+      <c r="F112">
         <v>1760</v>
       </c>
-      <c r="F112">
+      <c r="G112">
         <v>1540</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>99</v>
-      </c>
-      <c r="C113" s="1">
+        <v>103</v>
+      </c>
+      <c r="D113" s="1">
         <v>46206</v>
       </c>
-      <c r="D113">
+      <c r="E113">
         <v>1412</v>
       </c>
-      <c r="E113">
+      <c r="F113">
         <v>1586</v>
       </c>
-      <c r="F113">
+      <c r="G113">
         <v>1331</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
-      </c>
-      <c r="C114" s="1">
+        <v>105</v>
+      </c>
+      <c r="D114" s="1">
         <v>46206</v>
       </c>
-      <c r="D114">
+      <c r="E114">
         <v>1018</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>96</v>
-      </c>
-      <c r="C115" s="1">
+        <v>100</v>
+      </c>
+      <c r="D115" s="1">
         <v>46206</v>
       </c>
-      <c r="D115">
+      <c r="E115">
         <v>856</v>
       </c>
-      <c r="E115">
+      <c r="F115">
         <v>950</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>103</v>
-      </c>
-      <c r="C116" s="1">
+        <v>106</v>
+      </c>
+      <c r="D116" s="1">
         <v>46206</v>
       </c>
-      <c r="D116">
+      <c r="E116">
         <v>1027</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>104</v>
-      </c>
-      <c r="C117" s="1">
+        <v>107</v>
+      </c>
+      <c r="D117" s="1">
         <v>46206</v>
       </c>
-      <c r="D117">
+      <c r="E117">
         <v>1360</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>23</v>
-      </c>
-      <c r="C118" s="1">
+        <v>62</v>
+      </c>
+      <c r="D118" s="1">
         <v>46206</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>1882</v>
       </c>
-      <c r="E118">
+      <c r="F118">
         <v>2017</v>
       </c>
-      <c r="F118">
+      <c r="G118">
         <v>1810</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>105</v>
-      </c>
-      <c r="C119" s="1">
+        <v>40</v>
+      </c>
+      <c r="D119" s="1">
         <v>46209</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>235</v>
       </c>
-      <c r="E119">
+      <c r="F119">
         <v>288</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
-      <c r="B120" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C120" s="1">
+      <c r="B120" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" s="1">
         <v>46209</v>
       </c>
-      <c r="D120">
+      <c r="E120">
         <v>548</v>
       </c>
-      <c r="E120">
+      <c r="F120">
         <v>612</v>
       </c>
-      <c r="F120">
+      <c r="G120">
         <v>514</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>107</v>
-      </c>
-      <c r="C121" s="1">
+        <v>42</v>
+      </c>
+      <c r="D121" s="1">
         <v>46209</v>
       </c>
-      <c r="D121">
+      <c r="E121">
         <v>310</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B122" t="s">
+        <v>85</v>
+      </c>
+      <c r="D122" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E122">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" t="s">
+        <v>108</v>
+      </c>
+      <c r="D123" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E123">
+        <v>4484</v>
+      </c>
+      <c r="F123">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E124">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" t="s">
+        <v>43</v>
+      </c>
+      <c r="D125" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E125">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
+        <v>114</v>
+      </c>
+      <c r="D126" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E126">
+        <v>3213</v>
+      </c>
+      <c r="F126">
+        <v>3367</v>
+      </c>
+      <c r="G126">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C127" s="4"/>
+      <c r="D127" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E127">
+        <v>289</v>
+      </c>
+      <c r="F127">
+        <v>310</v>
+      </c>
+      <c r="G127">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E128">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
+        <v>118</v>
+      </c>
+      <c r="D129" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E129">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B130" t="s">
+        <v>100</v>
+      </c>
+      <c r="D130" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E130">
+        <v>848</v>
+      </c>
+      <c r="F130">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
+      <c r="B131" t="s">
+        <v>119</v>
+      </c>
+      <c r="D131" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E131">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>42</v>
+      </c>
+      <c r="C132" t="s">
+        <v>125</v>
+      </c>
+      <c r="D132" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E132">
+        <v>317</v>
+      </c>
+      <c r="F132">
+        <v>370</v>
+      </c>
+      <c r="G132">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>88</v>
+      </c>
+      <c r="D133" s="1">
+        <v>46212</v>
+      </c>
+      <c r="E133">
+        <v>415</v>
+      </c>
+      <c r="F133">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>120</v>
+      </c>
+      <c r="D134" s="1">
+        <v>46212</v>
+      </c>
+      <c r="E134">
+        <v>1132</v>
+      </c>
+      <c r="F134">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>121</v>
+      </c>
+      <c r="D135" s="1">
+        <v>46212</v>
+      </c>
+      <c r="E135">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D136" s="1">
+        <v>46212</v>
+      </c>
+      <c r="E136">
+        <v>1200</v>
+      </c>
+      <c r="F136">
+        <v>1300</v>
+      </c>
+      <c r="G136">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>42</v>
+      </c>
+      <c r="C137" t="s">
+        <v>125</v>
+      </c>
+      <c r="D137" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E137">
+        <v>317</v>
+      </c>
+      <c r="F137">
+        <v>370</v>
+      </c>
+      <c r="G137">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>67</v>
+      </c>
+      <c r="C138" t="s">
+        <v>126</v>
+      </c>
+      <c r="D138" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E138">
+        <v>328</v>
+      </c>
+      <c r="F138">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>89</v>
+      </c>
+      <c r="C139" t="s">
+        <v>126</v>
+      </c>
+      <c r="D139" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E139">
+        <v>13477</v>
+      </c>
+      <c r="F139">
+        <v>16100</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>33</v>
+      </c>
+      <c r="C140" t="s">
+        <v>127</v>
+      </c>
+      <c r="D140" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E140">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>129</v>
+      </c>
+      <c r="D141" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E141">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>128</v>
+      </c>
+      <c r="C142" t="s">
+        <v>127</v>
+      </c>
+      <c r="D142" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E142">
+        <v>3429</v>
+      </c>
+      <c r="F142">
+        <v>3715</v>
+      </c>
+      <c r="G142">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>130</v>
+      </c>
+      <c r="C143" t="s">
+        <v>133</v>
+      </c>
+      <c r="D143" s="1">
+        <v>46216</v>
+      </c>
+      <c r="E143">
+        <v>1431</v>
+      </c>
+      <c r="F143">
+        <v>1520</v>
+      </c>
+      <c r="G143">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>131</v>
+      </c>
+      <c r="C144" t="s">
+        <v>133</v>
+      </c>
+      <c r="D144" s="1">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>132</v>
+      </c>
+      <c r="D145" s="1">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>134</v>
+      </c>
+      <c r="D146" s="1">
+        <v>46216</v>
+      </c>
+      <c r="E146">
+        <v>321</v>
+      </c>
+      <c r="F146">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>135</v>
+      </c>
+      <c r="D147" s="1">
+        <v>46216</v>
+      </c>
+      <c r="E147">
+        <v>871</v>
+      </c>
+      <c r="F147">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>93</v>
+      </c>
+      <c r="C148" t="s">
+        <v>125</v>
+      </c>
+      <c r="D148" s="1">
+        <v>46216</v>
+      </c>
+      <c r="E148">
+        <v>1046</v>
+      </c>
+      <c r="F148">
+        <v>1205</v>
+      </c>
+      <c r="G148">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>136</v>
+      </c>
+      <c r="D149" s="1">
+        <v>46217</v>
+      </c>
+      <c r="E149">
+        <v>760</v>
+      </c>
+      <c r="F149">
+        <v>830</v>
+      </c>
+      <c r="G149">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>137</v>
+      </c>
+      <c r="C150" t="s">
+        <v>138</v>
+      </c>
+      <c r="D150" s="1">
+        <v>46217</v>
+      </c>
+      <c r="E150">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>139</v>
+      </c>
+      <c r="D151" s="1">
+        <v>46217</v>
+      </c>
+      <c r="E151">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>140</v>
+      </c>
+      <c r="D152" s="1">
+        <v>46217</v>
+      </c>
+      <c r="E152">
+        <v>3206</v>
+      </c>
+      <c r="F152">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>141</v>
+      </c>
+      <c r="D153" s="1">
+        <v>46217</v>
+      </c>
+      <c r="E153">
+        <v>1221</v>
+      </c>
+      <c r="F153">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>142</v>
+      </c>
+      <c r="C154" t="s">
+        <v>126</v>
+      </c>
+      <c r="D154" s="1">
+        <v>46218</v>
+      </c>
+      <c r="E154">
+        <v>168</v>
+      </c>
+      <c r="F154">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>143</v>
+      </c>
+      <c r="C155" t="s">
+        <v>144</v>
+      </c>
+      <c r="D155" s="1">
+        <v>46218</v>
+      </c>
+      <c r="E155">
+        <v>449</v>
+      </c>
+      <c r="F155">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>145</v>
+      </c>
+      <c r="C156" t="s">
+        <v>146</v>
+      </c>
+      <c r="D156" s="1">
+        <v>46218</v>
+      </c>
+      <c r="E156">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>147</v>
+      </c>
+      <c r="C157" t="s">
+        <v>146</v>
+      </c>
+      <c r="D157" s="1">
+        <v>46218</v>
+      </c>
+      <c r="E157">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C158" t="s">
+        <v>127</v>
+      </c>
+      <c r="D158" s="1">
+        <v>46218</v>
+      </c>
+      <c r="E158">
+        <v>1840</v>
+      </c>
+      <c r="F158">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C159" t="s">
+        <v>149</v>
+      </c>
+      <c r="D159" s="1">
+        <v>46219</v>
+      </c>
+      <c r="E159">
+        <v>1860</v>
+      </c>
+      <c r="F159">
+        <v>1980</v>
+      </c>
+      <c r="G159">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>150</v>
+      </c>
+      <c r="C160" t="s">
+        <v>146</v>
+      </c>
+      <c r="D160" s="1">
+        <v>46219</v>
+      </c>
+      <c r="E160">
+        <v>7203</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>151</v>
+      </c>
+      <c r="C161" t="s">
+        <v>146</v>
+      </c>
+      <c r="D161" s="1">
+        <v>46219</v>
+      </c>
+      <c r="E161">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>152</v>
+      </c>
+      <c r="C162" t="s">
+        <v>144</v>
+      </c>
+      <c r="D162" s="1">
+        <v>46219</v>
+      </c>
+      <c r="E162">
+        <v>1204</v>
+      </c>
+      <c r="F162">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>61</v>
+      </c>
+      <c r="C163" t="s">
+        <v>126</v>
+      </c>
+      <c r="D163" s="1">
+        <v>46219</v>
+      </c>
+      <c r="E163">
+        <v>216</v>
+      </c>
+      <c r="F163">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>115</v>
+      </c>
+      <c r="C164" t="s">
+        <v>125</v>
+      </c>
+      <c r="D164" s="1">
+        <v>46219</v>
+      </c>
+      <c r="E164">
+        <v>1132</v>
+      </c>
+      <c r="F164">
+        <v>1329</v>
+      </c>
+      <c r="G164">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>153</v>
+      </c>
+      <c r="E165">
+        <v>350</v>
+      </c>
+      <c r="F165">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>154</v>
+      </c>
+      <c r="E166">
+        <v>1510</v>
+      </c>
+      <c r="F166">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>155</v>
+      </c>
+      <c r="E167">
+        <v>2185</v>
+      </c>
+      <c r="F167">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E170">
+        <v>725</v>
+      </c>
+      <c r="F170">
+        <v>780</v>
+      </c>
+      <c r="G170">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A201">
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K84" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
+  <autoFilter ref="A1:L201" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="GROWW"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D732E0AF-64C8-4124-A0D7-87EDC5F828BC}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>2108.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>244.1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7D081D-0343-4D2E-8276-578E354BBF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAE28C3-2E2D-4C18-A7E1-2C3E9A89475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="7860" windowHeight="10170" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="11500" yWindow="0" windowWidth="7550" windowHeight="10170" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="169">
   <si>
     <t>S No.</t>
   </si>
@@ -520,6 +520,36 @@
   </si>
   <si>
     <t>HSCL</t>
+  </si>
+  <si>
+    <t>TIMETECHNO</t>
+  </si>
+  <si>
+    <t>ICICI BANK</t>
+  </si>
+  <si>
+    <t>JSW</t>
+  </si>
+  <si>
+    <t>ABREL</t>
+  </si>
+  <si>
+    <t>SANSERA</t>
+  </si>
+  <si>
+    <t>PAYTM</t>
+  </si>
+  <si>
+    <t>EMCURE PHARMA</t>
+  </si>
+  <si>
+    <t>LLOYD METALS</t>
+  </si>
+  <si>
+    <t>UNION BANK OF INDIA</t>
+  </si>
+  <si>
+    <t>NAVIN FLUORINE</t>
   </si>
 </sst>
 </file>
@@ -3389,7 +3419,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3456,7 +3485,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3486,7 +3515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3510,7 +3539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3540,7 +3569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3573,7 +3602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3600,7 +3629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3636,7 +3665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3663,7 +3692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3690,7 +3719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3717,7 +3746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3744,7 +3773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3771,7 +3800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3798,7 +3827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3849,7 +3878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3876,7 +3905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3906,7 +3935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3930,7 +3959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3960,7 +3989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3984,7 +4013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4008,7 +4037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4035,7 +4064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4068,7 +4097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4098,7 +4127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4134,7 +4163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4158,7 +4187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4188,7 +4217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4220,7 +4249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4246,7 +4275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4269,7 +4298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4292,7 +4321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4315,7 +4344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4341,7 +4370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4361,7 +4390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4381,7 +4410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4404,7 +4433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4430,7 +4459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4456,7 +4485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4479,7 +4508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4499,7 +4528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4519,7 +4548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4545,7 +4574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4571,7 +4600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4591,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4611,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4631,7 +4660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4651,7 +4680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4671,7 +4700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4691,7 +4720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4720,7 +4749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4746,7 +4775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4772,7 +4801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4792,7 +4821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4815,7 +4844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4835,7 +4864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4855,7 +4884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4882,7 +4911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4914,7 +4943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4937,7 +4966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4963,7 +4992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4983,7 +5012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5003,7 +5032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5023,7 +5052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5049,7 +5078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5075,7 +5104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5098,7 +5127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5121,7 +5150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5141,7 +5170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5161,7 +5190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5187,7 +5216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5207,7 +5236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5233,7 +5262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5262,7 +5291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5288,7 +5317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5308,7 +5337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5328,7 +5357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5348,7 +5377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5374,7 +5403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5406,7 +5435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5426,7 +5455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5446,7 +5475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5472,7 +5501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5501,7 +5530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5527,7 +5556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5550,7 +5579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5576,7 +5605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5602,7 +5631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5622,7 +5651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5642,7 +5671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5694,7 +5723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5720,7 +5749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5740,7 +5769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5766,7 +5795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5786,7 +5815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5812,7 +5841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5838,7 +5867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5858,7 +5887,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5872,7 +5901,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5889,7 +5918,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5906,7 +5935,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5926,7 +5955,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5946,7 +5975,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5963,7 +5992,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5977,7 +6006,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5991,7 +6020,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6011,7 +6040,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6028,7 +6057,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6045,7 +6074,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6059,7 +6088,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6073,7 +6102,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6093,7 +6122,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6113,7 +6142,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6127,7 +6156,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6144,7 +6173,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6158,7 +6187,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6172,7 +6201,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6192,7 +6221,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6209,7 +6238,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6229,7 +6258,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6243,7 +6272,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6257,7 +6286,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6274,7 +6303,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6288,7 +6317,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -6302,7 +6331,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6322,7 +6351,7 @@
         <v>3130</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -6343,7 +6372,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -6357,7 +6386,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6371,7 +6400,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6388,7 +6417,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -6402,7 +6431,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -6425,7 +6454,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -6442,7 +6471,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6459,7 +6488,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -6473,7 +6502,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -6496,7 +6525,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -6519,7 +6548,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -6539,7 +6568,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -6559,7 +6588,7 @@
         <v>16100</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -6576,7 +6605,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -6590,7 +6619,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -6613,7 +6642,7 @@
         <v>3290</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6636,7 +6665,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6650,7 +6679,7 @@
         <v>46216</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6661,7 +6690,7 @@
         <v>46216</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6678,7 +6707,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6695,7 +6724,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -6718,7 +6747,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -6738,7 +6767,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -6755,7 +6784,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -6769,7 +6798,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -6786,7 +6815,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -6803,7 +6832,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -6823,7 +6852,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -6843,7 +6872,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -6860,7 +6889,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -6877,7 +6906,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -6897,7 +6926,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -6920,7 +6949,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -6937,7 +6966,7 @@
         <v>7203</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -6954,7 +6983,7 @@
         <v>4133</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -6994,7 +7023,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -7017,13 +7046,16 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
       <c r="B165" t="s">
         <v>153</v>
       </c>
+      <c r="D165" s="1">
+        <v>46220</v>
+      </c>
       <c r="E165">
         <v>350</v>
       </c>
@@ -7031,13 +7063,16 @@
         <v>420</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
       <c r="B166" t="s">
         <v>154</v>
       </c>
+      <c r="D166" s="1">
+        <v>46220</v>
+      </c>
       <c r="E166">
         <v>1510</v>
       </c>
@@ -7045,13 +7080,16 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
       <c r="B167" t="s">
         <v>155</v>
       </c>
+      <c r="D167" s="1">
+        <v>46220</v>
+      </c>
       <c r="E167">
         <v>2185</v>
       </c>
@@ -7059,29 +7097,38 @@
         <v>2620</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
       <c r="B168" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D168" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D169" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>158</v>
       </c>
+      <c r="D170" s="1">
+        <v>46220</v>
+      </c>
       <c r="E170">
         <v>725</v>
       </c>
@@ -7092,169 +7139,301 @@
         <v>695</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B171" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C171" t="s">
+        <v>124</v>
+      </c>
+      <c r="D171" s="1">
+        <v>46223</v>
+      </c>
+      <c r="E171">
+        <v>435</v>
+      </c>
+      <c r="F171">
+        <v>475</v>
+      </c>
+      <c r="G171">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B172" t="s">
+        <v>139</v>
+      </c>
+      <c r="D172" s="1">
+        <v>46223</v>
+      </c>
+      <c r="E172">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B173" t="s">
+        <v>159</v>
+      </c>
+      <c r="D173" s="1">
+        <v>46223</v>
+      </c>
+      <c r="E173">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B174" t="s">
+        <v>160</v>
+      </c>
+      <c r="D174" s="1">
+        <v>46223</v>
+      </c>
+      <c r="E174">
+        <v>14444</v>
+      </c>
+      <c r="F174">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B175" t="s">
+        <v>161</v>
+      </c>
+      <c r="D175" s="1">
+        <v>46223</v>
+      </c>
+      <c r="E175">
+        <v>1237</v>
+      </c>
+      <c r="F175">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
-    </row>
-    <row r="177" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B176" t="s">
+        <v>162</v>
+      </c>
+      <c r="D176" s="1">
+        <v>46223</v>
+      </c>
+      <c r="E176">
+        <v>1412</v>
+      </c>
+      <c r="F176">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
-    </row>
-    <row r="178" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B177" t="s">
+        <v>163</v>
+      </c>
+      <c r="C177" t="s">
+        <v>124</v>
+      </c>
+      <c r="D177" s="1">
+        <v>46223</v>
+      </c>
+      <c r="E177">
+        <v>3388</v>
+      </c>
+      <c r="F177">
+        <v>3684</v>
+      </c>
+      <c r="G177">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
-    </row>
-    <row r="179" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B178" t="s">
+        <v>164</v>
+      </c>
+      <c r="D178" s="1">
+        <v>46224</v>
+      </c>
+      <c r="E178">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
-    </row>
-    <row r="180" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B179" t="s">
+        <v>165</v>
+      </c>
+      <c r="D179" s="1">
+        <v>46224</v>
+      </c>
+      <c r="E179">
+        <v>1862</v>
+      </c>
+      <c r="F179">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
-    </row>
-    <row r="181" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B180" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D180" s="1">
+        <v>46224</v>
+      </c>
+      <c r="E180">
+        <v>1908</v>
+      </c>
+      <c r="F180">
+        <v>2070</v>
+      </c>
+      <c r="G180">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
-    </row>
-    <row r="182" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B181" t="s">
+        <v>167</v>
+      </c>
+      <c r="D181" s="1">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
-    </row>
-    <row r="183" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B182" t="s">
+        <v>168</v>
+      </c>
+      <c r="D182" s="1">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
     </row>
-    <row r="199" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
     </row>
-    <row r="200" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
     </row>
-    <row r="201" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L201" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="GROWW"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L201" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAE28C3-2E2D-4C18-A7E1-2C3E9A89475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11500" yWindow="0" windowWidth="7550" windowHeight="10170" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAE28C3-2E2D-4C18-A7E1-2C3E9A89475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E454E277-F075-4582-84D7-FE127AC479FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Buy Sell" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$247</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="188">
   <si>
     <t>S No.</t>
   </si>
@@ -550,6 +550,63 @@
   </si>
   <si>
     <t>NAVIN FLUORINE</t>
+  </si>
+  <si>
+    <t>CYIENT DLM</t>
+  </si>
+  <si>
+    <t>BAJAJ AUTO</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>GODREJ PROPERTIES</t>
+  </si>
+  <si>
+    <t>NBCC</t>
+  </si>
+  <si>
+    <t>ROKERAFE RADAR</t>
+  </si>
+  <si>
+    <t>NESTLE INDIA</t>
+  </si>
+  <si>
+    <t>SONA BLW PRECISION</t>
+  </si>
+  <si>
+    <t>Fundamental actionable idea</t>
+  </si>
+  <si>
+    <t>NIPPON LIFE INDIA</t>
+  </si>
+  <si>
+    <t>MEESHO</t>
+  </si>
+  <si>
+    <t>VMM</t>
+  </si>
+  <si>
+    <t>M&amp;M</t>
+  </si>
+  <si>
+    <t>DALBHARAT</t>
+  </si>
+  <si>
+    <t>AZAD ENGINEERING</t>
+  </si>
+  <si>
+    <t>IDFC FIRST BANK</t>
+  </si>
+  <si>
+    <t>LENSKART</t>
+  </si>
+  <si>
+    <t>LODHA DEVELOPERS</t>
+  </si>
+  <si>
+    <t>NEWGEN</t>
   </si>
 </sst>
 </file>
@@ -3419,7 +3476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q247"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -7341,99 +7398,689 @@
       <c r="A183">
         <v>182</v>
       </c>
+      <c r="B183" t="s">
+        <v>169</v>
+      </c>
+      <c r="D183" s="1">
+        <v>46225</v>
+      </c>
+      <c r="E183">
+        <v>623</v>
+      </c>
+      <c r="F183">
+        <v>800</v>
+      </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
+      <c r="B184" t="s">
+        <v>170</v>
+      </c>
+      <c r="D184" s="1">
+        <v>46225</v>
+      </c>
+      <c r="E184">
+        <v>10404</v>
+      </c>
+      <c r="F184">
+        <v>12096</v>
+      </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
+      <c r="B185" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D185" s="1">
+        <v>46225</v>
+      </c>
+      <c r="E185">
+        <v>4582</v>
+      </c>
+      <c r="F185">
+        <v>4717</v>
+      </c>
+      <c r="G185">
+        <v>4450</v>
+      </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
+      <c r="B186" t="s">
+        <v>54</v>
+      </c>
+      <c r="D186" s="1">
+        <v>46225</v>
+      </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
+      <c r="B187" t="s">
+        <v>172</v>
+      </c>
+      <c r="D187" s="1">
+        <v>46225</v>
+      </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
+      <c r="B188" t="s">
+        <v>173</v>
+      </c>
+      <c r="D188" s="1">
+        <v>46225</v>
+      </c>
+      <c r="E188">
+        <v>94.36</v>
+      </c>
+      <c r="F188">
+        <v>92.4</v>
+      </c>
+      <c r="G188">
+        <v>95.7</v>
+      </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
+      <c r="B189" t="s">
+        <v>174</v>
+      </c>
+      <c r="D189" s="1">
+        <v>46226</v>
+      </c>
+      <c r="F189">
+        <v>373</v>
+      </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
+      <c r="B190" t="s">
+        <v>175</v>
+      </c>
+      <c r="C190" t="s">
+        <v>149</v>
+      </c>
+      <c r="D190" s="1">
+        <v>46226</v>
+      </c>
+      <c r="E190">
+        <v>1494</v>
+      </c>
+      <c r="F190">
+        <v>1600</v>
+      </c>
+      <c r="G190">
+        <v>1450</v>
+      </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
+      <c r="B191" t="s">
+        <v>121</v>
+      </c>
+      <c r="D191" s="1">
+        <v>46226</v>
+      </c>
+      <c r="E191">
+        <v>448</v>
+      </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B192" t="s">
+        <v>176</v>
+      </c>
+      <c r="C192" t="s">
+        <v>177</v>
+      </c>
+      <c r="D192" s="1">
+        <v>46226</v>
+      </c>
+      <c r="E192">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B193" t="s">
+        <v>178</v>
+      </c>
+      <c r="C193" t="s">
+        <v>177</v>
+      </c>
+      <c r="D193" s="1">
+        <v>46226</v>
+      </c>
+      <c r="E193">
+        <v>1148</v>
+      </c>
+      <c r="F193">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B194" t="s">
+        <v>179</v>
+      </c>
+      <c r="D194" s="1">
+        <v>46227</v>
+      </c>
+      <c r="E194">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B195" t="s">
+        <v>180</v>
+      </c>
+      <c r="D195" s="1">
+        <v>46227</v>
+      </c>
+      <c r="E195">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B196" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D196" s="1">
+        <v>46227</v>
+      </c>
+      <c r="E196">
+        <v>3230</v>
+      </c>
+      <c r="F196">
+        <v>3404</v>
+      </c>
+      <c r="G196">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B197" t="s">
+        <v>115</v>
+      </c>
+      <c r="D197" s="1">
+        <v>46227</v>
+      </c>
+      <c r="E197">
+        <v>1132</v>
+      </c>
+      <c r="F197">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B198" t="s">
+        <v>169</v>
+      </c>
+      <c r="D198" s="1">
+        <v>46227</v>
+      </c>
+      <c r="E198">
+        <v>668.2</v>
+      </c>
+      <c r="F198">
+        <v>678.5</v>
+      </c>
+      <c r="G198">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B199" t="s">
+        <v>182</v>
+      </c>
+      <c r="D199" s="1">
+        <v>46227</v>
+      </c>
+      <c r="E199">
+        <v>1846</v>
+      </c>
+      <c r="F199">
+        <v>1872</v>
+      </c>
+      <c r="G199">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B200" t="s">
+        <v>112</v>
+      </c>
+      <c r="D200" s="1">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
+      <c r="B201" t="s">
+        <v>183</v>
+      </c>
+      <c r="D201" s="1">
+        <v>46230</v>
+      </c>
+      <c r="E201">
+        <v>2439</v>
+      </c>
+      <c r="F201">
+        <v>2590</v>
+      </c>
+      <c r="G201">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>164</v>
+      </c>
+      <c r="C202" t="s">
+        <v>127</v>
+      </c>
+      <c r="D202" s="1">
+        <v>46230</v>
+      </c>
+      <c r="E202">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>184</v>
+      </c>
+      <c r="D203" s="1">
+        <v>46230</v>
+      </c>
+      <c r="E203">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>33</v>
+      </c>
+      <c r="D204" s="1">
+        <v>46230</v>
+      </c>
+      <c r="E204">
+        <v>1601</v>
+      </c>
+      <c r="F204">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>115</v>
+      </c>
+      <c r="D205" s="1">
+        <v>46230</v>
+      </c>
+      <c r="E205">
+        <v>1132</v>
+      </c>
+      <c r="F205">
+        <v>1329</v>
+      </c>
+      <c r="G205">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>185</v>
+      </c>
+      <c r="C207" t="s">
+        <v>124</v>
+      </c>
+      <c r="E207">
+        <v>572</v>
+      </c>
+      <c r="F207">
+        <v>615</v>
+      </c>
+      <c r="G207">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>181</v>
+      </c>
+      <c r="C208" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>179</v>
+      </c>
+      <c r="E209">
+        <v>185</v>
+      </c>
+      <c r="F209">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>186</v>
+      </c>
+      <c r="C211" t="s">
+        <v>177</v>
+      </c>
+      <c r="E211">
+        <v>1199</v>
+      </c>
+      <c r="F211">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>115</v>
+      </c>
+      <c r="C212" t="s">
+        <v>125</v>
+      </c>
+      <c r="E212">
+        <v>1132</v>
+      </c>
+      <c r="F212">
+        <v>1329</v>
+      </c>
+      <c r="G212">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>187</v>
+      </c>
+      <c r="E213">
+        <v>525</v>
+      </c>
+      <c r="F213">
+        <v>536</v>
+      </c>
+      <c r="G213">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>106</v>
+      </c>
+      <c r="E214">
+        <v>1220</v>
+      </c>
+      <c r="F214">
+        <v>1262</v>
+      </c>
+      <c r="G214">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A215">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A218">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A220">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A221">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A222">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A223">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A224">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A225">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A226">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A227">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A228">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A230">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A232">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A233">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A234">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A235">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A236">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A237">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A238">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A239">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A240">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A241">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A242">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A243">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A244">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A245">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A246">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A247">
+        <v>246</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L201" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
+  <autoFilter ref="A1:L247" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E454E277-F075-4582-84D7-FE127AC479FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4627E40D-D4FB-4F75-9F7F-D68791782707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Buy Sell" sheetId="2" r:id="rId2"/>
+    <sheet name="Detail1" sheetId="8" r:id="rId1"/>
+    <sheet name="Detail2" sheetId="9" r:id="rId2"/>
+    <sheet name="Detail3" sheetId="10" r:id="rId3"/>
+    <sheet name="Detail4" sheetId="11" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId5"/>
+    <sheet name="Main sheet" sheetId="1" r:id="rId6"/>
+    <sheet name="Buy Sell" sheetId="2" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Main sheet'!$A$1:$L$247</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="203">
   <si>
     <t>S No.</t>
   </si>
@@ -396,9 +401,6 @@
     <t>WELSPUN CORP</t>
   </si>
   <si>
-    <t>Frequency of Stocks</t>
-  </si>
-  <si>
     <t>PNB HOUSING FIN</t>
   </si>
   <si>
@@ -607,13 +609,61 @@
   </si>
   <si>
     <t>NEWGEN</t>
+  </si>
+  <si>
+    <t>Count of STOCK NAME</t>
+  </si>
+  <si>
+    <t>Details for Count of STOCK NAME - STOCK NAME: MARICO</t>
+  </si>
+  <si>
+    <t>Details for Count of STOCK NAME - STOCK NAME: LODHA DEVELOPERS</t>
+  </si>
+  <si>
+    <t>Details for Count of STOCK NAME - STOCK NAME: MEDANTA</t>
+  </si>
+  <si>
+    <t>TVS MOTORS</t>
+  </si>
+  <si>
+    <t>DIVI'S LAB</t>
+  </si>
+  <si>
+    <t>LARSEN &amp; TOUBRO</t>
+  </si>
+  <si>
+    <t>Fundamental Idea</t>
+  </si>
+  <si>
+    <t>CHOLAMANDALAM INVESTESTMENT &amp; FINANCE</t>
+  </si>
+  <si>
+    <t>MTAR TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>Positive View</t>
+  </si>
+  <si>
+    <t>DR LAL PATHLABS</t>
+  </si>
+  <si>
+    <t>Technical breakout</t>
+  </si>
+  <si>
+    <t>4-week track</t>
+  </si>
+  <si>
+    <t>1-week track</t>
+  </si>
+  <si>
+    <t>Details for Count of STOCK NAME - STOCK NAME: RADICO KHAITAN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,15 +672,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="6" tint="-0.499984740745262"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -651,7 +695,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.499984740745262"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -668,7 +712,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -678,49 +722,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <font>
-        <color theme="6" tint="-0.499984740745262"/>
-      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -736,16 +756,264 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ECO LOGIC" refreshedDate="46210.594272222224" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="125" xr:uid="{98144EDE-19C6-4FBA-BB3E-081ED993E514}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="ECO LOGIC" refreshedDate="46231.936734374998" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="247" xr:uid="{B84C5445-1205-4208-AC00-FEAA0EB4DA90}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:M126" sheet="Sheet1"/>
+    <worksheetSource ref="A1:M1048576" sheet="Main sheet"/>
   </cacheSource>
-  <cacheFields count="12">
+  <cacheFields count="13">
     <cacheField name="S No." numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="125"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="246" count="247">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="15"/>
+        <n v="16"/>
+        <n v="17"/>
+        <n v="18"/>
+        <n v="19"/>
+        <n v="20"/>
+        <n v="21"/>
+        <n v="22"/>
+        <n v="23"/>
+        <n v="24"/>
+        <n v="25"/>
+        <n v="26"/>
+        <n v="27"/>
+        <n v="28"/>
+        <n v="29"/>
+        <n v="30"/>
+        <n v="31"/>
+        <n v="32"/>
+        <n v="33"/>
+        <n v="34"/>
+        <n v="35"/>
+        <n v="36"/>
+        <n v="37"/>
+        <n v="38"/>
+        <n v="39"/>
+        <n v="40"/>
+        <n v="41"/>
+        <n v="42"/>
+        <n v="43"/>
+        <n v="44"/>
+        <n v="45"/>
+        <n v="46"/>
+        <n v="47"/>
+        <n v="48"/>
+        <n v="49"/>
+        <n v="50"/>
+        <n v="51"/>
+        <n v="52"/>
+        <n v="53"/>
+        <n v="54"/>
+        <n v="55"/>
+        <n v="56"/>
+        <n v="57"/>
+        <n v="58"/>
+        <n v="59"/>
+        <n v="60"/>
+        <n v="61"/>
+        <n v="62"/>
+        <n v="63"/>
+        <n v="64"/>
+        <n v="65"/>
+        <n v="66"/>
+        <n v="67"/>
+        <n v="68"/>
+        <n v="69"/>
+        <n v="70"/>
+        <n v="71"/>
+        <n v="72"/>
+        <n v="73"/>
+        <n v="74"/>
+        <n v="75"/>
+        <n v="76"/>
+        <n v="77"/>
+        <n v="78"/>
+        <n v="79"/>
+        <n v="80"/>
+        <n v="81"/>
+        <n v="82"/>
+        <n v="83"/>
+        <n v="84"/>
+        <n v="85"/>
+        <n v="86"/>
+        <n v="87"/>
+        <n v="88"/>
+        <n v="89"/>
+        <n v="90"/>
+        <n v="91"/>
+        <n v="92"/>
+        <n v="93"/>
+        <n v="94"/>
+        <n v="95"/>
+        <n v="96"/>
+        <n v="97"/>
+        <n v="98"/>
+        <n v="99"/>
+        <n v="100"/>
+        <n v="101"/>
+        <n v="102"/>
+        <n v="103"/>
+        <n v="104"/>
+        <n v="105"/>
+        <n v="106"/>
+        <n v="107"/>
+        <n v="108"/>
+        <n v="109"/>
+        <n v="110"/>
+        <n v="111"/>
+        <n v="112"/>
+        <n v="113"/>
+        <n v="114"/>
+        <n v="115"/>
+        <n v="116"/>
+        <n v="117"/>
+        <n v="118"/>
+        <n v="119"/>
+        <n v="120"/>
+        <n v="121"/>
+        <n v="122"/>
+        <n v="123"/>
+        <n v="124"/>
+        <n v="125"/>
+        <n v="126"/>
+        <n v="127"/>
+        <n v="128"/>
+        <n v="129"/>
+        <n v="130"/>
+        <n v="131"/>
+        <n v="132"/>
+        <n v="133"/>
+        <n v="134"/>
+        <n v="135"/>
+        <n v="136"/>
+        <n v="137"/>
+        <n v="138"/>
+        <n v="139"/>
+        <n v="140"/>
+        <n v="141"/>
+        <n v="142"/>
+        <n v="143"/>
+        <n v="144"/>
+        <n v="145"/>
+        <n v="146"/>
+        <n v="147"/>
+        <n v="148"/>
+        <n v="149"/>
+        <n v="150"/>
+        <n v="151"/>
+        <n v="152"/>
+        <n v="153"/>
+        <n v="154"/>
+        <n v="155"/>
+        <n v="156"/>
+        <n v="157"/>
+        <n v="158"/>
+        <n v="159"/>
+        <n v="160"/>
+        <n v="161"/>
+        <n v="162"/>
+        <n v="163"/>
+        <n v="164"/>
+        <n v="165"/>
+        <n v="166"/>
+        <n v="167"/>
+        <n v="168"/>
+        <n v="169"/>
+        <n v="170"/>
+        <n v="171"/>
+        <n v="172"/>
+        <n v="173"/>
+        <n v="174"/>
+        <n v="175"/>
+        <n v="176"/>
+        <n v="177"/>
+        <n v="178"/>
+        <n v="179"/>
+        <n v="180"/>
+        <n v="181"/>
+        <n v="182"/>
+        <n v="183"/>
+        <n v="184"/>
+        <n v="185"/>
+        <n v="186"/>
+        <n v="187"/>
+        <n v="188"/>
+        <n v="189"/>
+        <n v="190"/>
+        <n v="191"/>
+        <n v="192"/>
+        <n v="193"/>
+        <n v="194"/>
+        <n v="195"/>
+        <n v="196"/>
+        <n v="197"/>
+        <n v="198"/>
+        <n v="199"/>
+        <n v="200"/>
+        <n v="201"/>
+        <n v="202"/>
+        <n v="203"/>
+        <n v="204"/>
+        <n v="205"/>
+        <n v="206"/>
+        <n v="207"/>
+        <n v="208"/>
+        <n v="209"/>
+        <n v="210"/>
+        <n v="211"/>
+        <n v="212"/>
+        <n v="213"/>
+        <n v="214"/>
+        <n v="215"/>
+        <n v="216"/>
+        <n v="217"/>
+        <n v="218"/>
+        <n v="219"/>
+        <n v="220"/>
+        <n v="221"/>
+        <n v="222"/>
+        <n v="223"/>
+        <n v="224"/>
+        <n v="225"/>
+        <n v="226"/>
+        <n v="227"/>
+        <n v="228"/>
+        <n v="229"/>
+        <n v="230"/>
+        <n v="231"/>
+        <n v="232"/>
+        <n v="233"/>
+        <n v="234"/>
+        <n v="235"/>
+        <n v="236"/>
+        <n v="237"/>
+        <n v="238"/>
+        <n v="239"/>
+        <n v="240"/>
+        <n v="241"/>
+        <n v="242"/>
+        <n v="243"/>
+        <n v="244"/>
+        <n v="245"/>
+        <n v="246"/>
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="STOCK NAME" numFmtId="0">
-      <sharedItems count="107">
+      <sharedItems containsBlank="1" count="156">
         <s v="ICICI AMC"/>
         <s v="AEGIS LOGISTICS"/>
         <s v="RR KABHARAT ELECTRONICS "/>
@@ -842,30 +1110,260 @@
         <s v="TITAN"/>
         <s v="LLOYD"/>
         <s v="GRASIM INDUSTRIESUSTRIESUSTRIES IND"/>
-        <s v="RR KABEL " u="1"/>
-        <s v="GRASIM" u="1"/>
-        <s v="BHARATFORG" u="1"/>
-        <s v="BEL" u="1"/>
-        <s v="BHARAT FORGE" u="1"/>
-        <s v="WELCORP" u="1"/>
-        <s v="MAX HEALTH " u="1"/>
-        <s v="KIRLOSKAR OLI ENGINES" u="1"/>
-        <s v="CGPOWER " u="1"/>
-        <s v="GRASIM IND" u="1"/>
-        <s v=" BHARAT FORGE" u="1"/>
+        <s v="PNB HOUSING FIN"/>
+        <s v="ASTRA MICROWAVE"/>
+        <s v="UNO MINDA"/>
+        <s v="EXIDE IND"/>
+        <s v="ATHER ENERGY LTD"/>
+        <s v="ALKYLAMINE"/>
+        <s v="KAYNES"/>
+        <s v="CDSL"/>
+        <s v="DLF"/>
+        <s v="RBL"/>
+        <s v="L&amp;T FINANCE"/>
+        <s v="INDIAN BANK"/>
+        <s v="TATA TECHNOLOGIES"/>
+        <s v="JSWINFRA"/>
+        <s v="KARARVYSYA"/>
+        <s v="ICICI PREDENTIAL AMC"/>
+        <s v="HCL TECHNOLOGIES"/>
+        <s v="WELSPUN LIVING"/>
+        <s v="SAATVIK GREEN ENERGY"/>
+        <s v="ADANI GREEN"/>
+        <s v="LLOYDS METALS"/>
+        <s v="IPCA LABORATORIES"/>
+        <s v="ABB"/>
+        <s v="FLUOROCHEM"/>
+        <s v="UNIMECH AEROSPACE"/>
+        <s v="TARIL"/>
+        <s v="TECH MAHINDRA"/>
+        <s v="PIRAMAL FINANCE"/>
+        <s v="INFOEDGE"/>
+        <s v="SONACOMS"/>
+        <s v="HSCL"/>
+        <s v="TIMETECHNO"/>
+        <s v="ICICI BANK"/>
+        <s v="JSW"/>
+        <s v="ABREL"/>
+        <s v="SANSERA"/>
+        <s v="PAYTM"/>
+        <s v="EMCURE PHARMA"/>
+        <s v="LLOYD METALS"/>
+        <s v="UNION BANK OF INDIA"/>
+        <s v="NAVIN FLUORINE"/>
+        <s v="CYIENT DLM"/>
+        <s v="BAJAJ AUTO"/>
+        <s v="HAL"/>
+        <s v="GODREJ PROPERTIES"/>
+        <s v="NBCC"/>
+        <s v="ROKERAFE RADAR"/>
+        <s v="NESTLE INDIA"/>
+        <s v="SONA BLW PRECISION"/>
+        <s v="NIPPON LIFE INDIA"/>
+        <s v="MEESHO"/>
+        <s v="VMM"/>
+        <s v="M&amp;M"/>
+        <s v="DALBHARAT"/>
+        <s v="AZAD ENGINEERING"/>
+        <s v="IDFC FIRST BANK"/>
+        <s v="LENSKART"/>
+        <s v="LODHA DEVELOPERS"/>
+        <s v="NEWGEN"/>
+        <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Day when told" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-06-01T00:00:00" maxDate="2026-07-08T00:00:00"/>
+    <cacheField name="Idea Type" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Day when told" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-01T00:00:00" maxDate="2026-07-29T00:00:00"/>
     </cacheField>
     <cacheField name="Current price" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="59" maxValue="13735"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="59" maxValue="13735" count="177">
+        <n v="3538"/>
+        <n v="748"/>
+        <n v="2056"/>
+        <n v="1006"/>
+        <n v="5881"/>
+        <n v="1456"/>
+        <n v="439.39"/>
+        <n v="3104.84"/>
+        <n v="1208.33"/>
+        <n v="932.2"/>
+        <n v="3318.97"/>
+        <n v="1543"/>
+        <n v="434"/>
+        <n v="185"/>
+        <n v="1783"/>
+        <n v="767"/>
+        <n v="835"/>
+        <n v="537"/>
+        <n v="1074"/>
+        <n v="406"/>
+        <n v="1090"/>
+        <n v="2189"/>
+        <n v="305"/>
+        <n v="168.6"/>
+        <n v="268"/>
+        <n v="1438"/>
+        <n v="1506"/>
+        <n v="1039"/>
+        <n v="3145"/>
+        <n v="3089"/>
+        <n v="2779"/>
+        <n v="2306"/>
+        <n v="1510"/>
+        <n v="351"/>
+        <n v="86"/>
+        <n v="4710"/>
+        <n v="141"/>
+        <n v="2743"/>
+        <n v="276"/>
+        <n v="2020"/>
+        <n v="3171"/>
+        <n v="1860"/>
+        <n v="7625"/>
+        <m/>
+        <n v="210"/>
+        <n v="1953"/>
+        <n v="1079"/>
+        <n v="1465"/>
+        <n v="374"/>
+        <n v="1520"/>
+        <n v="217"/>
+        <n v="153"/>
+        <n v="419"/>
+        <n v="2210"/>
+        <n v="59"/>
+        <n v="1026"/>
+        <n v="420"/>
+        <n v="960"/>
+        <n v="3653"/>
+        <n v="353"/>
+        <n v="7965"/>
+        <n v="1446"/>
+        <n v="3013"/>
+        <n v="1992"/>
+        <n v="416"/>
+        <n v="1889"/>
+        <n v="264"/>
+        <n v="376"/>
+        <n v="1413"/>
+        <n v="1415"/>
+        <n v="2103"/>
+        <n v="484"/>
+        <n v="1288"/>
+        <n v="1336"/>
+        <n v="454"/>
+        <n v="12667"/>
+        <n v="829"/>
+        <n v="3891"/>
+        <n v="346"/>
+        <n v="1112"/>
+        <n v="199"/>
+        <n v="2123"/>
+        <n v="1019"/>
+        <n v="413"/>
+        <n v="1384"/>
+        <n v="1455"/>
+        <n v="13735"/>
+        <n v="391"/>
+        <n v="1231"/>
+        <n v="575"/>
+        <n v="1132"/>
+        <n v="1046"/>
+        <n v="2441"/>
+        <n v="840"/>
+        <n v="802"/>
+        <n v="4628"/>
+        <n v="1396"/>
+        <n v="1503"/>
+        <n v="976"/>
+        <n v="508"/>
+        <n v="1628"/>
+        <n v="1412"/>
+        <n v="1018"/>
+        <n v="856"/>
+        <n v="1027"/>
+        <n v="1360"/>
+        <n v="1882"/>
+        <n v="235"/>
+        <n v="548"/>
+        <n v="310"/>
+        <n v="352"/>
+        <n v="4484"/>
+        <n v="2246"/>
+        <n v="78"/>
+        <n v="3213"/>
+        <n v="289"/>
+        <n v="1516"/>
+        <n v="1110"/>
+        <n v="848"/>
+        <n v="1785"/>
+        <n v="317"/>
+        <n v="415"/>
+        <n v="421"/>
+        <n v="1200"/>
+        <n v="328"/>
+        <n v="13477"/>
+        <n v="1507"/>
+        <n v="1954"/>
+        <n v="3429"/>
+        <n v="1431"/>
+        <n v="321"/>
+        <n v="871"/>
+        <n v="760"/>
+        <n v="308"/>
+        <n v="3206"/>
+        <n v="1221"/>
+        <n v="168"/>
+        <n v="449"/>
+        <n v="1604"/>
+        <n v="1826"/>
+        <n v="1840"/>
+        <n v="7203"/>
+        <n v="4133"/>
+        <n v="1204"/>
+        <n v="216"/>
+        <n v="350"/>
+        <n v="2185"/>
+        <n v="725"/>
+        <n v="435"/>
+        <n v="204"/>
+        <n v="1444"/>
+        <n v="1237"/>
+        <n v="3388"/>
+        <n v="1348"/>
+        <n v="1862"/>
+        <n v="1908"/>
+        <n v="623"/>
+        <n v="10404"/>
+        <n v="4582"/>
+        <n v="94.36"/>
+        <n v="1494"/>
+        <n v="448"/>
+        <n v="726"/>
+        <n v="1148"/>
+        <n v="188"/>
+        <n v="109"/>
+        <n v="3230"/>
+        <n v="668.2"/>
+        <n v="1846"/>
+        <n v="2439"/>
+        <n v="1283"/>
+        <n v="81"/>
+        <n v="1601"/>
+        <n v="572"/>
+        <n v="1199"/>
+        <n v="525"/>
+        <n v="1220"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Target price" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="105" maxValue="15290"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="92.4" maxValue="16100"/>
     </cacheField>
     <cacheField name="Stop loss" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="76" maxValue="11400"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="76" maxValue="11400"/>
     </cacheField>
     <cacheField name="Today's closing price" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1033" maxValue="1153"/>
@@ -895,12 +1393,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="125">
-  <r>
-    <n v="1"/>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="247">
+  <r>
     <x v="0"/>
+    <x v="0"/>
+    <m/>
     <d v="2026-06-01T00:00:00"/>
-    <n v="3538"/>
+    <x v="0"/>
     <n v="3690"/>
     <n v="3450"/>
     <m/>
@@ -911,10 +1410,11 @@
     <m/>
   </r>
   <r>
-    <n v="2"/>
     <x v="1"/>
+    <x v="1"/>
+    <m/>
     <d v="2026-06-01T00:00:00"/>
-    <n v="748"/>
+    <x v="1"/>
     <m/>
     <m/>
     <m/>
@@ -925,10 +1425,11 @@
     <m/>
   </r>
   <r>
-    <n v="3"/>
     <x v="2"/>
+    <x v="2"/>
+    <m/>
     <d v="2026-06-01T00:00:00"/>
-    <n v="2056"/>
+    <x v="2"/>
     <m/>
     <m/>
     <m/>
@@ -939,10 +1440,11 @@
     <m/>
   </r>
   <r>
-    <n v="4"/>
     <x v="3"/>
+    <x v="3"/>
+    <m/>
     <d v="2026-06-01T00:00:00"/>
-    <n v="1006"/>
+    <x v="3"/>
     <n v="1160"/>
     <m/>
     <m/>
@@ -953,10 +1455,11 @@
     <m/>
   </r>
   <r>
-    <n v="5"/>
     <x v="4"/>
+    <x v="4"/>
+    <m/>
     <d v="2026-06-01T00:00:00"/>
-    <n v="5881"/>
+    <x v="4"/>
     <n v="6600"/>
     <m/>
     <m/>
@@ -967,10 +1470,11 @@
     <m/>
   </r>
   <r>
-    <n v="6"/>
     <x v="5"/>
+    <x v="5"/>
+    <m/>
     <d v="2026-06-01T00:00:00"/>
-    <n v="1456"/>
+    <x v="5"/>
     <n v="1483"/>
     <n v="1438"/>
     <m/>
@@ -981,10 +1485,11 @@
     <m/>
   </r>
   <r>
-    <n v="7"/>
     <x v="6"/>
+    <x v="6"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="439.39"/>
+    <x v="6"/>
     <n v="580"/>
     <m/>
     <m/>
@@ -995,10 +1500,11 @@
     <m/>
   </r>
   <r>
-    <n v="8"/>
     <x v="7"/>
+    <x v="7"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="3104.84"/>
+    <x v="7"/>
     <n v="3850"/>
     <m/>
     <m/>
@@ -1009,10 +1515,11 @@
     <m/>
   </r>
   <r>
-    <n v="9"/>
     <x v="8"/>
+    <x v="8"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="1208.33"/>
+    <x v="8"/>
     <n v="1450"/>
     <m/>
     <m/>
@@ -1023,10 +1530,11 @@
     <m/>
   </r>
   <r>
-    <n v="10"/>
     <x v="9"/>
+    <x v="9"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="932.2"/>
+    <x v="9"/>
     <n v="1100"/>
     <m/>
     <m/>
@@ -1037,10 +1545,11 @@
     <m/>
   </r>
   <r>
-    <n v="11"/>
     <x v="10"/>
+    <x v="10"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="3318.97"/>
+    <x v="10"/>
     <n v="3850"/>
     <m/>
     <m/>
@@ -1051,10 +1560,11 @@
     <m/>
   </r>
   <r>
-    <n v="12"/>
     <x v="11"/>
+    <x v="11"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="1543"/>
+    <x v="11"/>
     <n v="1720"/>
     <m/>
     <m/>
@@ -1065,10 +1575,11 @@
     <m/>
   </r>
   <r>
-    <n v="13"/>
     <x v="12"/>
+    <x v="12"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="434"/>
+    <x v="12"/>
     <m/>
     <m/>
     <m/>
@@ -1079,10 +1590,11 @@
     <m/>
   </r>
   <r>
-    <n v="14"/>
     <x v="13"/>
+    <x v="13"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="185"/>
+    <x v="13"/>
     <n v="235"/>
     <m/>
     <m/>
@@ -1093,10 +1605,11 @@
     <m/>
   </r>
   <r>
-    <n v="15"/>
     <x v="14"/>
+    <x v="14"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="1783"/>
+    <x v="14"/>
     <n v="2050"/>
     <m/>
     <m/>
@@ -1107,10 +1620,11 @@
     <m/>
   </r>
   <r>
-    <n v="16"/>
+    <x v="15"/>
     <x v="1"/>
+    <m/>
     <d v="2026-06-02T00:00:00"/>
-    <n v="767"/>
+    <x v="15"/>
     <n v="890"/>
     <n v="705"/>
     <m/>
@@ -1121,10 +1635,11 @@
     <m/>
   </r>
   <r>
-    <n v="17"/>
+    <x v="16"/>
     <x v="15"/>
+    <m/>
     <d v="2026-06-03T00:00:00"/>
-    <n v="835"/>
+    <x v="16"/>
     <m/>
     <m/>
     <m/>
@@ -1135,10 +1650,11 @@
     <m/>
   </r>
   <r>
-    <n v="18"/>
+    <x v="17"/>
     <x v="16"/>
+    <m/>
     <d v="2026-06-03T00:00:00"/>
-    <n v="537"/>
+    <x v="17"/>
     <n v="580"/>
     <n v="510"/>
     <m/>
@@ -1149,10 +1665,11 @@
     <m/>
   </r>
   <r>
-    <n v="19"/>
+    <x v="18"/>
     <x v="17"/>
+    <m/>
     <d v="2026-06-03T00:00:00"/>
-    <n v="1074"/>
+    <x v="18"/>
     <m/>
     <m/>
     <m/>
@@ -1163,10 +1680,11 @@
     <m/>
   </r>
   <r>
-    <n v="20"/>
+    <x v="19"/>
     <x v="18"/>
+    <m/>
     <d v="2026-06-03T00:00:00"/>
-    <n v="406"/>
+    <x v="19"/>
     <m/>
     <m/>
     <m/>
@@ -1177,10 +1695,11 @@
     <m/>
   </r>
   <r>
-    <n v="21"/>
+    <x v="20"/>
     <x v="19"/>
+    <m/>
     <d v="2026-06-03T00:00:00"/>
-    <n v="1090"/>
+    <x v="20"/>
     <n v="1200"/>
     <m/>
     <m/>
@@ -1191,10 +1710,11 @@
     <m/>
   </r>
   <r>
-    <n v="22"/>
+    <x v="21"/>
     <x v="1"/>
+    <m/>
     <d v="2026-06-03T00:00:00"/>
-    <n v="767"/>
+    <x v="15"/>
     <n v="890"/>
     <n v="705"/>
     <n v="1153"/>
@@ -1205,10 +1725,11 @@
     <m/>
   </r>
   <r>
-    <n v="23"/>
+    <x v="22"/>
     <x v="20"/>
+    <m/>
     <d v="2026-06-04T00:00:00"/>
-    <n v="2189"/>
+    <x v="21"/>
     <n v="2484"/>
     <n v="2040"/>
     <m/>
@@ -1219,10 +1740,11 @@
     <m/>
   </r>
   <r>
-    <n v="24"/>
+    <x v="23"/>
     <x v="21"/>
+    <m/>
     <d v="2026-06-09T00:00:00"/>
-    <n v="305"/>
+    <x v="22"/>
     <n v="325"/>
     <n v="295"/>
     <m/>
@@ -1233,10 +1755,11 @@
     <m/>
   </r>
   <r>
-    <n v="25"/>
+    <x v="24"/>
     <x v="22"/>
+    <m/>
     <d v="2026-06-09T00:00:00"/>
-    <n v="168.6"/>
+    <x v="23"/>
     <m/>
     <m/>
     <m/>
@@ -1247,10 +1770,11 @@
     <m/>
   </r>
   <r>
-    <n v="26"/>
+    <x v="25"/>
     <x v="23"/>
+    <m/>
     <d v="2026-06-09T00:00:00"/>
-    <n v="268"/>
+    <x v="24"/>
     <n v="360"/>
     <m/>
     <m/>
@@ -1261,10 +1785,11 @@
     <m/>
   </r>
   <r>
-    <n v="27"/>
+    <x v="26"/>
     <x v="1"/>
+    <m/>
     <d v="2026-06-09T00:00:00"/>
-    <n v="767"/>
+    <x v="15"/>
     <n v="890"/>
     <n v="705"/>
     <m/>
@@ -1275,10 +1800,11 @@
     <m/>
   </r>
   <r>
-    <n v="28"/>
+    <x v="27"/>
     <x v="24"/>
+    <m/>
     <d v="2026-06-11T00:00:00"/>
-    <n v="1438"/>
+    <x v="25"/>
     <n v="1550"/>
     <n v="1388"/>
     <m/>
@@ -1289,10 +1815,11 @@
     <m/>
   </r>
   <r>
-    <n v="29"/>
+    <x v="28"/>
     <x v="25"/>
+    <m/>
     <d v="2026-06-11T00:00:00"/>
-    <n v="1506"/>
+    <x v="26"/>
     <m/>
     <n v="1450"/>
     <m/>
@@ -1303,10 +1830,11 @@
     <m/>
   </r>
   <r>
-    <n v="30"/>
+    <x v="29"/>
     <x v="26"/>
+    <m/>
     <d v="2026-06-11T00:00:00"/>
-    <n v="1039"/>
+    <x v="27"/>
     <n v="1280"/>
     <m/>
     <m/>
@@ -1317,10 +1845,11 @@
     <m/>
   </r>
   <r>
-    <n v="31"/>
+    <x v="30"/>
     <x v="27"/>
+    <m/>
     <d v="2026-06-11T00:00:00"/>
-    <n v="3145"/>
+    <x v="28"/>
     <n v="3900"/>
     <m/>
     <m/>
@@ -1331,10 +1860,11 @@
     <m/>
   </r>
   <r>
-    <n v="32"/>
+    <x v="31"/>
     <x v="28"/>
+    <m/>
     <d v="2026-06-12T00:00:00"/>
-    <n v="3089"/>
+    <x v="29"/>
     <n v="3270"/>
     <n v="3000"/>
     <m/>
@@ -1345,38 +1875,41 @@
     <m/>
   </r>
   <r>
-    <n v="33"/>
+    <x v="32"/>
     <x v="29"/>
+    <m/>
     <d v="2026-06-12T00:00:00"/>
-    <n v="2779"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="34"/>
     <x v="30"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="30"/>
+    <m/>
     <d v="2026-06-12T00:00:00"/>
-    <n v="2306"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="35"/>
     <x v="31"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="31"/>
+    <m/>
     <d v="2026-06-12T00:00:00"/>
-    <n v="1510"/>
+    <x v="32"/>
     <n v="1860"/>
     <m/>
     <m/>
@@ -1387,10 +1920,11 @@
     <m/>
   </r>
   <r>
-    <n v="36"/>
+    <x v="35"/>
     <x v="32"/>
+    <m/>
     <d v="2026-06-12T00:00:00"/>
-    <n v="351"/>
+    <x v="33"/>
     <n v="405"/>
     <n v="322"/>
     <m/>
@@ -1401,10 +1935,11 @@
     <m/>
   </r>
   <r>
-    <n v="37"/>
+    <x v="36"/>
     <x v="33"/>
+    <m/>
     <d v="2026-06-15T00:00:00"/>
-    <n v="86"/>
+    <x v="34"/>
     <n v="105"/>
     <n v="76"/>
     <m/>
@@ -1415,10 +1950,11 @@
     <m/>
   </r>
   <r>
-    <n v="38"/>
+    <x v="37"/>
     <x v="34"/>
+    <m/>
     <d v="2026-06-15T00:00:00"/>
-    <n v="4710"/>
+    <x v="35"/>
     <n v="5600"/>
     <m/>
     <m/>
@@ -1429,38 +1965,41 @@
     <m/>
   </r>
   <r>
-    <n v="39"/>
+    <x v="38"/>
     <x v="35"/>
+    <m/>
     <d v="2026-06-15T00:00:00"/>
-    <n v="141"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="40"/>
     <x v="36"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="36"/>
+    <m/>
     <d v="2026-06-15T00:00:00"/>
-    <n v="2743"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="41"/>
     <x v="37"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="37"/>
+    <m/>
     <d v="2026-06-15T00:00:00"/>
-    <n v="276"/>
+    <x v="38"/>
     <n v="294"/>
     <n v="265"/>
     <m/>
@@ -1471,10 +2010,11 @@
     <m/>
   </r>
   <r>
-    <n v="42"/>
+    <x v="41"/>
     <x v="38"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <n v="2020"/>
+    <x v="39"/>
     <n v="2200"/>
     <n v="1940"/>
     <m/>
@@ -1485,52 +2025,56 @@
     <m/>
   </r>
   <r>
-    <n v="43"/>
+    <x v="42"/>
     <x v="28"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <n v="3171"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="44"/>
+    <x v="40"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="43"/>
     <x v="39"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <n v="1860"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="45"/>
+    <x v="41"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="44"/>
     <x v="40"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <n v="7625"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="46"/>
+    <x v="42"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="45"/>
     <x v="41"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <m/>
+    <x v="43"/>
     <n v="217"/>
     <m/>
     <m/>
@@ -1541,10 +2085,11 @@
     <m/>
   </r>
   <r>
-    <n v="47"/>
+    <x v="46"/>
     <x v="42"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <m/>
+    <x v="43"/>
     <n v="125"/>
     <m/>
     <m/>
@@ -1555,10 +2100,11 @@
     <m/>
   </r>
   <r>
-    <n v="48"/>
+    <x v="47"/>
     <x v="43"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <m/>
+    <x v="43"/>
     <n v="1765"/>
     <m/>
     <m/>
@@ -1569,10 +2115,11 @@
     <m/>
   </r>
   <r>
-    <n v="49"/>
+    <x v="48"/>
     <x v="44"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <n v="210"/>
+    <x v="44"/>
     <m/>
     <m/>
     <m/>
@@ -1583,10 +2130,11 @@
     <m/>
   </r>
   <r>
-    <n v="50"/>
+    <x v="49"/>
     <x v="33"/>
+    <m/>
     <d v="2026-06-16T00:00:00"/>
-    <n v="86"/>
+    <x v="34"/>
     <n v="105"/>
     <n v="76"/>
     <m/>
@@ -1597,10 +2145,11 @@
     <m/>
   </r>
   <r>
-    <n v="51"/>
+    <x v="50"/>
     <x v="38"/>
+    <m/>
     <d v="2026-06-17T00:00:00"/>
-    <n v="1953"/>
+    <x v="45"/>
     <n v="2220"/>
     <n v="1820"/>
     <m/>
@@ -1611,24 +2160,26 @@
     <m/>
   </r>
   <r>
-    <n v="52"/>
+    <x v="51"/>
     <x v="45"/>
+    <m/>
     <d v="2026-06-17T00:00:00"/>
-    <n v="1079"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="53"/>
+    <x v="46"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="52"/>
     <x v="5"/>
+    <m/>
     <d v="2026-06-17T00:00:00"/>
-    <n v="1465"/>
+    <x v="47"/>
     <n v="1900"/>
     <m/>
     <m/>
@@ -1639,38 +2190,41 @@
     <m/>
   </r>
   <r>
-    <n v="54"/>
+    <x v="53"/>
     <x v="46"/>
+    <m/>
     <d v="2026-06-17T00:00:00"/>
-    <n v="374"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="55"/>
+    <x v="48"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="54"/>
     <x v="47"/>
+    <m/>
     <d v="2026-06-17T00:00:00"/>
-    <n v="1520"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="56"/>
+    <x v="49"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="55"/>
     <x v="44"/>
+    <m/>
     <d v="2026-06-17T00:00:00"/>
-    <n v="217"/>
+    <x v="50"/>
     <n v="234"/>
     <n v="204"/>
     <m/>
@@ -1681,10 +2235,11 @@
     <m/>
   </r>
   <r>
-    <n v="57"/>
+    <x v="56"/>
     <x v="48"/>
+    <m/>
     <d v="2026-06-17T00:00:00"/>
-    <n v="153"/>
+    <x v="51"/>
     <n v="159"/>
     <n v="151"/>
     <m/>
@@ -1695,10 +2250,11 @@
     <m/>
   </r>
   <r>
-    <n v="58"/>
+    <x v="57"/>
     <x v="49"/>
+    <m/>
     <d v="2026-06-18T00:00:00"/>
-    <n v="419"/>
+    <x v="52"/>
     <n v="510"/>
     <m/>
     <m/>
@@ -1709,10 +2265,11 @@
     <m/>
   </r>
   <r>
-    <n v="59"/>
+    <x v="58"/>
     <x v="2"/>
+    <m/>
     <d v="2026-06-18T00:00:00"/>
-    <n v="2210"/>
+    <x v="53"/>
     <n v="2600"/>
     <m/>
     <m/>
@@ -1723,52 +2280,56 @@
     <m/>
   </r>
   <r>
-    <n v="60"/>
+    <x v="59"/>
     <x v="50"/>
+    <m/>
     <d v="2026-06-18T00:00:00"/>
-    <n v="59"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="61"/>
+    <x v="54"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="60"/>
     <x v="51"/>
+    <m/>
     <d v="2026-06-18T00:00:00"/>
-    <n v="1026"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="62"/>
+    <x v="55"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="61"/>
     <x v="49"/>
+    <m/>
     <d v="2026-06-18T00:00:00"/>
-    <n v="420"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="63"/>
+    <x v="56"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="62"/>
     <x v="52"/>
+    <m/>
     <d v="2026-06-18T00:00:00"/>
-    <n v="960"/>
+    <x v="57"/>
     <n v="1022"/>
     <n v="930"/>
     <m/>
@@ -1779,10 +2340,11 @@
     <m/>
   </r>
   <r>
-    <n v="64"/>
+    <x v="63"/>
     <x v="53"/>
+    <m/>
     <d v="2026-06-19T00:00:00"/>
-    <n v="3653"/>
+    <x v="58"/>
     <n v="4100"/>
     <n v="3415"/>
     <m/>
@@ -1793,10 +2355,11 @@
     <m/>
   </r>
   <r>
-    <n v="65"/>
+    <x v="64"/>
     <x v="54"/>
+    <m/>
     <d v="2026-06-19T00:00:00"/>
-    <n v="353"/>
+    <x v="59"/>
     <n v="400"/>
     <m/>
     <m/>
@@ -1807,10 +2370,11 @@
     <m/>
   </r>
   <r>
-    <n v="66"/>
+    <x v="65"/>
     <x v="55"/>
+    <m/>
     <d v="2026-06-19T00:00:00"/>
-    <n v="7965"/>
+    <x v="60"/>
     <n v="8450"/>
     <m/>
     <m/>
@@ -1821,38 +2385,41 @@
     <m/>
   </r>
   <r>
-    <n v="67"/>
+    <x v="66"/>
     <x v="56"/>
+    <m/>
     <d v="2026-06-19T00:00:00"/>
-    <n v="406"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="68"/>
+    <x v="19"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="67"/>
     <x v="57"/>
+    <m/>
     <d v="2026-06-19T00:00:00"/>
-    <n v="1446"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="69"/>
+    <x v="61"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="68"/>
     <x v="58"/>
+    <m/>
     <d v="2026-06-19T00:00:00"/>
-    <n v="3013"/>
+    <x v="62"/>
     <n v="3230"/>
     <n v="2845"/>
     <m/>
@@ -1863,10 +2430,11 @@
     <m/>
   </r>
   <r>
-    <n v="70"/>
+    <x v="69"/>
     <x v="59"/>
+    <m/>
     <d v="2026-06-19T00:00:00"/>
-    <m/>
+    <x v="43"/>
     <m/>
     <m/>
     <m/>
@@ -1877,10 +2445,11 @@
     <m/>
   </r>
   <r>
-    <n v="71"/>
+    <x v="70"/>
     <x v="53"/>
+    <m/>
     <d v="2026-06-22T00:00:00"/>
-    <n v="3653"/>
+    <x v="58"/>
     <n v="4100"/>
     <n v="3415"/>
     <m/>
@@ -1891,10 +2460,11 @@
     <m/>
   </r>
   <r>
-    <n v="72"/>
+    <x v="71"/>
     <x v="60"/>
+    <m/>
     <d v="2026-06-22T00:00:00"/>
-    <n v="1992"/>
+    <x v="63"/>
     <n v="2350"/>
     <m/>
     <m/>
@@ -1905,10 +2475,11 @@
     <m/>
   </r>
   <r>
-    <n v="73"/>
+    <x v="72"/>
     <x v="6"/>
+    <m/>
     <d v="2026-06-22T00:00:00"/>
-    <n v="416"/>
+    <x v="64"/>
     <n v="580"/>
     <m/>
     <m/>
@@ -1919,52 +2490,56 @@
     <m/>
   </r>
   <r>
-    <n v="74"/>
+    <x v="73"/>
     <x v="61"/>
+    <m/>
     <d v="2026-06-22T00:00:00"/>
-    <n v="1889"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="75"/>
+    <x v="65"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="74"/>
     <x v="62"/>
+    <m/>
     <d v="2026-06-22T00:00:00"/>
-    <n v="264"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="76"/>
+    <x v="66"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="75"/>
     <x v="46"/>
+    <m/>
     <d v="2026-06-22T00:00:00"/>
-    <n v="376"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="77"/>
+    <x v="67"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="76"/>
     <x v="63"/>
+    <m/>
     <d v="2026-06-22T00:00:00"/>
-    <n v="1413"/>
+    <x v="68"/>
     <n v="1560"/>
     <n v="1340"/>
     <m/>
@@ -1975,10 +2550,11 @@
     <m/>
   </r>
   <r>
-    <n v="78"/>
+    <x v="77"/>
     <x v="64"/>
+    <m/>
     <d v="2026-06-23T00:00:00"/>
-    <n v="1415"/>
+    <x v="69"/>
     <n v="1530"/>
     <n v="1360"/>
     <m/>
@@ -1989,38 +2565,41 @@
     <m/>
   </r>
   <r>
-    <n v="79"/>
+    <x v="78"/>
     <x v="38"/>
+    <m/>
     <d v="2026-06-23T00:00:00"/>
-    <n v="2103"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="80"/>
+    <x v="70"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="79"/>
     <x v="6"/>
+    <m/>
     <d v="2026-06-23T00:00:00"/>
-    <n v="484"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="81"/>
+    <x v="71"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="80"/>
     <x v="65"/>
+    <m/>
     <d v="2026-06-23T00:00:00"/>
-    <n v="1288"/>
+    <x v="72"/>
     <n v="1490"/>
     <m/>
     <m/>
@@ -2031,10 +2610,11 @@
     <m/>
   </r>
   <r>
-    <n v="82"/>
+    <x v="81"/>
     <x v="66"/>
+    <m/>
     <d v="2026-06-23T00:00:00"/>
-    <n v="1336"/>
+    <x v="73"/>
     <n v="1620"/>
     <m/>
     <m/>
@@ -2045,10 +2625,11 @@
     <m/>
   </r>
   <r>
-    <n v="83"/>
+    <x v="82"/>
     <x v="53"/>
+    <m/>
     <d v="2026-06-23T00:00:00"/>
-    <n v="3653"/>
+    <x v="58"/>
     <n v="4100"/>
     <n v="3415"/>
     <m/>
@@ -2059,10 +2640,11 @@
     <m/>
   </r>
   <r>
-    <n v="84"/>
+    <x v="83"/>
     <x v="67"/>
+    <m/>
     <d v="2026-06-24T00:00:00"/>
-    <n v="454"/>
+    <x v="74"/>
     <n v="540"/>
     <m/>
     <m/>
@@ -2073,10 +2655,11 @@
     <m/>
   </r>
   <r>
-    <n v="85"/>
+    <x v="84"/>
     <x v="68"/>
+    <m/>
     <d v="2026-06-24T00:00:00"/>
-    <n v="12667"/>
+    <x v="75"/>
     <n v="15290"/>
     <n v="11400"/>
     <m/>
@@ -2087,10 +2670,11 @@
     <m/>
   </r>
   <r>
-    <n v="86"/>
+    <x v="85"/>
     <x v="69"/>
+    <m/>
     <d v="2026-06-24T00:00:00"/>
-    <n v="829"/>
+    <x v="76"/>
     <n v="1110"/>
     <m/>
     <m/>
@@ -2101,38 +2685,41 @@
     <n v="12"/>
   </r>
   <r>
-    <n v="87"/>
+    <x v="86"/>
     <x v="70"/>
+    <m/>
     <d v="2026-06-24T00:00:00"/>
-    <n v="3891"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="88"/>
+    <x v="77"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="87"/>
     <x v="71"/>
+    <m/>
     <d v="2026-06-24T00:00:00"/>
-    <n v="346"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="89"/>
+    <x v="78"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="88"/>
     <x v="45"/>
+    <m/>
     <d v="2026-06-24T00:00:00"/>
-    <n v="1112"/>
+    <x v="79"/>
     <n v="1185"/>
     <n v="1080"/>
     <m/>
@@ -2143,10 +2730,11 @@
     <m/>
   </r>
   <r>
-    <n v="90"/>
+    <x v="89"/>
     <x v="13"/>
+    <m/>
     <d v="2026-06-24T00:00:00"/>
-    <n v="199"/>
+    <x v="80"/>
     <n v="204"/>
     <n v="197"/>
     <m/>
@@ -2157,10 +2745,11 @@
     <m/>
   </r>
   <r>
-    <n v="91"/>
+    <x v="90"/>
     <x v="53"/>
+    <m/>
     <d v="2026-06-25T00:00:00"/>
-    <n v="3653"/>
+    <x v="58"/>
     <n v="4100"/>
     <n v="3415"/>
     <m/>
@@ -2171,24 +2760,26 @@
     <m/>
   </r>
   <r>
-    <n v="92"/>
+    <x v="91"/>
     <x v="38"/>
+    <m/>
     <d v="2026-06-25T00:00:00"/>
-    <n v="2123"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="93"/>
+    <x v="81"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="92"/>
     <x v="72"/>
+    <m/>
     <d v="2026-06-25T00:00:00"/>
-    <n v="1019"/>
+    <x v="82"/>
     <n v="1175"/>
     <m/>
     <n v="1033"/>
@@ -2199,24 +2790,26 @@
     <m/>
   </r>
   <r>
-    <n v="94"/>
+    <x v="93"/>
     <x v="73"/>
+    <m/>
     <d v="2026-06-25T00:00:00"/>
-    <n v="413"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="95"/>
+    <x v="83"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="94"/>
     <x v="74"/>
+    <m/>
     <d v="2026-06-25T00:00:00"/>
-    <n v="1384"/>
+    <x v="84"/>
     <n v="1441"/>
     <n v="1350"/>
     <m/>
@@ -2227,10 +2820,11 @@
     <m/>
   </r>
   <r>
-    <n v="96"/>
+    <x v="95"/>
     <x v="75"/>
+    <m/>
     <d v="2026-06-29T00:00:00"/>
-    <n v="1455"/>
+    <x v="85"/>
     <n v="1570"/>
     <n v="1380"/>
     <m/>
@@ -2241,38 +2835,41 @@
     <m/>
   </r>
   <r>
-    <n v="97"/>
+    <x v="96"/>
     <x v="76"/>
+    <m/>
     <d v="2026-06-29T00:00:00"/>
-    <n v="13735"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="98"/>
+    <x v="86"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="97"/>
     <x v="77"/>
+    <m/>
     <d v="2026-06-29T00:00:00"/>
-    <n v="391"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="99"/>
+    <x v="87"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="98"/>
     <x v="78"/>
+    <m/>
     <d v="2026-06-29T00:00:00"/>
-    <n v="1231"/>
+    <x v="88"/>
     <n v="1520"/>
     <m/>
     <m/>
@@ -2283,10 +2880,11 @@
     <m/>
   </r>
   <r>
-    <n v="100"/>
+    <x v="99"/>
     <x v="79"/>
+    <m/>
     <d v="2026-06-29T00:00:00"/>
-    <n v="575"/>
+    <x v="89"/>
     <n v="700"/>
     <m/>
     <m/>
@@ -2297,10 +2895,11 @@
     <m/>
   </r>
   <r>
-    <n v="101"/>
+    <x v="100"/>
     <x v="80"/>
+    <m/>
     <d v="2026-06-29T00:00:00"/>
-    <n v="1132"/>
+    <x v="90"/>
     <n v="1329"/>
     <n v="1035"/>
     <m/>
@@ -2311,10 +2910,11 @@
     <m/>
   </r>
   <r>
-    <n v="102"/>
+    <x v="101"/>
     <x v="72"/>
+    <m/>
     <d v="2026-06-29T00:00:00"/>
-    <n v="1046"/>
+    <x v="91"/>
     <n v="1205"/>
     <n v="968"/>
     <m/>
@@ -2325,10 +2925,11 @@
     <m/>
   </r>
   <r>
-    <n v="103"/>
+    <x v="102"/>
     <x v="60"/>
+    <m/>
     <d v="2026-07-01T00:00:00"/>
-    <n v="2441"/>
+    <x v="92"/>
     <n v="2750"/>
     <m/>
     <m/>
@@ -2339,38 +2940,41 @@
     <m/>
   </r>
   <r>
-    <n v="104"/>
+    <x v="103"/>
     <x v="81"/>
+    <m/>
     <d v="2026-07-01T00:00:00"/>
-    <n v="840"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="105"/>
+    <x v="93"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="104"/>
     <x v="82"/>
+    <m/>
     <d v="2026-07-01T00:00:00"/>
-    <n v="802"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="106"/>
+    <x v="94"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="105"/>
     <x v="83"/>
+    <m/>
     <d v="2026-07-01T00:00:00"/>
-    <n v="4628"/>
+    <x v="95"/>
     <n v="4850"/>
     <n v="4500"/>
     <m/>
@@ -2381,10 +2985,11 @@
     <m/>
   </r>
   <r>
-    <n v="107"/>
+    <x v="106"/>
     <x v="84"/>
+    <m/>
     <d v="2026-07-02T00:00:00"/>
-    <n v="1396"/>
+    <x v="96"/>
     <n v="1940"/>
     <m/>
     <m/>
@@ -2395,10 +3000,11 @@
     <m/>
   </r>
   <r>
-    <n v="108"/>
+    <x v="107"/>
     <x v="85"/>
+    <m/>
     <d v="2026-07-02T00:00:00"/>
-    <n v="1503"/>
+    <x v="97"/>
     <n v="1780"/>
     <m/>
     <m/>
@@ -2409,38 +3015,41 @@
     <m/>
   </r>
   <r>
-    <n v="109"/>
+    <x v="108"/>
     <x v="86"/>
+    <m/>
     <d v="2026-07-02T00:00:00"/>
-    <n v="976"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="110"/>
+    <x v="98"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="109"/>
     <x v="6"/>
+    <m/>
     <d v="2026-07-02T00:00:00"/>
-    <n v="508"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="111"/>
+    <x v="99"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="110"/>
     <x v="47"/>
+    <m/>
     <d v="2026-07-02T00:00:00"/>
-    <n v="1628"/>
+    <x v="100"/>
     <n v="1760"/>
     <n v="1540"/>
     <m/>
@@ -2451,10 +3060,11 @@
     <m/>
   </r>
   <r>
-    <n v="112"/>
+    <x v="111"/>
     <x v="84"/>
+    <m/>
     <d v="2026-07-03T00:00:00"/>
-    <n v="1412"/>
+    <x v="101"/>
     <n v="1586"/>
     <n v="1331"/>
     <m/>
@@ -2465,24 +3075,26 @@
     <m/>
   </r>
   <r>
-    <n v="113"/>
+    <x v="112"/>
     <x v="87"/>
+    <m/>
     <d v="2026-07-03T00:00:00"/>
-    <n v="1018"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="114"/>
+    <x v="102"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="113"/>
     <x v="81"/>
+    <m/>
     <d v="2026-07-03T00:00:00"/>
-    <n v="856"/>
+    <x v="103"/>
     <n v="950"/>
     <m/>
     <m/>
@@ -2493,38 +3105,41 @@
     <m/>
   </r>
   <r>
-    <n v="115"/>
+    <x v="114"/>
     <x v="88"/>
+    <m/>
     <d v="2026-07-03T00:00:00"/>
-    <n v="1027"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="116"/>
+    <x v="104"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="115"/>
     <x v="89"/>
+    <m/>
     <d v="2026-07-03T00:00:00"/>
-    <n v="1360"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="117"/>
+    <x v="105"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="116"/>
     <x v="14"/>
+    <m/>
     <d v="2026-07-03T00:00:00"/>
-    <n v="1882"/>
+    <x v="106"/>
     <n v="2017"/>
     <n v="1810"/>
     <m/>
@@ -2535,10 +3150,11 @@
     <m/>
   </r>
   <r>
-    <n v="118"/>
+    <x v="117"/>
     <x v="90"/>
+    <m/>
     <d v="2026-07-06T00:00:00"/>
-    <n v="235"/>
+    <x v="107"/>
     <n v="288"/>
     <m/>
     <m/>
@@ -2549,10 +3165,11 @@
     <m/>
   </r>
   <r>
-    <n v="119"/>
+    <x v="118"/>
     <x v="91"/>
+    <m/>
     <d v="2026-07-06T00:00:00"/>
-    <n v="548"/>
+    <x v="108"/>
     <n v="612"/>
     <n v="514"/>
     <m/>
@@ -2563,38 +3180,41 @@
     <m/>
   </r>
   <r>
-    <n v="120"/>
+    <x v="119"/>
     <x v="92"/>
+    <m/>
     <d v="2026-07-06T00:00:00"/>
-    <n v="310"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="121"/>
+    <x v="109"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="120"/>
     <x v="54"/>
+    <m/>
     <d v="2026-07-07T00:00:00"/>
-    <n v="352"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="122"/>
+    <x v="110"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="121"/>
     <x v="93"/>
+    <m/>
     <d v="2026-07-07T00:00:00"/>
-    <n v="4484"/>
+    <x v="111"/>
     <n v="5250"/>
     <m/>
     <m/>
@@ -2605,40 +3225,1873 @@
     <m/>
   </r>
   <r>
-    <n v="123"/>
+    <x v="122"/>
     <x v="20"/>
+    <m/>
     <d v="2026-07-07T00:00:00"/>
-    <n v="2246"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="124"/>
+    <x v="112"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="123"/>
     <x v="94"/>
+    <m/>
     <d v="2026-07-07T00:00:00"/>
-    <n v="78"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-  <r>
-    <n v="125"/>
+    <x v="113"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="124"/>
     <x v="95"/>
+    <m/>
     <d v="2026-07-07T00:00:00"/>
-    <n v="3213"/>
+    <x v="114"/>
     <n v="3367"/>
     <n v="3130"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="125"/>
+    <x v="62"/>
+    <m/>
+    <d v="2026-07-08T00:00:00"/>
+    <x v="115"/>
+    <n v="310"/>
+    <n v="278"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="126"/>
+    <x v="5"/>
+    <m/>
+    <d v="2026-07-08T00:00:00"/>
+    <x v="116"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="127"/>
+    <x v="96"/>
+    <m/>
+    <d v="2026-07-08T00:00:00"/>
+    <x v="117"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="128"/>
+    <x v="81"/>
+    <m/>
+    <d v="2026-07-08T00:00:00"/>
+    <x v="118"/>
+    <n v="1000"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="129"/>
+    <x v="97"/>
+    <m/>
+    <d v="2026-07-08T00:00:00"/>
+    <x v="119"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="130"/>
+    <x v="92"/>
+    <s v="Velocity Idea"/>
+    <d v="2026-07-08T00:00:00"/>
+    <x v="120"/>
+    <n v="370"/>
+    <n v="290"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="131"/>
+    <x v="67"/>
+    <m/>
+    <d v="2026-07-09T00:00:00"/>
+    <x v="121"/>
+    <n v="540"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="132"/>
+    <x v="98"/>
+    <m/>
+    <d v="2026-07-09T00:00:00"/>
+    <x v="90"/>
+    <n v="1406"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="133"/>
+    <x v="99"/>
+    <m/>
+    <d v="2026-07-09T00:00:00"/>
+    <x v="122"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="134"/>
+    <x v="100"/>
+    <s v="Conviction Delivery Idea"/>
+    <d v="2026-07-09T00:00:00"/>
+    <x v="123"/>
+    <n v="1300"/>
+    <n v="1150"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="135"/>
+    <x v="92"/>
+    <s v="Velocity Idea"/>
+    <d v="2026-07-10T00:00:00"/>
+    <x v="120"/>
+    <n v="370"/>
+    <n v="290"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="136"/>
+    <x v="21"/>
+    <s v="Fundamental "/>
+    <d v="2026-07-10T00:00:00"/>
+    <x v="124"/>
+    <n v="375"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="137"/>
+    <x v="68"/>
+    <s v="Fundamental "/>
+    <d v="2026-07-10T00:00:00"/>
+    <x v="125"/>
+    <n v="16100"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="138"/>
+    <x v="63"/>
+    <s v="Technical Radar"/>
+    <d v="2026-07-10T00:00:00"/>
+    <x v="126"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="139"/>
+    <x v="101"/>
+    <m/>
+    <d v="2026-07-10T00:00:00"/>
+    <x v="127"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="140"/>
+    <x v="102"/>
+    <s v="Technical Radar"/>
+    <d v="2026-07-10T00:00:00"/>
+    <x v="128"/>
+    <n v="3715"/>
+    <n v="3290"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="141"/>
+    <x v="103"/>
+    <s v="Consolidation Breakout"/>
+    <d v="2026-07-13T00:00:00"/>
+    <x v="129"/>
+    <n v="1520"/>
+    <n v="1380"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="142"/>
+    <x v="104"/>
+    <s v="Consolidation Breakout"/>
+    <d v="2026-07-13T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="143"/>
+    <x v="105"/>
+    <m/>
+    <d v="2026-07-13T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="144"/>
+    <x v="106"/>
+    <m/>
+    <d v="2026-07-13T00:00:00"/>
+    <x v="130"/>
+    <n v="370"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="145"/>
+    <x v="107"/>
+    <m/>
+    <d v="2026-07-13T00:00:00"/>
+    <x v="131"/>
+    <n v="1025"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="146"/>
+    <x v="72"/>
+    <s v="Velocity Idea"/>
+    <d v="2026-07-13T00:00:00"/>
+    <x v="91"/>
+    <n v="1205"/>
+    <n v="968"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="147"/>
+    <x v="108"/>
+    <m/>
+    <d v="2026-07-14T00:00:00"/>
+    <x v="132"/>
+    <n v="830"/>
+    <n v="727"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="148"/>
+    <x v="109"/>
+    <s v="Range breakout bullish candle"/>
+    <d v="2026-07-14T00:00:00"/>
+    <x v="33"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="149"/>
+    <x v="110"/>
+    <m/>
+    <d v="2026-07-14T00:00:00"/>
+    <x v="133"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="150"/>
+    <x v="111"/>
+    <m/>
+    <d v="2026-07-14T00:00:00"/>
+    <x v="134"/>
+    <n v="3800"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="151"/>
+    <x v="112"/>
+    <m/>
+    <d v="2026-07-14T00:00:00"/>
+    <x v="135"/>
+    <n v="1450"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="152"/>
+    <x v="113"/>
+    <s v="Fundamental "/>
+    <d v="2026-07-15T00:00:00"/>
+    <x v="136"/>
+    <n v="200"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="153"/>
+    <x v="114"/>
+    <s v="Initiating coverage"/>
+    <d v="2026-07-15T00:00:00"/>
+    <x v="137"/>
+    <n v="565"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="154"/>
+    <x v="115"/>
+    <s v="Watchlist"/>
+    <d v="2026-07-15T00:00:00"/>
+    <x v="138"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="155"/>
+    <x v="116"/>
+    <s v="Watchlist"/>
+    <d v="2026-07-15T00:00:00"/>
+    <x v="139"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="156"/>
+    <x v="117"/>
+    <s v="Technical Radar"/>
+    <d v="2026-07-15T00:00:00"/>
+    <x v="140"/>
+    <n v="1790"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="157"/>
+    <x v="116"/>
+    <s v="Technical conviction"/>
+    <d v="2026-07-16T00:00:00"/>
+    <x v="41"/>
+    <n v="1980"/>
+    <n v="1800"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="158"/>
+    <x v="118"/>
+    <s v="Watchlist"/>
+    <d v="2026-07-16T00:00:00"/>
+    <x v="141"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="159"/>
+    <x v="119"/>
+    <s v="Watchlist"/>
+    <d v="2026-07-16T00:00:00"/>
+    <x v="142"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="160"/>
+    <x v="120"/>
+    <s v="Initiating coverage"/>
+    <d v="2026-07-16T00:00:00"/>
+    <x v="143"/>
+    <n v="1530"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="161"/>
+    <x v="13"/>
+    <s v="Fundamental "/>
+    <d v="2026-07-16T00:00:00"/>
+    <x v="144"/>
+    <n v="250"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="162"/>
+    <x v="80"/>
+    <s v="Velocity Idea"/>
+    <d v="2026-07-16T00:00:00"/>
+    <x v="90"/>
+    <n v="1329"/>
+    <n v="1035"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="163"/>
+    <x v="121"/>
+    <m/>
+    <d v="2026-07-17T00:00:00"/>
+    <x v="145"/>
+    <n v="420"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="164"/>
+    <x v="122"/>
+    <m/>
+    <d v="2026-07-17T00:00:00"/>
+    <x v="32"/>
+    <n v="1900"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="165"/>
+    <x v="123"/>
+    <m/>
+    <d v="2026-07-17T00:00:00"/>
+    <x v="146"/>
+    <n v="2620"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="166"/>
+    <x v="124"/>
+    <m/>
+    <d v="2026-07-17T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="167"/>
+    <x v="125"/>
+    <m/>
+    <d v="2026-07-17T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="168"/>
+    <x v="126"/>
+    <m/>
+    <d v="2026-07-17T00:00:00"/>
+    <x v="147"/>
+    <n v="780"/>
+    <n v="695"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="169"/>
+    <x v="99"/>
+    <s v="Conviction Delivery Idea"/>
+    <d v="2026-07-20T00:00:00"/>
+    <x v="148"/>
+    <n v="475"/>
+    <n v="415"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="170"/>
+    <x v="110"/>
+    <m/>
+    <d v="2026-07-20T00:00:00"/>
+    <x v="109"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="171"/>
+    <x v="127"/>
+    <m/>
+    <d v="2026-07-20T00:00:00"/>
+    <x v="149"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="172"/>
+    <x v="128"/>
+    <m/>
+    <d v="2026-07-20T00:00:00"/>
+    <x v="150"/>
+    <n v="1750"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="173"/>
+    <x v="129"/>
+    <m/>
+    <d v="2026-07-20T00:00:00"/>
+    <x v="151"/>
+    <n v="1470"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="174"/>
+    <x v="130"/>
+    <m/>
+    <d v="2026-07-20T00:00:00"/>
+    <x v="101"/>
+    <n v="1586"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="175"/>
+    <x v="131"/>
+    <s v="Conviction Delivery Idea"/>
+    <d v="2026-07-20T00:00:00"/>
+    <x v="152"/>
+    <n v="3684"/>
+    <n v="3240"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="176"/>
+    <x v="132"/>
+    <m/>
+    <d v="2026-07-21T00:00:00"/>
+    <x v="153"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="177"/>
+    <x v="133"/>
+    <m/>
+    <d v="2026-07-21T00:00:00"/>
+    <x v="154"/>
+    <n v="2260"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="178"/>
+    <x v="134"/>
+    <m/>
+    <d v="2026-07-21T00:00:00"/>
+    <x v="155"/>
+    <n v="2070"/>
+    <n v="1800"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="179"/>
+    <x v="135"/>
+    <m/>
+    <d v="2026-07-21T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="180"/>
+    <x v="136"/>
+    <m/>
+    <d v="2026-07-21T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="181"/>
+    <x v="137"/>
+    <m/>
+    <d v="2026-07-22T00:00:00"/>
+    <x v="156"/>
+    <n v="800"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="182"/>
+    <x v="138"/>
+    <m/>
+    <d v="2026-07-22T00:00:00"/>
+    <x v="157"/>
+    <n v="12096"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="183"/>
+    <x v="139"/>
+    <m/>
+    <d v="2026-07-22T00:00:00"/>
+    <x v="158"/>
+    <n v="4717"/>
+    <n v="4450"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="184"/>
+    <x v="4"/>
+    <m/>
+    <d v="2026-07-22T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="185"/>
+    <x v="140"/>
+    <m/>
+    <d v="2026-07-22T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="186"/>
+    <x v="141"/>
+    <m/>
+    <d v="2026-07-22T00:00:00"/>
+    <x v="159"/>
+    <n v="92.4"/>
+    <n v="95.7"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="187"/>
+    <x v="142"/>
+    <m/>
+    <d v="2026-07-23T00:00:00"/>
+    <x v="43"/>
+    <n v="373"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="188"/>
+    <x v="143"/>
+    <s v="Technical conviction"/>
+    <d v="2026-07-23T00:00:00"/>
+    <x v="160"/>
+    <n v="1600"/>
+    <n v="1450"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="189"/>
+    <x v="99"/>
+    <m/>
+    <d v="2026-07-23T00:00:00"/>
+    <x v="161"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="190"/>
+    <x v="144"/>
+    <s v="Fundamental actionable idea"/>
+    <d v="2026-07-23T00:00:00"/>
+    <x v="162"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="191"/>
+    <x v="145"/>
+    <s v="Fundamental actionable idea"/>
+    <d v="2026-07-23T00:00:00"/>
+    <x v="163"/>
+    <n v="1380"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="192"/>
+    <x v="146"/>
+    <m/>
+    <d v="2026-07-24T00:00:00"/>
+    <x v="164"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="193"/>
+    <x v="147"/>
+    <m/>
+    <d v="2026-07-24T00:00:00"/>
+    <x v="165"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="194"/>
+    <x v="148"/>
+    <m/>
+    <d v="2026-07-24T00:00:00"/>
+    <x v="166"/>
+    <n v="3404"/>
+    <n v="3145"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="195"/>
+    <x v="80"/>
+    <m/>
+    <d v="2026-07-24T00:00:00"/>
+    <x v="90"/>
+    <n v="1329"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="196"/>
+    <x v="137"/>
+    <m/>
+    <d v="2026-07-24T00:00:00"/>
+    <x v="167"/>
+    <n v="678.5"/>
+    <n v="664"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="197"/>
+    <x v="149"/>
+    <m/>
+    <d v="2026-07-24T00:00:00"/>
+    <x v="168"/>
+    <n v="1872"/>
+    <n v="1833"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="198"/>
+    <x v="86"/>
+    <m/>
+    <d v="2026-07-24T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="199"/>
+    <x v="150"/>
+    <m/>
+    <d v="2026-07-27T00:00:00"/>
+    <x v="169"/>
+    <n v="2590"/>
+    <n v="2360"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="200"/>
+    <x v="132"/>
+    <s v="Technical Radar"/>
+    <d v="2026-07-27T00:00:00"/>
+    <x v="170"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="201"/>
+    <x v="151"/>
+    <m/>
+    <d v="2026-07-27T00:00:00"/>
+    <x v="171"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="202"/>
+    <x v="63"/>
+    <m/>
+    <d v="2026-07-27T00:00:00"/>
+    <x v="172"/>
+    <n v="1980"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="203"/>
+    <x v="80"/>
+    <m/>
+    <d v="2026-07-27T00:00:00"/>
+    <x v="90"/>
+    <n v="1329"/>
+    <n v="1035"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="204"/>
+    <x v="75"/>
+    <m/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="205"/>
+    <x v="152"/>
+    <s v="Conviction Delivery Idea"/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="173"/>
+    <n v="615"/>
+    <n v="555"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="206"/>
+    <x v="148"/>
+    <s v="Consolidation Breakout"/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="207"/>
+    <x v="146"/>
+    <m/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="13"/>
+    <n v="240"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="208"/>
+    <x v="87"/>
+    <m/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="209"/>
+    <x v="153"/>
+    <s v="Fundamental actionable idea"/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="174"/>
+    <n v="1430"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="210"/>
+    <x v="80"/>
+    <s v="Velocity Idea"/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="90"/>
+    <n v="1329"/>
+    <n v="1035"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="211"/>
+    <x v="154"/>
+    <m/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="175"/>
+    <n v="536"/>
+    <n v="521"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="212"/>
+    <x v="88"/>
+    <m/>
+    <d v="2026-07-28T00:00:00"/>
+    <x v="176"/>
+    <n v="1262"/>
+    <n v="1200"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="213"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="214"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="215"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="216"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="217"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="218"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="219"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="220"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="221"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="222"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="223"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="224"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="225"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="226"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="227"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="228"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="229"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="230"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="231"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="232"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="233"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="234"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="235"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="236"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="237"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="238"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="239"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="240"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="241"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="242"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="243"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="244"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="245"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="246"/>
+    <x v="155"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <m/>
     <m/>
     <m/>
     <m/>
@@ -2650,120 +5103,420 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BFCE9BB-D4F6-4469-A5D2-5B061F18340D}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="P1:Q98" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
-      <items count="108">
-        <item m="1" x="106"/>
-        <item x="91"/>
-        <item x="46"/>
-        <item x="77"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74FB6B00-93B5-4C0A-B408-84CB87C3F183}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="248">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
         <item x="14"/>
-        <item x="58"/>
-        <item x="84"/>
-        <item x="1"/>
-        <item x="89"/>
-        <item x="55"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
         <item x="19"/>
-        <item x="54"/>
-        <item x="74"/>
         <item x="20"/>
-        <item x="87"/>
-        <item x="44"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
         <item x="33"/>
-        <item m="1" x="99"/>
-        <item x="49"/>
-        <item m="1" x="100"/>
-        <item x="38"/>
-        <item m="1" x="98"/>
-        <item x="56"/>
-        <item x="52"/>
-        <item x="86"/>
-        <item m="1" x="104"/>
-        <item x="64"/>
-        <item x="5"/>
-        <item x="85"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="68"/>
-        <item x="40"/>
-        <item x="62"/>
-        <item x="18"/>
-        <item x="21"/>
-        <item x="9"/>
-        <item x="22"/>
-        <item x="71"/>
-        <item x="30"/>
-        <item x="69"/>
-        <item x="82"/>
-        <item m="1" x="97"/>
-        <item m="1" x="105"/>
-        <item x="28"/>
-        <item x="95"/>
-        <item x="13"/>
-        <item x="70"/>
-        <item x="73"/>
-        <item x="26"/>
-        <item x="0"/>
-        <item x="10"/>
         <item x="34"/>
         <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
         <item x="41"/>
-        <item x="8"/>
-        <item x="23"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
         <item x="78"/>
-        <item x="60"/>
-        <item m="1" x="103"/>
-        <item x="37"/>
-        <item x="63"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
         <item x="94"/>
-        <item x="81"/>
-        <item x="76"/>
-        <item m="1" x="102"/>
-        <item x="80"/>
-        <item x="29"/>
-        <item x="65"/>
-        <item x="12"/>
-        <item x="88"/>
-        <item x="24"/>
-        <item x="31"/>
-        <item x="92"/>
-        <item x="57"/>
-        <item x="90"/>
-        <item x="39"/>
-        <item x="25"/>
-        <item x="48"/>
-        <item x="17"/>
-        <item x="47"/>
-        <item x="27"/>
-        <item x="53"/>
-        <item x="32"/>
-        <item m="1" x="96"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="51"/>
-        <item x="72"/>
-        <item x="36"/>
-        <item x="79"/>
-        <item x="50"/>
-        <item x="66"/>
-        <item x="61"/>
-        <item x="43"/>
-        <item x="11"/>
-        <item x="15"/>
-        <item x="93"/>
-        <item x="83"/>
-        <item x="16"/>
-        <item x="67"/>
-        <item x="7"/>
-        <item x="59"/>
-        <item m="1" x="101"/>
-        <item x="75"/>
-        <item x="42"/>
-        <item x="45"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
         <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
+      <items count="157">
+        <item h="1" sd="0" x="91"/>
+        <item h="1" sd="0" x="118"/>
+        <item h="1" sd="0" x="46"/>
+        <item h="1" sd="0" x="77"/>
+        <item h="1" sd="0" x="130"/>
+        <item h="1" sd="0" x="115"/>
+        <item h="1" sd="0" x="14"/>
+        <item h="1" sd="0" x="58"/>
+        <item h="1" sd="0" x="84"/>
+        <item h="1" sd="0" x="1"/>
+        <item h="1" sd="0" x="89"/>
+        <item h="1" sd="0" x="101"/>
+        <item h="1" sd="0" x="55"/>
+        <item h="1" sd="0" x="19"/>
+        <item h="1" sd="0" x="54"/>
+        <item h="1" sd="0" x="97"/>
+        <item h="1" sd="0" x="100"/>
+        <item h="1" sd="0" x="74"/>
+        <item h="1" sd="0" x="20"/>
+        <item h="1" sd="0" x="150"/>
+        <item h="1" sd="0" x="138"/>
+        <item h="1" sd="0" x="87"/>
+        <item h="1" sd="0" x="44"/>
+        <item h="1" sd="0" x="33"/>
+        <item h="1" sd="0" x="49"/>
+        <item h="1" sd="0" x="38"/>
+        <item h="1" sd="0" x="56"/>
+        <item h="1" sd="0" x="103"/>
+        <item h="1" sd="0" x="52"/>
+        <item h="1" sd="0" x="86"/>
+        <item h="1" sd="0" x="64"/>
+        <item h="1" sd="0" x="5"/>
+        <item h="1" sd="0" x="85"/>
+        <item h="1" sd="0" x="4"/>
+        <item h="1" sd="0" x="137"/>
+        <item h="1" sd="0" x="149"/>
+        <item h="1" sd="0" x="6"/>
+        <item h="1" sd="0" x="68"/>
+        <item h="1" sd="0" x="104"/>
+        <item h="1" sd="0" x="40"/>
+        <item h="1" sd="0" x="133"/>
+        <item h="1" sd="0" x="62"/>
+        <item h="1" sd="0" x="18"/>
+        <item h="1" sd="0" x="99"/>
+        <item h="1" sd="0" x="21"/>
+        <item h="1" sd="0" x="119"/>
+        <item h="1" sd="0" x="9"/>
+        <item h="1" sd="0" x="22"/>
+        <item h="1" sd="0" x="71"/>
+        <item h="1" sd="0" x="30"/>
+        <item h="1" sd="0" x="140"/>
+        <item h="1" sd="0" x="69"/>
+        <item h="1" sd="0" x="82"/>
+        <item h="1" sd="0" x="28"/>
+        <item h="1" sd="0" x="95"/>
+        <item h="1" sd="0" x="13"/>
+        <item h="1" sd="0" x="70"/>
+        <item h="1" sd="0" x="139"/>
+        <item h="1" sd="0" x="112"/>
+        <item h="1" sd="0" x="73"/>
+        <item h="1" sd="0" x="26"/>
+        <item h="1" sd="0" x="126"/>
+        <item h="1" sd="0" x="0"/>
+        <item h="1" sd="0" x="128"/>
+        <item h="1" sd="0" x="111"/>
+        <item h="1" sd="0" x="10"/>
+        <item h="1" sd="0" x="151"/>
+        <item h="1" sd="0" x="107"/>
+        <item h="1" sd="0" x="34"/>
+        <item h="1" sd="0" x="124"/>
+        <item h="1" sd="0" x="35"/>
+        <item h="1" sd="0" x="117"/>
+        <item h="1" sd="0" x="41"/>
+        <item h="1" sd="0" x="8"/>
+        <item h="1" sd="0" x="129"/>
+        <item h="1" sd="0" x="23"/>
+        <item h="1" sd="0" x="78"/>
+        <item h="1" sd="0" x="109"/>
+        <item h="1" sd="0" x="110"/>
+        <item h="1" sd="0" x="102"/>
+        <item h="1" sd="0" x="60"/>
+        <item h="1" sd="0" x="37"/>
+        <item h="1" sd="0" x="106"/>
+        <item h="1" sd="0" x="63"/>
+        <item h="1" sd="0" x="152"/>
+        <item h="1" sd="0" x="94"/>
+        <item h="1" sd="0" x="134"/>
+        <item h="1" sd="0" x="116"/>
+        <item h="1" sd="0" x="153"/>
+        <item h="1" sd="0" x="148"/>
+        <item h="1" sd="0" x="81"/>
+        <item h="1" sd="0" x="76"/>
+        <item h="1" sd="0" x="80"/>
+        <item h="1" sd="0" x="29"/>
+        <item h="1" sd="0" x="65"/>
+        <item h="1" sd="0" x="146"/>
+        <item h="1" sd="0" x="12"/>
+        <item h="1" sd="0" x="88"/>
+        <item h="1" sd="0" x="136"/>
+        <item h="1" sd="0" x="141"/>
+        <item h="1" sd="0" x="24"/>
+        <item h="1" sd="0" x="143"/>
+        <item h="1" sd="0" x="154"/>
+        <item h="1" sd="0" x="145"/>
+        <item h="1" sd="0" x="31"/>
+        <item h="1" sd="0" x="92"/>
+        <item h="1" sd="0" x="57"/>
+        <item h="1" sd="0" x="90"/>
+        <item h="1" sd="0" x="132"/>
+        <item h="1" sd="0" x="39"/>
+        <item h="1" sd="0" x="25"/>
+        <item h="1" sd="0" x="48"/>
+        <item h="1" sd="0" x="123"/>
+        <item h="1" sd="0" x="96"/>
+        <item h="1" sd="0" x="17"/>
+        <item h="1" sd="0" x="47"/>
+        <item h="1" sd="0" x="27"/>
+        <item sd="0" x="53"/>
+        <item h="1" sd="0" x="105"/>
+        <item h="1" sd="0" x="32"/>
+        <item h="1" sd="0" x="142"/>
+        <item h="1" sd="0" x="2"/>
+        <item h="1" sd="0" x="3"/>
+        <item h="1" sd="0" x="114"/>
+        <item h="1" sd="0" x="131"/>
+        <item h="1" sd="0" x="51"/>
+        <item h="1" sd="0" x="72"/>
+        <item h="1" sd="0" x="144"/>
+        <item h="1" sd="0" x="125"/>
+        <item h="1" sd="0" x="36"/>
+        <item h="1" sd="0" x="79"/>
+        <item h="1" sd="0" x="50"/>
+        <item h="1" sd="0" x="66"/>
+        <item h="1" sd="0" x="121"/>
+        <item h="1" sd="0" x="108"/>
+        <item h="1" sd="0" x="61"/>
+        <item h="1" sd="0" x="43"/>
+        <item h="1" sd="0" x="122"/>
+        <item h="1" sd="0" x="11"/>
+        <item h="1" sd="0" x="127"/>
+        <item h="1" sd="0" x="15"/>
+        <item h="1" sd="0" x="93"/>
+        <item h="1" sd="0" x="83"/>
+        <item h="1" sd="0" x="120"/>
+        <item h="1" sd="0" x="135"/>
+        <item h="1" sd="0" x="98"/>
+        <item h="1" sd="0" x="16"/>
+        <item h="1" sd="0" x="67"/>
+        <item h="1" sd="0" x="147"/>
+        <item h="1" sd="0" x="7"/>
+        <item h="1" sd="0" x="59"/>
+        <item h="1" sd="0" x="75"/>
+        <item h="1" sd="0" x="113"/>
+        <item h="1" sd="0" x="42"/>
+        <item h="1" sd="0" x="45"/>
+        <item h="1" sd="0" x="155"/>
+        <item t="default" sd="0"/>
       </items>
       <autoSortScope>
         <pivotArea dataOnly="0" outline="0" fieldPosition="0">
@@ -2777,6 +5530,188 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="178">
+        <item sd="0" x="54"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="43"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2786,297 +5721,13 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="1">
+  <rowFields count="2">
     <field x="1"/>
+    <field x="0"/>
   </rowFields>
-  <rowItems count="97">
+  <rowItems count="2">
     <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="82"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="58"/>
-    </i>
-    <i>
-      <x v="44"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="106"/>
-    </i>
-    <i>
-      <x v="80"/>
-    </i>
-    <i>
-      <x v="63"/>
-    </i>
-    <i>
-      <x v="85"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="88"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="60"/>
-    </i>
-    <i>
-      <x v="77"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="86"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="64"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="73"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="81"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="62"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="67"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="71"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="75"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="79"/>
-    </i>
-    <i>
-      <x v="37"/>
-    </i>
-    <i>
-      <x v="83"/>
-    </i>
-    <i>
-      <x v="38"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="39"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="66"/>
-    </i>
-    <i>
-      <x v="45"/>
-    </i>
-    <i>
-      <x v="68"/>
-    </i>
-    <i>
-      <x v="90"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="91"/>
-    </i>
-    <i>
-      <x v="72"/>
-    </i>
-    <i>
-      <x v="93"/>
-    </i>
-    <i>
-      <x v="74"/>
-    </i>
-    <i>
-      <x v="95"/>
-    </i>
-    <i>
-      <x v="76"/>
-    </i>
-    <i>
-      <x v="97"/>
-    </i>
-    <i>
-      <x v="78"/>
-    </i>
-    <i>
-      <x v="99"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="101"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="104"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="87"/>
-    </i>
-    <i>
-      <x v="55"/>
-    </i>
-    <i>
-      <x v="89"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="57"/>
-    </i>
-    <i>
-      <x v="92"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="94"/>
-    </i>
-    <i>
-      <x v="48"/>
-    </i>
-    <i>
-      <x v="96"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="98"/>
-    </i>
-    <i>
-      <x v="50"/>
-    </i>
-    <i>
-      <x v="100"/>
-    </i>
-    <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="102"/>
-    </i>
-    <i>
-      <x v="52"/>
-    </i>
-    <i>
-      <x v="105"/>
-    </i>
-    <i>
-      <x v="53"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="54"/>
+      <x v="117"/>
     </i>
     <i t="grand">
       <x/>
@@ -3086,67 +5737,8 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Frequency of Stocks" fld="1" subtotal="count" baseField="1" baseItem="1"/>
+    <dataField name="Count of STOCK NAME" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="5">
-    <format dxfId="4">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="4">
-            <x v="7"/>
-            <x v="20"/>
-            <x v="30"/>
-            <x v="82"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="4">
-            <x v="7"/>
-            <x v="20"/>
-            <x v="30"/>
-            <x v="82"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="4">
-            <x v="7"/>
-            <x v="20"/>
-            <x v="30"/>
-            <x v="82"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="4">
-            <x v="7"/>
-            <x v="20"/>
-            <x v="30"/>
-            <x v="82"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3157,6 +5749,94 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{463B9DCF-DB71-4E52-9ADC-9CCE20A5D4FD}" name="Table5" displayName="Table5" ref="A3:M4" totalsRowShown="0">
+  <autoFilter ref="A3:M4" xr:uid="{463B9DCF-DB71-4E52-9ADC-9CCE20A5D4FD}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{0BBDE297-6A4A-46DC-AEDA-7D0AE7BD8281}" name="S No."/>
+    <tableColumn id="2" xr3:uid="{567A195B-BA79-4FD7-9601-DA00902F59B9}" name="STOCK NAME"/>
+    <tableColumn id="3" xr3:uid="{0F5490D4-136C-418D-AF36-E5F4FFF78D59}" name="Idea Type"/>
+    <tableColumn id="4" xr3:uid="{BABEA534-5C9C-4935-935B-6C3F5566B5BF}" name="Day when told" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{691207CF-675C-42BA-9A2B-063441DF01DE}" name="Current price"/>
+    <tableColumn id="6" xr3:uid="{2C69DC99-0EF3-440A-B354-CEBC9006F850}" name="Target price"/>
+    <tableColumn id="7" xr3:uid="{642BFE52-CAEC-40D8-B209-13A7074E79FC}" name="Stop loss"/>
+    <tableColumn id="8" xr3:uid="{A6F3930D-B29F-4FDA-956F-AEED10AE5566}" name="Today's closing price"/>
+    <tableColumn id="9" xr3:uid="{D1342865-C73F-4E59-8B96-49385E1F7063}" name="Excepted Return"/>
+    <tableColumn id="10" xr3:uid="{7E974035-FFB8-47B6-A579-D6976A9C3203}" name="Result date"/>
+    <tableColumn id="11" xr3:uid="{E8D38A8D-07CF-4104-B4D5-2292C801EECD}" name="Result price"/>
+    <tableColumn id="12" xr3:uid="{2AFB6733-B86C-4041-AA73-724ABED46E19}" name="Profit / loss"/>
+    <tableColumn id="13" xr3:uid="{21584409-99CB-4BB2-89BE-84D9A9EE28AD}" name="Quantity"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{390FCD6F-2359-46E9-AAA5-CB2ADA057134}" name="Table6" displayName="Table6" ref="A3:M4" totalsRowShown="0">
+  <autoFilter ref="A3:M4" xr:uid="{390FCD6F-2359-46E9-AAA5-CB2ADA057134}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{065F2E3C-1BA3-4173-A247-890B3CC37257}" name="S No."/>
+    <tableColumn id="2" xr3:uid="{52AEA7E3-01DE-477B-AE7F-1FFEADF16590}" name="STOCK NAME"/>
+    <tableColumn id="3" xr3:uid="{7B6C07CB-DFFB-4AD0-9767-34B39D795F79}" name="Idea Type"/>
+    <tableColumn id="4" xr3:uid="{6276DDF8-026C-4730-ADDC-4DA2430FF452}" name="Day when told" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{5C9AE37E-9000-4014-AF5A-196796FE5251}" name="Current price"/>
+    <tableColumn id="6" xr3:uid="{28A5772D-C620-4DFC-902E-224037000235}" name="Target price"/>
+    <tableColumn id="7" xr3:uid="{5BDDEE73-4AEA-4932-9634-E445527D3230}" name="Stop loss"/>
+    <tableColumn id="8" xr3:uid="{1EBD6075-97C5-4BE6-8BBB-3239A602343D}" name="Today's closing price"/>
+    <tableColumn id="9" xr3:uid="{7B80CC82-8708-47F8-A4FA-00EAE8767520}" name="Excepted Return"/>
+    <tableColumn id="10" xr3:uid="{A0759BB3-0214-4027-8256-B964A0AFDC6D}" name="Result date"/>
+    <tableColumn id="11" xr3:uid="{6498DC28-7821-4D10-A8AB-B1E24614C67F}" name="Result price"/>
+    <tableColumn id="12" xr3:uid="{7AE1141B-41DF-4214-9B41-1DDF6BE4B25D}" name="Profit / loss"/>
+    <tableColumn id="13" xr3:uid="{3BD29281-3FD9-4F20-8B19-540F55DCDE73}" name="Quantity"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E578217E-8ACB-44CE-BC7E-8CB9E2089038}" name="Table7" displayName="Table7" ref="A3:M6" totalsRowShown="0">
+  <autoFilter ref="A3:M6" xr:uid="{E578217E-8ACB-44CE-BC7E-8CB9E2089038}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{6F787FA2-3F4D-47E7-8EDB-85477E795B87}" name="S No."/>
+    <tableColumn id="2" xr3:uid="{48B1CFEF-4907-4D01-B912-ACD9D4837D0E}" name="STOCK NAME"/>
+    <tableColumn id="3" xr3:uid="{876A3CC0-3A1B-4633-AD7A-419B17B4E1F6}" name="Idea Type"/>
+    <tableColumn id="4" xr3:uid="{90C079A3-38FD-45C3-A163-FDCBE6E9E2AC}" name="Day when told" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{6972F920-5B88-4439-A686-A7AE75E46A81}" name="Current price"/>
+    <tableColumn id="6" xr3:uid="{B03983C4-2AB4-4519-9711-3533C7A75A4E}" name="Target price"/>
+    <tableColumn id="7" xr3:uid="{44716317-7155-4F95-8034-22CAC6288976}" name="Stop loss"/>
+    <tableColumn id="8" xr3:uid="{03E764F3-35D7-4063-B5F6-F4D68B66FF94}" name="Today's closing price"/>
+    <tableColumn id="9" xr3:uid="{4A08A655-DA2F-4EB9-A92C-2DD35E8E9DE4}" name="Excepted Return"/>
+    <tableColumn id="10" xr3:uid="{F7A184C5-7827-4CFE-A840-51953956FA48}" name="Result date"/>
+    <tableColumn id="11" xr3:uid="{F929CD62-850A-4DE8-892F-A7C70F1B46C3}" name="Result price"/>
+    <tableColumn id="12" xr3:uid="{95D5BAE0-104A-49DB-9563-A728F461239C}" name="Profit / loss"/>
+    <tableColumn id="13" xr3:uid="{D7774800-158D-4DD2-8AE3-B8212BB64061}" name="Quantity"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6AF70662-5D94-4098-A492-EA5831AB78D3}" name="Table1" displayName="Table1" ref="A3:M7" totalsRowShown="0">
+  <autoFilter ref="A3:M7" xr:uid="{6AF70662-5D94-4098-A492-EA5831AB78D3}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{E8020F7F-6D12-4363-ABE7-1F6DFF63400F}" name="S No."/>
+    <tableColumn id="2" xr3:uid="{369663A8-D61A-4667-9A7D-67C59F017D6B}" name="STOCK NAME"/>
+    <tableColumn id="3" xr3:uid="{8654C9DF-195E-489B-B4F6-8358C4ED4343}" name="Idea Type"/>
+    <tableColumn id="4" xr3:uid="{9A1C96C1-8B83-4121-94D4-DF706CE5B623}" name="Day when told" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{35632F7B-C16C-4B3F-8F82-7D48AD1442C2}" name="Current price"/>
+    <tableColumn id="6" xr3:uid="{EBDDFE6D-9175-44D1-BD16-123B272E8496}" name="Target price"/>
+    <tableColumn id="7" xr3:uid="{61B8EB20-B2E3-42B0-BD34-E43122F36B4B}" name="Stop loss"/>
+    <tableColumn id="8" xr3:uid="{5F46C13F-F738-43BD-9F63-CC50845AA76F}" name="Today's closing price"/>
+    <tableColumn id="9" xr3:uid="{71F31F74-0FFE-4F56-A554-0DB243BC5E86}" name="Excepted Return"/>
+    <tableColumn id="10" xr3:uid="{2D3A5F36-6B06-4757-81E0-850C220C880E}" name="Result date"/>
+    <tableColumn id="11" xr3:uid="{985C4258-A2DE-4C1B-963E-FF289769F873}" name="Result price"/>
+    <tableColumn id="12" xr3:uid="{D58293A2-2A18-48B0-8DED-E43FCA7FA2F7}" name="Profit / loss"/>
+    <tableColumn id="13" xr3:uid="{EE684EC5-23C6-4526-B5CB-3FE46065DB80}" name="Quantity"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3475,6 +6155,508 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8403DD-9798-4B42-9B23-5C4CF38A08D7}">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>210</v>
+      </c>
+      <c r="B4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46231</v>
+      </c>
+      <c r="E4">
+        <v>1199</v>
+      </c>
+      <c r="F4">
+        <v>1430</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A2B7B4-FFB3-455A-8776-C63834F8DE3E}">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46196</v>
+      </c>
+      <c r="E4">
+        <v>1288</v>
+      </c>
+      <c r="F4">
+        <v>1490</v>
+      </c>
+      <c r="I4">
+        <v>0.16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E22511-F6BB-44B9-970B-3958EBAE1FFA}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46204</v>
+      </c>
+      <c r="E4">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E5">
+        <v>856</v>
+      </c>
+      <c r="F5">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E6">
+        <v>848</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34393706-6D94-430C-8AC0-020DD7FE6883}">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>64</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46192</v>
+      </c>
+      <c r="E4">
+        <v>3653</v>
+      </c>
+      <c r="F4">
+        <v>4100</v>
+      </c>
+      <c r="G4">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>71</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46195</v>
+      </c>
+      <c r="E5">
+        <v>3653</v>
+      </c>
+      <c r="F5">
+        <v>4100</v>
+      </c>
+      <c r="G5">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46196</v>
+      </c>
+      <c r="E6">
+        <v>3653</v>
+      </c>
+      <c r="F6">
+        <v>4100</v>
+      </c>
+      <c r="G6">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46198</v>
+      </c>
+      <c r="E7">
+        <v>3653</v>
+      </c>
+      <c r="F7">
+        <v>4100</v>
+      </c>
+      <c r="G7">
+        <v>3415</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34412554-9627-467B-AEAF-19EDD8AF4622}">
+  <dimension ref="A3:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="9">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
   <dimension ref="A1:Q247"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3503,7 +6685,7 @@
         <v>109</v>
       </c>
       <c r="C1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -3534,12 +6716,6 @@
       </c>
       <c r="M1" t="s">
         <v>38</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -3565,11 +6741,8 @@
         <f>(F2-E2)/E2</f>
         <v>4.2962125494629737E-2</v>
       </c>
-      <c r="P2" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q2" s="10">
-        <v>4</v>
+      <c r="Q2" s="8" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
@@ -3589,11 +6762,8 @@
         <f t="shared" ref="I3:I27" si="0">(F3-E3)/E3</f>
         <v>-1</v>
       </c>
-      <c r="P3" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>4</v>
+      <c r="Q3" s="4" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
@@ -3619,12 +6789,6 @@
       <c r="K4">
         <v>2365</v>
       </c>
-      <c r="P4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>4</v>
-      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -3652,12 +6816,6 @@
       <c r="K5">
         <v>1344</v>
       </c>
-      <c r="P5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>4</v>
-      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -3679,12 +6837,6 @@
         <f t="shared" si="0"/>
         <v>0.12225811936745451</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -3715,12 +6867,6 @@
       <c r="K7">
         <v>1488</v>
       </c>
-      <c r="P7" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -3742,12 +6888,6 @@
         <f t="shared" si="0"/>
         <v>0.3200118345888619</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -3769,12 +6909,6 @@
         <f t="shared" si="0"/>
         <v>0.23999948467553878</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q9">
-        <v>2</v>
-      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -3796,12 +6930,6 @@
         <f t="shared" si="0"/>
         <v>0.20000331035395966</v>
       </c>
-      <c r="P10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -3823,12 +6951,6 @@
         <f t="shared" si="0"/>
         <v>0.18000429092469422</v>
       </c>
-      <c r="P11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -3850,12 +6972,6 @@
         <f t="shared" si="0"/>
         <v>0.15999843324886945</v>
       </c>
-      <c r="P12" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q12">
-        <v>2</v>
-      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -3877,12 +6993,6 @@
         <f t="shared" si="0"/>
         <v>0.11471160077770577</v>
       </c>
-      <c r="P13" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q13">
-        <v>2</v>
-      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -3901,12 +7011,6 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="P14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q14">
-        <v>2</v>
-      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -3928,12 +7032,6 @@
         <f t="shared" si="0"/>
         <v>0.27027027027027029</v>
       </c>
-      <c r="P15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q15">
-        <v>2</v>
-      </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -3955,14 +7053,8 @@
         <f t="shared" si="0"/>
         <v>0.14974761637689288</v>
       </c>
-      <c r="P16" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3985,14 +7077,8 @@
         <f t="shared" si="0"/>
         <v>0.16036505867014342</v>
       </c>
-      <c r="P17" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4009,14 +7095,8 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="P18" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4039,14 +7119,8 @@
         <f t="shared" si="0"/>
         <v>8.0074487895716945E-2</v>
       </c>
-      <c r="P19" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4063,14 +7137,8 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="P20" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4087,14 +7155,8 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="P21" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4114,14 +7176,8 @@
         <f t="shared" si="0"/>
         <v>0.10091743119266056</v>
       </c>
-      <c r="P22" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4147,14 +7203,8 @@
         <f t="shared" si="0"/>
         <v>0.16036505867014342</v>
       </c>
-      <c r="P23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4177,14 +7227,8 @@
         <f t="shared" si="0"/>
         <v>0.13476473275468251</v>
       </c>
-      <c r="P24" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4213,14 +7257,8 @@
       <c r="K25">
         <v>320</v>
       </c>
-      <c r="P25" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4237,14 +7275,8 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="P26" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4267,14 +7299,8 @@
       <c r="K27">
         <v>348</v>
       </c>
-      <c r="P27" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4299,14 +7325,8 @@
       <c r="K28">
         <v>960</v>
       </c>
-      <c r="P28" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4325,14 +7345,8 @@
       <c r="G29">
         <v>1388</v>
       </c>
-      <c r="P29" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4348,14 +7362,8 @@
       <c r="G30">
         <v>1450</v>
       </c>
-      <c r="P30" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4371,14 +7379,8 @@
       <c r="F31">
         <v>1280</v>
       </c>
-      <c r="P31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4394,14 +7396,8 @@
       <c r="F32">
         <v>3900</v>
       </c>
-      <c r="P32" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4420,14 +7416,8 @@
       <c r="G33">
         <v>3000</v>
       </c>
-      <c r="P33" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4440,14 +7430,8 @@
       <c r="E34">
         <v>2779</v>
       </c>
-      <c r="P34" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4460,14 +7444,8 @@
       <c r="E35">
         <v>2306</v>
       </c>
-      <c r="P35" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4483,14 +7461,8 @@
       <c r="F36">
         <v>1860</v>
       </c>
-      <c r="P36" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4509,14 +7481,8 @@
       <c r="G37">
         <v>322</v>
       </c>
-      <c r="P37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4535,14 +7501,8 @@
       <c r="G38">
         <v>76</v>
       </c>
-      <c r="P38" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4558,14 +7518,8 @@
       <c r="F39">
         <v>5600</v>
       </c>
-      <c r="P39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4578,14 +7532,8 @@
       <c r="E40">
         <v>141</v>
       </c>
-      <c r="P40" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4598,14 +7546,8 @@
       <c r="E41">
         <v>2743</v>
       </c>
-      <c r="P41" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4624,14 +7566,8 @@
       <c r="G42">
         <v>265</v>
       </c>
-      <c r="P42" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4650,14 +7586,8 @@
       <c r="G43">
         <v>1940</v>
       </c>
-      <c r="P43" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4670,14 +7600,8 @@
       <c r="E44">
         <v>3171</v>
       </c>
-      <c r="P44" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4690,14 +7614,8 @@
       <c r="E45">
         <v>1860</v>
       </c>
-      <c r="P45" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4710,14 +7628,8 @@
       <c r="E46">
         <v>7625</v>
       </c>
-      <c r="P46" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4730,14 +7642,8 @@
       <c r="F47">
         <v>217</v>
       </c>
-      <c r="P47" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4750,14 +7656,8 @@
       <c r="F48">
         <v>125</v>
       </c>
-      <c r="P48" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4770,14 +7670,8 @@
       <c r="F49">
         <v>1765</v>
       </c>
-      <c r="P49" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4799,14 +7693,8 @@
       <c r="K50">
         <v>218</v>
       </c>
-      <c r="P50" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4825,14 +7713,8 @@
       <c r="G51">
         <v>76</v>
       </c>
-      <c r="P51" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4851,14 +7733,8 @@
       <c r="G52">
         <v>1820</v>
       </c>
-      <c r="P52" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4871,14 +7747,8 @@
       <c r="E53">
         <v>1079</v>
       </c>
-      <c r="P53" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4894,14 +7764,8 @@
       <c r="F54">
         <v>1900</v>
       </c>
-      <c r="P54" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4914,14 +7778,8 @@
       <c r="E55">
         <v>374</v>
       </c>
-      <c r="P55" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4934,14 +7792,8 @@
       <c r="E56">
         <v>1520</v>
       </c>
-      <c r="P56" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4961,14 +7813,8 @@
         <v>204</v>
       </c>
       <c r="J57" s="1"/>
-      <c r="P57" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4993,14 +7839,8 @@
       <c r="K58">
         <v>156.6</v>
       </c>
-      <c r="P58" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5016,14 +7856,8 @@
       <c r="F59">
         <v>510</v>
       </c>
-      <c r="P59" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5042,14 +7876,8 @@
       <c r="K60">
         <v>2450</v>
       </c>
-      <c r="P60" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5062,14 +7890,8 @@
       <c r="E61">
         <v>59</v>
       </c>
-      <c r="P61" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5082,14 +7904,8 @@
       <c r="E62">
         <v>1026</v>
       </c>
-      <c r="P62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5102,14 +7918,8 @@
       <c r="E63">
         <v>420</v>
       </c>
-      <c r="P63" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5128,14 +7938,8 @@
       <c r="G64">
         <v>930</v>
       </c>
-      <c r="P64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5154,14 +7958,8 @@
       <c r="G65">
         <v>3415</v>
       </c>
-      <c r="P65" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5177,14 +7975,8 @@
       <c r="F66">
         <v>400</v>
       </c>
-      <c r="P66" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5200,14 +7992,8 @@
       <c r="F67">
         <v>8450</v>
       </c>
-      <c r="P67" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5220,14 +8006,8 @@
       <c r="E68">
         <v>406</v>
       </c>
-      <c r="P68" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5240,14 +8020,8 @@
       <c r="E69">
         <v>1446</v>
       </c>
-      <c r="P69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5266,14 +8040,8 @@
       <c r="G70">
         <v>2845</v>
       </c>
-      <c r="P70" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5286,14 +8054,8 @@
       <c r="I71" s="3">
         <v>0.09</v>
       </c>
-      <c r="P71" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5312,14 +8074,8 @@
       <c r="G72">
         <v>3415</v>
       </c>
-      <c r="P72" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5341,14 +8097,8 @@
       <c r="J73" s="1">
         <v>46195</v>
       </c>
-      <c r="P73" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5367,14 +8117,8 @@
       <c r="I74" s="3">
         <v>0.05</v>
       </c>
-      <c r="P74" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5387,14 +8131,8 @@
       <c r="E75">
         <v>1889</v>
       </c>
-      <c r="P75" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5407,14 +8145,8 @@
       <c r="E76">
         <v>264</v>
       </c>
-      <c r="P76" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5427,14 +8159,8 @@
       <c r="E77">
         <v>376</v>
       </c>
-      <c r="P77" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5453,14 +8179,8 @@
       <c r="G78">
         <v>1340</v>
       </c>
-      <c r="P78" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5485,14 +8205,8 @@
       <c r="K79">
         <v>1485</v>
       </c>
-      <c r="P79" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5505,14 +8219,8 @@
       <c r="E80">
         <v>2103</v>
       </c>
-      <c r="P80" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5525,14 +8233,8 @@
       <c r="E81">
         <v>484</v>
       </c>
-      <c r="P81" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5551,14 +8253,8 @@
       <c r="I82" s="3">
         <v>0.16</v>
       </c>
-      <c r="P82" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5580,14 +8276,8 @@
       <c r="K83">
         <v>1430</v>
       </c>
-      <c r="P83" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5606,14 +8296,8 @@
       <c r="G84">
         <v>3415</v>
       </c>
-      <c r="P84" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5629,14 +8313,8 @@
       <c r="F85">
         <v>540</v>
       </c>
-      <c r="P85" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5655,14 +8333,8 @@
       <c r="G86">
         <v>11400</v>
       </c>
-      <c r="P86" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5681,14 +8353,8 @@
       <c r="M87">
         <v>12</v>
       </c>
-      <c r="P87" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5701,14 +8367,8 @@
       <c r="E88">
         <v>3891</v>
       </c>
-      <c r="P88" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5721,14 +8381,8 @@
       <c r="E89">
         <v>346</v>
       </c>
-      <c r="P89" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5747,14 +8401,8 @@
       <c r="G90">
         <v>1080</v>
       </c>
-      <c r="P90" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5773,14 +8421,8 @@
       <c r="G91">
         <v>197</v>
       </c>
-      <c r="P91" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5799,14 +8441,8 @@
       <c r="G92">
         <v>3415</v>
       </c>
-      <c r="P92" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5819,14 +8455,8 @@
       <c r="E93">
         <v>2123</v>
       </c>
-      <c r="P93" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5845,14 +8475,8 @@
       <c r="H94">
         <v>1033</v>
       </c>
-      <c r="P94" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5865,14 +8489,8 @@
       <c r="E95">
         <v>413</v>
       </c>
-      <c r="P95" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5891,14 +8509,8 @@
       <c r="G96">
         <v>1350</v>
       </c>
-      <c r="P96" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5917,14 +8529,8 @@
       <c r="G97">
         <v>1380</v>
       </c>
-      <c r="P97" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5937,14 +8543,8 @@
       <c r="E98">
         <v>13735</v>
       </c>
-      <c r="P98" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q98">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5958,7 +8558,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5975,7 +8575,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5992,7 +8592,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6012,7 +8612,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6032,7 +8632,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6049,7 +8649,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6063,7 +8663,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6077,7 +8677,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6097,7 +8697,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6114,7 +8714,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6131,7 +8731,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6145,7 +8745,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6159,7 +8759,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6448,7 +9048,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D129" s="1">
         <v>46211</v>
@@ -6479,7 +9079,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D131" s="1">
         <v>46211</v>
@@ -6496,7 +9096,7 @@
         <v>42</v>
       </c>
       <c r="C132" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D132" s="1">
         <v>46211</v>
@@ -6533,7 +9133,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D134" s="1">
         <v>46212</v>
@@ -6550,7 +9150,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D135" s="1">
         <v>46212</v>
@@ -6564,10 +9164,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D136" s="1">
         <v>46212</v>
@@ -6590,7 +9190,7 @@
         <v>42</v>
       </c>
       <c r="C137" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D137" s="1">
         <v>46213</v>
@@ -6613,7 +9213,7 @@
         <v>67</v>
       </c>
       <c r="C138" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D138" s="1">
         <v>46213</v>
@@ -6633,7 +9233,7 @@
         <v>89</v>
       </c>
       <c r="C139" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D139" s="1">
         <v>46213</v>
@@ -6653,7 +9253,7 @@
         <v>33</v>
       </c>
       <c r="C140" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D140" s="1">
         <v>46213</v>
@@ -6667,7 +9267,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D141" s="1">
         <v>46213</v>
@@ -6681,10 +9281,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C142" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D142" s="1">
         <v>46213</v>
@@ -6704,10 +9304,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C143" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D143" s="1">
         <v>46216</v>
@@ -6727,10 +9327,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C144" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D144" s="1">
         <v>46216</v>
@@ -6741,7 +9341,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D145" s="1">
         <v>46216</v>
@@ -6752,7 +9352,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D146" s="1">
         <v>46216</v>
@@ -6769,7 +9369,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D147" s="1">
         <v>46216</v>
@@ -6789,7 +9389,7 @@
         <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D148" s="1">
         <v>46216</v>
@@ -6809,7 +9409,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D149" s="1">
         <v>46217</v>
@@ -6829,10 +9429,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
+        <v>136</v>
+      </c>
+      <c r="C150" t="s">
         <v>137</v>
-      </c>
-      <c r="C150" t="s">
-        <v>138</v>
       </c>
       <c r="D150" s="1">
         <v>46217</v>
@@ -6846,7 +9446,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D151" s="1">
         <v>46217</v>
@@ -6860,7 +9460,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D152" s="1">
         <v>46217</v>
@@ -6877,7 +9477,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D153" s="1">
         <v>46217</v>
@@ -6894,10 +9494,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C154" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D154" s="1">
         <v>46218</v>
@@ -6914,10 +9514,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
+        <v>142</v>
+      </c>
+      <c r="C155" t="s">
         <v>143</v>
-      </c>
-      <c r="C155" t="s">
-        <v>144</v>
       </c>
       <c r="D155" s="1">
         <v>46218</v>
@@ -6934,10 +9534,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
+        <v>144</v>
+      </c>
+      <c r="C156" t="s">
         <v>145</v>
-      </c>
-      <c r="C156" t="s">
-        <v>146</v>
       </c>
       <c r="D156" s="1">
         <v>46218</v>
@@ -6951,10 +9551,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C157" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D157" s="1">
         <v>46218</v>
@@ -6968,10 +9568,10 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C158" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D158" s="1">
         <v>46218</v>
@@ -6988,10 +9588,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D159" s="1">
         <v>46219</v>
@@ -7011,10 +9611,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C160" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D160" s="1">
         <v>46219</v>
@@ -7028,10 +9628,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C161" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D161" s="1">
         <v>46219</v>
@@ -7045,10 +9645,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C162" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D162" s="1">
         <v>46219</v>
@@ -7068,7 +9668,7 @@
         <v>61</v>
       </c>
       <c r="C163" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D163" s="1">
         <v>46219</v>
@@ -7088,7 +9688,7 @@
         <v>115</v>
       </c>
       <c r="C164" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D164" s="1">
         <v>46219</v>
@@ -7108,7 +9708,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D165" s="1">
         <v>46220</v>
@@ -7125,7 +9725,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D166" s="1">
         <v>46220</v>
@@ -7142,7 +9742,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D167" s="1">
         <v>46220</v>
@@ -7159,7 +9759,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D168" s="1">
         <v>46220</v>
@@ -7170,7 +9770,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D169" s="1">
         <v>46220</v>
@@ -7181,7 +9781,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D170" s="1">
         <v>46220</v>
@@ -7201,10 +9801,10 @@
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C171" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D171" s="1">
         <v>46223</v>
@@ -7224,7 +9824,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D172" s="1">
         <v>46223</v>
@@ -7238,7 +9838,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D173" s="1">
         <v>46223</v>
@@ -7252,13 +9852,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D174" s="1">
         <v>46223</v>
       </c>
       <c r="E174">
-        <v>14444</v>
+        <v>1444</v>
       </c>
       <c r="F174">
         <v>1750</v>
@@ -7269,7 +9869,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D175" s="1">
         <v>46223</v>
@@ -7286,7 +9886,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D176" s="1">
         <v>46223</v>
@@ -7303,10 +9903,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C177" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D177" s="1">
         <v>46223</v>
@@ -7326,7 +9926,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D178" s="1">
         <v>46224</v>
@@ -7340,7 +9940,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D179" s="1">
         <v>46224</v>
@@ -7357,7 +9957,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D180" s="1">
         <v>46224</v>
@@ -7377,7 +9977,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D181" s="1">
         <v>46224</v>
@@ -7388,7 +9988,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D182" s="1">
         <v>46224</v>
@@ -7399,7 +9999,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D183" s="1">
         <v>46225</v>
@@ -7416,7 +10016,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D184" s="1">
         <v>46225</v>
@@ -7433,7 +10033,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D185" s="1">
         <v>46225</v>
@@ -7464,7 +10064,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D187" s="1">
         <v>46225</v>
@@ -7475,7 +10075,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D188" s="1">
         <v>46225</v>
@@ -7495,7 +10095,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D189" s="1">
         <v>46226</v>
@@ -7509,10 +10109,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C190" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D190" s="1">
         <v>46226</v>
@@ -7532,7 +10132,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D191" s="1">
         <v>46226</v>
@@ -7546,10 +10146,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>175</v>
+      </c>
+      <c r="C192" t="s">
         <v>176</v>
-      </c>
-      <c r="C192" t="s">
-        <v>177</v>
       </c>
       <c r="D192" s="1">
         <v>46226</v>
@@ -7563,10 +10163,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C193" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D193" s="1">
         <v>46226</v>
@@ -7583,7 +10183,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D194" s="1">
         <v>46227</v>
@@ -7597,7 +10197,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D195" s="1">
         <v>46227</v>
@@ -7611,7 +10211,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D196" s="1">
         <v>46227</v>
@@ -7648,7 +10248,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D198" s="1">
         <v>46227</v>
@@ -7668,7 +10268,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D199" s="1">
         <v>46227</v>
@@ -7699,7 +10299,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D201" s="1">
         <v>46230</v>
@@ -7719,10 +10319,10 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C202" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D202" s="1">
         <v>46230</v>
@@ -7736,7 +10336,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D203" s="1">
         <v>46230</v>
@@ -7789,16 +10389,22 @@
       <c r="B206" t="s">
         <v>116</v>
       </c>
+      <c r="D206" s="1">
+        <v>46231</v>
+      </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
-      <c r="B207" t="s">
-        <v>185</v>
+      <c r="B207" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="C207" t="s">
-        <v>124</v>
+        <v>123</v>
+      </c>
+      <c r="D207" s="1">
+        <v>46231</v>
       </c>
       <c r="E207">
         <v>572</v>
@@ -7815,10 +10421,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C208" t="s">
-        <v>133</v>
+        <v>132</v>
+      </c>
+      <c r="D208" s="1">
+        <v>46231</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
@@ -7826,7 +10435,10 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>179</v>
+        <v>178</v>
+      </c>
+      <c r="D209" s="1">
+        <v>46231</v>
       </c>
       <c r="E209">
         <v>185</v>
@@ -7842,16 +10454,22 @@
       <c r="B210" t="s">
         <v>105</v>
       </c>
+      <c r="D210" s="1">
+        <v>46231</v>
+      </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C211" t="s">
-        <v>177</v>
+        <v>176</v>
+      </c>
+      <c r="D211" s="1">
+        <v>46231</v>
       </c>
       <c r="E211">
         <v>1199</v>
@@ -7868,7 +10486,10 @@
         <v>115</v>
       </c>
       <c r="C212" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="D212" s="1">
+        <v>46231</v>
       </c>
       <c r="E212">
         <v>1132</v>
@@ -7885,7 +10506,10 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>187</v>
+        <v>186</v>
+      </c>
+      <c r="D213" s="1">
+        <v>46231</v>
       </c>
       <c r="E213">
         <v>525</v>
@@ -7904,6 +10528,9 @@
       <c r="B214" t="s">
         <v>106</v>
       </c>
+      <c r="D214" s="1">
+        <v>46231</v>
+      </c>
       <c r="E214">
         <v>1220</v>
       </c>
@@ -7918,128 +10545,350 @@
       <c r="A215">
         <v>214</v>
       </c>
+      <c r="B215" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C215" t="s">
+        <v>123</v>
+      </c>
+      <c r="D215" s="1">
+        <v>46232</v>
+      </c>
+      <c r="E215">
+        <v>3994</v>
+      </c>
+      <c r="F215">
+        <v>3850</v>
+      </c>
+      <c r="G215">
+        <v>4250</v>
+      </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
+      <c r="B216" t="s">
+        <v>192</v>
+      </c>
+      <c r="C216" t="s">
+        <v>132</v>
+      </c>
+      <c r="D216" s="1">
+        <v>46232</v>
+      </c>
+      <c r="E216">
+        <v>7425</v>
+      </c>
+      <c r="G216">
+        <v>7300</v>
+      </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
+      <c r="B217" t="s">
+        <v>42</v>
+      </c>
+      <c r="C217" t="s">
+        <v>132</v>
+      </c>
+      <c r="D217" s="1">
+        <v>46232</v>
+      </c>
+      <c r="E217">
+        <v>330</v>
+      </c>
+      <c r="G217">
+        <v>315</v>
+      </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
+      <c r="B218" t="s">
+        <v>193</v>
+      </c>
+      <c r="C218" t="s">
+        <v>194</v>
+      </c>
+      <c r="D218" s="1">
+        <v>46232</v>
+      </c>
+      <c r="E218">
+        <v>3833</v>
+      </c>
+      <c r="F218">
+        <v>4550</v>
+      </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
+      <c r="B219" t="s">
+        <v>195</v>
+      </c>
+      <c r="C219" t="s">
+        <v>194</v>
+      </c>
+      <c r="D219" s="1">
+        <v>46232</v>
+      </c>
+      <c r="E219">
+        <v>1753</v>
+      </c>
+      <c r="F219">
+        <v>2140</v>
+      </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
+      <c r="B220" t="s">
+        <v>84</v>
+      </c>
+      <c r="C220" t="s">
+        <v>124</v>
+      </c>
+      <c r="D220" s="1">
+        <v>46232</v>
+      </c>
+      <c r="E220">
+        <v>4327</v>
+      </c>
+      <c r="F220">
+        <v>5250</v>
+      </c>
+      <c r="G220">
+        <v>3870</v>
+      </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
+      <c r="B221" t="s">
+        <v>84</v>
+      </c>
+      <c r="C221" t="s">
+        <v>124</v>
+      </c>
+      <c r="D221" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E221">
+        <v>4327</v>
+      </c>
+      <c r="F221">
+        <v>5250</v>
+      </c>
+      <c r="G221">
+        <v>3870</v>
+      </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
+      <c r="B222" t="s">
+        <v>37</v>
+      </c>
+      <c r="C222" t="s">
+        <v>194</v>
+      </c>
+      <c r="D222" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E222">
+        <v>1343</v>
+      </c>
+      <c r="F222">
+        <v>1630</v>
+      </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
+      <c r="B223" t="s">
+        <v>21</v>
+      </c>
+      <c r="C223" t="s">
+        <v>194</v>
+      </c>
+      <c r="D223" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E223">
+        <v>1523</v>
+      </c>
+      <c r="F223">
+        <v>1765</v>
+      </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B224" t="s">
+        <v>62</v>
+      </c>
+      <c r="C224" t="s">
+        <v>197</v>
+      </c>
+      <c r="D224" s="1">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B225" t="s">
+        <v>196</v>
+      </c>
+      <c r="C225" t="s">
+        <v>197</v>
+      </c>
+      <c r="D225" s="1">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B226" t="s">
+        <v>193</v>
+      </c>
+      <c r="C226" t="s">
+        <v>197</v>
+      </c>
+      <c r="D226" s="1">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B227" t="s">
+        <v>98</v>
+      </c>
+      <c r="D227" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E227">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B228" t="s">
+        <v>138</v>
+      </c>
+      <c r="D228" s="1">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B229" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C229" t="s">
+        <v>123</v>
+      </c>
+      <c r="D229" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E229">
+        <v>1630</v>
+      </c>
+      <c r="F229">
+        <v>1750</v>
+      </c>
+      <c r="G229">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B230" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C230" t="s">
+        <v>199</v>
+      </c>
+      <c r="D230" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E230">
+        <v>1871</v>
+      </c>
+      <c r="F230">
+        <v>2176</v>
+      </c>
+      <c r="G230">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
@@ -8082,11 +10931,11 @@
   </sheetData>
   <autoFilter ref="A1:L247" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D732E0AF-64C8-4124-A0D7-87EDC5F828BC}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA24CAC-91B9-40D8-82A7-7925B28A1432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287AC331-242A-4770-8250-CE15396CE869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-150" yWindow="0" windowWidth="7130" windowHeight="10170" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="223">
   <si>
     <t>S No.</t>
   </si>
@@ -683,6 +683,39 @@
   </si>
   <si>
     <t>BPCL</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>APOLLO HOSPITALS</t>
+  </si>
+  <si>
+    <t>BSE</t>
+  </si>
+  <si>
+    <t>HEG</t>
+  </si>
+  <si>
+    <t>JTL</t>
+  </si>
+  <si>
+    <t>EXIDE INDUSTRIES</t>
+  </si>
+  <si>
+    <t>PEARL GLOBAL INDUSTRIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRATECH CEMENT </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>360 ONE WAM LTD</t>
+  </si>
+  <si>
+    <t>JSW STEEL LTD</t>
   </si>
 </sst>
 </file>
@@ -744,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -756,6 +789,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7698,7 +7732,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <dimension ref="A1:Q247"/>
+  <dimension ref="A1:Q260"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -12946,6 +12980,245 @@
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>212</v>
+      </c>
+      <c r="D247" s="1">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>213</v>
+      </c>
+      <c r="D248" s="1">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>71</v>
+      </c>
+      <c r="D249" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E249">
+        <v>1020</v>
+      </c>
+      <c r="F249">
+        <v>1070</v>
+      </c>
+      <c r="G249">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>100</v>
+      </c>
+      <c r="D250" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E250">
+        <v>875</v>
+      </c>
+      <c r="F250">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>214</v>
+      </c>
+      <c r="D251" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E251">
+        <v>3618</v>
+      </c>
+      <c r="F251">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>17</v>
+      </c>
+      <c r="D252" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E252">
+        <v>143.56</v>
+      </c>
+      <c r="F252">
+        <v>149.97</v>
+      </c>
+      <c r="G252">
+        <v>140.4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>215</v>
+      </c>
+      <c r="D253" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E253">
+        <v>689.1</v>
+      </c>
+      <c r="F253">
+        <v>738.2</v>
+      </c>
+      <c r="G253">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>216</v>
+      </c>
+      <c r="D254" s="1">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>217</v>
+      </c>
+      <c r="C255" t="s">
+        <v>124</v>
+      </c>
+      <c r="D255" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E255">
+        <v>453</v>
+      </c>
+      <c r="F255">
+        <v>520</v>
+      </c>
+      <c r="G255">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>71</v>
+      </c>
+      <c r="C256" t="s">
+        <v>191</v>
+      </c>
+      <c r="D256" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E256">
+        <v>1040</v>
+      </c>
+      <c r="F256">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>218</v>
+      </c>
+      <c r="C257" t="s">
+        <v>191</v>
+      </c>
+      <c r="D257" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E257">
+        <v>2105</v>
+      </c>
+      <c r="F257">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>219</v>
+      </c>
+      <c r="C258" t="s">
+        <v>220</v>
+      </c>
+      <c r="D258" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E258" s="9">
+        <v>12190</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>221</v>
+      </c>
+      <c r="D259" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E259">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>222</v>
+      </c>
+      <c r="C260" t="s">
+        <v>123</v>
+      </c>
+      <c r="D260" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E260">
+        <v>1330</v>
+      </c>
+      <c r="F260">
+        <v>1420</v>
+      </c>
+      <c r="G260">
+        <v>1285</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287AC331-242A-4770-8250-CE15396CE869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375079ED-BC58-4425-BC6A-4FB55569AA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Buy Sell" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$260</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -7732,6 +7732,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q260"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7792,7 +7793,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7819,7 +7820,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7840,7 +7841,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7864,7 +7865,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7891,7 +7892,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7912,7 +7913,7 @@
         <v>0.12225811936745451</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7942,7 +7943,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7963,7 +7964,7 @@
         <v>0.3200118345888619</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7984,7 +7985,7 @@
         <v>0.23999948467553878</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -8005,7 +8006,7 @@
         <v>0.20000331035395966</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8026,7 +8027,7 @@
         <v>0.18000429092469422</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -8047,7 +8048,7 @@
         <v>0.15999843324886945</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -8068,7 +8069,7 @@
         <v>0.11471160077770577</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -8086,7 +8087,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8107,7 +8108,7 @@
         <v>0.27027027027027029</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -8128,7 +8129,7 @@
         <v>0.14974761637689288</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8152,7 +8153,7 @@
         <v>0.16036505867014342</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8170,7 +8171,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8194,7 +8195,7 @@
         <v>8.0074487895716945E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8212,7 +8213,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8230,7 +8231,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8251,7 +8252,7 @@
         <v>0.10091743119266056</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8278,7 +8279,7 @@
         <v>0.16036505867014342</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8302,7 +8303,7 @@
         <v>0.13476473275468251</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8332,7 +8333,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8350,7 +8351,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8374,7 +8375,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8404,7 +8405,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8428,7 +8429,7 @@
         <v>7.7885952712100137E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8449,7 +8450,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8470,7 +8471,7 @@
         <v>0.23195380173243504</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8491,7 +8492,7 @@
         <v>0.24006359300476948</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8515,7 +8516,7 @@
         <v>5.8595014567821305E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8533,7 +8534,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8551,7 +8552,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8572,7 +8573,7 @@
         <v>0.23178807947019867</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -8596,7 +8597,7 @@
         <v>0.15384615384615385</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -8620,7 +8621,7 @@
         <v>0.22093023255813954</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8641,7 +8642,7 @@
         <v>0.18895966029723993</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -8659,7 +8660,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -8677,7 +8678,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -8701,7 +8702,7 @@
         <v>6.5217391304347824E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8725,7 +8726,7 @@
         <v>8.9108910891089105E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8743,7 +8744,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8761,7 +8762,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8779,7 +8780,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8797,7 +8798,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8815,7 +8816,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8833,7 +8834,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8857,7 +8858,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8881,7 +8882,7 @@
         <v>0.22093023255813954</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8905,7 +8906,7 @@
         <v>0.13671274961597543</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8923,7 +8924,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8944,7 +8945,7 @@
         <v>0.29692832764505117</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8962,7 +8963,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8980,7 +8981,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -9005,7 +9006,7 @@
       </c>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -9035,7 +9036,7 @@
         <v>156.6</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -9056,7 +9057,7 @@
         <v>0.21718377088305491</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -9080,7 +9081,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -9098,7 +9099,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -9116,7 +9117,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9134,7 +9135,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9158,7 +9159,7 @@
         <v>6.458333333333334E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9182,7 +9183,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9203,7 +9204,7 @@
         <v>0.13314447592067988</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9224,7 +9225,7 @@
         <v>6.0891399874450719E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9242,7 +9243,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9260,7 +9261,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9284,7 +9285,7 @@
         <v>7.2021241287753071E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9299,7 +9300,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9323,7 +9324,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9347,7 +9348,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -9368,7 +9369,7 @@
         <v>0.39423076923076922</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -9386,7 +9387,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -9404,7 +9405,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -9422,7 +9423,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -9446,7 +9447,7 @@
         <v>0.1040339702760085</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -9476,7 +9477,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -9494,7 +9495,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -9533,7 +9534,7 @@
         <v>0.15683229813664595</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9557,7 +9558,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9581,7 +9582,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9602,7 +9603,7 @@
         <v>0.1894273127753304</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9626,7 +9627,7 @@
         <v>0.20707349806584038</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -9650,7 +9651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -9668,7 +9669,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -9686,7 +9687,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -9710,7 +9711,7 @@
         <v>6.5647482014388484E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9734,7 +9735,7 @@
         <v>2.5125628140703519E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9758,7 +9759,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -9776,7 +9777,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9800,7 +9801,7 @@
         <v>0.15309126594700687</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -9818,7 +9819,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -9842,7 +9843,7 @@
         <v>4.1184971098265896E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9866,7 +9867,7 @@
         <v>7.903780068728522E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -9902,7 +9903,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -9923,7 +9924,7 @@
         <v>0.23476848090982941</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -9944,7 +9945,7 @@
         <v>0.21739130434782608</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -9968,7 +9969,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -9992,7 +9993,7 @@
         <v>0.15200764818355642</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10013,7 +10014,7 @@
         <v>0.12658746415403524</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10031,7 +10032,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10049,7 +10050,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10073,7 +10074,7 @@
         <v>4.7968885047536734E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10094,7 +10095,7 @@
         <v>0.38968481375358166</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10115,7 +10116,7 @@
         <v>0.18429807052561545</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10133,7 +10134,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10151,7 +10152,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10175,7 +10176,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10199,7 +10200,7 @@
         <v>0.12322946175637393</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -10217,7 +10218,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10238,7 +10239,7 @@
         <v>0.10981308411214953</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10256,7 +10257,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10274,7 +10275,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -10298,7 +10299,7 @@
         <v>7.1732199787460149E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10319,7 +10320,7 @@
         <v>0.22553191489361701</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -10343,7 +10344,7 @@
         <v>0.11678832116788321</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -10361,7 +10362,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -10379,7 +10380,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -10400,7 +10401,7 @@
         <v>0.17082961641391614</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -10418,7 +10419,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -10436,7 +10437,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -10460,7 +10461,7 @@
         <v>4.793028322440087E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -10485,7 +10486,7 @@
         <v>7.2664359861591699E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -10503,7 +10504,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -10521,7 +10522,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10542,7 +10543,7 @@
         <v>0.17924528301886791</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10560,7 +10561,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10587,7 +10588,7 @@
         <v>0.16719242902208201</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10608,7 +10609,7 @@
         <v>0.30120481927710846</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -10629,7 +10630,7 @@
         <v>0.24204946996466431</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -10647,7 +10648,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10674,7 +10675,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -10701,7 +10702,7 @@
         <v>0.16719242902208201</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -10725,7 +10726,7 @@
         <v>0.14329268292682926</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -10749,7 +10750,7 @@
         <v>0.19462788454403798</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -10770,7 +10771,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -10788,7 +10789,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -10815,7 +10816,7 @@
         <v>8.3406240886555849E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -10842,7 +10843,7 @@
         <v>6.2194269741439552E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -10860,7 +10861,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -10875,7 +10876,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -10896,7 +10897,7 @@
         <v>0.15264797507788161</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -10917,7 +10918,7 @@
         <v>0.17680826636050517</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -10944,7 +10945,7 @@
         <v>0.15200764818355642</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -10968,7 +10969,7 @@
         <v>9.2105263157894732E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -10989,7 +10990,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -11007,7 +11008,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -11028,7 +11029,7 @@
         <v>0.18527760449157829</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -11049,7 +11050,7 @@
         <v>0.18755118755118755</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -11073,7 +11074,7 @@
         <v>0.19047619047619047</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -11097,7 +11098,7 @@
         <v>0.25835189309576839</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -11118,7 +11119,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -11139,7 +11140,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -11163,7 +11164,7 @@
         <v>-2.717391304347826E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -11190,7 +11191,7 @@
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -11211,7 +11212,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -11232,7 +11233,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -11256,7 +11257,7 @@
         <v>0.2707641196013289</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -11280,7 +11281,7 @@
         <v>0.15740740740740741</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -11307,7 +11308,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -11328,7 +11329,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -11349,7 +11350,7 @@
         <v>0.25827814569536423</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -11370,7 +11371,7 @@
         <v>0.19908466819221968</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -11385,7 +11386,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -11400,7 +11401,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -11424,7 +11425,7 @@
         <v>7.586206896551724E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -11451,7 +11452,7 @@
         <v>9.1954022988505746E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -11469,7 +11470,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -11487,7 +11488,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -11508,7 +11509,7 @@
         <v>0.21191135734072022</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -11529,7 +11530,7 @@
         <v>0.1883589329021827</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -11550,7 +11551,7 @@
         <v>0.12322946175637393</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -11577,7 +11578,7 @@
         <v>8.7367178276269192E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -11595,7 +11596,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -11616,7 +11617,7 @@
         <v>0.21374865735767992</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11640,7 +11641,7 @@
         <v>8.4905660377358486E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11655,7 +11656,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -11670,7 +11671,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -11691,7 +11692,7 @@
         <v>0.2841091492776886</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -11712,7 +11713,7 @@
         <v>0.16262975778546712</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -11736,7 +11737,7 @@
         <v>2.9463116542994324E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -11751,7 +11752,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -11766,7 +11767,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -11790,7 +11791,7 @@
         <v>-2.077151335311566E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -11808,7 +11809,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -11835,7 +11836,7 @@
         <v>7.0950468540829981E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -11853,7 +11854,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -11874,7 +11875,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -11898,7 +11899,7 @@
         <v>0.20209059233449478</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -11916,7 +11917,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -11934,7 +11935,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -11958,7 +11959,7 @@
         <v>5.3869969040247677E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -11979,7 +11980,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -12003,7 +12004,7 @@
         <v>1.5414546542951144E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -12027,7 +12028,7 @@
         <v>1.4084507042253521E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -12042,7 +12043,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -12066,7 +12067,7 @@
         <v>6.1910619106191063E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -12087,7 +12088,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -12105,7 +12106,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -12126,7 +12127,7 @@
         <v>0.23672704559650218</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -12150,7 +12151,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -12165,7 +12166,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -12192,7 +12193,7 @@
         <v>7.5174825174825169E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -12210,7 +12211,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -12231,7 +12232,7 @@
         <v>0.29729729729729731</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12246,7 +12247,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12270,7 +12271,7 @@
         <v>0.19266055045871561</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12297,7 +12298,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12321,7 +12322,7 @@
         <v>2.0952380952380951E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12345,7 +12346,7 @@
         <v>3.4426229508196723E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12372,7 +12373,7 @@
         <v>-3.6054081121682527E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12396,7 +12397,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
@@ -12420,7 +12421,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12444,7 +12445,7 @@
         <v>0.18705974432559352</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12468,7 +12469,7 @@
         <v>0.22076440387906446</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12495,7 +12496,7 @@
         <v>0.2133117633464294</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12522,7 +12523,7 @@
         <v>0.2133117633464294</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
@@ -12546,7 +12547,7 @@
         <v>0.21370067014147431</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
@@ -12570,7 +12571,7 @@
         <v>0.15889691398555483</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
@@ -12588,7 +12589,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
@@ -12606,7 +12607,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
@@ -12624,7 +12625,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
@@ -12642,7 +12643,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
@@ -12657,7 +12658,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
@@ -12684,7 +12685,7 @@
         <v>7.3619631901840496E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
@@ -12711,7 +12712,7 @@
         <v>0.1630144307856761</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
@@ -12728,7 +12729,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
@@ -12739,7 +12740,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
@@ -12753,7 +12754,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
@@ -12767,7 +12768,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
@@ -12781,7 +12782,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
@@ -12801,7 +12802,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
@@ -12821,7 +12822,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
@@ -12835,7 +12836,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
@@ -12855,7 +12856,7 @@
         <v>294.8</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
@@ -12875,7 +12876,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
@@ -12895,7 +12896,7 @@
         <v>5450</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
@@ -12912,7 +12913,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
@@ -12929,7 +12930,7 @@
         <v>6610</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
@@ -12949,7 +12950,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
@@ -12963,7 +12964,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
@@ -12977,7 +12978,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
@@ -12988,7 +12989,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
@@ -12999,7 +13000,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
@@ -13019,7 +13020,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
@@ -13036,7 +13037,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13053,7 +13054,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
@@ -13073,7 +13074,7 @@
         <v>140.4</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
@@ -13093,7 +13094,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
@@ -13104,7 +13105,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>254</v>
       </c>
@@ -13127,7 +13128,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>255</v>
       </c>
@@ -13147,7 +13148,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>256</v>
       </c>
@@ -13167,7 +13168,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>257</v>
       </c>
@@ -13184,7 +13185,7 @@
         <v>12190</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>258</v>
       </c>
@@ -13198,7 +13199,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>259</v>
       </c>
@@ -13222,7 +13223,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L247" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
+  <autoFilter ref="A1:L260" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="MEDANTA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375079ED-BC58-4425-BC6A-4FB55569AA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D69A74-9C84-49BA-B7D7-9629245FA46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Buy Sell" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$259</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -46,8 +46,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="235">
   <si>
     <t>S No.</t>
   </si>
@@ -700,9 +722,6 @@
     <t>JTL</t>
   </si>
   <si>
-    <t>EXIDE INDUSTRIES</t>
-  </si>
-  <si>
     <t>PEARL GLOBAL INDUSTRIES</t>
   </si>
   <si>
@@ -716,6 +735,45 @@
   </si>
   <si>
     <t>JSW STEEL LTD</t>
+  </si>
+  <si>
+    <t>MOTHERSON</t>
+  </si>
+  <si>
+    <t>AU SMALL FINANCE BANK</t>
+  </si>
+  <si>
+    <t>JG CHEM</t>
+  </si>
+  <si>
+    <t>ANAND RATHI WEALTH</t>
+  </si>
+  <si>
+    <t>AEQUS</t>
+  </si>
+  <si>
+    <t>STATE BANK OF INDIA</t>
+  </si>
+  <si>
+    <t>WALCHANNAG</t>
+  </si>
+  <si>
+    <t>PIDILITE IND</t>
+  </si>
+  <si>
+    <t>technical delivery idea</t>
+  </si>
+  <si>
+    <t>JSW ENERGY</t>
+  </si>
+  <si>
+    <t>BRIGADE ENTERPRICE</t>
+  </si>
+  <si>
+    <t>FUSION FINANCE</t>
+  </si>
+  <si>
+    <t>SHAILY ENGINEERING PLASTICS</t>
   </si>
 </sst>
 </file>
@@ -7732,8 +7790,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q260"/>
+  <dimension ref="A1:Q281"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -7793,7 +7850,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7820,7 +7877,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7841,7 +7898,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7865,7 +7922,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7892,7 +7949,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7913,7 +7970,7 @@
         <v>0.12225811936745451</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7943,7 +8000,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7964,7 +8021,7 @@
         <v>0.3200118345888619</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7985,7 +8042,7 @@
         <v>0.23999948467553878</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -8006,7 +8063,7 @@
         <v>0.20000331035395966</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8027,7 +8084,7 @@
         <v>0.18000429092469422</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -8048,7 +8105,7 @@
         <v>0.15999843324886945</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -8069,7 +8126,7 @@
         <v>0.11471160077770577</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -8087,7 +8144,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8108,7 +8165,7 @@
         <v>0.27027027027027029</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -8129,7 +8186,7 @@
         <v>0.14974761637689288</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8153,7 +8210,7 @@
         <v>0.16036505867014342</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8171,7 +8228,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8195,7 +8252,7 @@
         <v>8.0074487895716945E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8213,7 +8270,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8231,7 +8288,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8252,7 +8309,7 @@
         <v>0.10091743119266056</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8279,7 +8336,7 @@
         <v>0.16036505867014342</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8303,7 +8360,7 @@
         <v>0.13476473275468251</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8333,7 +8390,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8351,7 +8408,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8375,7 +8432,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8405,7 +8462,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8429,7 +8486,7 @@
         <v>7.7885952712100137E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8450,7 +8507,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8471,7 +8528,7 @@
         <v>0.23195380173243504</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8492,7 +8549,7 @@
         <v>0.24006359300476948</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8516,7 +8573,7 @@
         <v>5.8595014567821305E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8534,7 +8591,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8552,7 +8609,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8573,7 +8630,7 @@
         <v>0.23178807947019867</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -8597,7 +8654,7 @@
         <v>0.15384615384615385</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -8621,7 +8678,7 @@
         <v>0.22093023255813954</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8642,7 +8699,7 @@
         <v>0.18895966029723993</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -8660,7 +8717,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -8678,7 +8735,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -8702,7 +8759,7 @@
         <v>6.5217391304347824E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8726,7 +8783,7 @@
         <v>8.9108910891089105E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8744,7 +8801,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8762,7 +8819,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8780,7 +8837,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8798,7 +8855,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8816,7 +8873,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8834,7 +8891,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8858,7 +8915,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8882,7 +8939,7 @@
         <v>0.22093023255813954</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8906,7 +8963,7 @@
         <v>0.13671274961597543</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8924,7 +8981,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8945,7 +9002,7 @@
         <v>0.29692832764505117</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8963,7 +9020,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8981,7 +9038,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -9006,7 +9063,7 @@
       </c>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -9036,7 +9093,7 @@
         <v>156.6</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -9057,7 +9114,7 @@
         <v>0.21718377088305491</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -9081,7 +9138,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -9099,7 +9156,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -9117,7 +9174,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9135,7 +9192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9159,7 +9216,7 @@
         <v>6.458333333333334E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9183,7 +9240,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9204,7 +9261,7 @@
         <v>0.13314447592067988</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9225,7 +9282,7 @@
         <v>6.0891399874450719E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9243,7 +9300,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9261,7 +9318,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9285,7 +9342,7 @@
         <v>7.2021241287753071E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9300,7 +9357,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9324,7 +9381,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9348,7 +9405,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -9369,7 +9426,7 @@
         <v>0.39423076923076922</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -9387,7 +9444,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -9405,7 +9462,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -9423,7 +9480,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -9447,7 +9504,7 @@
         <v>0.1040339702760085</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -9477,7 +9534,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -9495,7 +9552,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -9534,7 +9591,7 @@
         <v>0.15683229813664595</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9558,7 +9615,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9582,7 +9639,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9603,7 +9660,7 @@
         <v>0.1894273127753304</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9627,7 +9684,7 @@
         <v>0.20707349806584038</v>
       </c>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -9651,7 +9708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -9669,7 +9726,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -9687,7 +9744,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -9711,7 +9768,7 @@
         <v>6.5647482014388484E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9735,7 +9792,7 @@
         <v>2.5125628140703519E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9759,7 +9816,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -9777,7 +9834,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9801,7 +9858,7 @@
         <v>0.15309126594700687</v>
       </c>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -9819,7 +9876,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -9843,7 +9900,7 @@
         <v>4.1184971098265896E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9867,7 +9924,7 @@
         <v>7.903780068728522E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -9885,7 +9942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -9903,7 +9960,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -9924,7 +9981,7 @@
         <v>0.23476848090982941</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -9945,7 +10002,7 @@
         <v>0.21739130434782608</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -9969,7 +10026,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -9993,7 +10050,7 @@
         <v>0.15200764818355642</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10014,7 +10071,7 @@
         <v>0.12658746415403524</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10032,7 +10089,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10050,7 +10107,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10074,7 +10131,7 @@
         <v>4.7968885047536734E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10095,7 +10152,7 @@
         <v>0.38968481375358166</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10116,7 +10173,7 @@
         <v>0.18429807052561545</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10134,7 +10191,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10152,7 +10209,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10176,7 +10233,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10200,7 +10257,7 @@
         <v>0.12322946175637393</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -10218,7 +10275,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10239,7 +10296,7 @@
         <v>0.10981308411214953</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10257,7 +10314,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10275,7 +10332,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -10299,7 +10356,7 @@
         <v>7.1732199787460149E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10320,7 +10377,7 @@
         <v>0.22553191489361701</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -10344,7 +10401,7 @@
         <v>0.11678832116788321</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -10362,7 +10419,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -10380,7 +10437,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -10401,7 +10458,7 @@
         <v>0.17082961641391614</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -10419,7 +10476,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -10437,7 +10494,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -10461,7 +10518,7 @@
         <v>4.793028322440087E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -10486,7 +10543,7 @@
         <v>7.2664359861591699E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -10504,7 +10561,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -10522,7 +10579,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10543,7 +10600,7 @@
         <v>0.17924528301886791</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10561,7 +10618,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10588,7 +10645,7 @@
         <v>0.16719242902208201</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10609,7 +10666,7 @@
         <v>0.30120481927710846</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -10630,7 +10687,7 @@
         <v>0.24204946996466431</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -10648,7 +10705,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10675,7 +10732,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -10702,7 +10759,7 @@
         <v>0.16719242902208201</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -10726,7 +10783,7 @@
         <v>0.14329268292682926</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -10750,7 +10807,7 @@
         <v>0.19462788454403798</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -10771,7 +10828,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -10789,7 +10846,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -10816,7 +10873,7 @@
         <v>8.3406240886555849E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -10843,7 +10900,7 @@
         <v>6.2194269741439552E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -10861,7 +10918,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -10876,7 +10933,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -10897,7 +10954,7 @@
         <v>0.15264797507788161</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -10918,7 +10975,7 @@
         <v>0.17680826636050517</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -10945,7 +11002,7 @@
         <v>0.15200764818355642</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -10969,7 +11026,7 @@
         <v>9.2105263157894732E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -10990,7 +11047,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -11008,7 +11065,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -11029,7 +11086,7 @@
         <v>0.18527760449157829</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -11050,7 +11107,7 @@
         <v>0.18755118755118755</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -11074,7 +11131,7 @@
         <v>0.19047619047619047</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -11098,7 +11155,7 @@
         <v>0.25835189309576839</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -11119,7 +11176,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -11140,7 +11197,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -11164,7 +11221,7 @@
         <v>-2.717391304347826E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -11191,7 +11248,7 @@
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -11212,7 +11269,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -11233,7 +11290,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -11257,7 +11314,7 @@
         <v>0.2707641196013289</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -11281,7 +11338,7 @@
         <v>0.15740740740740741</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -11308,7 +11365,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -11329,7 +11386,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -11350,7 +11407,7 @@
         <v>0.25827814569536423</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -11371,7 +11428,7 @@
         <v>0.19908466819221968</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -11386,7 +11443,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -11401,7 +11458,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -11425,7 +11482,7 @@
         <v>7.586206896551724E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -11452,7 +11509,7 @@
         <v>9.1954022988505746E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -11470,7 +11527,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -11488,7 +11545,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -11509,7 +11566,7 @@
         <v>0.21191135734072022</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -11530,7 +11587,7 @@
         <v>0.1883589329021827</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -11551,7 +11608,7 @@
         <v>0.12322946175637393</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -11578,7 +11635,7 @@
         <v>8.7367178276269192E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -11596,7 +11653,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -11617,7 +11674,7 @@
         <v>0.21374865735767992</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11641,7 +11698,7 @@
         <v>8.4905660377358486E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11656,7 +11713,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -11671,7 +11728,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -11692,7 +11749,7 @@
         <v>0.2841091492776886</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -11713,7 +11770,7 @@
         <v>0.16262975778546712</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -11737,7 +11794,7 @@
         <v>2.9463116542994324E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -11752,7 +11809,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -11767,7 +11824,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -11791,7 +11848,7 @@
         <v>-2.077151335311566E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -11809,7 +11866,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -11836,7 +11893,7 @@
         <v>7.0950468540829981E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -11854,7 +11911,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -11875,7 +11932,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -11899,7 +11956,7 @@
         <v>0.20209059233449478</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -11917,7 +11974,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -11935,7 +11992,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -11959,7 +12016,7 @@
         <v>5.3869969040247677E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -11980,7 +12037,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -12004,7 +12061,7 @@
         <v>1.5414546542951144E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -12028,7 +12085,7 @@
         <v>1.4084507042253521E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -12043,7 +12100,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -12067,7 +12124,7 @@
         <v>6.1910619106191063E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -12088,7 +12145,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -12106,7 +12163,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -12127,7 +12184,7 @@
         <v>0.23672704559650218</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -12151,7 +12208,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -12166,7 +12223,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -12193,7 +12250,7 @@
         <v>7.5174825174825169E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -12211,7 +12268,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -12232,7 +12289,7 @@
         <v>0.29729729729729731</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12247,7 +12304,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12271,7 +12328,7 @@
         <v>0.19266055045871561</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12298,7 +12355,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12322,7 +12379,7 @@
         <v>2.0952380952380951E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12346,7 +12403,7 @@
         <v>3.4426229508196723E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12373,7 +12430,7 @@
         <v>-3.6054081121682527E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12397,7 +12454,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
@@ -12421,7 +12478,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12445,7 +12502,7 @@
         <v>0.18705974432559352</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12469,7 +12526,7 @@
         <v>0.22076440387906446</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12496,7 +12553,7 @@
         <v>0.2133117633464294</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12523,7 +12580,7 @@
         <v>0.2133117633464294</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
@@ -12547,7 +12604,7 @@
         <v>0.21370067014147431</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
@@ -12571,7 +12628,7 @@
         <v>0.15889691398555483</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
@@ -12589,7 +12646,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
@@ -12607,7 +12664,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
@@ -12625,7 +12682,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
@@ -12643,7 +12700,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
@@ -12658,7 +12715,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
@@ -12685,7 +12742,7 @@
         <v>7.3619631901840496E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
@@ -12712,12 +12769,12 @@
         <v>0.1630144307856761</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="D231" s="1">
         <v>46237</v>
@@ -12729,7 +12786,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
@@ -12740,7 +12797,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
@@ -12754,7 +12811,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
@@ -12768,7 +12825,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
@@ -12782,7 +12839,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
@@ -12802,12 +12859,13 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
-      <c r="B237" t="s">
-        <v>204</v>
+      <c r="B237" t="e" cm="1">
+        <f t="array" ref="B237">B237:E258VARROC</f>
+        <v>#NAME?</v>
       </c>
       <c r="D237" s="1">
         <v>46237</v>
@@ -12822,7 +12880,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
@@ -12836,7 +12894,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
@@ -12856,7 +12914,7 @@
         <v>294.8</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
@@ -12876,7 +12934,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
@@ -12896,7 +12954,7 @@
         <v>5450</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
@@ -12913,7 +12971,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
@@ -12930,7 +12988,7 @@
         <v>6610</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
@@ -12950,7 +13008,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
@@ -12964,7 +13022,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
@@ -12978,7 +13036,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
@@ -12989,7 +13047,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
@@ -13000,7 +13058,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
@@ -13020,7 +13078,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
@@ -13037,7 +13095,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13054,7 +13112,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
@@ -13074,7 +13132,7 @@
         <v>140.4</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
@@ -13094,7 +13152,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
@@ -13105,35 +13163,32 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B255" t="s">
-        <v>217</v>
+        <v>71</v>
       </c>
       <c r="C255" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="D255" s="1">
         <v>46240</v>
       </c>
       <c r="E255">
-        <v>453</v>
+        <v>1040</v>
       </c>
       <c r="F255">
-        <v>520</v>
-      </c>
-      <c r="G255">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B256" t="s">
-        <v>71</v>
+        <v>217</v>
       </c>
       <c r="C256" t="s">
         <v>191</v>
@@ -13142,94 +13197,415 @@
         <v>46240</v>
       </c>
       <c r="E256">
-        <v>1040</v>
+        <v>2105</v>
       </c>
       <c r="F256">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B257" t="s">
         <v>218</v>
       </c>
       <c r="C257" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D257" s="1">
         <v>46240</v>
       </c>
-      <c r="E257">
-        <v>2105</v>
-      </c>
-      <c r="F257">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="E257" s="9">
+        <v>12190</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B258" t="s">
-        <v>219</v>
-      </c>
-      <c r="C258" t="s">
         <v>220</v>
       </c>
       <c r="D258" s="1">
         <v>46240</v>
       </c>
-      <c r="E258" s="9">
-        <v>12190</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="E258">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B259" t="s">
         <v>221</v>
       </c>
+      <c r="C259" t="s">
+        <v>123</v>
+      </c>
       <c r="D259" s="1">
         <v>46240</v>
       </c>
       <c r="E259">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+        <v>1330</v>
+      </c>
+      <c r="F259">
+        <v>1420</v>
+      </c>
+      <c r="G259">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B260" t="s">
         <v>222</v>
       </c>
-      <c r="C260" t="s">
+      <c r="D260" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E260">
+        <v>155</v>
+      </c>
+      <c r="F260">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A261">
+        <v>261</v>
+      </c>
+      <c r="B261" t="s">
+        <v>212</v>
+      </c>
+      <c r="D261" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E261">
+        <v>3252</v>
+      </c>
+      <c r="F261">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A262">
+        <v>262</v>
+      </c>
+      <c r="B262" t="s">
+        <v>188</v>
+      </c>
+      <c r="D262" s="1">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A263">
+        <v>263</v>
+      </c>
+      <c r="B263" t="s">
+        <v>32</v>
+      </c>
+      <c r="D263" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E263">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A264">
+        <v>264</v>
+      </c>
+      <c r="B264" t="s">
+        <v>223</v>
+      </c>
+      <c r="D264" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E264">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265">
+        <v>265</v>
+      </c>
+      <c r="B265" t="s">
+        <v>166</v>
+      </c>
+      <c r="C265" t="s">
         <v>123</v>
       </c>
-      <c r="D260" s="1">
-        <v>46240</v>
-      </c>
-      <c r="E260">
-        <v>1330</v>
-      </c>
-      <c r="F260">
-        <v>1420</v>
-      </c>
-      <c r="G260">
-        <v>1285</v>
+      <c r="D265" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E265">
+        <v>182</v>
+      </c>
+      <c r="F265">
+        <v>195</v>
+      </c>
+      <c r="G265">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266">
+        <v>266</v>
+      </c>
+      <c r="B266" t="s">
+        <v>224</v>
+      </c>
+      <c r="D266" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E266">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A267">
+        <v>267</v>
+      </c>
+      <c r="B267" t="s">
+        <v>225</v>
+      </c>
+      <c r="D267" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E267">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A268">
+        <v>268</v>
+      </c>
+      <c r="B268" t="s">
+        <v>226</v>
+      </c>
+      <c r="D268" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E268">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269">
+        <v>269</v>
+      </c>
+      <c r="B269" t="s">
+        <v>182</v>
+      </c>
+      <c r="D269" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E269">
+        <v>2489</v>
+      </c>
+      <c r="F269">
+        <v>2700</v>
+      </c>
+      <c r="G269">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270">
+        <v>270</v>
+      </c>
+      <c r="B270" t="s">
+        <v>71</v>
+      </c>
+      <c r="D270" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E270">
+        <v>1060</v>
+      </c>
+      <c r="F270">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A271">
+        <v>271</v>
+      </c>
+      <c r="B271" t="s">
+        <v>227</v>
+      </c>
+      <c r="D271" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E271">
+        <v>1097</v>
+      </c>
+      <c r="F271">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A272">
+        <v>272</v>
+      </c>
+      <c r="B272" t="s">
+        <v>84</v>
+      </c>
+      <c r="D272" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E272">
+        <v>4327</v>
+      </c>
+      <c r="F272">
+        <v>5250</v>
+      </c>
+      <c r="G272">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273">
+        <v>273</v>
+      </c>
+      <c r="B273" t="s">
+        <v>228</v>
+      </c>
+      <c r="D273" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E273">
+        <v>237.11</v>
+      </c>
+      <c r="F273">
+        <v>253.43</v>
+      </c>
+      <c r="G273">
+        <v>228.8</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A274">
+        <v>274</v>
+      </c>
+      <c r="B274" t="s">
+        <v>229</v>
+      </c>
+      <c r="C274" t="s">
+        <v>230</v>
+      </c>
+      <c r="D274" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E274">
+        <v>1685</v>
+      </c>
+      <c r="F274">
+        <v>1775</v>
+      </c>
+      <c r="G274">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A275">
+        <v>275</v>
+      </c>
+      <c r="B275" t="s">
+        <v>231</v>
+      </c>
+      <c r="D275" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E275">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A276">
+        <v>276</v>
+      </c>
+      <c r="B276" t="s">
+        <v>232</v>
+      </c>
+      <c r="D276" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E276">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A277">
+        <v>277</v>
+      </c>
+      <c r="B277" t="s">
+        <v>15</v>
+      </c>
+      <c r="D277" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E277">
+        <v>2667</v>
+      </c>
+      <c r="F277">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A278">
+        <v>278</v>
+      </c>
+      <c r="B278" t="s">
+        <v>233</v>
+      </c>
+      <c r="D278" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E278">
+        <v>207</v>
+      </c>
+      <c r="F278">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A279">
+        <v>279</v>
+      </c>
+      <c r="B279" t="s">
+        <v>234</v>
+      </c>
+      <c r="D279" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E279">
+        <v>3250</v>
+      </c>
+      <c r="F279">
+        <v>3950</v>
+      </c>
+      <c r="G279">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A280">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A281">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L260" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="MEDANTA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L259" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D69A74-9C84-49BA-B7D7-9629245FA46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95008CFE-A925-4155-8DB6-CD70469C9A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="3680" yWindow="1860" windowWidth="7500" windowHeight="8390" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Buy Sell" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$281</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -7790,7 +7790,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <dimension ref="A1:Q281"/>
+  <dimension ref="A1:Q297"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -13604,8 +13604,88 @@
         <v>281</v>
       </c>
     </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A282">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A283">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A284">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A285">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A286">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A287">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A288">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A289">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A290">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A291">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A292">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A293">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A294">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A295">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A296">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A297">
+        <v>297</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L259" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
+  <autoFilter ref="A1:L281" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95008CFE-A925-4155-8DB6-CD70469C9A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFA4E77-F581-43AA-8688-24DBC92C1B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3680" yWindow="1860" windowWidth="7500" windowHeight="8390" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Buy Sell" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$297</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="258">
   <si>
     <t>S No.</t>
   </si>
@@ -774,6 +774,75 @@
   </si>
   <si>
     <t>SHAILY ENGINEERING PLASTICS</t>
+  </si>
+  <si>
+    <t>DIVIS LABS</t>
+  </si>
+  <si>
+    <t>SOLAR INDUSTRIES</t>
+  </si>
+  <si>
+    <t>MANAPPURAM FINANACE</t>
+  </si>
+  <si>
+    <t>AMAR RAJA</t>
+  </si>
+  <si>
+    <t>KPIL</t>
+  </si>
+  <si>
+    <t>AARTI INDUSTRIES</t>
+  </si>
+  <si>
+    <t>Breakout</t>
+  </si>
+  <si>
+    <t>POONAWALLA FINCORP</t>
+  </si>
+  <si>
+    <t>LG ELECTRONICS</t>
+  </si>
+  <si>
+    <t>MAX FINANCIALS</t>
+  </si>
+  <si>
+    <t>SAPPHIRE</t>
+  </si>
+  <si>
+    <t>IPCA</t>
+  </si>
+  <si>
+    <t>DIXON</t>
+  </si>
+  <si>
+    <t>BDL</t>
+  </si>
+  <si>
+    <t>IFCI</t>
+  </si>
+  <si>
+    <t>Overnight</t>
+  </si>
+  <si>
+    <t>AVALON TECH</t>
+  </si>
+  <si>
+    <t>OBEROI REALTY</t>
+  </si>
+  <si>
+    <t>HINDUSTAN COPPER</t>
+  </si>
+  <si>
+    <t>Uptrend</t>
+  </si>
+  <si>
+    <t>SYRMA SGS TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>IDEA</t>
+  </si>
+  <si>
+    <t>ZEN TECHNOLOGIES</t>
   </si>
 </sst>
 </file>
@@ -7790,7 +7859,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <dimension ref="A1:Q297"/>
+  <dimension ref="A1:Q324"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -13598,94 +13667,754 @@
       <c r="A280">
         <v>280</v>
       </c>
+      <c r="B280" t="s">
+        <v>235</v>
+      </c>
+      <c r="C280" t="s">
+        <v>123</v>
+      </c>
+      <c r="D280" s="1">
+        <v>46246</v>
+      </c>
+      <c r="E280">
+        <v>8578</v>
+      </c>
+      <c r="F280">
+        <v>9000</v>
+      </c>
+      <c r="G280">
+        <v>8350</v>
+      </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>281</v>
       </c>
+      <c r="B281" t="s">
+        <v>14</v>
+      </c>
+      <c r="C281" t="s">
+        <v>124</v>
+      </c>
+      <c r="D281" s="1">
+        <v>46246</v>
+      </c>
+      <c r="E281">
+        <v>2814</v>
+      </c>
+      <c r="F281">
+        <v>3260</v>
+      </c>
+      <c r="G281">
+        <v>2590</v>
+      </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>282</v>
       </c>
+      <c r="B282" t="s">
+        <v>236</v>
+      </c>
+      <c r="D282" s="1">
+        <v>46246</v>
+      </c>
+      <c r="E282" s="9">
+        <v>18770</v>
+      </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>283</v>
       </c>
+      <c r="B283" t="s">
+        <v>237</v>
+      </c>
+      <c r="D283" s="1">
+        <v>46246</v>
+      </c>
+      <c r="E283">
+        <v>360</v>
+      </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>284</v>
       </c>
+      <c r="B284" t="s">
+        <v>238</v>
+      </c>
+      <c r="D284" s="1">
+        <v>46246</v>
+      </c>
+      <c r="E284">
+        <v>970</v>
+      </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>285</v>
       </c>
+      <c r="B285" t="s">
+        <v>239</v>
+      </c>
+      <c r="D285" s="1">
+        <v>46246</v>
+      </c>
+      <c r="E285">
+        <v>1394</v>
+      </c>
+      <c r="F285">
+        <v>1600</v>
+      </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>286</v>
       </c>
+      <c r="B286" t="s">
+        <v>240</v>
+      </c>
+      <c r="C286" t="s">
+        <v>241</v>
+      </c>
+      <c r="D286" s="1">
+        <v>46247</v>
+      </c>
+      <c r="E286">
+        <v>531</v>
+      </c>
+      <c r="F286">
+        <v>570</v>
+      </c>
+      <c r="G286">
+        <v>510</v>
+      </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>287</v>
       </c>
+      <c r="B287" t="s">
+        <v>166</v>
+      </c>
+      <c r="D287" s="1">
+        <v>46247</v>
+      </c>
+      <c r="E287">
+        <v>187</v>
+      </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>288</v>
       </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" s="1">
+        <v>46247</v>
+      </c>
+      <c r="E288">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>289</v>
       </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B289" t="s">
+        <v>90</v>
+      </c>
+      <c r="D289" s="1">
+        <v>46247</v>
+      </c>
+      <c r="E289">
+        <v>761</v>
+      </c>
+      <c r="F289">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>290</v>
       </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B290" t="s">
+        <v>184</v>
+      </c>
+      <c r="D290" s="1">
+        <v>46247</v>
+      </c>
+      <c r="E290">
+        <v>586</v>
+      </c>
+      <c r="F290">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>291</v>
       </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B291" t="s">
+        <v>242</v>
+      </c>
+      <c r="C291" t="s">
+        <v>123</v>
+      </c>
+      <c r="D291" s="1">
+        <v>46248</v>
+      </c>
+      <c r="E291">
+        <v>503</v>
+      </c>
+      <c r="F291">
+        <v>540</v>
+      </c>
+      <c r="G291">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>292</v>
       </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B292" t="s">
+        <v>130</v>
+      </c>
+      <c r="D292" s="1">
+        <v>46248</v>
+      </c>
+      <c r="E292">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>293</v>
       </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B293" t="s">
+        <v>157</v>
+      </c>
+      <c r="D293" s="1">
+        <v>46248</v>
+      </c>
+      <c r="E293">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>294</v>
       </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B294" t="s">
+        <v>243</v>
+      </c>
+      <c r="D294" s="1">
+        <v>46248</v>
+      </c>
+      <c r="E294">
+        <v>1580</v>
+      </c>
+      <c r="F294">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>295</v>
       </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B295" t="s">
+        <v>244</v>
+      </c>
+      <c r="D295" s="1">
+        <v>46248</v>
+      </c>
+      <c r="E295">
+        <v>1512</v>
+      </c>
+      <c r="F295">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>296</v>
       </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B296" t="s">
+        <v>90</v>
+      </c>
+      <c r="D296" s="1">
+        <v>46248</v>
+      </c>
+      <c r="E296">
+        <v>761</v>
+      </c>
+      <c r="F296">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>297</v>
       </c>
+      <c r="B297" t="s">
+        <v>245</v>
+      </c>
+      <c r="C297" t="s">
+        <v>123</v>
+      </c>
+      <c r="D297" s="1">
+        <v>46248</v>
+      </c>
+      <c r="E297">
+        <v>238.39</v>
+      </c>
+      <c r="F297">
+        <v>261.56</v>
+      </c>
+      <c r="G297">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A298">
+        <v>298</v>
+      </c>
+      <c r="B298" t="s">
+        <v>178</v>
+      </c>
+      <c r="D298" s="1">
+        <v>46248</v>
+      </c>
+      <c r="F298">
+        <v>200</v>
+      </c>
+      <c r="G298">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A299">
+        <v>299</v>
+      </c>
+      <c r="B299" t="s">
+        <v>207</v>
+      </c>
+      <c r="D299" s="1">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A300">
+        <v>300</v>
+      </c>
+      <c r="B300" t="s">
+        <v>14</v>
+      </c>
+      <c r="D300" s="1">
+        <v>46251</v>
+      </c>
+      <c r="E300">
+        <v>2814</v>
+      </c>
+      <c r="F300">
+        <v>3260</v>
+      </c>
+      <c r="G300">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A301">
+        <v>301</v>
+      </c>
+      <c r="B301" t="s">
+        <v>246</v>
+      </c>
+      <c r="C301" t="s">
+        <v>191</v>
+      </c>
+      <c r="D301" s="1">
+        <v>46251</v>
+      </c>
+      <c r="E301">
+        <v>1734</v>
+      </c>
+      <c r="F301">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A302">
+        <v>302</v>
+      </c>
+      <c r="B302" t="s">
+        <v>53</v>
+      </c>
+      <c r="C302" t="s">
+        <v>191</v>
+      </c>
+      <c r="D302" s="1">
+        <v>46251</v>
+      </c>
+      <c r="E302">
+        <v>1617</v>
+      </c>
+      <c r="F302">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A303">
+        <v>303</v>
+      </c>
+      <c r="B303" t="s">
+        <v>247</v>
+      </c>
+      <c r="C303" t="s">
+        <v>241</v>
+      </c>
+      <c r="D303" s="1">
+        <v>46251</v>
+      </c>
+      <c r="E303">
+        <v>14130</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A304">
+        <v>304</v>
+      </c>
+      <c r="B304" t="s">
+        <v>248</v>
+      </c>
+      <c r="D304" s="1">
+        <v>46251</v>
+      </c>
+      <c r="E304">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A305">
+        <v>305</v>
+      </c>
+      <c r="B305" t="s">
+        <v>185</v>
+      </c>
+      <c r="D305" s="1">
+        <v>46251</v>
+      </c>
+      <c r="E305">
+        <v>1244</v>
+      </c>
+      <c r="F305">
+        <v>1340</v>
+      </c>
+      <c r="G305">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A306">
+        <v>306</v>
+      </c>
+      <c r="B306" t="s">
+        <v>249</v>
+      </c>
+      <c r="C306" t="s">
+        <v>250</v>
+      </c>
+      <c r="D306" s="1">
+        <v>46251</v>
+      </c>
+      <c r="E306">
+        <v>79.23</v>
+      </c>
+      <c r="F306">
+        <v>84.2</v>
+      </c>
+      <c r="G306">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A307">
+        <v>307</v>
+      </c>
+      <c r="B307" t="s">
+        <v>251</v>
+      </c>
+      <c r="D307" s="1">
+        <v>46251</v>
+      </c>
+      <c r="E307">
+        <v>2040</v>
+      </c>
+      <c r="F307">
+        <v>2202</v>
+      </c>
+      <c r="G307">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A308">
+        <v>308</v>
+      </c>
+      <c r="B308" t="s">
+        <v>118</v>
+      </c>
+      <c r="C308" t="s">
+        <v>191</v>
+      </c>
+      <c r="D308" s="1">
+        <v>46252</v>
+      </c>
+      <c r="E308">
+        <v>1734</v>
+      </c>
+      <c r="F308">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A309">
+        <v>309</v>
+      </c>
+      <c r="B309" t="s">
+        <v>252</v>
+      </c>
+      <c r="C309" t="s">
+        <v>241</v>
+      </c>
+      <c r="D309" s="1">
+        <v>46252</v>
+      </c>
+      <c r="E309">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A310">
+        <v>310</v>
+      </c>
+      <c r="B310" t="s">
+        <v>253</v>
+      </c>
+      <c r="C310" t="s">
+        <v>254</v>
+      </c>
+      <c r="D310" s="1">
+        <v>46252</v>
+      </c>
+      <c r="E310">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A311">
+        <v>311</v>
+      </c>
+      <c r="B311" t="s">
+        <v>27</v>
+      </c>
+      <c r="C311" t="s">
+        <v>148</v>
+      </c>
+      <c r="D311" s="1">
+        <v>46252</v>
+      </c>
+      <c r="E311">
+        <v>435</v>
+      </c>
+      <c r="F311">
+        <v>460</v>
+      </c>
+      <c r="G311">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A312">
+        <v>312</v>
+      </c>
+      <c r="B312" t="s">
+        <v>255</v>
+      </c>
+      <c r="D312" s="1">
+        <v>46252</v>
+      </c>
+      <c r="E312">
+        <v>1467</v>
+      </c>
+      <c r="F312">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A313">
+        <v>313</v>
+      </c>
+      <c r="B313" t="s">
+        <v>256</v>
+      </c>
+      <c r="C313" t="s">
+        <v>250</v>
+      </c>
+      <c r="D313" s="1">
+        <v>46252</v>
+      </c>
+      <c r="E313">
+        <v>13.99</v>
+      </c>
+      <c r="F313">
+        <v>14.57</v>
+      </c>
+      <c r="G313">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A314">
+        <v>314</v>
+      </c>
+      <c r="B314" t="s">
+        <v>156</v>
+      </c>
+      <c r="C314" t="s">
+        <v>123</v>
+      </c>
+      <c r="D314" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E314">
+        <v>824</v>
+      </c>
+      <c r="F314">
+        <v>875</v>
+      </c>
+      <c r="G314">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A315">
+        <v>315</v>
+      </c>
+      <c r="B315" t="s">
+        <v>222</v>
+      </c>
+      <c r="C315" t="s">
+        <v>241</v>
+      </c>
+      <c r="D315" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E315">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A316">
+        <v>316</v>
+      </c>
+      <c r="B316" t="s">
+        <v>257</v>
+      </c>
+      <c r="D316" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E316">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A317">
+        <v>317</v>
+      </c>
+      <c r="B317" t="s">
+        <v>139</v>
+      </c>
+      <c r="D317" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E317">
+        <v>3092</v>
+      </c>
+      <c r="F317">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A318">
+        <v>318</v>
+      </c>
+      <c r="B318" t="s">
+        <v>133</v>
+      </c>
+      <c r="D318" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E318">
+        <v>325</v>
+      </c>
+      <c r="F318">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A319">
+        <v>319</v>
+      </c>
+      <c r="B319" t="s">
+        <v>226</v>
+      </c>
+      <c r="C319" t="s">
+        <v>124</v>
+      </c>
+      <c r="D319" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E319">
+        <v>257</v>
+      </c>
+      <c r="F319">
+        <v>320</v>
+      </c>
+      <c r="G319">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A320">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A321">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A322">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A323">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A324">
+        <v>324</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L281" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
+  <autoFilter ref="A1:L297" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFA4E77-F581-43AA-8688-24DBC92C1B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238E721F-D979-493D-AB2F-9DF792099093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Buy Sell" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$324</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -7859,6 +7859,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q324"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7919,7 +7920,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7946,7 +7947,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7967,7 +7968,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7991,7 +7992,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8018,7 +8019,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -8039,7 +8040,7 @@
         <v>0.12225811936745451</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8069,7 +8070,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8090,7 +8091,7 @@
         <v>0.3200118345888619</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8111,7 +8112,7 @@
         <v>0.23999948467553878</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -8132,7 +8133,7 @@
         <v>0.20000331035395966</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8153,7 +8154,7 @@
         <v>0.18000429092469422</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -8174,7 +8175,7 @@
         <v>0.15999843324886945</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -8195,7 +8196,7 @@
         <v>0.11471160077770577</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -8213,7 +8214,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8234,7 +8235,7 @@
         <v>0.27027027027027029</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -8255,7 +8256,7 @@
         <v>0.14974761637689288</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8279,7 +8280,7 @@
         <v>0.16036505867014342</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8297,7 +8298,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8321,7 +8322,7 @@
         <v>8.0074487895716945E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8339,7 +8340,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8357,7 +8358,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8378,7 +8379,7 @@
         <v>0.10091743119266056</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8405,7 +8406,7 @@
         <v>0.16036505867014342</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8429,7 +8430,7 @@
         <v>0.13476473275468251</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8459,7 +8460,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8477,7 +8478,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8501,7 +8502,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8531,7 +8532,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8555,7 +8556,7 @@
         <v>7.7885952712100137E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8576,7 +8577,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8597,7 +8598,7 @@
         <v>0.23195380173243504</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8618,7 +8619,7 @@
         <v>0.24006359300476948</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8642,7 +8643,7 @@
         <v>5.8595014567821305E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8660,7 +8661,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8678,7 +8679,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8699,7 +8700,7 @@
         <v>0.23178807947019867</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -8723,7 +8724,7 @@
         <v>0.15384615384615385</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -8747,7 +8748,7 @@
         <v>0.22093023255813954</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8768,7 +8769,7 @@
         <v>0.18895966029723993</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -8786,7 +8787,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -8804,7 +8805,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -8828,7 +8829,7 @@
         <v>6.5217391304347824E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8852,7 +8853,7 @@
         <v>8.9108910891089105E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8870,7 +8871,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8888,7 +8889,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8906,7 +8907,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8924,7 +8925,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8942,7 +8943,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8960,7 +8961,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8984,7 +8985,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -9008,7 +9009,7 @@
         <v>0.22093023255813954</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -9032,7 +9033,7 @@
         <v>0.13671274961597543</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -9050,7 +9051,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -9071,7 +9072,7 @@
         <v>0.29692832764505117</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -9089,7 +9090,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -9107,7 +9108,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -9132,7 +9133,7 @@
       </c>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -9162,7 +9163,7 @@
         <v>156.6</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -9183,7 +9184,7 @@
         <v>0.21718377088305491</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -9207,7 +9208,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -9225,7 +9226,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -9243,7 +9244,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9261,7 +9262,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9285,7 +9286,7 @@
         <v>6.458333333333334E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9309,7 +9310,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9330,7 +9331,7 @@
         <v>0.13314447592067988</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9351,7 +9352,7 @@
         <v>6.0891399874450719E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9369,7 +9370,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9387,7 +9388,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9411,7 +9412,7 @@
         <v>7.2021241287753071E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9426,7 +9427,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9450,7 +9451,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9474,7 +9475,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -9495,7 +9496,7 @@
         <v>0.39423076923076922</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -9513,7 +9514,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -9531,7 +9532,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -9549,7 +9550,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -9573,7 +9574,7 @@
         <v>0.1040339702760085</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -9603,7 +9604,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -9621,7 +9622,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -9639,7 +9640,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -9660,7 +9661,7 @@
         <v>0.15683229813664595</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9684,7 +9685,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9708,7 +9709,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9729,7 +9730,7 @@
         <v>0.1894273127753304</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9777,7 +9778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -9795,7 +9796,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -9813,7 +9814,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -9837,7 +9838,7 @@
         <v>6.5647482014388484E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9861,7 +9862,7 @@
         <v>2.5125628140703519E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9885,7 +9886,7 @@
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -9903,7 +9904,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9927,7 +9928,7 @@
         <v>0.15309126594700687</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -9945,7 +9946,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -9969,7 +9970,7 @@
         <v>4.1184971098265896E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9993,7 +9994,7 @@
         <v>7.903780068728522E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -10011,7 +10012,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -10029,7 +10030,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -10050,7 +10051,7 @@
         <v>0.23476848090982941</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -10071,7 +10072,7 @@
         <v>0.21739130434782608</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -10095,7 +10096,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -10119,7 +10120,7 @@
         <v>0.15200764818355642</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10140,7 +10141,7 @@
         <v>0.12658746415403524</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10158,7 +10159,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10176,7 +10177,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10200,7 +10201,7 @@
         <v>4.7968885047536734E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10221,7 +10222,7 @@
         <v>0.38968481375358166</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10242,7 +10243,7 @@
         <v>0.18429807052561545</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10260,7 +10261,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10278,7 +10279,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10302,7 +10303,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10326,7 +10327,7 @@
         <v>0.12322946175637393</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -10344,7 +10345,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10365,7 +10366,7 @@
         <v>0.10981308411214953</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10383,7 +10384,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10401,7 +10402,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -10425,7 +10426,7 @@
         <v>7.1732199787460149E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10446,7 +10447,7 @@
         <v>0.22553191489361701</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -10470,7 +10471,7 @@
         <v>0.11678832116788321</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -10488,7 +10489,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -10506,7 +10507,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -10527,7 +10528,7 @@
         <v>0.17082961641391614</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -10545,7 +10546,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -10563,7 +10564,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -10587,7 +10588,7 @@
         <v>4.793028322440087E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -10612,7 +10613,7 @@
         <v>7.2664359861591699E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -10630,7 +10631,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -10648,7 +10649,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10669,7 +10670,7 @@
         <v>0.17924528301886791</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10687,7 +10688,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10714,7 +10715,7 @@
         <v>0.16719242902208201</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10735,7 +10736,7 @@
         <v>0.30120481927710846</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -10756,7 +10757,7 @@
         <v>0.24204946996466431</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -10774,7 +10775,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10801,7 +10802,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -10828,7 +10829,7 @@
         <v>0.16719242902208201</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -10852,7 +10853,7 @@
         <v>0.14329268292682926</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -10876,7 +10877,7 @@
         <v>0.19462788454403798</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -10897,7 +10898,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -10915,7 +10916,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -10942,7 +10943,7 @@
         <v>8.3406240886555849E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -10969,7 +10970,7 @@
         <v>6.2194269741439552E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -10987,7 +10988,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -11002,7 +11003,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -11023,7 +11024,7 @@
         <v>0.15264797507788161</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -11044,7 +11045,7 @@
         <v>0.17680826636050517</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -11071,7 +11072,7 @@
         <v>0.15200764818355642</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -11095,7 +11096,7 @@
         <v>9.2105263157894732E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -11116,7 +11117,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -11134,7 +11135,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -11155,7 +11156,7 @@
         <v>0.18527760449157829</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -11176,7 +11177,7 @@
         <v>0.18755118755118755</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -11200,7 +11201,7 @@
         <v>0.19047619047619047</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -11224,7 +11225,7 @@
         <v>0.25835189309576839</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -11245,7 +11246,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -11266,7 +11267,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -11290,7 +11291,7 @@
         <v>-2.717391304347826E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -11317,7 +11318,7 @@
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -11338,7 +11339,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -11359,7 +11360,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -11383,7 +11384,7 @@
         <v>0.2707641196013289</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -11407,7 +11408,7 @@
         <v>0.15740740740740741</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -11434,7 +11435,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -11455,7 +11456,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -11476,7 +11477,7 @@
         <v>0.25827814569536423</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -11497,7 +11498,7 @@
         <v>0.19908466819221968</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -11512,7 +11513,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -11527,7 +11528,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -11551,7 +11552,7 @@
         <v>7.586206896551724E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -11578,7 +11579,7 @@
         <v>9.1954022988505746E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -11596,7 +11597,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -11614,7 +11615,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -11635,7 +11636,7 @@
         <v>0.21191135734072022</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -11656,7 +11657,7 @@
         <v>0.1883589329021827</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -11677,7 +11678,7 @@
         <v>0.12322946175637393</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -11704,7 +11705,7 @@
         <v>8.7367178276269192E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -11722,7 +11723,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -11743,7 +11744,7 @@
         <v>0.21374865735767992</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11767,7 +11768,7 @@
         <v>8.4905660377358486E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11782,7 +11783,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -11797,7 +11798,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -11818,7 +11819,7 @@
         <v>0.2841091492776886</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -11839,7 +11840,7 @@
         <v>0.16262975778546712</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -11863,7 +11864,7 @@
         <v>2.9463116542994324E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -11878,7 +11879,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -11893,7 +11894,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -11917,7 +11918,7 @@
         <v>-2.077151335311566E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -11935,7 +11936,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -11962,7 +11963,7 @@
         <v>7.0950468540829981E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -11980,7 +11981,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -12001,7 +12002,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -12025,7 +12026,7 @@
         <v>0.20209059233449478</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -12043,7 +12044,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -12061,7 +12062,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -12085,7 +12086,7 @@
         <v>5.3869969040247677E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -12106,7 +12107,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -12130,7 +12131,7 @@
         <v>1.5414546542951144E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -12154,7 +12155,7 @@
         <v>1.4084507042253521E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -12169,7 +12170,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -12193,7 +12194,7 @@
         <v>6.1910619106191063E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -12214,7 +12215,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -12232,7 +12233,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -12253,7 +12254,7 @@
         <v>0.23672704559650218</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -12277,7 +12278,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -12292,7 +12293,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -12319,7 +12320,7 @@
         <v>7.5174825174825169E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -12337,7 +12338,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -12358,7 +12359,7 @@
         <v>0.29729729729729731</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12373,7 +12374,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12397,7 +12398,7 @@
         <v>0.19266055045871561</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12424,7 +12425,7 @@
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12448,7 +12449,7 @@
         <v>2.0952380952380951E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12472,7 +12473,7 @@
         <v>3.4426229508196723E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12499,7 +12500,7 @@
         <v>-3.6054081121682527E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12523,7 +12524,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
@@ -12547,7 +12548,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12571,7 +12572,7 @@
         <v>0.18705974432559352</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12595,7 +12596,7 @@
         <v>0.22076440387906446</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12622,7 +12623,7 @@
         <v>0.2133117633464294</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12649,7 +12650,7 @@
         <v>0.2133117633464294</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
@@ -12673,7 +12674,7 @@
         <v>0.21370067014147431</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
@@ -12697,7 +12698,7 @@
         <v>0.15889691398555483</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
@@ -12715,7 +12716,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
@@ -12733,7 +12734,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
@@ -12751,7 +12752,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
@@ -12769,7 +12770,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
@@ -12784,7 +12785,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
@@ -12811,7 +12812,7 @@
         <v>7.3619631901840496E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
@@ -12838,7 +12839,7 @@
         <v>0.1630144307856761</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
@@ -12855,7 +12856,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
@@ -12866,7 +12867,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
@@ -12880,7 +12881,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
@@ -12894,7 +12895,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
@@ -12908,7 +12909,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
@@ -12928,7 +12929,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
@@ -12949,7 +12950,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
@@ -12963,7 +12964,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
@@ -12983,7 +12984,7 @@
         <v>294.8</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
@@ -13003,7 +13004,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
@@ -13023,7 +13024,7 @@
         <v>5450</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
@@ -13040,7 +13041,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
@@ -13057,7 +13058,7 @@
         <v>6610</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
@@ -13077,7 +13078,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
@@ -13091,7 +13092,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
@@ -13105,7 +13106,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
@@ -13116,7 +13117,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
@@ -13127,7 +13128,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
@@ -13147,7 +13148,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
@@ -13164,7 +13165,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13181,7 +13182,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
@@ -13201,7 +13202,7 @@
         <v>140.4</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
@@ -13221,7 +13222,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
@@ -13232,7 +13233,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>255</v>
       </c>
@@ -13252,7 +13253,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>256</v>
       </c>
@@ -13272,7 +13273,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>257</v>
       </c>
@@ -13289,7 +13290,7 @@
         <v>12190</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>258</v>
       </c>
@@ -13303,7 +13304,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>259</v>
       </c>
@@ -13326,7 +13327,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>260</v>
       </c>
@@ -13343,7 +13344,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>261</v>
       </c>
@@ -13360,7 +13361,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>262</v>
       </c>
@@ -13371,7 +13372,7 @@
         <v>46241</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>263</v>
       </c>
@@ -13385,7 +13386,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>264</v>
       </c>
@@ -13399,7 +13400,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>265</v>
       </c>
@@ -13422,7 +13423,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>266</v>
       </c>
@@ -13436,7 +13437,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>267</v>
       </c>
@@ -13450,7 +13451,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>268</v>
       </c>
@@ -13464,7 +13465,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>269</v>
       </c>
@@ -13484,7 +13485,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>270</v>
       </c>
@@ -13501,7 +13502,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>271</v>
       </c>
@@ -13518,7 +13519,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>272</v>
       </c>
@@ -13538,7 +13539,7 @@
         <v>3870</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>273</v>
       </c>
@@ -13558,7 +13559,7 @@
         <v>228.8</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>274</v>
       </c>
@@ -13581,7 +13582,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>275</v>
       </c>
@@ -13595,7 +13596,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>276</v>
       </c>
@@ -13609,7 +13610,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>277</v>
       </c>
@@ -13626,7 +13627,7 @@
         <v>3080</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>278</v>
       </c>
@@ -13643,7 +13644,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>279</v>
       </c>
@@ -13663,7 +13664,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>280</v>
       </c>
@@ -13686,7 +13687,7 @@
         <v>8350</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>281</v>
       </c>
@@ -13709,7 +13710,7 @@
         <v>2590</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>282</v>
       </c>
@@ -13723,7 +13724,7 @@
         <v>18770</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>283</v>
       </c>
@@ -13737,7 +13738,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>284</v>
       </c>
@@ -13751,7 +13752,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>285</v>
       </c>
@@ -13768,7 +13769,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>286</v>
       </c>
@@ -13791,7 +13792,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>287</v>
       </c>
@@ -13805,7 +13806,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>288</v>
       </c>
@@ -13836,7 +13837,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>290</v>
       </c>
@@ -13853,7 +13854,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>291</v>
       </c>
@@ -13876,7 +13877,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>292</v>
       </c>
@@ -13890,7 +13891,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>293</v>
       </c>
@@ -13904,7 +13905,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>294</v>
       </c>
@@ -13921,7 +13922,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>295</v>
       </c>
@@ -13955,7 +13956,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>297</v>
       </c>
@@ -13978,7 +13979,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>298</v>
       </c>
@@ -13995,7 +13996,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>299</v>
       </c>
@@ -14006,7 +14007,7 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>300</v>
       </c>
@@ -14026,7 +14027,7 @@
         <v>2590</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>301</v>
       </c>
@@ -14046,7 +14047,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>302</v>
       </c>
@@ -14066,7 +14067,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>303</v>
       </c>
@@ -14083,7 +14084,7 @@
         <v>14130</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>304</v>
       </c>
@@ -14097,7 +14098,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>305</v>
       </c>
@@ -14117,7 +14118,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>306</v>
       </c>
@@ -14140,7 +14141,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>307</v>
       </c>
@@ -14160,7 +14161,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>308</v>
       </c>
@@ -14180,7 +14181,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>309</v>
       </c>
@@ -14197,7 +14198,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>310</v>
       </c>
@@ -14214,7 +14215,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>311</v>
       </c>
@@ -14237,7 +14238,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>312</v>
       </c>
@@ -14254,7 +14255,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>313</v>
       </c>
@@ -14277,7 +14278,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>314</v>
       </c>
@@ -14300,7 +14301,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>315</v>
       </c>
@@ -14317,7 +14318,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>316</v>
       </c>
@@ -14331,7 +14332,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>317</v>
       </c>
@@ -14348,7 +14349,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>318</v>
       </c>
@@ -14365,7 +14366,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>319</v>
       </c>
@@ -14388,33 +14389,39 @@
         <v>225</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>320</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>321</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>322</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>323</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>324</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L297" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}"/>
+  <autoFilter ref="A1:L324" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="GOKALDAS EXPORTS"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238E721F-D979-493D-AB2F-9DF792099093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42DCC23-E3D9-4259-8281-7F0C911D8445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -9754,7 +9754,7 @@
         <v>0.20707349806584038</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>0.11678832116788321</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -12524,7 +12524,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
@@ -13820,7 +13820,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>289</v>
       </c>
@@ -13939,7 +13939,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>296</v>
       </c>
@@ -14418,7 +14418,7 @@
   <autoFilter ref="A1:L324" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
     <filterColumn colId="1">
       <filters>
-        <filter val="GOKALDAS EXPORTS"/>
+        <filter val="NYKAA"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42DCC23-E3D9-4259-8281-7F0C911D8445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6092B9C-19F5-45EC-B879-08A18F7B1914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Buy Sell" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Main sheet'!$A$1:$L$515</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="283">
   <si>
     <t>S No.</t>
   </si>
@@ -843,6 +843,81 @@
   </si>
   <si>
     <t>ZEN TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>INVENTURUS KNOWLEDGE SOLUTION</t>
+  </si>
+  <si>
+    <t>Immediate support</t>
+  </si>
+  <si>
+    <t>NAM INDIA</t>
+  </si>
+  <si>
+    <t>NAM-INDIA</t>
+  </si>
+  <si>
+    <t>CROMPTON GREAVES</t>
+  </si>
+  <si>
+    <t>ACME SOLAR</t>
+  </si>
+  <si>
+    <t>CRAFTMAN AUTOMATION</t>
+  </si>
+  <si>
+    <t>URBAN COMPANY</t>
+  </si>
+  <si>
+    <t>AU BANK</t>
+  </si>
+  <si>
+    <t>COCHIN SHIPYARD</t>
+  </si>
+  <si>
+    <t>VARUN BREVRAGES</t>
+  </si>
+  <si>
+    <t>ADANI ENTERPRISES</t>
+  </si>
+  <si>
+    <t>VA TECH WABAG</t>
+  </si>
+  <si>
+    <t>SAIL</t>
+  </si>
+  <si>
+    <t>ASHOK LEYLAND</t>
+  </si>
+  <si>
+    <t>LAURUS LABS</t>
+  </si>
+  <si>
+    <t>OMAXE</t>
+  </si>
+  <si>
+    <t>PC JEWELLERS</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>KALYAN JEWELLERS</t>
+  </si>
+  <si>
+    <t>CYIENT</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>TEJAS NETWORK</t>
+  </si>
+  <si>
+    <t>EICHER MOTORS</t>
+  </si>
+  <si>
+    <t>GLENMARK PHARMA</t>
   </si>
 </sst>
 </file>
@@ -7859,8 +7934,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q324"/>
+  <dimension ref="A1:Q515"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -7920,7 +7994,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7947,7 +8021,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7961,14 +8035,14 @@
         <v>748</v>
       </c>
       <c r="I3" s="2">
-        <f t="shared" ref="I3:I66" si="0">(F3-E3)/E3</f>
+        <f>(F3-E3)/E3</f>
         <v>-1</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7982,7 +8056,7 @@
         <v>2056</v>
       </c>
       <c r="I4" s="2">
-        <f t="shared" si="0"/>
+        <f>(F4-E4)/E4</f>
         <v>-1</v>
       </c>
       <c r="J4" s="1">
@@ -7992,7 +8066,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8009,7 +8083,7 @@
         <v>1160</v>
       </c>
       <c r="I5" s="2">
-        <f t="shared" si="0"/>
+        <f>(F5-E5)/E5</f>
         <v>0.15308151093439365</v>
       </c>
       <c r="J5" s="1">
@@ -8019,7 +8093,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -8036,11 +8110,11 @@
         <v>6600</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" si="0"/>
+        <f>(F6-E6)/E6</f>
         <v>0.12225811936745451</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8060,7 +8134,7 @@
         <v>1438</v>
       </c>
       <c r="I7" s="2">
-        <f t="shared" si="0"/>
+        <f>(F7-E7)/E7</f>
         <v>1.8543956043956044E-2</v>
       </c>
       <c r="J7" s="1">
@@ -8070,7 +8144,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8087,11 +8161,11 @@
         <v>580</v>
       </c>
       <c r="I8" s="2">
-        <f t="shared" si="0"/>
+        <f>(F8-E8)/E8</f>
         <v>0.3200118345888619</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8112,7 +8186,7 @@
         <v>0.23999948467553878</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -8129,11 +8203,11 @@
         <v>1450</v>
       </c>
       <c r="I10" s="2">
-        <f t="shared" si="0"/>
+        <f>(F10-E10)/E10</f>
         <v>0.20000331035395966</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8150,11 +8224,11 @@
         <v>1100</v>
       </c>
       <c r="I11" s="2">
-        <f t="shared" si="0"/>
+        <f>(F11-E11)/E11</f>
         <v>0.18000429092469422</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -8171,11 +8245,11 @@
         <v>3850</v>
       </c>
       <c r="I12" s="2">
-        <f t="shared" si="0"/>
+        <f>(F12-E12)/E12</f>
         <v>0.15999843324886945</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -8192,11 +8266,11 @@
         <v>1720</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="0"/>
+        <f>(F13-E13)/E13</f>
         <v>0.11471160077770577</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -8210,11 +8284,11 @@
         <v>434</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="0"/>
+        <f>(F14-E14)/E14</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8231,11 +8305,11 @@
         <v>235</v>
       </c>
       <c r="I15" s="2">
-        <f t="shared" si="0"/>
+        <f>(F15-E15)/E15</f>
         <v>0.27027027027027029</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -8252,11 +8326,11 @@
         <v>2050</v>
       </c>
       <c r="I16" s="2">
-        <f t="shared" si="0"/>
+        <f>(F16-E16)/E16</f>
         <v>0.14974761637689288</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8276,11 +8350,11 @@
         <v>705</v>
       </c>
       <c r="I17" s="2">
-        <f t="shared" si="0"/>
+        <f>(F17-E17)/E17</f>
         <v>0.16036505867014342</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8294,11 +8368,11 @@
         <v>835</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" si="0"/>
+        <f>(F18-E18)/E18</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8318,11 +8392,11 @@
         <v>510</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="0"/>
+        <f>(F19-E19)/E19</f>
         <v>8.0074487895716945E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8336,11 +8410,11 @@
         <v>1074</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="0"/>
+        <f>(F20-E20)/E20</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8354,11 +8428,11 @@
         <v>406</v>
       </c>
       <c r="I21" s="2">
-        <f t="shared" si="0"/>
+        <f>(F21-E21)/E21</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8375,11 +8449,11 @@
         <v>1200</v>
       </c>
       <c r="I22" s="2">
-        <f t="shared" si="0"/>
+        <f>(F22-E22)/E22</f>
         <v>0.10091743119266056</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8402,11 +8476,11 @@
         <v>1153</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="0"/>
+        <f>(F23-E23)/E23</f>
         <v>0.16036505867014342</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8426,11 +8500,11 @@
         <v>2040</v>
       </c>
       <c r="I24" s="2">
-        <f t="shared" si="0"/>
+        <f>(F24-E24)/E24</f>
         <v>0.13476473275468251</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8450,7 +8524,7 @@
         <v>295</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" si="0"/>
+        <f>(F25-E25)/E25</f>
         <v>6.5573770491803282E-2</v>
       </c>
       <c r="J25" s="1">
@@ -8460,7 +8534,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8474,11 +8548,11 @@
         <v>168.6</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" si="0"/>
+        <f>(F26-E26)/E26</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8495,14 +8569,14 @@
         <v>360</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="0"/>
+        <f>(F27-E27)/E27</f>
         <v>0.34328358208955223</v>
       </c>
       <c r="K27">
         <v>348</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8522,7 +8596,7 @@
         <v>705</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="0"/>
+        <f>(F28-E28)/E28</f>
         <v>0.16036505867014342</v>
       </c>
       <c r="J28" s="1">
@@ -8532,7 +8606,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8552,11 +8626,11 @@
         <v>1388</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="0"/>
+        <f>(F29-E29)/E29</f>
         <v>7.7885952712100137E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8573,11 +8647,11 @@
         <v>1450</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="0"/>
+        <f>(F30-E30)/E30</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8594,11 +8668,11 @@
         <v>1280</v>
       </c>
       <c r="I31" s="2">
-        <f t="shared" si="0"/>
+        <f>(F31-E31)/E31</f>
         <v>0.23195380173243504</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8615,11 +8689,11 @@
         <v>3900</v>
       </c>
       <c r="I32" s="2">
-        <f t="shared" si="0"/>
+        <f>(F32-E32)/E32</f>
         <v>0.24006359300476948</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8639,11 +8713,11 @@
         <v>3000</v>
       </c>
       <c r="I33" s="2">
-        <f t="shared" si="0"/>
+        <f>(F33-E33)/E33</f>
         <v>5.8595014567821305E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8657,11 +8731,11 @@
         <v>2779</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="0"/>
+        <f>(F34-E34)/E34</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8675,11 +8749,11 @@
         <v>2306</v>
       </c>
       <c r="I35" s="2">
-        <f t="shared" si="0"/>
+        <f>(F35-E35)/E35</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8696,11 +8770,11 @@
         <v>1860</v>
       </c>
       <c r="I36" s="2">
-        <f t="shared" si="0"/>
+        <f>(F36-E36)/E36</f>
         <v>0.23178807947019867</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -8720,11 +8794,11 @@
         <v>322</v>
       </c>
       <c r="I37" s="2">
-        <f t="shared" si="0"/>
+        <f>(F37-E37)/E37</f>
         <v>0.15384615384615385</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -8744,11 +8818,11 @@
         <v>76</v>
       </c>
       <c r="I38" s="2">
-        <f t="shared" si="0"/>
+        <f>(F38-E38)/E38</f>
         <v>0.22093023255813954</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8765,11 +8839,11 @@
         <v>5600</v>
       </c>
       <c r="I39" s="2">
-        <f t="shared" si="0"/>
+        <f>(F39-E39)/E39</f>
         <v>0.18895966029723993</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -8783,11 +8857,11 @@
         <v>141</v>
       </c>
       <c r="I40" s="2">
-        <f t="shared" si="0"/>
+        <f>(F40-E40)/E40</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -8801,11 +8875,11 @@
         <v>2743</v>
       </c>
       <c r="I41" s="2">
-        <f t="shared" si="0"/>
+        <f>(F41-E41)/E41</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -8825,11 +8899,11 @@
         <v>265</v>
       </c>
       <c r="I42" s="2">
-        <f t="shared" si="0"/>
+        <f>(F42-E42)/E42</f>
         <v>6.5217391304347824E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8849,11 +8923,11 @@
         <v>1940</v>
       </c>
       <c r="I43" s="2">
-        <f t="shared" si="0"/>
+        <f>(F43-E43)/E43</f>
         <v>8.9108910891089105E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8867,11 +8941,11 @@
         <v>3171</v>
       </c>
       <c r="I44" s="2">
-        <f t="shared" si="0"/>
+        <f>(F44-E44)/E44</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8885,11 +8959,11 @@
         <v>1860</v>
       </c>
       <c r="I45" s="2">
-        <f t="shared" si="0"/>
+        <f>(F45-E45)/E45</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8903,11 +8977,11 @@
         <v>7625</v>
       </c>
       <c r="I46" s="2">
-        <f t="shared" si="0"/>
+        <f>(F46-E46)/E46</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8921,11 +8995,11 @@
         <v>217</v>
       </c>
       <c r="I47" s="2" t="e">
-        <f t="shared" si="0"/>
+        <f>(F47-E47)/E47</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8939,11 +9013,11 @@
         <v>125</v>
       </c>
       <c r="I48" s="2" t="e">
-        <f t="shared" si="0"/>
+        <f>(F48-E48)/E48</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8957,11 +9031,11 @@
         <v>1765</v>
       </c>
       <c r="I49" s="2" t="e">
-        <f t="shared" si="0"/>
+        <f>(F49-E49)/E49</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8975,7 +9049,7 @@
         <v>210</v>
       </c>
       <c r="I50" s="2">
-        <f t="shared" si="0"/>
+        <f>(F50-E50)/E50</f>
         <v>-1</v>
       </c>
       <c r="J50" s="1">
@@ -8985,7 +9059,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -9005,11 +9079,11 @@
         <v>76</v>
       </c>
       <c r="I51" s="2">
-        <f t="shared" si="0"/>
+        <f>(F51-E51)/E51</f>
         <v>0.22093023255813954</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -9029,11 +9103,11 @@
         <v>1820</v>
       </c>
       <c r="I52" s="2">
-        <f t="shared" si="0"/>
+        <f>(F52-E52)/E52</f>
         <v>0.13671274961597543</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -9047,11 +9121,11 @@
         <v>1079</v>
       </c>
       <c r="I53" s="2">
-        <f t="shared" si="0"/>
+        <f>(F53-E53)/E53</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -9068,11 +9142,11 @@
         <v>1900</v>
       </c>
       <c r="I54" s="2">
-        <f t="shared" si="0"/>
+        <f>(F54-E54)/E54</f>
         <v>0.29692832764505117</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -9086,11 +9160,11 @@
         <v>374</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="0"/>
+        <f>(F55-E55)/E55</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -9104,11 +9178,11 @@
         <v>1520</v>
       </c>
       <c r="I56" s="2">
-        <f t="shared" si="0"/>
+        <f>(F56-E56)/E56</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -9128,12 +9202,12 @@
         <v>204</v>
       </c>
       <c r="I57" s="2">
-        <f t="shared" si="0"/>
+        <f>(F57-E57)/E57</f>
         <v>7.8341013824884786E-2</v>
       </c>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -9153,7 +9227,7 @@
         <v>151</v>
       </c>
       <c r="I58" s="2">
-        <f t="shared" si="0"/>
+        <f>(F58-E58)/E58</f>
         <v>3.9215686274509803E-2</v>
       </c>
       <c r="J58" s="1">
@@ -9163,7 +9237,7 @@
         <v>156.6</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -9180,11 +9254,11 @@
         <v>510</v>
       </c>
       <c r="I59" s="2">
-        <f t="shared" si="0"/>
+        <f>(F59-E59)/E59</f>
         <v>0.21718377088305491</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -9201,14 +9275,14 @@
         <v>2600</v>
       </c>
       <c r="I60" s="2">
-        <f t="shared" si="0"/>
+        <f>(F60-E60)/E60</f>
         <v>0.17647058823529413</v>
       </c>
       <c r="K60">
         <v>2450</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -9222,11 +9296,11 @@
         <v>59</v>
       </c>
       <c r="I61" s="2">
-        <f t="shared" si="0"/>
+        <f>(F61-E61)/E61</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -9240,11 +9314,11 @@
         <v>1026</v>
       </c>
       <c r="I62" s="2">
-        <f t="shared" si="0"/>
+        <f>(F62-E62)/E62</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9258,11 +9332,11 @@
         <v>420</v>
       </c>
       <c r="I63" s="2">
-        <f t="shared" si="0"/>
+        <f>(F63-E63)/E63</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9282,11 +9356,11 @@
         <v>930</v>
       </c>
       <c r="I64" s="2">
-        <f t="shared" si="0"/>
+        <f>(F64-E64)/E64</f>
         <v>6.458333333333334E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9306,11 +9380,11 @@
         <v>3415</v>
       </c>
       <c r="I65" s="2">
-        <f t="shared" si="0"/>
+        <f>(F65-E65)/E65</f>
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9327,11 +9401,11 @@
         <v>400</v>
       </c>
       <c r="I66" s="2">
-        <f t="shared" si="0"/>
+        <f>(F66-E66)/E66</f>
         <v>0.13314447592067988</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9348,11 +9422,11 @@
         <v>8450</v>
       </c>
       <c r="I67" s="2">
-        <f t="shared" ref="I67:I130" si="1">(F67-E67)/E67</f>
+        <f>(F67-E67)/E67</f>
         <v>6.0891399874450719E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9366,11 +9440,11 @@
         <v>406</v>
       </c>
       <c r="I68" s="2">
-        <f t="shared" si="1"/>
+        <f>(F68-E68)/E68</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9384,11 +9458,11 @@
         <v>1446</v>
       </c>
       <c r="I69" s="2">
-        <f t="shared" si="1"/>
+        <f>(F69-E69)/E69</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9408,11 +9482,11 @@
         <v>2845</v>
       </c>
       <c r="I70" s="2">
-        <f t="shared" si="1"/>
+        <f>(F70-E70)/E70</f>
         <v>7.2021241287753071E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9423,11 +9497,11 @@
         <v>46192</v>
       </c>
       <c r="I71" s="2" t="e">
-        <f t="shared" si="1"/>
+        <f>(F71-E71)/E71</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9447,11 +9521,11 @@
         <v>3415</v>
       </c>
       <c r="I72" s="2">
-        <f t="shared" si="1"/>
+        <f>(F72-E72)/E72</f>
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9468,14 +9542,14 @@
         <v>2350</v>
       </c>
       <c r="I73" s="2">
-        <f t="shared" si="1"/>
+        <f>(F73-E73)/E73</f>
         <v>0.17971887550200802</v>
       </c>
       <c r="J73" s="1">
         <v>46195</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -9492,11 +9566,11 @@
         <v>580</v>
       </c>
       <c r="I74" s="2">
-        <f t="shared" si="1"/>
+        <f>(F74-E74)/E74</f>
         <v>0.39423076923076922</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -9510,11 +9584,11 @@
         <v>1889</v>
       </c>
       <c r="I75" s="2">
-        <f t="shared" si="1"/>
+        <f>(F75-E75)/E75</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -9528,11 +9602,11 @@
         <v>264</v>
       </c>
       <c r="I76" s="2">
-        <f t="shared" si="1"/>
+        <f>(F76-E76)/E76</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -9546,11 +9620,11 @@
         <v>376</v>
       </c>
       <c r="I77" s="2">
-        <f t="shared" si="1"/>
+        <f>(F77-E77)/E77</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -9570,11 +9644,11 @@
         <v>1340</v>
       </c>
       <c r="I78" s="2">
-        <f t="shared" si="1"/>
+        <f>(F78-E78)/E78</f>
         <v>0.1040339702760085</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -9594,7 +9668,7 @@
         <v>1360</v>
       </c>
       <c r="I79" s="2">
-        <f t="shared" si="1"/>
+        <f>(F79-E79)/E79</f>
         <v>8.1272084805653705E-2</v>
       </c>
       <c r="J79" s="1">
@@ -9604,7 +9678,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -9618,11 +9692,11 @@
         <v>2103</v>
       </c>
       <c r="I80" s="2">
-        <f t="shared" si="1"/>
+        <f>(F80-E80)/E80</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -9636,11 +9710,11 @@
         <v>484</v>
       </c>
       <c r="I81" s="2">
-        <f t="shared" si="1"/>
+        <f>(F81-E81)/E81</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -9657,11 +9731,11 @@
         <v>1490</v>
       </c>
       <c r="I82" s="2">
-        <f t="shared" si="1"/>
+        <f>(F82-E82)/E82</f>
         <v>0.15683229813664595</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9678,14 +9752,14 @@
         <v>1620</v>
       </c>
       <c r="I83" s="2">
-        <f t="shared" si="1"/>
+        <f>(F83-E83)/E83</f>
         <v>0.21257485029940121</v>
       </c>
       <c r="K83">
         <v>1430</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9705,11 +9779,11 @@
         <v>3415</v>
       </c>
       <c r="I84" s="2">
-        <f t="shared" si="1"/>
+        <f>(F84-E84)/E84</f>
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9726,11 +9800,11 @@
         <v>540</v>
       </c>
       <c r="I85" s="2">
-        <f t="shared" si="1"/>
+        <f>(F85-E85)/E85</f>
         <v>0.1894273127753304</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9750,11 +9824,11 @@
         <v>11400</v>
       </c>
       <c r="I86" s="2">
-        <f t="shared" si="1"/>
+        <f>(F86-E86)/E86</f>
         <v>0.20707349806584038</v>
       </c>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -9771,14 +9845,14 @@
         <v>1110</v>
       </c>
       <c r="I87" s="2">
-        <f t="shared" si="1"/>
+        <f>(F87-E87)/E87</f>
         <v>0.33896260554885405</v>
       </c>
       <c r="M87">
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -9792,11 +9866,11 @@
         <v>3891</v>
       </c>
       <c r="I88" s="2">
-        <f t="shared" si="1"/>
+        <f>(F88-E88)/E88</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -9810,11 +9884,11 @@
         <v>346</v>
       </c>
       <c r="I89" s="2">
-        <f t="shared" si="1"/>
+        <f>(F89-E89)/E89</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -9834,11 +9908,11 @@
         <v>1080</v>
       </c>
       <c r="I90" s="2">
-        <f t="shared" si="1"/>
+        <f>(F90-E90)/E90</f>
         <v>6.5647482014388484E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9858,11 +9932,11 @@
         <v>197</v>
       </c>
       <c r="I91" s="2">
-        <f t="shared" si="1"/>
+        <f>(F91-E91)/E91</f>
         <v>2.5125628140703519E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9882,11 +9956,11 @@
         <v>3415</v>
       </c>
       <c r="I92" s="2">
-        <f t="shared" si="1"/>
+        <f>(F92-E92)/E92</f>
         <v>0.12236517930468109</v>
       </c>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -9900,11 +9974,11 @@
         <v>2123</v>
       </c>
       <c r="I93" s="2">
-        <f t="shared" si="1"/>
+        <f>(F93-E93)/E93</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9924,11 +9998,11 @@
         <v>1033</v>
       </c>
       <c r="I94" s="2">
-        <f t="shared" si="1"/>
+        <f>(F94-E94)/E94</f>
         <v>0.15309126594700687</v>
       </c>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -9942,11 +10016,11 @@
         <v>413</v>
       </c>
       <c r="I95" s="2">
-        <f t="shared" si="1"/>
+        <f>(F95-E95)/E95</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -9966,11 +10040,11 @@
         <v>1350</v>
       </c>
       <c r="I96" s="2">
-        <f t="shared" si="1"/>
+        <f>(F96-E96)/E96</f>
         <v>4.1184971098265896E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9990,11 +10064,11 @@
         <v>1380</v>
       </c>
       <c r="I97" s="2">
-        <f t="shared" si="1"/>
+        <f>(F97-E97)/E97</f>
         <v>7.903780068728522E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -10008,11 +10082,11 @@
         <v>13735</v>
       </c>
       <c r="I98" s="2">
-        <f t="shared" si="1"/>
+        <f>(F98-E98)/E98</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -10026,11 +10100,11 @@
         <v>391</v>
       </c>
       <c r="I99" s="2">
-        <f t="shared" si="1"/>
+        <f>(F99-E99)/E99</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -10047,11 +10121,11 @@
         <v>1520</v>
       </c>
       <c r="I100" s="2">
-        <f t="shared" si="1"/>
+        <f>(F100-E100)/E100</f>
         <v>0.23476848090982941</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -10068,11 +10142,11 @@
         <v>700</v>
       </c>
       <c r="I101" s="2">
-        <f t="shared" si="1"/>
+        <f>(F101-E101)/E101</f>
         <v>0.21739130434782608</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -10092,11 +10166,11 @@
         <v>1035</v>
       </c>
       <c r="I102" s="2">
-        <f t="shared" si="1"/>
+        <f>(F102-E102)/E102</f>
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -10116,11 +10190,11 @@
         <v>968</v>
       </c>
       <c r="I103" s="2">
-        <f t="shared" si="1"/>
+        <f>(F103-E103)/E103</f>
         <v>0.15200764818355642</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10137,11 +10211,11 @@
         <v>2750</v>
       </c>
       <c r="I104" s="2">
-        <f t="shared" si="1"/>
+        <f>(F104-E104)/E104</f>
         <v>0.12658746415403524</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10155,11 +10229,11 @@
         <v>840</v>
       </c>
       <c r="I105" s="2">
-        <f t="shared" si="1"/>
+        <f>(F105-E105)/E105</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10173,11 +10247,11 @@
         <v>802</v>
       </c>
       <c r="I106" s="2">
-        <f t="shared" si="1"/>
+        <f>(F106-E106)/E106</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10197,11 +10271,11 @@
         <v>4500</v>
       </c>
       <c r="I107" s="2">
-        <f t="shared" si="1"/>
+        <f>(F107-E107)/E107</f>
         <v>4.7968885047536734E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10218,11 +10292,11 @@
         <v>1940</v>
       </c>
       <c r="I108" s="2">
-        <f t="shared" si="1"/>
+        <f>(F108-E108)/E108</f>
         <v>0.38968481375358166</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10239,11 +10313,11 @@
         <v>1780</v>
       </c>
       <c r="I109" s="2">
-        <f t="shared" si="1"/>
+        <f>(F109-E109)/E109</f>
         <v>0.18429807052561545</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10257,11 +10331,11 @@
         <v>976</v>
       </c>
       <c r="I110" s="2">
-        <f t="shared" si="1"/>
+        <f>(F110-E110)/E110</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10275,11 +10349,11 @@
         <v>508</v>
       </c>
       <c r="I111" s="2">
-        <f t="shared" si="1"/>
+        <f>(F111-E111)/E111</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10299,11 +10373,11 @@
         <v>1540</v>
       </c>
       <c r="I112" s="2">
-        <f t="shared" si="1"/>
+        <f>(F112-E112)/E112</f>
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10323,11 +10397,11 @@
         <v>1331</v>
       </c>
       <c r="I113" s="2">
-        <f t="shared" si="1"/>
+        <f>(F113-E113)/E113</f>
         <v>0.12322946175637393</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -10341,11 +10415,11 @@
         <v>1018</v>
       </c>
       <c r="I114" s="2">
-        <f t="shared" si="1"/>
+        <f>(F114-E114)/E114</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10362,11 +10436,11 @@
         <v>950</v>
       </c>
       <c r="I115" s="2">
-        <f t="shared" si="1"/>
+        <f>(F115-E115)/E115</f>
         <v>0.10981308411214953</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10380,11 +10454,11 @@
         <v>1027</v>
       </c>
       <c r="I116" s="2">
-        <f t="shared" si="1"/>
+        <f>(F116-E116)/E116</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10398,11 +10472,11 @@
         <v>1360</v>
       </c>
       <c r="I117" s="2">
-        <f t="shared" si="1"/>
+        <f>(F117-E117)/E117</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -10422,11 +10496,11 @@
         <v>1810</v>
       </c>
       <c r="I118" s="2">
-        <f t="shared" si="1"/>
+        <f>(F118-E118)/E118</f>
         <v>7.1732199787460149E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10443,11 +10517,11 @@
         <v>288</v>
       </c>
       <c r="I119" s="2">
-        <f t="shared" si="1"/>
+        <f>(F119-E119)/E119</f>
         <v>0.22553191489361701</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -10467,7 +10541,7 @@
         <v>514</v>
       </c>
       <c r="I120" s="2">
-        <f t="shared" si="1"/>
+        <f>(F120-E120)/E120</f>
         <v>0.11678832116788321</v>
       </c>
     </row>
@@ -10485,11 +10559,11 @@
         <v>310</v>
       </c>
       <c r="I121" s="2">
-        <f t="shared" si="1"/>
+        <f>(F121-E121)/E121</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -10503,11 +10577,11 @@
         <v>352</v>
       </c>
       <c r="I122" s="2">
-        <f t="shared" si="1"/>
+        <f>(F122-E122)/E122</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -10524,11 +10598,11 @@
         <v>5250</v>
       </c>
       <c r="I123" s="2">
-        <f t="shared" si="1"/>
+        <f>(F123-E123)/E123</f>
         <v>0.17082961641391614</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -10542,11 +10616,11 @@
         <v>2246</v>
       </c>
       <c r="I124" s="2">
-        <f t="shared" si="1"/>
+        <f>(F124-E124)/E124</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -10560,11 +10634,11 @@
         <v>78</v>
       </c>
       <c r="I125" s="2">
-        <f t="shared" si="1"/>
+        <f>(F125-E125)/E125</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -10584,11 +10658,11 @@
         <v>3130</v>
       </c>
       <c r="I126" s="2">
-        <f t="shared" si="1"/>
+        <f>(F126-E126)/E126</f>
         <v>4.793028322440087E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -10609,11 +10683,11 @@
         <v>278</v>
       </c>
       <c r="I127" s="2">
-        <f t="shared" si="1"/>
+        <f>(F127-E127)/E127</f>
         <v>7.2664359861591699E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -10627,11 +10701,11 @@
         <v>1516</v>
       </c>
       <c r="I128" s="2">
-        <f t="shared" si="1"/>
+        <f>(F128-E128)/E128</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -10645,11 +10719,11 @@
         <v>1110</v>
       </c>
       <c r="I129" s="2">
-        <f t="shared" si="1"/>
+        <f>(F129-E129)/E129</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10666,11 +10740,11 @@
         <v>1000</v>
       </c>
       <c r="I130" s="2">
-        <f t="shared" si="1"/>
+        <f>(F130-E130)/E130</f>
         <v>0.17924528301886791</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10684,7 +10758,7 @@
         <v>1785</v>
       </c>
       <c r="I131" s="2">
-        <f t="shared" ref="I131:I194" si="2">(F131-E131)/E131</f>
+        <f>(F131-E131)/E131</f>
         <v>-1</v>
       </c>
     </row>
@@ -10711,11 +10785,11 @@
         <v>290</v>
       </c>
       <c r="I132" s="2">
-        <f t="shared" si="2"/>
+        <f>(F132-E132)/E132</f>
         <v>0.16719242902208201</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10732,11 +10806,11 @@
         <v>540</v>
       </c>
       <c r="I133" s="2">
-        <f t="shared" si="2"/>
+        <f>(F133-E133)/E133</f>
         <v>0.30120481927710846</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -10753,11 +10827,11 @@
         <v>1406</v>
       </c>
       <c r="I134" s="2">
-        <f t="shared" si="2"/>
+        <f>(F134-E134)/E134</f>
         <v>0.24204946996466431</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -10771,11 +10845,11 @@
         <v>421</v>
       </c>
       <c r="I135" s="2">
-        <f t="shared" si="2"/>
+        <f>(F135-E135)/E135</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10798,7 +10872,7 @@
         <v>1150</v>
       </c>
       <c r="I136" s="2">
-        <f t="shared" si="2"/>
+        <f>(F136-E136)/E136</f>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -10825,11 +10899,11 @@
         <v>290</v>
       </c>
       <c r="I137" s="2">
-        <f t="shared" si="2"/>
+        <f>(F137-E137)/E137</f>
         <v>0.16719242902208201</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -10849,11 +10923,11 @@
         <v>375</v>
       </c>
       <c r="I138" s="2">
-        <f t="shared" si="2"/>
+        <f>(F138-E138)/E138</f>
         <v>0.14329268292682926</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -10873,11 +10947,11 @@
         <v>16100</v>
       </c>
       <c r="I139" s="2">
-        <f t="shared" si="2"/>
+        <f>(F139-E139)/E139</f>
         <v>0.19462788454403798</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -10894,11 +10968,11 @@
         <v>1507</v>
       </c>
       <c r="I140" s="2">
-        <f t="shared" si="2"/>
+        <f>(F140-E140)/E140</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -10912,11 +10986,11 @@
         <v>1954</v>
       </c>
       <c r="I141" s="2">
-        <f t="shared" si="2"/>
+        <f>(F141-E141)/E141</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -10939,11 +11013,11 @@
         <v>3290</v>
       </c>
       <c r="I142" s="2">
-        <f t="shared" si="2"/>
+        <f>(F142-E142)/E142</f>
         <v>8.3406240886555849E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -10966,11 +11040,11 @@
         <v>1380</v>
       </c>
       <c r="I143" s="2">
-        <f t="shared" si="2"/>
+        <f>(F143-E143)/E143</f>
         <v>6.2194269741439552E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -10984,11 +11058,11 @@
         <v>46216</v>
       </c>
       <c r="I144" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F144-E144)/E144</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -10999,11 +11073,11 @@
         <v>46216</v>
       </c>
       <c r="I145" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F145-E145)/E145</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -11020,11 +11094,11 @@
         <v>370</v>
       </c>
       <c r="I146" s="2">
-        <f t="shared" si="2"/>
+        <f>(F146-E146)/E146</f>
         <v>0.15264797507788161</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -11041,11 +11115,11 @@
         <v>1025</v>
       </c>
       <c r="I147" s="2">
-        <f t="shared" si="2"/>
+        <f>(F147-E147)/E147</f>
         <v>0.17680826636050517</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -11068,11 +11142,11 @@
         <v>968</v>
       </c>
       <c r="I148" s="2">
-        <f t="shared" si="2"/>
+        <f>(F148-E148)/E148</f>
         <v>0.15200764818355642</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -11092,11 +11166,11 @@
         <v>727</v>
       </c>
       <c r="I149" s="2">
-        <f t="shared" si="2"/>
+        <f>(F149-E149)/E149</f>
         <v>9.2105263157894732E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -11113,11 +11187,11 @@
         <v>351</v>
       </c>
       <c r="I150" s="2">
-        <f t="shared" si="2"/>
+        <f>(F150-E150)/E150</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -11131,11 +11205,11 @@
         <v>308</v>
       </c>
       <c r="I151" s="2">
-        <f t="shared" si="2"/>
+        <f>(F151-E151)/E151</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -11152,11 +11226,11 @@
         <v>3800</v>
       </c>
       <c r="I152" s="2">
-        <f t="shared" si="2"/>
+        <f>(F152-E152)/E152</f>
         <v>0.18527760449157829</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -11173,11 +11247,11 @@
         <v>1450</v>
       </c>
       <c r="I153" s="2">
-        <f t="shared" si="2"/>
+        <f>(F153-E153)/E153</f>
         <v>0.18755118755118755</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -11197,11 +11271,11 @@
         <v>200</v>
       </c>
       <c r="I154" s="2">
-        <f t="shared" si="2"/>
+        <f>(F154-E154)/E154</f>
         <v>0.19047619047619047</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -11221,11 +11295,11 @@
         <v>565</v>
       </c>
       <c r="I155" s="2">
-        <f t="shared" si="2"/>
+        <f>(F155-E155)/E155</f>
         <v>0.25835189309576839</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -11242,11 +11316,11 @@
         <v>1604</v>
       </c>
       <c r="I156" s="2">
-        <f t="shared" si="2"/>
+        <f>(F156-E156)/E156</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -11263,11 +11337,11 @@
         <v>1826</v>
       </c>
       <c r="I157" s="2">
-        <f t="shared" si="2"/>
+        <f>(F157-E157)/E157</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -11287,11 +11361,11 @@
         <v>1790</v>
       </c>
       <c r="I158" s="2">
-        <f t="shared" si="2"/>
+        <f>(F158-E158)/E158</f>
         <v>-2.717391304347826E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -11314,11 +11388,11 @@
         <v>1800</v>
       </c>
       <c r="I159" s="2">
-        <f t="shared" si="2"/>
+        <f>(F159-E159)/E159</f>
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -11335,11 +11409,11 @@
         <v>7203</v>
       </c>
       <c r="I160" s="2">
-        <f t="shared" si="2"/>
+        <f>(F160-E160)/E160</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -11356,11 +11430,11 @@
         <v>4133</v>
       </c>
       <c r="I161" s="2">
-        <f t="shared" si="2"/>
+        <f>(F161-E161)/E161</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -11380,11 +11454,11 @@
         <v>1530</v>
       </c>
       <c r="I162" s="2">
-        <f t="shared" si="2"/>
+        <f>(F162-E162)/E162</f>
         <v>0.2707641196013289</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -11404,11 +11478,11 @@
         <v>250</v>
       </c>
       <c r="I163" s="2">
-        <f t="shared" si="2"/>
+        <f>(F163-E163)/E163</f>
         <v>0.15740740740740741</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -11431,11 +11505,11 @@
         <v>1035</v>
       </c>
       <c r="I164" s="2">
-        <f t="shared" si="2"/>
+        <f>(F164-E164)/E164</f>
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -11452,11 +11526,11 @@
         <v>420</v>
       </c>
       <c r="I165" s="2">
-        <f t="shared" si="2"/>
+        <f>(F165-E165)/E165</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -11473,11 +11547,11 @@
         <v>1900</v>
       </c>
       <c r="I166" s="2">
-        <f t="shared" si="2"/>
+        <f>(F166-E166)/E166</f>
         <v>0.25827814569536423</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -11494,11 +11568,11 @@
         <v>2620</v>
       </c>
       <c r="I167" s="2">
-        <f t="shared" si="2"/>
+        <f>(F167-E167)/E167</f>
         <v>0.19908466819221968</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -11509,11 +11583,11 @@
         <v>46220</v>
       </c>
       <c r="I168" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F168-E168)/E168</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -11524,11 +11598,11 @@
         <v>46220</v>
       </c>
       <c r="I169" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F169-E169)/E169</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -11548,11 +11622,11 @@
         <v>695</v>
       </c>
       <c r="I170" s="2">
-        <f t="shared" si="2"/>
+        <f>(F170-E170)/E170</f>
         <v>7.586206896551724E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -11575,11 +11649,11 @@
         <v>415</v>
       </c>
       <c r="I171" s="2">
-        <f t="shared" si="2"/>
+        <f>(F171-E171)/E171</f>
         <v>9.1954022988505746E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -11593,11 +11667,11 @@
         <v>310</v>
       </c>
       <c r="I172" s="2">
-        <f t="shared" si="2"/>
+        <f>(F172-E172)/E172</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -11611,11 +11685,11 @@
         <v>204</v>
       </c>
       <c r="I173" s="2">
-        <f t="shared" si="2"/>
+        <f>(F173-E173)/E173</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -11632,11 +11706,11 @@
         <v>1750</v>
       </c>
       <c r="I174" s="2">
-        <f t="shared" si="2"/>
+        <f>(F174-E174)/E174</f>
         <v>0.21191135734072022</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -11653,11 +11727,11 @@
         <v>1470</v>
       </c>
       <c r="I175" s="2">
-        <f t="shared" si="2"/>
+        <f>(F175-E175)/E175</f>
         <v>0.1883589329021827</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -11674,11 +11748,11 @@
         <v>1586</v>
       </c>
       <c r="I176" s="2">
-        <f t="shared" si="2"/>
+        <f>(F176-E176)/E176</f>
         <v>0.12322946175637393</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -11701,11 +11775,11 @@
         <v>3240</v>
       </c>
       <c r="I177" s="2">
-        <f t="shared" si="2"/>
+        <f>(F177-E177)/E177</f>
         <v>8.7367178276269192E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -11719,11 +11793,11 @@
         <v>1348</v>
       </c>
       <c r="I178" s="2">
-        <f t="shared" si="2"/>
+        <f>(F178-E178)/E178</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -11740,11 +11814,11 @@
         <v>2260</v>
       </c>
       <c r="I179" s="2">
-        <f t="shared" si="2"/>
+        <f>(F179-E179)/E179</f>
         <v>0.21374865735767992</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11764,11 +11838,11 @@
         <v>1800</v>
       </c>
       <c r="I180" s="2">
-        <f t="shared" si="2"/>
+        <f>(F180-E180)/E180</f>
         <v>8.4905660377358486E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11779,11 +11853,11 @@
         <v>46224</v>
       </c>
       <c r="I181" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F181-E181)/E181</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -11794,11 +11868,11 @@
         <v>46224</v>
       </c>
       <c r="I182" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F182-E182)/E182</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -11815,11 +11889,11 @@
         <v>800</v>
       </c>
       <c r="I183" s="2">
-        <f t="shared" si="2"/>
+        <f>(F183-E183)/E183</f>
         <v>0.2841091492776886</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -11836,11 +11910,11 @@
         <v>12096</v>
       </c>
       <c r="I184" s="2">
-        <f t="shared" si="2"/>
+        <f>(F184-E184)/E184</f>
         <v>0.16262975778546712</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -11860,11 +11934,11 @@
         <v>4450</v>
       </c>
       <c r="I185" s="2">
-        <f t="shared" si="2"/>
+        <f>(F185-E185)/E185</f>
         <v>2.9463116542994324E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -11875,11 +11949,11 @@
         <v>46225</v>
       </c>
       <c r="I186" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F186-E186)/E186</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -11890,11 +11964,11 @@
         <v>46225</v>
       </c>
       <c r="I187" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F187-E187)/E187</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -11914,11 +11988,11 @@
         <v>95.7</v>
       </c>
       <c r="I188" s="2">
-        <f t="shared" si="2"/>
+        <f>(F188-E188)/E188</f>
         <v>-2.077151335311566E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -11932,11 +12006,11 @@
         <v>373</v>
       </c>
       <c r="I189" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f>(F189-E189)/E189</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -11959,11 +12033,11 @@
         <v>1450</v>
       </c>
       <c r="I190" s="2">
-        <f t="shared" si="2"/>
+        <f>(F190-E190)/E190</f>
         <v>7.0950468540829981E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -11977,11 +12051,11 @@
         <v>448</v>
       </c>
       <c r="I191" s="2">
-        <f t="shared" si="2"/>
+        <f>(F191-E191)/E191</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -11998,11 +12072,11 @@
         <v>726</v>
       </c>
       <c r="I192" s="2">
-        <f t="shared" si="2"/>
+        <f>(F192-E192)/E192</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -12022,11 +12096,11 @@
         <v>1380</v>
       </c>
       <c r="I193" s="2">
-        <f t="shared" si="2"/>
+        <f>(F193-E193)/E193</f>
         <v>0.20209059233449478</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -12040,11 +12114,11 @@
         <v>188</v>
       </c>
       <c r="I194" s="2">
-        <f t="shared" si="2"/>
+        <f>(F194-E194)/E194</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -12058,11 +12132,11 @@
         <v>109</v>
       </c>
       <c r="I195" s="2">
-        <f t="shared" ref="I195:I229" si="3">(F195-E195)/E195</f>
+        <f>(F195-E195)/E195</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -12082,11 +12156,11 @@
         <v>3145</v>
       </c>
       <c r="I196" s="2">
-        <f t="shared" si="3"/>
+        <f>(F196-E196)/E196</f>
         <v>5.3869969040247677E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -12103,11 +12177,11 @@
         <v>1329</v>
       </c>
       <c r="I197" s="2">
-        <f t="shared" si="3"/>
+        <f>(F197-E197)/E197</f>
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -12127,11 +12201,11 @@
         <v>664</v>
       </c>
       <c r="I198" s="2">
-        <f t="shared" si="3"/>
+        <f>(F198-E198)/E198</f>
         <v>1.5414546542951144E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -12151,11 +12225,11 @@
         <v>1833</v>
       </c>
       <c r="I199" s="2">
-        <f t="shared" si="3"/>
+        <f>(F199-E199)/E199</f>
         <v>1.4084507042253521E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -12166,11 +12240,11 @@
         <v>46227</v>
       </c>
       <c r="I200" s="2" t="e">
-        <f t="shared" si="3"/>
+        <f>(F200-E200)/E200</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -12190,11 +12264,11 @@
         <v>2360</v>
       </c>
       <c r="I201" s="2">
-        <f t="shared" si="3"/>
+        <f>(F201-E201)/E201</f>
         <v>6.1910619106191063E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -12211,11 +12285,11 @@
         <v>1283</v>
       </c>
       <c r="I202" s="2">
-        <f t="shared" si="3"/>
+        <f>(F202-E202)/E202</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -12229,11 +12303,11 @@
         <v>81</v>
       </c>
       <c r="I203" s="2">
-        <f t="shared" si="3"/>
+        <f>(F203-E203)/E203</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -12250,11 +12324,11 @@
         <v>1980</v>
       </c>
       <c r="I204" s="2">
-        <f t="shared" si="3"/>
+        <f>(F204-E204)/E204</f>
         <v>0.23672704559650218</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -12274,11 +12348,11 @@
         <v>1035</v>
       </c>
       <c r="I205" s="2">
-        <f t="shared" si="3"/>
+        <f>(F205-E205)/E205</f>
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -12289,11 +12363,11 @@
         <v>46231</v>
       </c>
       <c r="I206" s="2" t="e">
-        <f t="shared" si="3"/>
+        <f>(F206-E206)/E206</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -12316,11 +12390,11 @@
         <v>555</v>
       </c>
       <c r="I207" s="2">
-        <f t="shared" si="3"/>
+        <f>(F207-E207)/E207</f>
         <v>7.5174825174825169E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -12334,11 +12408,11 @@
         <v>46231</v>
       </c>
       <c r="I208" s="2" t="e">
-        <f t="shared" si="3"/>
+        <f>(F208-E208)/E208</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -12355,11 +12429,11 @@
         <v>240</v>
       </c>
       <c r="I209" s="2">
-        <f t="shared" si="3"/>
+        <f>(F209-E209)/E209</f>
         <v>0.29729729729729731</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12370,11 +12444,11 @@
         <v>46231</v>
       </c>
       <c r="I210" s="2" t="e">
-        <f t="shared" si="3"/>
+        <f>(F210-E210)/E210</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12394,11 +12468,11 @@
         <v>1430</v>
       </c>
       <c r="I211" s="2">
-        <f t="shared" si="3"/>
+        <f>(F211-E211)/E211</f>
         <v>0.19266055045871561</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12421,11 +12495,11 @@
         <v>1035</v>
       </c>
       <c r="I212" s="2">
-        <f t="shared" si="3"/>
+        <f>(F212-E212)/E212</f>
         <v>0.17402826855123674</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12445,11 +12519,11 @@
         <v>521</v>
       </c>
       <c r="I213" s="2">
-        <f t="shared" si="3"/>
+        <f>(F213-E213)/E213</f>
         <v>2.0952380952380951E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12469,11 +12543,11 @@
         <v>1200</v>
       </c>
       <c r="I214" s="2">
-        <f t="shared" si="3"/>
+        <f>(F214-E214)/E214</f>
         <v>3.4426229508196723E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12496,11 +12570,11 @@
         <v>4250</v>
       </c>
       <c r="I215" s="2">
-        <f t="shared" si="3"/>
+        <f>(F215-E215)/E215</f>
         <v>-3.6054081121682527E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12520,7 +12594,7 @@
         <v>7300</v>
       </c>
       <c r="I216" s="2">
-        <f t="shared" si="3"/>
+        <f>(F216-E216)/E216</f>
         <v>-1</v>
       </c>
     </row>
@@ -12544,11 +12618,11 @@
         <v>315</v>
       </c>
       <c r="I217" s="2">
-        <f t="shared" si="3"/>
+        <f>(F217-E217)/E217</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12568,11 +12642,11 @@
         <v>4550</v>
       </c>
       <c r="I218" s="2">
-        <f t="shared" si="3"/>
+        <f>(F218-E218)/E218</f>
         <v>0.18705974432559352</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12592,11 +12666,11 @@
         <v>2140</v>
       </c>
       <c r="I219" s="2">
-        <f t="shared" si="3"/>
+        <f>(F219-E219)/E219</f>
         <v>0.22076440387906446</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12619,11 +12693,11 @@
         <v>3870</v>
       </c>
       <c r="I220" s="2">
-        <f t="shared" si="3"/>
+        <f>(F220-E220)/E220</f>
         <v>0.2133117633464294</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12646,11 +12720,11 @@
         <v>3870</v>
       </c>
       <c r="I221" s="2">
-        <f t="shared" si="3"/>
+        <f>(F221-E221)/E221</f>
         <v>0.2133117633464294</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
@@ -12670,11 +12744,11 @@
         <v>1630</v>
       </c>
       <c r="I222" s="2">
-        <f t="shared" si="3"/>
+        <f>(F222-E222)/E222</f>
         <v>0.21370067014147431</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
@@ -12694,11 +12768,11 @@
         <v>1765</v>
       </c>
       <c r="I223" s="2">
-        <f t="shared" si="3"/>
+        <f>(F223-E223)/E223</f>
         <v>0.15889691398555483</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
@@ -12712,11 +12786,11 @@
         <v>46233</v>
       </c>
       <c r="I224" s="2" t="e">
-        <f t="shared" si="3"/>
+        <f>(F224-E224)/E224</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
@@ -12730,11 +12804,11 @@
         <v>46233</v>
       </c>
       <c r="I225" s="2" t="e">
-        <f t="shared" si="3"/>
+        <f>(F225-E225)/E225</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
@@ -12748,11 +12822,11 @@
         <v>46233</v>
       </c>
       <c r="I226" s="2" t="e">
-        <f t="shared" si="3"/>
+        <f>(F226-E226)/E226</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
@@ -12766,11 +12840,11 @@
         <v>1277</v>
       </c>
       <c r="I227" s="2">
-        <f t="shared" si="3"/>
+        <f>(F227-E227)/E227</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
@@ -12781,11 +12855,11 @@
         <v>46233</v>
       </c>
       <c r="I228" s="2" t="e">
-        <f t="shared" si="3"/>
+        <f>(F228-E228)/E228</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
@@ -12808,11 +12882,11 @@
         <v>1570</v>
       </c>
       <c r="I229" s="2">
-        <f t="shared" si="3"/>
+        <f>(F229-E229)/E229</f>
         <v>7.3619631901840496E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
@@ -12839,7 +12913,7 @@
         <v>0.1630144307856761</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
@@ -12856,7 +12930,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
@@ -12867,7 +12941,7 @@
         <v>46237</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
@@ -12881,7 +12955,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
@@ -12895,7 +12969,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
@@ -12909,7 +12983,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
@@ -12929,7 +13003,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
@@ -12946,11 +13020,11 @@
       <c r="F237">
         <v>751</v>
       </c>
-      <c r="G237">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="G237" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
@@ -12964,7 +13038,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
@@ -12984,7 +13058,7 @@
         <v>294.8</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
@@ -13004,7 +13078,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
@@ -13024,7 +13098,7 @@
         <v>5450</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
@@ -13041,7 +13115,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
@@ -13058,7 +13132,7 @@
         <v>6610</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
@@ -13078,7 +13152,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
@@ -13106,7 +13180,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
@@ -13117,7 +13191,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
@@ -13128,7 +13202,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
@@ -13148,7 +13222,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
@@ -13165,7 +13239,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13182,7 +13256,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
@@ -13202,7 +13276,7 @@
         <v>140.4</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
@@ -13222,7 +13296,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
@@ -13233,7 +13307,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>255</v>
       </c>
@@ -13253,7 +13327,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>256</v>
       </c>
@@ -13273,7 +13347,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>257</v>
       </c>
@@ -13290,7 +13364,7 @@
         <v>12190</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>258</v>
       </c>
@@ -13304,7 +13378,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>259</v>
       </c>
@@ -13327,7 +13401,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>260</v>
       </c>
@@ -13344,7 +13418,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>261</v>
       </c>
@@ -13361,7 +13435,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>262</v>
       </c>
@@ -13372,7 +13446,7 @@
         <v>46241</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>263</v>
       </c>
@@ -13386,7 +13460,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>264</v>
       </c>
@@ -13400,7 +13474,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>265</v>
       </c>
@@ -13423,7 +13497,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>266</v>
       </c>
@@ -13437,7 +13511,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>267</v>
       </c>
@@ -13451,7 +13525,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>268</v>
       </c>
@@ -13465,7 +13539,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>269</v>
       </c>
@@ -13485,7 +13559,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>270</v>
       </c>
@@ -13502,7 +13576,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>271</v>
       </c>
@@ -13519,7 +13593,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>272</v>
       </c>
@@ -13539,7 +13613,7 @@
         <v>3870</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>273</v>
       </c>
@@ -13559,7 +13633,7 @@
         <v>228.8</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>274</v>
       </c>
@@ -13582,7 +13656,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>275</v>
       </c>
@@ -13596,7 +13670,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>276</v>
       </c>
@@ -13610,7 +13684,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>277</v>
       </c>
@@ -13627,7 +13701,7 @@
         <v>3080</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>278</v>
       </c>
@@ -13644,7 +13718,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>279</v>
       </c>
@@ -13664,7 +13738,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>280</v>
       </c>
@@ -13687,7 +13761,7 @@
         <v>8350</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>281</v>
       </c>
@@ -13710,7 +13784,7 @@
         <v>2590</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>282</v>
       </c>
@@ -13724,7 +13798,7 @@
         <v>18770</v>
       </c>
     </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>283</v>
       </c>
@@ -13738,7 +13812,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>284</v>
       </c>
@@ -13752,7 +13826,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>285</v>
       </c>
@@ -13769,7 +13843,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>286</v>
       </c>
@@ -13792,7 +13866,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>287</v>
       </c>
@@ -13806,7 +13880,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>288</v>
       </c>
@@ -13820,7 +13894,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>289</v>
       </c>
@@ -13837,7 +13911,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>290</v>
       </c>
@@ -13854,7 +13928,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>291</v>
       </c>
@@ -13877,7 +13951,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>292</v>
       </c>
@@ -13891,7 +13965,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>293</v>
       </c>
@@ -13905,7 +13979,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>294</v>
       </c>
@@ -13922,7 +13996,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>295</v>
       </c>
@@ -13939,7 +14013,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>296</v>
       </c>
@@ -13956,7 +14030,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>297</v>
       </c>
@@ -13979,7 +14053,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>298</v>
       </c>
@@ -13996,7 +14070,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>299</v>
       </c>
@@ -14007,7 +14081,7 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>300</v>
       </c>
@@ -14027,7 +14101,7 @@
         <v>2590</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>301</v>
       </c>
@@ -14047,7 +14121,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>302</v>
       </c>
@@ -14067,7 +14141,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>303</v>
       </c>
@@ -14084,7 +14158,7 @@
         <v>14130</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>304</v>
       </c>
@@ -14098,7 +14172,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>305</v>
       </c>
@@ -14118,7 +14192,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>306</v>
       </c>
@@ -14141,7 +14215,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>307</v>
       </c>
@@ -14161,7 +14235,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>308</v>
       </c>
@@ -14181,7 +14255,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>309</v>
       </c>
@@ -14198,7 +14272,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>310</v>
       </c>
@@ -14215,7 +14289,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>311</v>
       </c>
@@ -14238,7 +14312,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>312</v>
       </c>
@@ -14255,7 +14329,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>313</v>
       </c>
@@ -14278,7 +14352,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>314</v>
       </c>
@@ -14301,7 +14375,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>315</v>
       </c>
@@ -14318,7 +14392,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>316</v>
       </c>
@@ -14332,7 +14406,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>317</v>
       </c>
@@ -14349,7 +14423,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>318</v>
       </c>
@@ -14366,7 +14440,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>319</v>
       </c>
@@ -14389,38 +14463,1717 @@
         <v>225</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>320</v>
       </c>
-    </row>
-    <row r="321" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B320" t="s">
+        <v>258</v>
+      </c>
+      <c r="C320" t="s">
+        <v>176</v>
+      </c>
+      <c r="D320" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E320">
+        <v>1812</v>
+      </c>
+      <c r="F320">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>321</v>
       </c>
-    </row>
-    <row r="322" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B321" t="s">
+        <v>247</v>
+      </c>
+      <c r="C321" t="s">
+        <v>259</v>
+      </c>
+      <c r="D321" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E321">
+        <v>14462</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>322</v>
       </c>
-    </row>
-    <row r="323" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B322" t="s">
+        <v>260</v>
+      </c>
+      <c r="C322" t="s">
+        <v>259</v>
+      </c>
+      <c r="D322" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E322">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>323</v>
       </c>
-    </row>
-    <row r="324" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B323" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C323" t="s">
+        <v>148</v>
+      </c>
+      <c r="D323" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E323">
+        <v>1174</v>
+      </c>
+      <c r="F323">
+        <v>1250</v>
+      </c>
+      <c r="G323">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>324</v>
       </c>
+      <c r="B324" t="s">
+        <v>261</v>
+      </c>
+      <c r="C324" t="s">
+        <v>123</v>
+      </c>
+      <c r="D324" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E324">
+        <v>1240</v>
+      </c>
+      <c r="F324">
+        <v>1326</v>
+      </c>
+      <c r="G324">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A325">
+        <v>325</v>
+      </c>
+      <c r="B325" t="s">
+        <v>226</v>
+      </c>
+      <c r="C325" t="s">
+        <v>124</v>
+      </c>
+      <c r="D325" s="1">
+        <v>46255</v>
+      </c>
+      <c r="E325">
+        <v>257</v>
+      </c>
+      <c r="F325">
+        <v>320</v>
+      </c>
+      <c r="G325">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A326">
+        <v>326</v>
+      </c>
+      <c r="B326" t="s">
+        <v>237</v>
+      </c>
+      <c r="C326" t="s">
+        <v>176</v>
+      </c>
+      <c r="D326" s="1">
+        <v>46255</v>
+      </c>
+      <c r="E326">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A327">
+        <v>327</v>
+      </c>
+      <c r="B327" t="s">
+        <v>262</v>
+      </c>
+      <c r="C327" t="s">
+        <v>176</v>
+      </c>
+      <c r="D327" s="1">
+        <v>46255</v>
+      </c>
+      <c r="E327">
+        <v>252</v>
+      </c>
+      <c r="F327">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A328">
+        <v>328</v>
+      </c>
+      <c r="B328" t="s">
+        <v>208</v>
+      </c>
+      <c r="D328" s="1">
+        <v>46255</v>
+      </c>
+      <c r="E328">
+        <v>5674</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A329">
+        <v>329</v>
+      </c>
+      <c r="B329" t="s">
+        <v>263</v>
+      </c>
+      <c r="D329" s="1">
+        <v>46255</v>
+      </c>
+      <c r="E329">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A330">
+        <v>330</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C330" t="s">
+        <v>148</v>
+      </c>
+      <c r="D330" s="1">
+        <v>46255</v>
+      </c>
+      <c r="E330">
+        <v>328</v>
+      </c>
+      <c r="F330">
+        <v>350</v>
+      </c>
+      <c r="G330">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A331">
+        <v>331</v>
+      </c>
+      <c r="B331" t="s">
+        <v>226</v>
+      </c>
+      <c r="C331" t="s">
+        <v>196</v>
+      </c>
+      <c r="D331" s="1">
+        <v>46258</v>
+      </c>
+      <c r="E331">
+        <v>257</v>
+      </c>
+      <c r="F331">
+        <v>320</v>
+      </c>
+      <c r="G331">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A332">
+        <v>332</v>
+      </c>
+      <c r="B332" t="s">
+        <v>264</v>
+      </c>
+      <c r="D332" s="1">
+        <v>46258</v>
+      </c>
+      <c r="E332">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A333">
+        <v>333</v>
+      </c>
+      <c r="B333" t="s">
+        <v>265</v>
+      </c>
+      <c r="D333" s="1">
+        <v>46258</v>
+      </c>
+      <c r="E333">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A334">
+        <v>334</v>
+      </c>
+      <c r="B334" t="s">
+        <v>237</v>
+      </c>
+      <c r="D334" s="1">
+        <v>46258</v>
+      </c>
+      <c r="E334">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A335">
+        <v>335</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D335" s="1">
+        <v>46258</v>
+      </c>
+      <c r="E335">
+        <v>14850</v>
+      </c>
+      <c r="F335">
+        <v>15900</v>
+      </c>
+      <c r="G335">
+        <v>14100</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A336">
+        <v>336</v>
+      </c>
+      <c r="B336" t="s">
+        <v>226</v>
+      </c>
+      <c r="C336" t="s">
+        <v>124</v>
+      </c>
+      <c r="D336" s="1">
+        <v>46259</v>
+      </c>
+      <c r="E336">
+        <v>257</v>
+      </c>
+      <c r="F336">
+        <v>320</v>
+      </c>
+      <c r="G336">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A337">
+        <v>337</v>
+      </c>
+      <c r="B337" t="s">
+        <v>108</v>
+      </c>
+      <c r="C337" t="s">
+        <v>176</v>
+      </c>
+      <c r="D337" s="1">
+        <v>46259</v>
+      </c>
+      <c r="E337">
+        <v>5080</v>
+      </c>
+      <c r="F337">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A338">
+        <v>338</v>
+      </c>
+      <c r="B338" t="s">
+        <v>90</v>
+      </c>
+      <c r="C338" t="s">
+        <v>176</v>
+      </c>
+      <c r="D338" s="1">
+        <v>46259</v>
+      </c>
+      <c r="E338">
+        <v>797</v>
+      </c>
+      <c r="F338">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A339">
+        <v>339</v>
+      </c>
+      <c r="B339" t="s">
+        <v>266</v>
+      </c>
+      <c r="D339" s="1">
+        <v>46259</v>
+      </c>
+      <c r="E339">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A340">
+        <v>340</v>
+      </c>
+      <c r="B340" t="s">
+        <v>267</v>
+      </c>
+      <c r="D340" s="1">
+        <v>46259</v>
+      </c>
+      <c r="E340">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A341">
+        <v>341</v>
+      </c>
+      <c r="B341" t="s">
+        <v>212</v>
+      </c>
+      <c r="C341" t="s">
+        <v>148</v>
+      </c>
+      <c r="D341" s="1">
+        <v>46259</v>
+      </c>
+      <c r="E341">
+        <v>4114</v>
+      </c>
+      <c r="F341">
+        <v>4400</v>
+      </c>
+      <c r="G341">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A342">
+        <v>342</v>
+      </c>
+      <c r="B342" t="s">
+        <v>268</v>
+      </c>
+      <c r="C342" t="s">
+        <v>176</v>
+      </c>
+      <c r="D342" s="1">
+        <v>46260</v>
+      </c>
+      <c r="E342">
+        <v>438</v>
+      </c>
+      <c r="F342">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A343">
+        <v>343</v>
+      </c>
+      <c r="B343" t="s">
+        <v>88</v>
+      </c>
+      <c r="C343" t="s">
+        <v>176</v>
+      </c>
+      <c r="D343" s="1">
+        <v>46260</v>
+      </c>
+      <c r="E343">
+        <v>448</v>
+      </c>
+      <c r="F343">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A344">
+        <v>344</v>
+      </c>
+      <c r="B344" t="s">
+        <v>269</v>
+      </c>
+      <c r="D344" s="1">
+        <v>46260</v>
+      </c>
+      <c r="E344">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A345">
+        <v>345</v>
+      </c>
+      <c r="B345" t="s">
+        <v>188</v>
+      </c>
+      <c r="D345" s="1">
+        <v>46260</v>
+      </c>
+      <c r="E345">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A346">
+        <v>346</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C346" t="s">
+        <v>148</v>
+      </c>
+      <c r="D346" s="1">
+        <v>46260</v>
+      </c>
+      <c r="E346">
+        <v>8744</v>
+      </c>
+      <c r="F346">
+        <v>9256</v>
+      </c>
+      <c r="G346">
+        <v>8488</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A347">
+        <v>347</v>
+      </c>
+      <c r="B347" t="s">
+        <v>129</v>
+      </c>
+      <c r="C347" t="s">
+        <v>124</v>
+      </c>
+      <c r="D347" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E347">
+        <v>1406</v>
+      </c>
+      <c r="F347">
+        <v>1620</v>
+      </c>
+      <c r="G347">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A348">
+        <v>348</v>
+      </c>
+      <c r="B348" t="s">
+        <v>270</v>
+      </c>
+      <c r="C348" t="s">
+        <v>176</v>
+      </c>
+      <c r="D348" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E348">
+        <v>2155</v>
+      </c>
+      <c r="F348">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A349">
+        <v>349</v>
+      </c>
+      <c r="B349" t="s">
+        <v>271</v>
+      </c>
+      <c r="C349" t="s">
+        <v>176</v>
+      </c>
+      <c r="D349" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E349">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A350">
+        <v>350</v>
+      </c>
+      <c r="B350" t="s">
+        <v>272</v>
+      </c>
+      <c r="D350" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E350">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A351">
+        <v>351</v>
+      </c>
+      <c r="B351" t="s">
+        <v>273</v>
+      </c>
+      <c r="D351" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E351">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A352">
+        <v>352</v>
+      </c>
+      <c r="B352" t="s">
+        <v>221</v>
+      </c>
+      <c r="C352" t="s">
+        <v>148</v>
+      </c>
+      <c r="D352" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E352">
+        <v>1341</v>
+      </c>
+      <c r="F352">
+        <v>1439</v>
+      </c>
+      <c r="G352">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A353">
+        <v>353</v>
+      </c>
+      <c r="B353" t="s">
+        <v>274</v>
+      </c>
+      <c r="D353" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E353">
+        <v>110</v>
+      </c>
+      <c r="F353">
+        <v>115</v>
+      </c>
+      <c r="G353">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A354">
+        <v>354</v>
+      </c>
+      <c r="B354" t="s">
+        <v>275</v>
+      </c>
+      <c r="D354" s="1">
+        <v>46261</v>
+      </c>
+      <c r="E354">
+        <v>11.26</v>
+      </c>
+      <c r="F354">
+        <v>11.92</v>
+      </c>
+      <c r="G354">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A355">
+        <v>355</v>
+      </c>
+      <c r="B355" t="s">
+        <v>129</v>
+      </c>
+      <c r="C355" t="s">
+        <v>241</v>
+      </c>
+      <c r="D355" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E355">
+        <v>1406</v>
+      </c>
+      <c r="F355">
+        <v>1620</v>
+      </c>
+      <c r="G355">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A356">
+        <v>356</v>
+      </c>
+      <c r="B356" t="s">
+        <v>89</v>
+      </c>
+      <c r="D356" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E356">
+        <v>14711</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A357">
+        <v>357</v>
+      </c>
+      <c r="B357" t="s">
+        <v>269</v>
+      </c>
+      <c r="D357" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E357">
+        <v>3169</v>
+      </c>
+      <c r="F357">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A358">
+        <v>358</v>
+      </c>
+      <c r="B358" t="s">
+        <v>236</v>
+      </c>
+      <c r="C358" t="s">
+        <v>241</v>
+      </c>
+      <c r="D358" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E358">
+        <v>20580</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A359">
+        <v>359</v>
+      </c>
+      <c r="B359" t="s">
+        <v>277</v>
+      </c>
+      <c r="D359" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E359">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A360">
+        <v>360</v>
+      </c>
+      <c r="B360" t="s">
+        <v>156</v>
+      </c>
+      <c r="D360" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E360">
+        <v>819</v>
+      </c>
+      <c r="F360">
+        <v>870</v>
+      </c>
+      <c r="G360">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A361">
+        <v>361</v>
+      </c>
+      <c r="B361" t="s">
+        <v>10</v>
+      </c>
+      <c r="D361" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E361">
+        <v>1627</v>
+      </c>
+      <c r="F361">
+        <v>1655</v>
+      </c>
+      <c r="G361">
+        <v>1604.5</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A362">
+        <v>362</v>
+      </c>
+      <c r="B362" t="s">
+        <v>9</v>
+      </c>
+      <c r="D362" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E362">
+        <v>1965</v>
+      </c>
+      <c r="F362">
+        <v>1990</v>
+      </c>
+      <c r="G362">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A363">
+        <v>363</v>
+      </c>
+      <c r="B363" t="s">
+        <v>278</v>
+      </c>
+      <c r="D363" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E363">
+        <v>1072</v>
+      </c>
+      <c r="F363">
+        <v>1105</v>
+      </c>
+      <c r="G363">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A364">
+        <v>364</v>
+      </c>
+      <c r="B364" t="s">
+        <v>279</v>
+      </c>
+      <c r="D364" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E364">
+        <v>2321</v>
+      </c>
+      <c r="F364">
+        <v>2850</v>
+      </c>
+      <c r="G364">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A365">
+        <v>365</v>
+      </c>
+      <c r="B365" t="s">
+        <v>280</v>
+      </c>
+      <c r="D365" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E365">
+        <v>563</v>
+      </c>
+      <c r="F365">
+        <v>577</v>
+      </c>
+      <c r="G365">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A366">
+        <v>366</v>
+      </c>
+      <c r="B366" t="s">
+        <v>32</v>
+      </c>
+      <c r="C366" t="s">
+        <v>123</v>
+      </c>
+      <c r="D366" s="1">
+        <v>46265</v>
+      </c>
+      <c r="E366">
+        <v>331.65</v>
+      </c>
+      <c r="F366">
+        <v>358.65</v>
+      </c>
+      <c r="G366">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A367">
+        <v>367</v>
+      </c>
+      <c r="B367" t="s">
+        <v>129</v>
+      </c>
+      <c r="C367" t="s">
+        <v>124</v>
+      </c>
+      <c r="D367" s="1">
+        <v>46265</v>
+      </c>
+      <c r="E367">
+        <v>1406</v>
+      </c>
+      <c r="F367">
+        <v>1620</v>
+      </c>
+      <c r="G367">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A368">
+        <v>368</v>
+      </c>
+      <c r="B368" t="s">
+        <v>180</v>
+      </c>
+      <c r="C368" t="s">
+        <v>191</v>
+      </c>
+      <c r="D368" s="1">
+        <v>46265</v>
+      </c>
+      <c r="E368">
+        <v>3332</v>
+      </c>
+      <c r="F368">
+        <v>4108</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A369">
+        <v>369</v>
+      </c>
+      <c r="B369" t="s">
+        <v>14</v>
+      </c>
+      <c r="C369" t="s">
+        <v>191</v>
+      </c>
+      <c r="D369" s="1">
+        <v>46265</v>
+      </c>
+      <c r="E369">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A370">
+        <v>370</v>
+      </c>
+      <c r="B370" t="s">
+        <v>281</v>
+      </c>
+      <c r="D370" s="1">
+        <v>46265</v>
+      </c>
+      <c r="E370">
+        <v>8059</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A371">
+        <v>371</v>
+      </c>
+      <c r="B371" t="s">
+        <v>282</v>
+      </c>
+      <c r="D371" s="1">
+        <v>46265</v>
+      </c>
+      <c r="E371">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A372">
+        <v>372</v>
+      </c>
+      <c r="B372" t="s">
+        <v>271</v>
+      </c>
+      <c r="C372" t="s">
+        <v>148</v>
+      </c>
+      <c r="D372" s="1">
+        <v>46265</v>
+      </c>
+      <c r="E372">
+        <v>200</v>
+      </c>
+      <c r="F372">
+        <v>210</v>
+      </c>
+      <c r="G372">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A373">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A374">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A375">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A376">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A377">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A378">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A379">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A380">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A381">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A382">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A383">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A384">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A385">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A386">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A387">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A388">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A389">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A390">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A391">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A392">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A393">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A394">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A395">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A396">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A397">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A398">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A399">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A400">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A401">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A402">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A403">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A404">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A405">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A406">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A407">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A408">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A409">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A410">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A411">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A412">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A413">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A414">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A415">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A416">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A417">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A418">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A419">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A420">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A421">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A422">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A423">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A424">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A425">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A426">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A427">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A428">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A429">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A430">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A431">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A432">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A433">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A434">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A435">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A436">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A437">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A438">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A439">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A440">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A441">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A442">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A443">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A444">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A445">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A446">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A447">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A448">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A449">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A450">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A451">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A452">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A453">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A454">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A455">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A456">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A457">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A458">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A459">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A460">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A461">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A462">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A463">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A464">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A465">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A466">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A467">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A468">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A469">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A470">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A471">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A472">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A473">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A474">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A475">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A476">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A477">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A478">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A479">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A480">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A481">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A482">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A483">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A484">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A485">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A486">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A487">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A488">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A489">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A490">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A491">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A492">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A493">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A494">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A495">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A496">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A497">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A498">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A499">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A500">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A501">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A502">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A503">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A504">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A505">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A506">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A507">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A508">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A509">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A510">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A511">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A512">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A513">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A514">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A515">
+        <v>515</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L324" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="NYKAA"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:L515" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L515">
+      <sortCondition ref="A1:A515"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6092B9C-19F5-45EC-B879-08A18F7B1914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2D1E3F-F551-4B46-A5D4-9927C2507122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="287">
   <si>
     <t>S No.</t>
   </si>
@@ -918,6 +918,18 @@
   </si>
   <si>
     <t>GLENMARK PHARMA</t>
+  </si>
+  <si>
+    <t>AUROBINDO PHARMA</t>
+  </si>
+  <si>
+    <t>ENGINEERS INDIA LTD</t>
+  </si>
+  <si>
+    <t>SBI FUNDS MANAGEMENT</t>
+  </si>
+  <si>
+    <t>SUN PHARMA</t>
   </si>
 </sst>
 </file>
@@ -8014,7 +8026,7 @@
         <v>3450</v>
       </c>
       <c r="I2" s="2">
-        <f>(F2-E2)/E2</f>
+        <f t="shared" ref="I2:I65" si="0">(F2-E2)/E2</f>
         <v>4.2962125494629737E-2</v>
       </c>
       <c r="Q2" s="7" t="s">
@@ -8035,7 +8047,7 @@
         <v>748</v>
       </c>
       <c r="I3" s="2">
-        <f>(F3-E3)/E3</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
       <c r="Q3" s="3" t="s">
@@ -8056,7 +8068,7 @@
         <v>2056</v>
       </c>
       <c r="I4" s="2">
-        <f>(F4-E4)/E4</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
       <c r="J4" s="1">
@@ -8083,7 +8095,7 @@
         <v>1160</v>
       </c>
       <c r="I5" s="2">
-        <f>(F5-E5)/E5</f>
+        <f t="shared" si="0"/>
         <v>0.15308151093439365</v>
       </c>
       <c r="J5" s="1">
@@ -8110,7 +8122,7 @@
         <v>6600</v>
       </c>
       <c r="I6" s="2">
-        <f>(F6-E6)/E6</f>
+        <f t="shared" si="0"/>
         <v>0.12225811936745451</v>
       </c>
     </row>
@@ -8134,7 +8146,7 @@
         <v>1438</v>
       </c>
       <c r="I7" s="2">
-        <f>(F7-E7)/E7</f>
+        <f t="shared" si="0"/>
         <v>1.8543956043956044E-2</v>
       </c>
       <c r="J7" s="1">
@@ -8161,7 +8173,7 @@
         <v>580</v>
       </c>
       <c r="I8" s="2">
-        <f>(F8-E8)/E8</f>
+        <f t="shared" si="0"/>
         <v>0.3200118345888619</v>
       </c>
     </row>
@@ -8182,7 +8194,7 @@
         <v>3850</v>
       </c>
       <c r="I9" s="2">
-        <f>(F9-E9)/E9</f>
+        <f t="shared" si="0"/>
         <v>0.23999948467553878</v>
       </c>
     </row>
@@ -8203,7 +8215,7 @@
         <v>1450</v>
       </c>
       <c r="I10" s="2">
-        <f>(F10-E10)/E10</f>
+        <f t="shared" si="0"/>
         <v>0.20000331035395966</v>
       </c>
     </row>
@@ -8224,7 +8236,7 @@
         <v>1100</v>
       </c>
       <c r="I11" s="2">
-        <f>(F11-E11)/E11</f>
+        <f t="shared" si="0"/>
         <v>0.18000429092469422</v>
       </c>
     </row>
@@ -8245,7 +8257,7 @@
         <v>3850</v>
       </c>
       <c r="I12" s="2">
-        <f>(F12-E12)/E12</f>
+        <f t="shared" si="0"/>
         <v>0.15999843324886945</v>
       </c>
     </row>
@@ -8266,7 +8278,7 @@
         <v>1720</v>
       </c>
       <c r="I13" s="2">
-        <f>(F13-E13)/E13</f>
+        <f t="shared" si="0"/>
         <v>0.11471160077770577</v>
       </c>
     </row>
@@ -8284,7 +8296,7 @@
         <v>434</v>
       </c>
       <c r="I14" s="2">
-        <f>(F14-E14)/E14</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8305,7 +8317,7 @@
         <v>235</v>
       </c>
       <c r="I15" s="2">
-        <f>(F15-E15)/E15</f>
+        <f t="shared" si="0"/>
         <v>0.27027027027027029</v>
       </c>
     </row>
@@ -8326,7 +8338,7 @@
         <v>2050</v>
       </c>
       <c r="I16" s="2">
-        <f>(F16-E16)/E16</f>
+        <f t="shared" si="0"/>
         <v>0.14974761637689288</v>
       </c>
     </row>
@@ -8350,7 +8362,7 @@
         <v>705</v>
       </c>
       <c r="I17" s="2">
-        <f>(F17-E17)/E17</f>
+        <f t="shared" si="0"/>
         <v>0.16036505867014342</v>
       </c>
     </row>
@@ -8368,7 +8380,7 @@
         <v>835</v>
       </c>
       <c r="I18" s="2">
-        <f>(F18-E18)/E18</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8392,7 +8404,7 @@
         <v>510</v>
       </c>
       <c r="I19" s="2">
-        <f>(F19-E19)/E19</f>
+        <f t="shared" si="0"/>
         <v>8.0074487895716945E-2</v>
       </c>
     </row>
@@ -8410,7 +8422,7 @@
         <v>1074</v>
       </c>
       <c r="I20" s="2">
-        <f>(F20-E20)/E20</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8428,7 +8440,7 @@
         <v>406</v>
       </c>
       <c r="I21" s="2">
-        <f>(F21-E21)/E21</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8449,7 +8461,7 @@
         <v>1200</v>
       </c>
       <c r="I22" s="2">
-        <f>(F22-E22)/E22</f>
+        <f t="shared" si="0"/>
         <v>0.10091743119266056</v>
       </c>
     </row>
@@ -8476,7 +8488,7 @@
         <v>1153</v>
       </c>
       <c r="I23" s="2">
-        <f>(F23-E23)/E23</f>
+        <f t="shared" si="0"/>
         <v>0.16036505867014342</v>
       </c>
     </row>
@@ -8500,7 +8512,7 @@
         <v>2040</v>
       </c>
       <c r="I24" s="2">
-        <f>(F24-E24)/E24</f>
+        <f t="shared" si="0"/>
         <v>0.13476473275468251</v>
       </c>
     </row>
@@ -8524,7 +8536,7 @@
         <v>295</v>
       </c>
       <c r="I25" s="2">
-        <f>(F25-E25)/E25</f>
+        <f t="shared" si="0"/>
         <v>6.5573770491803282E-2</v>
       </c>
       <c r="J25" s="1">
@@ -8548,7 +8560,7 @@
         <v>168.6</v>
       </c>
       <c r="I26" s="2">
-        <f>(F26-E26)/E26</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8569,7 +8581,7 @@
         <v>360</v>
       </c>
       <c r="I27" s="2">
-        <f>(F27-E27)/E27</f>
+        <f t="shared" si="0"/>
         <v>0.34328358208955223</v>
       </c>
       <c r="K27">
@@ -8596,7 +8608,7 @@
         <v>705</v>
       </c>
       <c r="I28" s="2">
-        <f>(F28-E28)/E28</f>
+        <f t="shared" si="0"/>
         <v>0.16036505867014342</v>
       </c>
       <c r="J28" s="1">
@@ -8626,7 +8638,7 @@
         <v>1388</v>
       </c>
       <c r="I29" s="2">
-        <f>(F29-E29)/E29</f>
+        <f t="shared" si="0"/>
         <v>7.7885952712100137E-2</v>
       </c>
     </row>
@@ -8647,7 +8659,7 @@
         <v>1450</v>
       </c>
       <c r="I30" s="2">
-        <f>(F30-E30)/E30</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8668,7 +8680,7 @@
         <v>1280</v>
       </c>
       <c r="I31" s="2">
-        <f>(F31-E31)/E31</f>
+        <f t="shared" si="0"/>
         <v>0.23195380173243504</v>
       </c>
     </row>
@@ -8689,7 +8701,7 @@
         <v>3900</v>
       </c>
       <c r="I32" s="2">
-        <f>(F32-E32)/E32</f>
+        <f t="shared" si="0"/>
         <v>0.24006359300476948</v>
       </c>
     </row>
@@ -8713,7 +8725,7 @@
         <v>3000</v>
       </c>
       <c r="I33" s="2">
-        <f>(F33-E33)/E33</f>
+        <f t="shared" si="0"/>
         <v>5.8595014567821305E-2</v>
       </c>
     </row>
@@ -8731,7 +8743,7 @@
         <v>2779</v>
       </c>
       <c r="I34" s="2">
-        <f>(F34-E34)/E34</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8749,7 +8761,7 @@
         <v>2306</v>
       </c>
       <c r="I35" s="2">
-        <f>(F35-E35)/E35</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8770,7 +8782,7 @@
         <v>1860</v>
       </c>
       <c r="I36" s="2">
-        <f>(F36-E36)/E36</f>
+        <f t="shared" si="0"/>
         <v>0.23178807947019867</v>
       </c>
     </row>
@@ -8794,7 +8806,7 @@
         <v>322</v>
       </c>
       <c r="I37" s="2">
-        <f>(F37-E37)/E37</f>
+        <f t="shared" si="0"/>
         <v>0.15384615384615385</v>
       </c>
     </row>
@@ -8818,7 +8830,7 @@
         <v>76</v>
       </c>
       <c r="I38" s="2">
-        <f>(F38-E38)/E38</f>
+        <f t="shared" si="0"/>
         <v>0.22093023255813954</v>
       </c>
     </row>
@@ -8839,7 +8851,7 @@
         <v>5600</v>
       </c>
       <c r="I39" s="2">
-        <f>(F39-E39)/E39</f>
+        <f t="shared" si="0"/>
         <v>0.18895966029723993</v>
       </c>
     </row>
@@ -8857,7 +8869,7 @@
         <v>141</v>
       </c>
       <c r="I40" s="2">
-        <f>(F40-E40)/E40</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8875,7 +8887,7 @@
         <v>2743</v>
       </c>
       <c r="I41" s="2">
-        <f>(F41-E41)/E41</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8899,7 +8911,7 @@
         <v>265</v>
       </c>
       <c r="I42" s="2">
-        <f>(F42-E42)/E42</f>
+        <f t="shared" si="0"/>
         <v>6.5217391304347824E-2</v>
       </c>
     </row>
@@ -8923,7 +8935,7 @@
         <v>1940</v>
       </c>
       <c r="I43" s="2">
-        <f>(F43-E43)/E43</f>
+        <f t="shared" si="0"/>
         <v>8.9108910891089105E-2</v>
       </c>
     </row>
@@ -8941,7 +8953,7 @@
         <v>3171</v>
       </c>
       <c r="I44" s="2">
-        <f>(F44-E44)/E44</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8959,7 +8971,7 @@
         <v>1860</v>
       </c>
       <c r="I45" s="2">
-        <f>(F45-E45)/E45</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8977,7 +8989,7 @@
         <v>7625</v>
       </c>
       <c r="I46" s="2">
-        <f>(F46-E46)/E46</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -8995,7 +9007,7 @@
         <v>217</v>
       </c>
       <c r="I47" s="2" t="e">
-        <f>(F47-E47)/E47</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9013,7 +9025,7 @@
         <v>125</v>
       </c>
       <c r="I48" s="2" t="e">
-        <f>(F48-E48)/E48</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9031,7 +9043,7 @@
         <v>1765</v>
       </c>
       <c r="I49" s="2" t="e">
-        <f>(F49-E49)/E49</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9049,7 +9061,7 @@
         <v>210</v>
       </c>
       <c r="I50" s="2">
-        <f>(F50-E50)/E50</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
       <c r="J50" s="1">
@@ -9079,7 +9091,7 @@
         <v>76</v>
       </c>
       <c r="I51" s="2">
-        <f>(F51-E51)/E51</f>
+        <f t="shared" si="0"/>
         <v>0.22093023255813954</v>
       </c>
     </row>
@@ -9103,7 +9115,7 @@
         <v>1820</v>
       </c>
       <c r="I52" s="2">
-        <f>(F52-E52)/E52</f>
+        <f t="shared" si="0"/>
         <v>0.13671274961597543</v>
       </c>
     </row>
@@ -9121,7 +9133,7 @@
         <v>1079</v>
       </c>
       <c r="I53" s="2">
-        <f>(F53-E53)/E53</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -9142,7 +9154,7 @@
         <v>1900</v>
       </c>
       <c r="I54" s="2">
-        <f>(F54-E54)/E54</f>
+        <f t="shared" si="0"/>
         <v>0.29692832764505117</v>
       </c>
     </row>
@@ -9160,7 +9172,7 @@
         <v>374</v>
       </c>
       <c r="I55" s="2">
-        <f>(F55-E55)/E55</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -9178,7 +9190,7 @@
         <v>1520</v>
       </c>
       <c r="I56" s="2">
-        <f>(F56-E56)/E56</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -9202,7 +9214,7 @@
         <v>204</v>
       </c>
       <c r="I57" s="2">
-        <f>(F57-E57)/E57</f>
+        <f t="shared" si="0"/>
         <v>7.8341013824884786E-2</v>
       </c>
       <c r="J57" s="1"/>
@@ -9227,7 +9239,7 @@
         <v>151</v>
       </c>
       <c r="I58" s="2">
-        <f>(F58-E58)/E58</f>
+        <f t="shared" si="0"/>
         <v>3.9215686274509803E-2</v>
       </c>
       <c r="J58" s="1">
@@ -9254,7 +9266,7 @@
         <v>510</v>
       </c>
       <c r="I59" s="2">
-        <f>(F59-E59)/E59</f>
+        <f t="shared" si="0"/>
         <v>0.21718377088305491</v>
       </c>
     </row>
@@ -9275,7 +9287,7 @@
         <v>2600</v>
       </c>
       <c r="I60" s="2">
-        <f>(F60-E60)/E60</f>
+        <f t="shared" si="0"/>
         <v>0.17647058823529413</v>
       </c>
       <c r="K60">
@@ -9296,7 +9308,7 @@
         <v>59</v>
       </c>
       <c r="I61" s="2">
-        <f>(F61-E61)/E61</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -9314,7 +9326,7 @@
         <v>1026</v>
       </c>
       <c r="I62" s="2">
-        <f>(F62-E62)/E62</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -9332,7 +9344,7 @@
         <v>420</v>
       </c>
       <c r="I63" s="2">
-        <f>(F63-E63)/E63</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
@@ -9356,7 +9368,7 @@
         <v>930</v>
       </c>
       <c r="I64" s="2">
-        <f>(F64-E64)/E64</f>
+        <f t="shared" si="0"/>
         <v>6.458333333333334E-2</v>
       </c>
     </row>
@@ -9380,7 +9392,7 @@
         <v>3415</v>
       </c>
       <c r="I65" s="2">
-        <f>(F65-E65)/E65</f>
+        <f t="shared" si="0"/>
         <v>0.12236517930468109</v>
       </c>
     </row>
@@ -9401,7 +9413,7 @@
         <v>400</v>
       </c>
       <c r="I66" s="2">
-        <f>(F66-E66)/E66</f>
+        <f t="shared" ref="I66:I129" si="1">(F66-E66)/E66</f>
         <v>0.13314447592067988</v>
       </c>
     </row>
@@ -9422,7 +9434,7 @@
         <v>8450</v>
       </c>
       <c r="I67" s="2">
-        <f>(F67-E67)/E67</f>
+        <f t="shared" si="1"/>
         <v>6.0891399874450719E-2</v>
       </c>
     </row>
@@ -9440,7 +9452,7 @@
         <v>406</v>
       </c>
       <c r="I68" s="2">
-        <f>(F68-E68)/E68</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9458,7 +9470,7 @@
         <v>1446</v>
       </c>
       <c r="I69" s="2">
-        <f>(F69-E69)/E69</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9482,7 +9494,7 @@
         <v>2845</v>
       </c>
       <c r="I70" s="2">
-        <f>(F70-E70)/E70</f>
+        <f t="shared" si="1"/>
         <v>7.2021241287753071E-2</v>
       </c>
     </row>
@@ -9497,7 +9509,7 @@
         <v>46192</v>
       </c>
       <c r="I71" s="2" t="e">
-        <f>(F71-E71)/E71</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9521,7 +9533,7 @@
         <v>3415</v>
       </c>
       <c r="I72" s="2">
-        <f>(F72-E72)/E72</f>
+        <f t="shared" si="1"/>
         <v>0.12236517930468109</v>
       </c>
     </row>
@@ -9542,7 +9554,7 @@
         <v>2350</v>
       </c>
       <c r="I73" s="2">
-        <f>(F73-E73)/E73</f>
+        <f t="shared" si="1"/>
         <v>0.17971887550200802</v>
       </c>
       <c r="J73" s="1">
@@ -9566,7 +9578,7 @@
         <v>580</v>
       </c>
       <c r="I74" s="2">
-        <f>(F74-E74)/E74</f>
+        <f t="shared" si="1"/>
         <v>0.39423076923076922</v>
       </c>
     </row>
@@ -9584,7 +9596,7 @@
         <v>1889</v>
       </c>
       <c r="I75" s="2">
-        <f>(F75-E75)/E75</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9602,7 +9614,7 @@
         <v>264</v>
       </c>
       <c r="I76" s="2">
-        <f>(F76-E76)/E76</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9620,7 +9632,7 @@
         <v>376</v>
       </c>
       <c r="I77" s="2">
-        <f>(F77-E77)/E77</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9644,7 +9656,7 @@
         <v>1340</v>
       </c>
       <c r="I78" s="2">
-        <f>(F78-E78)/E78</f>
+        <f t="shared" si="1"/>
         <v>0.1040339702760085</v>
       </c>
     </row>
@@ -9668,7 +9680,7 @@
         <v>1360</v>
       </c>
       <c r="I79" s="2">
-        <f>(F79-E79)/E79</f>
+        <f t="shared" si="1"/>
         <v>8.1272084805653705E-2</v>
       </c>
       <c r="J79" s="1">
@@ -9692,7 +9704,7 @@
         <v>2103</v>
       </c>
       <c r="I80" s="2">
-        <f>(F80-E80)/E80</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9710,7 +9722,7 @@
         <v>484</v>
       </c>
       <c r="I81" s="2">
-        <f>(F81-E81)/E81</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9731,7 +9743,7 @@
         <v>1490</v>
       </c>
       <c r="I82" s="2">
-        <f>(F82-E82)/E82</f>
+        <f t="shared" si="1"/>
         <v>0.15683229813664595</v>
       </c>
     </row>
@@ -9752,7 +9764,7 @@
         <v>1620</v>
       </c>
       <c r="I83" s="2">
-        <f>(F83-E83)/E83</f>
+        <f t="shared" si="1"/>
         <v>0.21257485029940121</v>
       </c>
       <c r="K83">
@@ -9779,7 +9791,7 @@
         <v>3415</v>
       </c>
       <c r="I84" s="2">
-        <f>(F84-E84)/E84</f>
+        <f t="shared" si="1"/>
         <v>0.12236517930468109</v>
       </c>
     </row>
@@ -9800,7 +9812,7 @@
         <v>540</v>
       </c>
       <c r="I85" s="2">
-        <f>(F85-E85)/E85</f>
+        <f t="shared" si="1"/>
         <v>0.1894273127753304</v>
       </c>
     </row>
@@ -9824,7 +9836,7 @@
         <v>11400</v>
       </c>
       <c r="I86" s="2">
-        <f>(F86-E86)/E86</f>
+        <f t="shared" si="1"/>
         <v>0.20707349806584038</v>
       </c>
     </row>
@@ -9845,7 +9857,7 @@
         <v>1110</v>
       </c>
       <c r="I87" s="2">
-        <f>(F87-E87)/E87</f>
+        <f t="shared" si="1"/>
         <v>0.33896260554885405</v>
       </c>
       <c r="M87">
@@ -9866,7 +9878,7 @@
         <v>3891</v>
       </c>
       <c r="I88" s="2">
-        <f>(F88-E88)/E88</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9884,7 +9896,7 @@
         <v>346</v>
       </c>
       <c r="I89" s="2">
-        <f>(F89-E89)/E89</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9908,7 +9920,7 @@
         <v>1080</v>
       </c>
       <c r="I90" s="2">
-        <f>(F90-E90)/E90</f>
+        <f t="shared" si="1"/>
         <v>6.5647482014388484E-2</v>
       </c>
     </row>
@@ -9932,7 +9944,7 @@
         <v>197</v>
       </c>
       <c r="I91" s="2">
-        <f>(F91-E91)/E91</f>
+        <f t="shared" si="1"/>
         <v>2.5125628140703519E-2</v>
       </c>
     </row>
@@ -9956,7 +9968,7 @@
         <v>3415</v>
       </c>
       <c r="I92" s="2">
-        <f>(F92-E92)/E92</f>
+        <f t="shared" si="1"/>
         <v>0.12236517930468109</v>
       </c>
     </row>
@@ -9974,7 +9986,7 @@
         <v>2123</v>
       </c>
       <c r="I93" s="2">
-        <f>(F93-E93)/E93</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -9998,7 +10010,7 @@
         <v>1033</v>
       </c>
       <c r="I94" s="2">
-        <f>(F94-E94)/E94</f>
+        <f t="shared" si="1"/>
         <v>0.15309126594700687</v>
       </c>
     </row>
@@ -10016,7 +10028,7 @@
         <v>413</v>
       </c>
       <c r="I95" s="2">
-        <f>(F95-E95)/E95</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10040,7 +10052,7 @@
         <v>1350</v>
       </c>
       <c r="I96" s="2">
-        <f>(F96-E96)/E96</f>
+        <f t="shared" si="1"/>
         <v>4.1184971098265896E-2</v>
       </c>
     </row>
@@ -10064,7 +10076,7 @@
         <v>1380</v>
       </c>
       <c r="I97" s="2">
-        <f>(F97-E97)/E97</f>
+        <f t="shared" si="1"/>
         <v>7.903780068728522E-2</v>
       </c>
     </row>
@@ -10082,7 +10094,7 @@
         <v>13735</v>
       </c>
       <c r="I98" s="2">
-        <f>(F98-E98)/E98</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10100,7 +10112,7 @@
         <v>391</v>
       </c>
       <c r="I99" s="2">
-        <f>(F99-E99)/E99</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10121,7 +10133,7 @@
         <v>1520</v>
       </c>
       <c r="I100" s="2">
-        <f>(F100-E100)/E100</f>
+        <f t="shared" si="1"/>
         <v>0.23476848090982941</v>
       </c>
     </row>
@@ -10142,7 +10154,7 @@
         <v>700</v>
       </c>
       <c r="I101" s="2">
-        <f>(F101-E101)/E101</f>
+        <f t="shared" si="1"/>
         <v>0.21739130434782608</v>
       </c>
     </row>
@@ -10166,7 +10178,7 @@
         <v>1035</v>
       </c>
       <c r="I102" s="2">
-        <f>(F102-E102)/E102</f>
+        <f t="shared" si="1"/>
         <v>0.17402826855123674</v>
       </c>
     </row>
@@ -10190,7 +10202,7 @@
         <v>968</v>
       </c>
       <c r="I103" s="2">
-        <f>(F103-E103)/E103</f>
+        <f t="shared" si="1"/>
         <v>0.15200764818355642</v>
       </c>
     </row>
@@ -10211,7 +10223,7 @@
         <v>2750</v>
       </c>
       <c r="I104" s="2">
-        <f>(F104-E104)/E104</f>
+        <f t="shared" si="1"/>
         <v>0.12658746415403524</v>
       </c>
     </row>
@@ -10229,7 +10241,7 @@
         <v>840</v>
       </c>
       <c r="I105" s="2">
-        <f>(F105-E105)/E105</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10247,7 +10259,7 @@
         <v>802</v>
       </c>
       <c r="I106" s="2">
-        <f>(F106-E106)/E106</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10271,7 +10283,7 @@
         <v>4500</v>
       </c>
       <c r="I107" s="2">
-        <f>(F107-E107)/E107</f>
+        <f t="shared" si="1"/>
         <v>4.7968885047536734E-2</v>
       </c>
     </row>
@@ -10292,7 +10304,7 @@
         <v>1940</v>
       </c>
       <c r="I108" s="2">
-        <f>(F108-E108)/E108</f>
+        <f t="shared" si="1"/>
         <v>0.38968481375358166</v>
       </c>
     </row>
@@ -10313,7 +10325,7 @@
         <v>1780</v>
       </c>
       <c r="I109" s="2">
-        <f>(F109-E109)/E109</f>
+        <f t="shared" si="1"/>
         <v>0.18429807052561545</v>
       </c>
     </row>
@@ -10331,7 +10343,7 @@
         <v>976</v>
       </c>
       <c r="I110" s="2">
-        <f>(F110-E110)/E110</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10349,7 +10361,7 @@
         <v>508</v>
       </c>
       <c r="I111" s="2">
-        <f>(F111-E111)/E111</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10373,7 +10385,7 @@
         <v>1540</v>
       </c>
       <c r="I112" s="2">
-        <f>(F112-E112)/E112</f>
+        <f t="shared" si="1"/>
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
@@ -10397,7 +10409,7 @@
         <v>1331</v>
       </c>
       <c r="I113" s="2">
-        <f>(F113-E113)/E113</f>
+        <f t="shared" si="1"/>
         <v>0.12322946175637393</v>
       </c>
     </row>
@@ -10415,7 +10427,7 @@
         <v>1018</v>
       </c>
       <c r="I114" s="2">
-        <f>(F114-E114)/E114</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10436,7 +10448,7 @@
         <v>950</v>
       </c>
       <c r="I115" s="2">
-        <f>(F115-E115)/E115</f>
+        <f t="shared" si="1"/>
         <v>0.10981308411214953</v>
       </c>
     </row>
@@ -10454,7 +10466,7 @@
         <v>1027</v>
       </c>
       <c r="I116" s="2">
-        <f>(F116-E116)/E116</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10472,7 +10484,7 @@
         <v>1360</v>
       </c>
       <c r="I117" s="2">
-        <f>(F117-E117)/E117</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10496,7 +10508,7 @@
         <v>1810</v>
       </c>
       <c r="I118" s="2">
-        <f>(F118-E118)/E118</f>
+        <f t="shared" si="1"/>
         <v>7.1732199787460149E-2</v>
       </c>
     </row>
@@ -10517,7 +10529,7 @@
         <v>288</v>
       </c>
       <c r="I119" s="2">
-        <f>(F119-E119)/E119</f>
+        <f t="shared" si="1"/>
         <v>0.22553191489361701</v>
       </c>
     </row>
@@ -10541,7 +10553,7 @@
         <v>514</v>
       </c>
       <c r="I120" s="2">
-        <f>(F120-E120)/E120</f>
+        <f t="shared" si="1"/>
         <v>0.11678832116788321</v>
       </c>
     </row>
@@ -10559,7 +10571,7 @@
         <v>310</v>
       </c>
       <c r="I121" s="2">
-        <f>(F121-E121)/E121</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10577,7 +10589,7 @@
         <v>352</v>
       </c>
       <c r="I122" s="2">
-        <f>(F122-E122)/E122</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10598,7 +10610,7 @@
         <v>5250</v>
       </c>
       <c r="I123" s="2">
-        <f>(F123-E123)/E123</f>
+        <f t="shared" si="1"/>
         <v>0.17082961641391614</v>
       </c>
     </row>
@@ -10616,7 +10628,7 @@
         <v>2246</v>
       </c>
       <c r="I124" s="2">
-        <f>(F124-E124)/E124</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10634,7 +10646,7 @@
         <v>78</v>
       </c>
       <c r="I125" s="2">
-        <f>(F125-E125)/E125</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10658,7 +10670,7 @@
         <v>3130</v>
       </c>
       <c r="I126" s="2">
-        <f>(F126-E126)/E126</f>
+        <f t="shared" si="1"/>
         <v>4.793028322440087E-2</v>
       </c>
     </row>
@@ -10683,7 +10695,7 @@
         <v>278</v>
       </c>
       <c r="I127" s="2">
-        <f>(F127-E127)/E127</f>
+        <f t="shared" si="1"/>
         <v>7.2664359861591699E-2</v>
       </c>
     </row>
@@ -10701,7 +10713,7 @@
         <v>1516</v>
       </c>
       <c r="I128" s="2">
-        <f>(F128-E128)/E128</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10719,7 +10731,7 @@
         <v>1110</v>
       </c>
       <c r="I129" s="2">
-        <f>(F129-E129)/E129</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
     </row>
@@ -10740,7 +10752,7 @@
         <v>1000</v>
       </c>
       <c r="I130" s="2">
-        <f>(F130-E130)/E130</f>
+        <f t="shared" ref="I130:I193" si="2">(F130-E130)/E130</f>
         <v>0.17924528301886791</v>
       </c>
     </row>
@@ -10758,7 +10770,7 @@
         <v>1785</v>
       </c>
       <c r="I131" s="2">
-        <f>(F131-E131)/E131</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -10785,7 +10797,7 @@
         <v>290</v>
       </c>
       <c r="I132" s="2">
-        <f>(F132-E132)/E132</f>
+        <f t="shared" si="2"/>
         <v>0.16719242902208201</v>
       </c>
     </row>
@@ -10806,7 +10818,7 @@
         <v>540</v>
       </c>
       <c r="I133" s="2">
-        <f>(F133-E133)/E133</f>
+        <f t="shared" si="2"/>
         <v>0.30120481927710846</v>
       </c>
     </row>
@@ -10827,7 +10839,7 @@
         <v>1406</v>
       </c>
       <c r="I134" s="2">
-        <f>(F134-E134)/E134</f>
+        <f t="shared" si="2"/>
         <v>0.24204946996466431</v>
       </c>
     </row>
@@ -10845,7 +10857,7 @@
         <v>421</v>
       </c>
       <c r="I135" s="2">
-        <f>(F135-E135)/E135</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -10872,7 +10884,7 @@
         <v>1150</v>
       </c>
       <c r="I136" s="2">
-        <f>(F136-E136)/E136</f>
+        <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -10899,7 +10911,7 @@
         <v>290</v>
       </c>
       <c r="I137" s="2">
-        <f>(F137-E137)/E137</f>
+        <f t="shared" si="2"/>
         <v>0.16719242902208201</v>
       </c>
     </row>
@@ -10923,7 +10935,7 @@
         <v>375</v>
       </c>
       <c r="I138" s="2">
-        <f>(F138-E138)/E138</f>
+        <f t="shared" si="2"/>
         <v>0.14329268292682926</v>
       </c>
     </row>
@@ -10947,7 +10959,7 @@
         <v>16100</v>
       </c>
       <c r="I139" s="2">
-        <f>(F139-E139)/E139</f>
+        <f t="shared" si="2"/>
         <v>0.19462788454403798</v>
       </c>
     </row>
@@ -10968,7 +10980,7 @@
         <v>1507</v>
       </c>
       <c r="I140" s="2">
-        <f>(F140-E140)/E140</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -10986,7 +10998,7 @@
         <v>1954</v>
       </c>
       <c r="I141" s="2">
-        <f>(F141-E141)/E141</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11013,7 +11025,7 @@
         <v>3290</v>
       </c>
       <c r="I142" s="2">
-        <f>(F142-E142)/E142</f>
+        <f t="shared" si="2"/>
         <v>8.3406240886555849E-2</v>
       </c>
     </row>
@@ -11040,7 +11052,7 @@
         <v>1380</v>
       </c>
       <c r="I143" s="2">
-        <f>(F143-E143)/E143</f>
+        <f t="shared" si="2"/>
         <v>6.2194269741439552E-2</v>
       </c>
     </row>
@@ -11058,7 +11070,7 @@
         <v>46216</v>
       </c>
       <c r="I144" s="2" t="e">
-        <f>(F144-E144)/E144</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11073,7 +11085,7 @@
         <v>46216</v>
       </c>
       <c r="I145" s="2" t="e">
-        <f>(F145-E145)/E145</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11094,7 +11106,7 @@
         <v>370</v>
       </c>
       <c r="I146" s="2">
-        <f>(F146-E146)/E146</f>
+        <f t="shared" si="2"/>
         <v>0.15264797507788161</v>
       </c>
     </row>
@@ -11115,7 +11127,7 @@
         <v>1025</v>
       </c>
       <c r="I147" s="2">
-        <f>(F147-E147)/E147</f>
+        <f t="shared" si="2"/>
         <v>0.17680826636050517</v>
       </c>
     </row>
@@ -11142,7 +11154,7 @@
         <v>968</v>
       </c>
       <c r="I148" s="2">
-        <f>(F148-E148)/E148</f>
+        <f t="shared" si="2"/>
         <v>0.15200764818355642</v>
       </c>
     </row>
@@ -11166,7 +11178,7 @@
         <v>727</v>
       </c>
       <c r="I149" s="2">
-        <f>(F149-E149)/E149</f>
+        <f t="shared" si="2"/>
         <v>9.2105263157894732E-2</v>
       </c>
     </row>
@@ -11187,7 +11199,7 @@
         <v>351</v>
       </c>
       <c r="I150" s="2">
-        <f>(F150-E150)/E150</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11205,7 +11217,7 @@
         <v>308</v>
       </c>
       <c r="I151" s="2">
-        <f>(F151-E151)/E151</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11226,7 +11238,7 @@
         <v>3800</v>
       </c>
       <c r="I152" s="2">
-        <f>(F152-E152)/E152</f>
+        <f t="shared" si="2"/>
         <v>0.18527760449157829</v>
       </c>
     </row>
@@ -11247,7 +11259,7 @@
         <v>1450</v>
       </c>
       <c r="I153" s="2">
-        <f>(F153-E153)/E153</f>
+        <f t="shared" si="2"/>
         <v>0.18755118755118755</v>
       </c>
     </row>
@@ -11271,7 +11283,7 @@
         <v>200</v>
       </c>
       <c r="I154" s="2">
-        <f>(F154-E154)/E154</f>
+        <f t="shared" si="2"/>
         <v>0.19047619047619047</v>
       </c>
     </row>
@@ -11295,7 +11307,7 @@
         <v>565</v>
       </c>
       <c r="I155" s="2">
-        <f>(F155-E155)/E155</f>
+        <f t="shared" si="2"/>
         <v>0.25835189309576839</v>
       </c>
     </row>
@@ -11316,7 +11328,7 @@
         <v>1604</v>
       </c>
       <c r="I156" s="2">
-        <f>(F156-E156)/E156</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11337,7 +11349,7 @@
         <v>1826</v>
       </c>
       <c r="I157" s="2">
-        <f>(F157-E157)/E157</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11361,7 +11373,7 @@
         <v>1790</v>
       </c>
       <c r="I158" s="2">
-        <f>(F158-E158)/E158</f>
+        <f t="shared" si="2"/>
         <v>-2.717391304347826E-2</v>
       </c>
     </row>
@@ -11388,7 +11400,7 @@
         <v>1800</v>
       </c>
       <c r="I159" s="2">
-        <f>(F159-E159)/E159</f>
+        <f t="shared" si="2"/>
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
@@ -11409,7 +11421,7 @@
         <v>7203</v>
       </c>
       <c r="I160" s="2">
-        <f>(F160-E160)/E160</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11430,7 +11442,7 @@
         <v>4133</v>
       </c>
       <c r="I161" s="2">
-        <f>(F161-E161)/E161</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11454,7 +11466,7 @@
         <v>1530</v>
       </c>
       <c r="I162" s="2">
-        <f>(F162-E162)/E162</f>
+        <f t="shared" si="2"/>
         <v>0.2707641196013289</v>
       </c>
     </row>
@@ -11478,7 +11490,7 @@
         <v>250</v>
       </c>
       <c r="I163" s="2">
-        <f>(F163-E163)/E163</f>
+        <f t="shared" si="2"/>
         <v>0.15740740740740741</v>
       </c>
     </row>
@@ -11505,7 +11517,7 @@
         <v>1035</v>
       </c>
       <c r="I164" s="2">
-        <f>(F164-E164)/E164</f>
+        <f t="shared" si="2"/>
         <v>0.17402826855123674</v>
       </c>
     </row>
@@ -11526,7 +11538,7 @@
         <v>420</v>
       </c>
       <c r="I165" s="2">
-        <f>(F165-E165)/E165</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
     </row>
@@ -11547,7 +11559,7 @@
         <v>1900</v>
       </c>
       <c r="I166" s="2">
-        <f>(F166-E166)/E166</f>
+        <f t="shared" si="2"/>
         <v>0.25827814569536423</v>
       </c>
     </row>
@@ -11568,7 +11580,7 @@
         <v>2620</v>
       </c>
       <c r="I167" s="2">
-        <f>(F167-E167)/E167</f>
+        <f t="shared" si="2"/>
         <v>0.19908466819221968</v>
       </c>
     </row>
@@ -11583,7 +11595,7 @@
         <v>46220</v>
       </c>
       <c r="I168" s="2" t="e">
-        <f>(F168-E168)/E168</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11598,7 +11610,7 @@
         <v>46220</v>
       </c>
       <c r="I169" s="2" t="e">
-        <f>(F169-E169)/E169</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11622,7 +11634,7 @@
         <v>695</v>
       </c>
       <c r="I170" s="2">
-        <f>(F170-E170)/E170</f>
+        <f t="shared" si="2"/>
         <v>7.586206896551724E-2</v>
       </c>
     </row>
@@ -11649,7 +11661,7 @@
         <v>415</v>
       </c>
       <c r="I171" s="2">
-        <f>(F171-E171)/E171</f>
+        <f t="shared" si="2"/>
         <v>9.1954022988505746E-2</v>
       </c>
     </row>
@@ -11667,7 +11679,7 @@
         <v>310</v>
       </c>
       <c r="I172" s="2">
-        <f>(F172-E172)/E172</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11685,7 +11697,7 @@
         <v>204</v>
       </c>
       <c r="I173" s="2">
-        <f>(F173-E173)/E173</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11706,7 +11718,7 @@
         <v>1750</v>
       </c>
       <c r="I174" s="2">
-        <f>(F174-E174)/E174</f>
+        <f t="shared" si="2"/>
         <v>0.21191135734072022</v>
       </c>
     </row>
@@ -11727,7 +11739,7 @@
         <v>1470</v>
       </c>
       <c r="I175" s="2">
-        <f>(F175-E175)/E175</f>
+        <f t="shared" si="2"/>
         <v>0.1883589329021827</v>
       </c>
     </row>
@@ -11748,7 +11760,7 @@
         <v>1586</v>
       </c>
       <c r="I176" s="2">
-        <f>(F176-E176)/E176</f>
+        <f t="shared" si="2"/>
         <v>0.12322946175637393</v>
       </c>
     </row>
@@ -11775,7 +11787,7 @@
         <v>3240</v>
       </c>
       <c r="I177" s="2">
-        <f>(F177-E177)/E177</f>
+        <f t="shared" si="2"/>
         <v>8.7367178276269192E-2</v>
       </c>
     </row>
@@ -11793,7 +11805,7 @@
         <v>1348</v>
       </c>
       <c r="I178" s="2">
-        <f>(F178-E178)/E178</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -11814,7 +11826,7 @@
         <v>2260</v>
       </c>
       <c r="I179" s="2">
-        <f>(F179-E179)/E179</f>
+        <f t="shared" si="2"/>
         <v>0.21374865735767992</v>
       </c>
     </row>
@@ -11838,7 +11850,7 @@
         <v>1800</v>
       </c>
       <c r="I180" s="2">
-        <f>(F180-E180)/E180</f>
+        <f t="shared" si="2"/>
         <v>8.4905660377358486E-2</v>
       </c>
     </row>
@@ -11853,7 +11865,7 @@
         <v>46224</v>
       </c>
       <c r="I181" s="2" t="e">
-        <f>(F181-E181)/E181</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11868,7 +11880,7 @@
         <v>46224</v>
       </c>
       <c r="I182" s="2" t="e">
-        <f>(F182-E182)/E182</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11889,7 +11901,7 @@
         <v>800</v>
       </c>
       <c r="I183" s="2">
-        <f>(F183-E183)/E183</f>
+        <f t="shared" si="2"/>
         <v>0.2841091492776886</v>
       </c>
     </row>
@@ -11910,7 +11922,7 @@
         <v>12096</v>
       </c>
       <c r="I184" s="2">
-        <f>(F184-E184)/E184</f>
+        <f t="shared" si="2"/>
         <v>0.16262975778546712</v>
       </c>
     </row>
@@ -11934,7 +11946,7 @@
         <v>4450</v>
       </c>
       <c r="I185" s="2">
-        <f>(F185-E185)/E185</f>
+        <f t="shared" si="2"/>
         <v>2.9463116542994324E-2</v>
       </c>
     </row>
@@ -11949,7 +11961,7 @@
         <v>46225</v>
       </c>
       <c r="I186" s="2" t="e">
-        <f>(F186-E186)/E186</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11964,7 +11976,7 @@
         <v>46225</v>
       </c>
       <c r="I187" s="2" t="e">
-        <f>(F187-E187)/E187</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11988,7 +12000,7 @@
         <v>95.7</v>
       </c>
       <c r="I188" s="2">
-        <f>(F188-E188)/E188</f>
+        <f t="shared" si="2"/>
         <v>-2.077151335311566E-2</v>
       </c>
     </row>
@@ -12006,7 +12018,7 @@
         <v>373</v>
       </c>
       <c r="I189" s="2" t="e">
-        <f>(F189-E189)/E189</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12033,7 +12045,7 @@
         <v>1450</v>
       </c>
       <c r="I190" s="2">
-        <f>(F190-E190)/E190</f>
+        <f t="shared" si="2"/>
         <v>7.0950468540829981E-2</v>
       </c>
     </row>
@@ -12051,7 +12063,7 @@
         <v>448</v>
       </c>
       <c r="I191" s="2">
-        <f>(F191-E191)/E191</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -12072,7 +12084,7 @@
         <v>726</v>
       </c>
       <c r="I192" s="2">
-        <f>(F192-E192)/E192</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
     </row>
@@ -12096,7 +12108,7 @@
         <v>1380</v>
       </c>
       <c r="I193" s="2">
-        <f>(F193-E193)/E193</f>
+        <f t="shared" si="2"/>
         <v>0.20209059233449478</v>
       </c>
     </row>
@@ -12114,7 +12126,7 @@
         <v>188</v>
       </c>
       <c r="I194" s="2">
-        <f>(F194-E194)/E194</f>
+        <f t="shared" ref="I194:I230" si="3">(F194-E194)/E194</f>
         <v>-1</v>
       </c>
     </row>
@@ -12132,7 +12144,7 @@
         <v>109</v>
       </c>
       <c r="I195" s="2">
-        <f>(F195-E195)/E195</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
@@ -12156,7 +12168,7 @@
         <v>3145</v>
       </c>
       <c r="I196" s="2">
-        <f>(F196-E196)/E196</f>
+        <f t="shared" si="3"/>
         <v>5.3869969040247677E-2</v>
       </c>
     </row>
@@ -12177,7 +12189,7 @@
         <v>1329</v>
       </c>
       <c r="I197" s="2">
-        <f>(F197-E197)/E197</f>
+        <f t="shared" si="3"/>
         <v>0.17402826855123674</v>
       </c>
     </row>
@@ -12201,7 +12213,7 @@
         <v>664</v>
       </c>
       <c r="I198" s="2">
-        <f>(F198-E198)/E198</f>
+        <f t="shared" si="3"/>
         <v>1.5414546542951144E-2</v>
       </c>
     </row>
@@ -12225,7 +12237,7 @@
         <v>1833</v>
       </c>
       <c r="I199" s="2">
-        <f>(F199-E199)/E199</f>
+        <f t="shared" si="3"/>
         <v>1.4084507042253521E-2</v>
       </c>
     </row>
@@ -12240,7 +12252,7 @@
         <v>46227</v>
       </c>
       <c r="I200" s="2" t="e">
-        <f>(F200-E200)/E200</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12264,7 +12276,7 @@
         <v>2360</v>
       </c>
       <c r="I201" s="2">
-        <f>(F201-E201)/E201</f>
+        <f t="shared" si="3"/>
         <v>6.1910619106191063E-2</v>
       </c>
     </row>
@@ -12285,7 +12297,7 @@
         <v>1283</v>
       </c>
       <c r="I202" s="2">
-        <f>(F202-E202)/E202</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
@@ -12303,7 +12315,7 @@
         <v>81</v>
       </c>
       <c r="I203" s="2">
-        <f>(F203-E203)/E203</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
@@ -12324,7 +12336,7 @@
         <v>1980</v>
       </c>
       <c r="I204" s="2">
-        <f>(F204-E204)/E204</f>
+        <f t="shared" si="3"/>
         <v>0.23672704559650218</v>
       </c>
     </row>
@@ -12348,7 +12360,7 @@
         <v>1035</v>
       </c>
       <c r="I205" s="2">
-        <f>(F205-E205)/E205</f>
+        <f t="shared" si="3"/>
         <v>0.17402826855123674</v>
       </c>
     </row>
@@ -12363,7 +12375,7 @@
         <v>46231</v>
       </c>
       <c r="I206" s="2" t="e">
-        <f>(F206-E206)/E206</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12390,7 +12402,7 @@
         <v>555</v>
       </c>
       <c r="I207" s="2">
-        <f>(F207-E207)/E207</f>
+        <f t="shared" si="3"/>
         <v>7.5174825174825169E-2</v>
       </c>
     </row>
@@ -12408,7 +12420,7 @@
         <v>46231</v>
       </c>
       <c r="I208" s="2" t="e">
-        <f>(F208-E208)/E208</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12429,7 +12441,7 @@
         <v>240</v>
       </c>
       <c r="I209" s="2">
-        <f>(F209-E209)/E209</f>
+        <f t="shared" si="3"/>
         <v>0.29729729729729731</v>
       </c>
     </row>
@@ -12444,7 +12456,7 @@
         <v>46231</v>
       </c>
       <c r="I210" s="2" t="e">
-        <f>(F210-E210)/E210</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12468,7 +12480,7 @@
         <v>1430</v>
       </c>
       <c r="I211" s="2">
-        <f>(F211-E211)/E211</f>
+        <f t="shared" si="3"/>
         <v>0.19266055045871561</v>
       </c>
     </row>
@@ -12495,7 +12507,7 @@
         <v>1035</v>
       </c>
       <c r="I212" s="2">
-        <f>(F212-E212)/E212</f>
+        <f t="shared" si="3"/>
         <v>0.17402826855123674</v>
       </c>
     </row>
@@ -12519,7 +12531,7 @@
         <v>521</v>
       </c>
       <c r="I213" s="2">
-        <f>(F213-E213)/E213</f>
+        <f t="shared" si="3"/>
         <v>2.0952380952380951E-2</v>
       </c>
     </row>
@@ -12543,7 +12555,7 @@
         <v>1200</v>
       </c>
       <c r="I214" s="2">
-        <f>(F214-E214)/E214</f>
+        <f t="shared" si="3"/>
         <v>3.4426229508196723E-2</v>
       </c>
     </row>
@@ -12570,7 +12582,7 @@
         <v>4250</v>
       </c>
       <c r="I215" s="2">
-        <f>(F215-E215)/E215</f>
+        <f t="shared" si="3"/>
         <v>-3.6054081121682527E-2</v>
       </c>
     </row>
@@ -12594,7 +12606,7 @@
         <v>7300</v>
       </c>
       <c r="I216" s="2">
-        <f>(F216-E216)/E216</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
@@ -12618,7 +12630,7 @@
         <v>315</v>
       </c>
       <c r="I217" s="2">
-        <f>(F217-E217)/E217</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
@@ -12642,7 +12654,7 @@
         <v>4550</v>
       </c>
       <c r="I218" s="2">
-        <f>(F218-E218)/E218</f>
+        <f t="shared" si="3"/>
         <v>0.18705974432559352</v>
       </c>
     </row>
@@ -12666,7 +12678,7 @@
         <v>2140</v>
       </c>
       <c r="I219" s="2">
-        <f>(F219-E219)/E219</f>
+        <f t="shared" si="3"/>
         <v>0.22076440387906446</v>
       </c>
     </row>
@@ -12693,7 +12705,7 @@
         <v>3870</v>
       </c>
       <c r="I220" s="2">
-        <f>(F220-E220)/E220</f>
+        <f t="shared" si="3"/>
         <v>0.2133117633464294</v>
       </c>
     </row>
@@ -12720,7 +12732,7 @@
         <v>3870</v>
       </c>
       <c r="I221" s="2">
-        <f>(F221-E221)/E221</f>
+        <f t="shared" si="3"/>
         <v>0.2133117633464294</v>
       </c>
     </row>
@@ -12744,7 +12756,7 @@
         <v>1630</v>
       </c>
       <c r="I222" s="2">
-        <f>(F222-E222)/E222</f>
+        <f t="shared" si="3"/>
         <v>0.21370067014147431</v>
       </c>
     </row>
@@ -12768,7 +12780,7 @@
         <v>1765</v>
       </c>
       <c r="I223" s="2">
-        <f>(F223-E223)/E223</f>
+        <f t="shared" si="3"/>
         <v>0.15889691398555483</v>
       </c>
     </row>
@@ -12786,7 +12798,7 @@
         <v>46233</v>
       </c>
       <c r="I224" s="2" t="e">
-        <f>(F224-E224)/E224</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12804,7 +12816,7 @@
         <v>46233</v>
       </c>
       <c r="I225" s="2" t="e">
-        <f>(F225-E225)/E225</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12822,7 +12834,7 @@
         <v>46233</v>
       </c>
       <c r="I226" s="2" t="e">
-        <f>(F226-E226)/E226</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12840,7 +12852,7 @@
         <v>1277</v>
       </c>
       <c r="I227" s="2">
-        <f>(F227-E227)/E227</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
     </row>
@@ -12855,7 +12867,7 @@
         <v>46233</v>
       </c>
       <c r="I228" s="2" t="e">
-        <f>(F228-E228)/E228</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -12882,7 +12894,7 @@
         <v>1570</v>
       </c>
       <c r="I229" s="2">
-        <f>(F229-E229)/E229</f>
+        <f t="shared" si="3"/>
         <v>7.3619631901840496E-2</v>
       </c>
     </row>
@@ -12909,7 +12921,7 @@
         <v>1720</v>
       </c>
       <c r="I230" s="2">
-        <f>(F230-E230)/E230</f>
+        <f t="shared" si="3"/>
         <v>0.1630144307856761</v>
       </c>
     </row>
@@ -15458,25 +15470,79 @@
       <c r="A373">
         <v>373</v>
       </c>
+      <c r="B373" t="s">
+        <v>163</v>
+      </c>
+      <c r="C373" t="s">
+        <v>123</v>
+      </c>
+      <c r="E373">
+        <v>1717</v>
+      </c>
+      <c r="F373">
+        <v>1811</v>
+      </c>
+      <c r="G373">
+        <v>1670</v>
+      </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>374</v>
       </c>
+      <c r="B374" t="s">
+        <v>283</v>
+      </c>
+      <c r="C374" t="s">
+        <v>241</v>
+      </c>
+      <c r="E374">
+        <v>1717</v>
+      </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>375</v>
       </c>
+      <c r="B375" t="s">
+        <v>284</v>
+      </c>
+      <c r="E375">
+        <v>262</v>
+      </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>376</v>
       </c>
+      <c r="B376" t="s">
+        <v>285</v>
+      </c>
+      <c r="C376" t="s">
+        <v>143</v>
+      </c>
+      <c r="E376">
+        <v>564</v>
+      </c>
+      <c r="F376">
+        <v>720</v>
+      </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>377</v>
+      </c>
+      <c r="B377" t="s">
+        <v>286</v>
+      </c>
+      <c r="C377" t="s">
+        <v>176</v>
+      </c>
+      <c r="E377">
+        <v>1984</v>
+      </c>
+      <c r="F377">
+        <v>2310</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.35">

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2D1E3F-F551-4B46-A5D4-9927C2507122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2058C2-048E-4D4A-8B1E-84A134E63C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="292">
   <si>
     <t>S No.</t>
   </si>
@@ -930,6 +930,21 @@
   </si>
   <si>
     <t>SUN PHARMA</t>
+  </si>
+  <si>
+    <t>COAL INDIA</t>
+  </si>
+  <si>
+    <t>OIL INDIA</t>
+  </si>
+  <si>
+    <t>AEGIS VOPAK</t>
+  </si>
+  <si>
+    <t>Good bounce</t>
+  </si>
+  <si>
+    <t>SAI LIFE</t>
   </si>
 </sst>
 </file>
@@ -15476,6 +15491,9 @@
       <c r="C373" t="s">
         <v>123</v>
       </c>
+      <c r="D373" s="1">
+        <v>46266</v>
+      </c>
       <c r="E373">
         <v>1717</v>
       </c>
@@ -15496,6 +15514,9 @@
       <c r="C374" t="s">
         <v>241</v>
       </c>
+      <c r="D374" s="1">
+        <v>46266</v>
+      </c>
       <c r="E374">
         <v>1717</v>
       </c>
@@ -15507,6 +15528,9 @@
       <c r="B375" t="s">
         <v>284</v>
       </c>
+      <c r="D375" s="1">
+        <v>46266</v>
+      </c>
       <c r="E375">
         <v>262</v>
       </c>
@@ -15521,6 +15545,9 @@
       <c r="C376" t="s">
         <v>143</v>
       </c>
+      <c r="D376" s="1">
+        <v>46266</v>
+      </c>
       <c r="E376">
         <v>564</v>
       </c>
@@ -15538,6 +15565,9 @@
       <c r="C377" t="s">
         <v>176</v>
       </c>
+      <c r="D377" s="1">
+        <v>46266</v>
+      </c>
       <c r="E377">
         <v>1984</v>
       </c>
@@ -15549,113 +15579,224 @@
       <c r="A378">
         <v>378</v>
       </c>
+      <c r="B378" t="s">
+        <v>140</v>
+      </c>
+      <c r="C378" t="s">
+        <v>123</v>
+      </c>
+      <c r="D378" s="1">
+        <v>46267</v>
+      </c>
+      <c r="E378">
+        <v>1351</v>
+      </c>
+      <c r="F378">
+        <v>1425</v>
+      </c>
+      <c r="G378">
+        <v>1315</v>
+      </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>379</v>
       </c>
+      <c r="B379" t="s">
+        <v>287</v>
+      </c>
+      <c r="C379" t="s">
+        <v>176</v>
+      </c>
+      <c r="D379" s="1">
+        <v>46267</v>
+      </c>
+      <c r="E379">
+        <v>402</v>
+      </c>
+      <c r="F379">
+        <v>510</v>
+      </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>380</v>
       </c>
+      <c r="B380" t="s">
+        <v>288</v>
+      </c>
+      <c r="C380" t="s">
+        <v>176</v>
+      </c>
+      <c r="D380" s="1">
+        <v>46267</v>
+      </c>
+      <c r="E380">
+        <v>490</v>
+      </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>381</v>
       </c>
+      <c r="B381" t="s">
+        <v>116</v>
+      </c>
+      <c r="D381" s="1">
+        <v>46267</v>
+      </c>
+      <c r="F381">
+        <v>3250</v>
+      </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>382</v>
       </c>
+      <c r="B382" t="s">
+        <v>289</v>
+      </c>
+      <c r="C382" t="s">
+        <v>290</v>
+      </c>
+      <c r="D382" s="1">
+        <v>46267</v>
+      </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>383</v>
       </c>
+      <c r="B383" t="s">
+        <v>249</v>
+      </c>
+      <c r="C383" t="s">
+        <v>241</v>
+      </c>
+      <c r="D383" s="1">
+        <v>46267</v>
+      </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>384</v>
       </c>
-    </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B384" t="s">
+        <v>291</v>
+      </c>
+      <c r="E384">
+        <v>1587</v>
+      </c>
+      <c r="F384">
+        <v>1677</v>
+      </c>
+      <c r="G384">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>385</v>
       </c>
-    </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B385" t="s">
+        <v>263</v>
+      </c>
+      <c r="E385">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>386</v>
       </c>
-    </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B386" t="s">
+        <v>265</v>
+      </c>
+      <c r="E386">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>387</v>
       </c>
-    </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B387" t="s">
+        <v>16</v>
+      </c>
+      <c r="E387">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>388</v>
       </c>
-    </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B388" t="s">
+        <v>269</v>
+      </c>
+      <c r="E388">
+        <v>208</v>
+      </c>
+      <c r="F388">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>389</v>
       </c>
     </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>390</v>
       </c>
     </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>391</v>
       </c>
     </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>392</v>
       </c>
     </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>393</v>
       </c>
     </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>394</v>
       </c>
     </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>395</v>
       </c>
     </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>396</v>
       </c>
     </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>397</v>
       </c>
     </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>398</v>
       </c>
     </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>399</v>
       </c>
     </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>400</v>
       </c>
